--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287685</v>
+        <v>120287681</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>79160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615181</v>
+        <v>615320</v>
       </c>
       <c r="R2" t="n">
-        <v>6560482</v>
+        <v>6560647</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +797,7 @@
         <v>120287686</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,7 +916,7 @@
         <v>120287679</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1024,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287682</v>
+        <v>120287687</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,24 +1044,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1067,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615292</v>
+        <v>615148</v>
       </c>
       <c r="R5" t="n">
-        <v>6560674</v>
+        <v>6560597</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287687</v>
+        <v>120287685</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,32 +1159,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1186,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615148</v>
+        <v>615181</v>
       </c>
       <c r="R6" t="n">
-        <v>6560597</v>
+        <v>6560482</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287683</v>
+        <v>120287682</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615121</v>
+        <v>615292</v>
       </c>
       <c r="R7" t="n">
-        <v>6560512</v>
+        <v>6560674</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120287681</v>
+        <v>120287683</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,11 +1412,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615320</v>
+        <v>615121</v>
       </c>
       <c r="R8" t="n">
-        <v>6560647</v>
+        <v>6560512</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287681</v>
+        <v>120287687</v>
       </c>
       <c r="B2" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615320</v>
+        <v>615148</v>
       </c>
       <c r="R2" t="n">
-        <v>6560647</v>
+        <v>6560597</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287686</v>
+        <v>120287681</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,30 +810,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615132</v>
+        <v>615320</v>
       </c>
       <c r="R3" t="n">
-        <v>6560670</v>
+        <v>6560647</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287679</v>
+        <v>120287685</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615119</v>
+        <v>615181</v>
       </c>
       <c r="R4" t="n">
-        <v>6560500</v>
+        <v>6560482</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287687</v>
+        <v>120287679</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,28 +1044,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615148</v>
+        <v>615119</v>
       </c>
       <c r="R5" t="n">
-        <v>6560597</v>
+        <v>6560500</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287685</v>
+        <v>120287683</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615181</v>
+        <v>615121</v>
       </c>
       <c r="R6" t="n">
-        <v>6560482</v>
+        <v>6560512</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120287683</v>
+        <v>120287686</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,24 +1389,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615121</v>
+        <v>615132</v>
       </c>
       <c r="R8" t="n">
-        <v>6560512</v>
+        <v>6560670</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287687</v>
+        <v>120287682</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615148</v>
+        <v>615292</v>
       </c>
       <c r="R2" t="n">
-        <v>6560597</v>
+        <v>6560674</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287681</v>
+        <v>120287687</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,30 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615320</v>
+        <v>615148</v>
       </c>
       <c r="R3" t="n">
-        <v>6560647</v>
+        <v>6560597</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287685</v>
+        <v>120287686</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,28 +921,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615181</v>
+        <v>615132</v>
       </c>
       <c r="R4" t="n">
-        <v>6560482</v>
+        <v>6560670</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287683</v>
+        <v>120287681</v>
       </c>
       <c r="B6" t="n">
         <v>79160</v>
@@ -1178,7 +1178,11 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615121</v>
+        <v>615320</v>
       </c>
       <c r="R6" t="n">
-        <v>6560512</v>
+        <v>6560647</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287682</v>
+        <v>120287683</v>
       </c>
       <c r="B7" t="n">
         <v>79160</v>
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615292</v>
+        <v>615121</v>
       </c>
       <c r="R7" t="n">
-        <v>6560674</v>
+        <v>6560512</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120287686</v>
+        <v>120287685</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,32 +1389,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615132</v>
+        <v>615181</v>
       </c>
       <c r="R8" t="n">
-        <v>6560670</v>
+        <v>6560482</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287682</v>
+        <v>120287681</v>
       </c>
       <c r="B2" t="n">
         <v>79160</v>
@@ -710,7 +710,11 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615292</v>
+        <v>615320</v>
       </c>
       <c r="R2" t="n">
-        <v>6560674</v>
+        <v>6560647</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287687</v>
+        <v>120287686</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -825,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615148</v>
+        <v>615132</v>
       </c>
       <c r="R3" t="n">
-        <v>6560597</v>
+        <v>6560670</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287686</v>
+        <v>120287679</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,28 +929,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615132</v>
+        <v>615119</v>
       </c>
       <c r="R4" t="n">
-        <v>6560670</v>
+        <v>6560500</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287679</v>
+        <v>120287687</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,24 +1044,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1071,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615119</v>
+        <v>615148</v>
       </c>
       <c r="R5" t="n">
-        <v>6560500</v>
+        <v>6560597</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287681</v>
+        <v>120287683</v>
       </c>
       <c r="B6" t="n">
         <v>79160</v>
@@ -1178,11 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615320</v>
+        <v>615121</v>
       </c>
       <c r="R6" t="n">
-        <v>6560647</v>
+        <v>6560512</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287683</v>
+        <v>120287682</v>
       </c>
       <c r="B7" t="n">
         <v>79160</v>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615121</v>
+        <v>615292</v>
       </c>
       <c r="R7" t="n">
-        <v>6560512</v>
+        <v>6560674</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287681</v>
+        <v>120287682</v>
       </c>
       <c r="B2" t="n">
         <v>79160</v>
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615320</v>
+        <v>615292</v>
       </c>
       <c r="R2" t="n">
-        <v>6560647</v>
+        <v>6560674</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287679</v>
+        <v>120287687</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,24 +925,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615119</v>
+        <v>615148</v>
       </c>
       <c r="R4" t="n">
-        <v>6560500</v>
+        <v>6560597</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287687</v>
+        <v>120287683</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,28 +1044,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615148</v>
+        <v>615121</v>
       </c>
       <c r="R5" t="n">
-        <v>6560597</v>
+        <v>6560512</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287683</v>
+        <v>120287685</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615121</v>
+        <v>615181</v>
       </c>
       <c r="R6" t="n">
-        <v>6560512</v>
+        <v>6560482</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287682</v>
+        <v>120287679</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615292</v>
+        <v>615119</v>
       </c>
       <c r="R7" t="n">
-        <v>6560674</v>
+        <v>6560500</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120287685</v>
+        <v>120287681</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,30 +1385,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615181</v>
+        <v>615320</v>
       </c>
       <c r="R8" t="n">
-        <v>6560482</v>
+        <v>6560647</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287682</v>
+        <v>120287683</v>
       </c>
       <c r="B2" t="n">
         <v>79160</v>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615292</v>
+        <v>615121</v>
       </c>
       <c r="R2" t="n">
-        <v>6560674</v>
+        <v>6560512</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287686</v>
+        <v>120287681</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,30 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615132</v>
+        <v>615320</v>
       </c>
       <c r="R3" t="n">
-        <v>6560670</v>
+        <v>6560647</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287687</v>
+        <v>120287682</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,28 +925,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615148</v>
+        <v>615292</v>
       </c>
       <c r="R4" t="n">
-        <v>6560597</v>
+        <v>6560674</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287683</v>
+        <v>120287686</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,24 +1040,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615121</v>
+        <v>615132</v>
       </c>
       <c r="R5" t="n">
-        <v>6560512</v>
+        <v>6560670</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287679</v>
+        <v>120287687</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,24 +1274,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1301,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615119</v>
+        <v>615148</v>
       </c>
       <c r="R7" t="n">
-        <v>6560500</v>
+        <v>6560597</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1336,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120287681</v>
+        <v>120287679</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,30 +1393,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615320</v>
+        <v>615119</v>
       </c>
       <c r="R8" t="n">
-        <v>6560647</v>
+        <v>6560500</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287683</v>
+        <v>120287682</v>
       </c>
       <c r="B2" t="n">
         <v>79160</v>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615121</v>
+        <v>615292</v>
       </c>
       <c r="R2" t="n">
-        <v>6560512</v>
+        <v>6560674</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287681</v>
+        <v>120287686</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,30 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615320</v>
+        <v>615132</v>
       </c>
       <c r="R3" t="n">
-        <v>6560647</v>
+        <v>6560670</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287682</v>
+        <v>120287687</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,24 +925,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -952,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615292</v>
+        <v>615148</v>
       </c>
       <c r="R4" t="n">
-        <v>6560674</v>
+        <v>6560597</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287686</v>
+        <v>120287685</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,32 +1040,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615132</v>
+        <v>615181</v>
       </c>
       <c r="R5" t="n">
-        <v>6560670</v>
+        <v>6560482</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287685</v>
+        <v>120287683</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615181</v>
+        <v>615121</v>
       </c>
       <c r="R6" t="n">
-        <v>6560482</v>
+        <v>6560512</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287687</v>
+        <v>120287681</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,30 +1274,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615148</v>
+        <v>615320</v>
       </c>
       <c r="R7" t="n">
-        <v>6560597</v>
+        <v>6560647</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>120743622</v>
       </c>
       <c r="B12" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -1855,11 +1855,6 @@
       <c r="E12" t="n">
         <v>100138</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>120743622</v>
       </c>
       <c r="B12" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,6 +1854,11 @@
       </c>
       <c r="E12" t="n">
         <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>120743622</v>
       </c>
       <c r="B12" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,6 +2192,324 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122747220</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svarttj. SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>615234</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6560540</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122747219</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Krankpunsen V, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>615229</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6560552</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122747218</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78305</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>353</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svarttj. SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>615184</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6560537</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747218</v>
+        <v>122747220</v>
       </c>
       <c r="B15" t="n">
-        <v>78407</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,21 +2210,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615184</v>
+        <v>615234</v>
       </c>
       <c r="R15" t="n">
-        <v>6560537</v>
+        <v>6560540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
         <v>122747219</v>
       </c>
       <c r="B16" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747220</v>
+        <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>79380</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615234</v>
+        <v>615184</v>
       </c>
       <c r="R17" t="n">
-        <v>6560540</v>
+        <v>6560537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2300,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747219</v>
+        <v>122747218</v>
       </c>
       <c r="B16" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,34 +2316,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615229</v>
+        <v>615184</v>
       </c>
       <c r="R16" t="n">
-        <v>6560552</v>
+        <v>6560537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747218</v>
+        <v>122747219</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615184</v>
+        <v>615229</v>
       </c>
       <c r="R17" t="n">
-        <v>6560537</v>
+        <v>6560552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2194,7 +2194,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747220</v>
+        <v>122747219</v>
       </c>
       <c r="B15" t="n">
         <v>79384</v>
@@ -2230,14 +2230,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615234</v>
+        <v>615229</v>
       </c>
       <c r="R15" t="n">
-        <v>6560540</v>
+        <v>6560552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747218</v>
+        <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615184</v>
+        <v>615234</v>
       </c>
       <c r="R16" t="n">
-        <v>6560537</v>
+        <v>6560540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747219</v>
+        <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615229</v>
+        <v>615184</v>
       </c>
       <c r="R17" t="n">
-        <v>6560552</v>
+        <v>6560537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2194,7 +2194,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747219</v>
+        <v>122747220</v>
       </c>
       <c r="B15" t="n">
         <v>79384</v>
@@ -2230,14 +2230,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615229</v>
+        <v>615234</v>
       </c>
       <c r="R15" t="n">
-        <v>6560552</v>
+        <v>6560540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747220</v>
+        <v>122747218</v>
       </c>
       <c r="B16" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615234</v>
+        <v>615184</v>
       </c>
       <c r="R16" t="n">
-        <v>6560540</v>
+        <v>6560537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747218</v>
+        <v>122747219</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615184</v>
+        <v>615229</v>
       </c>
       <c r="R17" t="n">
-        <v>6560537</v>
+        <v>6560552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2300,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747218</v>
+        <v>122747219</v>
       </c>
       <c r="B16" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,34 +2316,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615184</v>
+        <v>615229</v>
       </c>
       <c r="R16" t="n">
-        <v>6560537</v>
+        <v>6560552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747219</v>
+        <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615229</v>
+        <v>615184</v>
       </c>
       <c r="R17" t="n">
-        <v>6560552</v>
+        <v>6560537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747220</v>
+        <v>122747218</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,21 +2210,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615234</v>
+        <v>615184</v>
       </c>
       <c r="R15" t="n">
-        <v>6560540</v>
+        <v>6560537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747218</v>
+        <v>122747220</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615184</v>
+        <v>615234</v>
       </c>
       <c r="R17" t="n">
-        <v>6560537</v>
+        <v>6560540</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2300,7 +2300,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747219</v>
+        <v>122747220</v>
       </c>
       <c r="B16" t="n">
         <v>79384</v>
@@ -2336,14 +2336,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615229</v>
+        <v>615234</v>
       </c>
       <c r="R16" t="n">
-        <v>6560552</v>
+        <v>6560540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747220</v>
+        <v>122747219</v>
       </c>
       <c r="B17" t="n">
         <v>79384</v>
@@ -2442,14 +2442,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615234</v>
+        <v>615229</v>
       </c>
       <c r="R17" t="n">
-        <v>6560540</v>
+        <v>6560552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747218</v>
+        <v>122747220</v>
       </c>
       <c r="B15" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,21 +2210,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615184</v>
+        <v>615234</v>
       </c>
       <c r="R15" t="n">
-        <v>6560537</v>
+        <v>6560540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747220</v>
+        <v>122747219</v>
       </c>
       <c r="B16" t="n">
         <v>79384</v>
@@ -2336,14 +2336,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615234</v>
+        <v>615229</v>
       </c>
       <c r="R16" t="n">
-        <v>6560540</v>
+        <v>6560552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747219</v>
+        <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>79384</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615229</v>
+        <v>615184</v>
       </c>
       <c r="R17" t="n">
-        <v>6560552</v>
+        <v>6560537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747220</v>
+        <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,14 +2230,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615234</v>
+        <v>615229</v>
       </c>
       <c r="R15" t="n">
-        <v>6560540</v>
+        <v>6560552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747219</v>
+        <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,14 +2336,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615229</v>
+        <v>615234</v>
       </c>
       <c r="R16" t="n">
-        <v>6560552</v>
+        <v>6560540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>78414</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78414</v>
+        <v>78416</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131739009</v>
+        <v>131737614</v>
       </c>
       <c r="B18" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,34 +2523,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614998</v>
+        <v>614857</v>
       </c>
       <c r="R18" t="n">
-        <v>6560540</v>
+        <v>6560612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131739006</v>
+        <v>131737671</v>
       </c>
       <c r="B19" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614970</v>
+        <v>614965</v>
       </c>
       <c r="R19" t="n">
-        <v>6560568</v>
+        <v>6560580</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131738992</v>
+        <v>131737631</v>
       </c>
       <c r="B20" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,34 +2725,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614903</v>
+        <v>614937</v>
       </c>
       <c r="R20" t="n">
-        <v>6560580</v>
+        <v>6560625</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737671</v>
+        <v>131737632</v>
       </c>
       <c r="B21" t="n">
         <v>93154</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614965</v>
+        <v>614949</v>
       </c>
       <c r="R21" t="n">
-        <v>6560580</v>
+        <v>6560635</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737631</v>
+        <v>131737647</v>
       </c>
       <c r="B22" t="n">
         <v>93154</v>
@@ -2947,14 +2947,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614937</v>
+        <v>615295</v>
       </c>
       <c r="R22" t="n">
-        <v>6560625</v>
+        <v>6560678</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737632</v>
+        <v>131737637</v>
       </c>
       <c r="B23" t="n">
         <v>93154</v>
@@ -3055,7 +3055,7 @@
         <v>614949</v>
       </c>
       <c r="R23" t="n">
-        <v>6560635</v>
+        <v>6560610</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737647</v>
+        <v>131737650</v>
       </c>
       <c r="B24" t="n">
         <v>93154</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615295</v>
+        <v>615325</v>
       </c>
       <c r="R24" t="n">
-        <v>6560678</v>
+        <v>6560719</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737637</v>
+        <v>131737654</v>
       </c>
       <c r="B25" t="n">
         <v>93154</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614949</v>
+        <v>615282</v>
       </c>
       <c r="R25" t="n">
-        <v>6560610</v>
+        <v>6560780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737650</v>
+        <v>131739009</v>
       </c>
       <c r="B26" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,34 +3331,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615325</v>
+        <v>614998</v>
       </c>
       <c r="R26" t="n">
-        <v>6560719</v>
+        <v>6560540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737654</v>
+        <v>131739006</v>
       </c>
       <c r="B27" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615282</v>
+        <v>614970</v>
       </c>
       <c r="R27" t="n">
-        <v>6560780</v>
+        <v>6560568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737614</v>
+        <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,21 +3533,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614857</v>
+        <v>614903</v>
       </c>
       <c r="R28" t="n">
-        <v>6560612</v>
+        <v>6560580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737685</v>
+        <v>131737620</v>
       </c>
       <c r="B37" t="n">
         <v>93154</v>
@@ -4489,14 +4489,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>615324</v>
+        <v>614896</v>
       </c>
       <c r="R37" t="n">
-        <v>6560604</v>
+        <v>6560613</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737672</v>
+        <v>131737685</v>
       </c>
       <c r="B38" t="n">
         <v>93154</v>
@@ -4590,14 +4590,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614950</v>
+        <v>615324</v>
       </c>
       <c r="R38" t="n">
-        <v>6560576</v>
+        <v>6560604</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737786</v>
+        <v>131737672</v>
       </c>
       <c r="B39" t="n">
         <v>93154</v>
@@ -4688,21 +4688,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615335</v>
+        <v>614950</v>
       </c>
       <c r="R39" t="n">
-        <v>6560536</v>
+        <v>6560576</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,17 +4725,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,7 +4761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737662</v>
+        <v>131737786</v>
       </c>
       <c r="B40" t="n">
         <v>93154</v>
@@ -4798,17 +4789,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615040</v>
+        <v>615335</v>
       </c>
       <c r="R40" t="n">
-        <v>6560530</v>
+        <v>6560536</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4835,12 +4830,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,7 +4871,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737620</v>
+        <v>131737662</v>
       </c>
       <c r="B41" t="n">
         <v>93154</v>
@@ -4902,14 +4902,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614896</v>
+        <v>615040</v>
       </c>
       <c r="R41" t="n">
-        <v>6560613</v>
+        <v>6560530</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739002</v>
+        <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614953</v>
+        <v>614963</v>
       </c>
       <c r="R46" t="n">
-        <v>6560567</v>
+        <v>6560615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B47" t="n">
         <v>93154</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R47" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131737618</v>
+        <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614881</v>
+        <v>614953</v>
       </c>
       <c r="R48" t="n">
-        <v>6560601</v>
+        <v>6560567</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131739012</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615022</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560527</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,45 +5780,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737925</v>
       </c>
       <c r="B50" t="n">
-        <v>93154</v>
+        <v>8453</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615343</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560656</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737925</v>
+        <v>131737677</v>
       </c>
       <c r="B51" t="n">
-        <v>8453</v>
+        <v>93154</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615343</v>
+        <v>615064</v>
       </c>
       <c r="R51" t="n">
-        <v>6560656</v>
+        <v>6560525</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,7 +5982,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737677</v>
+        <v>131737684</v>
       </c>
       <c r="B52" t="n">
         <v>93154</v>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615064</v>
+        <v>615333</v>
       </c>
       <c r="R52" t="n">
-        <v>6560525</v>
+        <v>6560608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B53" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6094,34 +6094,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R53" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737675</v>
+        <v>131737617</v>
       </c>
       <c r="B54" t="n">
         <v>93154</v>
@@ -6215,14 +6215,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614961</v>
+        <v>614867</v>
       </c>
       <c r="R54" t="n">
-        <v>6560552</v>
+        <v>6560588</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737617</v>
+        <v>131737675</v>
       </c>
       <c r="B55" t="n">
         <v>93154</v>
@@ -6316,14 +6316,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614867</v>
+        <v>614961</v>
       </c>
       <c r="R55" t="n">
-        <v>6560588</v>
+        <v>6560552</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737633</v>
+        <v>131737615</v>
       </c>
       <c r="B57" t="n">
         <v>93154</v>
@@ -6518,14 +6518,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614946</v>
+        <v>614854</v>
       </c>
       <c r="R57" t="n">
-        <v>6560623</v>
+        <v>6560611</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737657</v>
+        <v>131737633</v>
       </c>
       <c r="B58" t="n">
         <v>93154</v>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>615264</v>
+        <v>614946</v>
       </c>
       <c r="R58" t="n">
-        <v>6560736</v>
+        <v>6560623</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737615</v>
+        <v>131737657</v>
       </c>
       <c r="B59" t="n">
         <v>93154</v>
@@ -6720,14 +6720,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614854</v>
+        <v>615264</v>
       </c>
       <c r="R59" t="n">
-        <v>6560611</v>
+        <v>6560736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B60" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R60" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739008</v>
+        <v>131737688</v>
       </c>
       <c r="B61" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,34 +6902,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614995</v>
+        <v>615310</v>
       </c>
       <c r="R61" t="n">
-        <v>6560547</v>
+        <v>6560543</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739005</v>
+        <v>131738993</v>
       </c>
       <c r="B62" t="n">
         <v>79879</v>
@@ -7023,14 +7023,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614968</v>
+        <v>614904</v>
       </c>
       <c r="R62" t="n">
-        <v>6560572</v>
+        <v>6560578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737652</v>
+        <v>131739008</v>
       </c>
       <c r="B63" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615301</v>
+        <v>614995</v>
       </c>
       <c r="R63" t="n">
-        <v>6560755</v>
+        <v>6560547</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737688</v>
+        <v>131739005</v>
       </c>
       <c r="B64" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7205,34 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>615310</v>
+        <v>614968</v>
       </c>
       <c r="R64" t="n">
-        <v>6560543</v>
+        <v>6560572</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737686</v>
+        <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93154</v>
+        <v>93132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7306,21 +7306,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615314</v>
+        <v>615336</v>
       </c>
       <c r="R65" t="n">
-        <v>6560599</v>
+        <v>6560577</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,7 +7396,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737643</v>
+        <v>131737686</v>
       </c>
       <c r="B66" t="n">
         <v>93154</v>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615322</v>
+        <v>615314</v>
       </c>
       <c r="R66" t="n">
-        <v>6560634</v>
+        <v>6560599</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131736575</v>
+        <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93132</v>
+        <v>93154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615336</v>
+        <v>615322</v>
       </c>
       <c r="R67" t="n">
-        <v>6560577</v>
+        <v>6560634</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131740360</v>
+        <v>131737667</v>
       </c>
       <c r="B68" t="n">
-        <v>93145</v>
+        <v>93154</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,34 +7609,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615296</v>
+        <v>614991</v>
       </c>
       <c r="R68" t="n">
-        <v>6560688</v>
+        <v>6560587</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7671,18 +7671,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7705,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131739010</v>
+        <v>131737638</v>
       </c>
       <c r="B69" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7716,21 +7710,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7740,10 +7734,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615012</v>
+        <v>614943</v>
       </c>
       <c r="R69" t="n">
-        <v>6560549</v>
+        <v>6560591</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7806,10 +7800,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131739015</v>
+        <v>131737658</v>
       </c>
       <c r="B70" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7817,21 +7811,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7841,10 +7835,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>615373</v>
+        <v>615282</v>
       </c>
       <c r="R70" t="n">
-        <v>6560555</v>
+        <v>6560684</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,10 +7901,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737667</v>
+        <v>131740360</v>
       </c>
       <c r="B71" t="n">
-        <v>93154</v>
+        <v>93145</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7918,34 +7912,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614991</v>
+        <v>615296</v>
       </c>
       <c r="R71" t="n">
-        <v>6560587</v>
+        <v>6560688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7980,12 +7974,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737638</v>
+        <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614943</v>
+        <v>615012</v>
       </c>
       <c r="R72" t="n">
-        <v>6560591</v>
+        <v>6560549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737658</v>
+        <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615282</v>
+        <v>615373</v>
       </c>
       <c r="R73" t="n">
-        <v>6560684</v>
+        <v>6560555</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131738989</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614945</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560637</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131739011</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615080</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560512</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,32 +8513,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737644</v>
+        <v>131737924</v>
       </c>
       <c r="B77" t="n">
-        <v>93154</v>
+        <v>8453</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615331</v>
+        <v>615091</v>
       </c>
       <c r="R77" t="n">
-        <v>6560676</v>
+        <v>6560504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737639</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614942</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560579</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737668</v>
+        <v>131739041</v>
       </c>
       <c r="B79" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614990</v>
+        <v>615269</v>
       </c>
       <c r="R79" t="n">
-        <v>6560601</v>
+        <v>6560500</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737924</v>
+        <v>131739011</v>
       </c>
       <c r="B80" t="n">
-        <v>8453</v>
+        <v>79879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615091</v>
+        <v>615080</v>
       </c>
       <c r="R80" t="n">
-        <v>6560504</v>
+        <v>6560512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131738998</v>
+        <v>131737783</v>
       </c>
       <c r="B90" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,34 +9846,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615020</v>
+        <v>615276</v>
       </c>
       <c r="R90" t="n">
-        <v>6560533</v>
+        <v>6560495</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9900,12 +9904,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9936,7 +9945,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737783</v>
+        <v>131737641</v>
       </c>
       <c r="B91" t="n">
         <v>93154</v>
@@ -9964,21 +9973,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615276</v>
+        <v>614893</v>
       </c>
       <c r="R91" t="n">
-        <v>6560495</v>
+        <v>6560582</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10005,17 +10010,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10046,7 +10046,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737641</v>
+        <v>131737656</v>
       </c>
       <c r="B92" t="n">
         <v>93154</v>
@@ -10077,14 +10077,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614893</v>
+        <v>615271</v>
       </c>
       <c r="R92" t="n">
-        <v>6560582</v>
+        <v>6560749</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,7 +10147,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737656</v>
+        <v>131737666</v>
       </c>
       <c r="B93" t="n">
         <v>93154</v>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615271</v>
+        <v>614995</v>
       </c>
       <c r="R93" t="n">
-        <v>6560749</v>
+        <v>6560571</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737666</v>
+        <v>131737676</v>
       </c>
       <c r="B94" t="n">
         <v>93154</v>
@@ -10279,14 +10279,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614995</v>
+        <v>615060</v>
       </c>
       <c r="R94" t="n">
-        <v>6560571</v>
+        <v>6560536</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10349,7 +10349,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737676</v>
+        <v>131737646</v>
       </c>
       <c r="B95" t="n">
         <v>93154</v>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615060</v>
+        <v>615289</v>
       </c>
       <c r="R95" t="n">
-        <v>6560536</v>
+        <v>6560695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737646</v>
+        <v>131737690</v>
       </c>
       <c r="B96" t="n">
         <v>93154</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615289</v>
+        <v>615387</v>
       </c>
       <c r="R96" t="n">
-        <v>6560695</v>
+        <v>6560558</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,10 +10551,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737690</v>
+        <v>131738998</v>
       </c>
       <c r="B97" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10562,34 +10562,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615387</v>
+        <v>615020</v>
       </c>
       <c r="R97" t="n">
-        <v>6560558</v>
+        <v>6560533</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739013</v>
+        <v>131737619</v>
       </c>
       <c r="B100" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615376</v>
+        <v>614885</v>
       </c>
       <c r="R100" t="n">
-        <v>6560556</v>
+        <v>6560613</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739004</v>
+        <v>131737625</v>
       </c>
       <c r="B101" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614958</v>
+        <v>614918</v>
       </c>
       <c r="R101" t="n">
-        <v>6560561</v>
+        <v>6560620</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739001</v>
+        <v>131737645</v>
       </c>
       <c r="B102" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614955</v>
+        <v>615304</v>
       </c>
       <c r="R102" t="n">
-        <v>6560579</v>
+        <v>6560686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737625</v>
+        <v>131737655</v>
       </c>
       <c r="B103" t="n">
         <v>93154</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614918</v>
+        <v>615267</v>
       </c>
       <c r="R103" t="n">
-        <v>6560620</v>
+        <v>6560777</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737645</v>
+        <v>131737636</v>
       </c>
       <c r="B104" t="n">
         <v>93154</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615304</v>
+        <v>614960</v>
       </c>
       <c r="R104" t="n">
-        <v>6560686</v>
+        <v>6560601</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737655</v>
+        <v>131737691</v>
       </c>
       <c r="B105" t="n">
         <v>93154</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615267</v>
+        <v>615367</v>
       </c>
       <c r="R105" t="n">
-        <v>6560777</v>
+        <v>6560553</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737636</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
         <v>93154</v>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614960</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560601</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737619</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614885</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560613</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737664</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614942</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560568</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,45 +11864,53 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131737627</v>
+        <v>131740030</v>
       </c>
       <c r="B110" t="n">
-        <v>93154</v>
+        <v>57086</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614921</v>
+        <v>614953</v>
       </c>
       <c r="R110" t="n">
-        <v>6560604</v>
+        <v>6560578</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11935,6 +11943,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11965,7 +11978,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737648</v>
+        <v>131737627</v>
       </c>
       <c r="B111" t="n">
         <v>93154</v>
@@ -11996,14 +12009,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615306</v>
+        <v>614921</v>
       </c>
       <c r="R111" t="n">
-        <v>6560663</v>
+        <v>6560604</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12066,7 +12079,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737630</v>
+        <v>131737648</v>
       </c>
       <c r="B112" t="n">
         <v>93154</v>
@@ -12097,14 +12110,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614948</v>
+        <v>615306</v>
       </c>
       <c r="R112" t="n">
-        <v>6560611</v>
+        <v>6560663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12167,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131736566</v>
+        <v>131737630</v>
       </c>
       <c r="B113" t="n">
-        <v>93132</v>
+        <v>93154</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12178,38 +12191,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615319</v>
+        <v>614948</v>
       </c>
       <c r="R113" t="n">
-        <v>6560579</v>
+        <v>6560611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12242,11 +12251,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12277,53 +12281,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740030</v>
+        <v>131740361</v>
       </c>
       <c r="B114" t="n">
-        <v>57086</v>
+        <v>93145</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614953</v>
+        <v>615309</v>
       </c>
       <c r="R114" t="n">
-        <v>6560578</v>
+        <v>6560557</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12358,17 +12350,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12391,10 +12379,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131740361</v>
+        <v>131736566</v>
       </c>
       <c r="B115" t="n">
-        <v>93145</v>
+        <v>93132</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12402,30 +12390,38 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615309</v>
+        <v>615319</v>
       </c>
       <c r="R115" t="n">
-        <v>6560557</v>
+        <v>6560579</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12460,13 +12456,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737665</v>
+        <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>93154</v>
+        <v>91849</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614993</v>
+        <v>614974</v>
       </c>
       <c r="R118" t="n">
-        <v>6560559</v>
+        <v>6560628</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,7 +12792,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737670</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
         <v>93154</v>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614972</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560590</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131739003</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614959</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560556</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131740081</v>
+        <v>131739003</v>
       </c>
       <c r="B121" t="n">
-        <v>91849</v>
+        <v>79879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614974</v>
+        <v>614959</v>
       </c>
       <c r="R121" t="n">
-        <v>6560628</v>
+        <v>6560556</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13059,12 +13059,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13407,10 +13407,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131739026</v>
+        <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13418,34 +13418,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>615203</v>
+        <v>614898</v>
       </c>
       <c r="R125" t="n">
-        <v>6560503</v>
+        <v>6560601</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13472,12 +13472,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13508,10 +13508,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131738997</v>
+        <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13519,34 +13519,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615026</v>
+        <v>615337</v>
       </c>
       <c r="R126" t="n">
-        <v>6560531</v>
+        <v>6560617</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13609,7 +13609,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737622</v>
+        <v>131737678</v>
       </c>
       <c r="B127" t="n">
         <v>93154</v>
@@ -13640,14 +13640,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614898</v>
+        <v>615054</v>
       </c>
       <c r="R127" t="n">
-        <v>6560601</v>
+        <v>6560523</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737683</v>
+        <v>131737681</v>
       </c>
       <c r="B128" t="n">
         <v>93154</v>
@@ -13741,14 +13741,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615337</v>
+        <v>615383</v>
       </c>
       <c r="R128" t="n">
-        <v>6560617</v>
+        <v>6560632</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737678</v>
+        <v>131739026</v>
       </c>
       <c r="B129" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13822,21 +13822,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13846,10 +13846,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615054</v>
+        <v>615203</v>
       </c>
       <c r="R129" t="n">
-        <v>6560523</v>
+        <v>6560503</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13876,12 +13876,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13912,10 +13912,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131737681</v>
+        <v>131738997</v>
       </c>
       <c r="B130" t="n">
-        <v>93154</v>
+        <v>79879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13923,34 +13923,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615383</v>
+        <v>615026</v>
       </c>
       <c r="R130" t="n">
-        <v>6560632</v>
+        <v>6560531</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14013,10 +14013,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131738996</v>
+        <v>131737682</v>
       </c>
       <c r="B131" t="n">
-        <v>79879</v>
+        <v>93154</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14024,21 +14024,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615290</v>
+        <v>615350</v>
       </c>
       <c r="R131" t="n">
-        <v>6560715</v>
+        <v>6560611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B132" t="n">
         <v>93154</v>
@@ -14145,14 +14145,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R132" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737663</v>
+        <v>131737673</v>
       </c>
       <c r="B133" t="n">
         <v>93154</v>
@@ -14250,10 +14250,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615046</v>
+        <v>614957</v>
       </c>
       <c r="R133" t="n">
-        <v>6560537</v>
+        <v>6560564</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737673</v>
+        <v>131737661</v>
       </c>
       <c r="B134" t="n">
         <v>93154</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614957</v>
+        <v>615060</v>
       </c>
       <c r="R134" t="n">
-        <v>6560564</v>
+        <v>6560565</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,45 +14417,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737661</v>
+        <v>131735760</v>
       </c>
       <c r="B135" t="n">
-        <v>93154</v>
+        <v>90593</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615060</v>
+        <v>615279</v>
       </c>
       <c r="R135" t="n">
-        <v>6560565</v>
+        <v>6560699</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,32 +14518,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>90593</v>
+        <v>79879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R136" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737614</v>
+        <v>131737671</v>
       </c>
       <c r="B18" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,14 +2543,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614857</v>
+        <v>614965</v>
       </c>
       <c r="R18" t="n">
-        <v>6560612</v>
+        <v>6560580</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737671</v>
+        <v>131737631</v>
       </c>
       <c r="B19" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614965</v>
+        <v>614937</v>
       </c>
       <c r="R19" t="n">
-        <v>6560580</v>
+        <v>6560625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737631</v>
+        <v>131737632</v>
       </c>
       <c r="B20" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614937</v>
+        <v>614949</v>
       </c>
       <c r="R20" t="n">
-        <v>6560625</v>
+        <v>6560635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737632</v>
+        <v>131737637</v>
       </c>
       <c r="B21" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>614949</v>
       </c>
       <c r="R21" t="n">
-        <v>6560635</v>
+        <v>6560610</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737647</v>
+        <v>131737654</v>
       </c>
       <c r="B22" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,14 +2947,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615295</v>
+        <v>615282</v>
       </c>
       <c r="R22" t="n">
-        <v>6560678</v>
+        <v>6560780</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737637</v>
+        <v>131737614</v>
       </c>
       <c r="B23" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,14 +3048,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614949</v>
+        <v>614857</v>
       </c>
       <c r="R23" t="n">
-        <v>6560610</v>
+        <v>6560612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737650</v>
+        <v>131739009</v>
       </c>
       <c r="B24" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,34 +3129,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615325</v>
+        <v>614998</v>
       </c>
       <c r="R24" t="n">
-        <v>6560719</v>
+        <v>6560540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737654</v>
+        <v>131737647</v>
       </c>
       <c r="B25" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,14 +3250,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615282</v>
+        <v>615295</v>
       </c>
       <c r="R25" t="n">
-        <v>6560780</v>
+        <v>6560678</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131739009</v>
+        <v>131737650</v>
       </c>
       <c r="B26" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,34 +3331,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614998</v>
+        <v>615325</v>
       </c>
       <c r="R26" t="n">
-        <v>6560540</v>
+        <v>6560719</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
         <v>131739006</v>
       </c>
       <c r="B27" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>131737787</v>
       </c>
       <c r="B29" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737651</v>
+        <v>131737785</v>
       </c>
       <c r="B30" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3761,17 +3761,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615311</v>
+        <v>615314</v>
       </c>
       <c r="R30" t="n">
-        <v>6560742</v>
+        <v>6560513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,12 +3802,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737785</v>
+        <v>131737784</v>
       </c>
       <c r="B31" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,7 +3873,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3873,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615314</v>
+        <v>615291</v>
       </c>
       <c r="R31" t="n">
-        <v>6560513</v>
+        <v>6560497</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3922,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3953,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737784</v>
+        <v>131737629</v>
       </c>
       <c r="B32" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,21 +3981,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615291</v>
+        <v>614941</v>
       </c>
       <c r="R32" t="n">
-        <v>6560497</v>
+        <v>6560607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,17 +4018,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737629</v>
+        <v>131737651</v>
       </c>
       <c r="B33" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4085,14 +4085,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614941</v>
+        <v>615311</v>
       </c>
       <c r="R33" t="n">
-        <v>6560607</v>
+        <v>6560742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,7 +4158,7 @@
         <v>131738991</v>
       </c>
       <c r="B34" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>131739043</v>
       </c>
       <c r="B35" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>131739007</v>
       </c>
       <c r="B36" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737620</v>
+        <v>131737786</v>
       </c>
       <c r="B37" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,17 +4486,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614896</v>
+        <v>615335</v>
       </c>
       <c r="R37" t="n">
-        <v>6560613</v>
+        <v>6560536</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4523,12 +4527,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4559,10 +4568,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737685</v>
+        <v>131737669</v>
       </c>
       <c r="B38" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4590,14 +4599,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615324</v>
+        <v>614973</v>
       </c>
       <c r="R38" t="n">
-        <v>6560604</v>
+        <v>6560600</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4660,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737672</v>
+        <v>131737685</v>
       </c>
       <c r="B39" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4691,14 +4700,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614950</v>
+        <v>615324</v>
       </c>
       <c r="R39" t="n">
-        <v>6560576</v>
+        <v>6560604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737786</v>
+        <v>131737672</v>
       </c>
       <c r="B40" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,21 +4798,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615335</v>
+        <v>614950</v>
       </c>
       <c r="R40" t="n">
-        <v>6560536</v>
+        <v>6560576</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,17 +4835,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737662</v>
+        <v>131737620</v>
       </c>
       <c r="B41" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4902,14 +4902,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>615040</v>
+        <v>614896</v>
       </c>
       <c r="R41" t="n">
-        <v>6560530</v>
+        <v>6560613</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737634</v>
+        <v>131737660</v>
       </c>
       <c r="B42" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,14 +5003,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614954</v>
+        <v>615278</v>
       </c>
       <c r="R42" t="n">
-        <v>6560617</v>
+        <v>6560662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737669</v>
+        <v>131737640</v>
       </c>
       <c r="B43" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,14 +5104,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614973</v>
+        <v>614934</v>
       </c>
       <c r="R43" t="n">
-        <v>6560600</v>
+        <v>6560578</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737660</v>
+        <v>131737662</v>
       </c>
       <c r="B44" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615278</v>
+        <v>615040</v>
       </c>
       <c r="R44" t="n">
-        <v>6560662</v>
+        <v>6560530</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737640</v>
+        <v>131737634</v>
       </c>
       <c r="B45" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614934</v>
+        <v>614954</v>
       </c>
       <c r="R45" t="n">
-        <v>6560578</v>
+        <v>6560617</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5379,7 +5379,7 @@
         <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>131737618</v>
       </c>
       <c r="B47" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>615022</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,45 +5780,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737925</v>
+        <v>131737616</v>
       </c>
       <c r="B50" t="n">
-        <v>8453</v>
+        <v>93155</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615343</v>
+        <v>614862</v>
       </c>
       <c r="R50" t="n">
-        <v>6560656</v>
+        <v>6560592</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737677</v>
+        <v>131737925</v>
       </c>
       <c r="B51" t="n">
-        <v>93154</v>
+        <v>8454</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615064</v>
+        <v>615343</v>
       </c>
       <c r="R51" t="n">
-        <v>6560525</v>
+        <v>6560656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737684</v>
+        <v>131737677</v>
       </c>
       <c r="B52" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615333</v>
+        <v>615064</v>
       </c>
       <c r="R52" t="n">
-        <v>6560608</v>
+        <v>6560525</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131739012</v>
+        <v>131737684</v>
       </c>
       <c r="B53" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6094,34 +6094,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615022</v>
+        <v>615333</v>
       </c>
       <c r="R53" t="n">
-        <v>6560527</v>
+        <v>6560608</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
         <v>131737617</v>
       </c>
       <c r="B54" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>131737675</v>
       </c>
       <c r="B55" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737615</v>
+        <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6518,14 +6518,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614854</v>
+        <v>614946</v>
       </c>
       <c r="R57" t="n">
-        <v>6560611</v>
+        <v>6560623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737633</v>
+        <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614946</v>
+        <v>615264</v>
       </c>
       <c r="R58" t="n">
-        <v>6560623</v>
+        <v>6560736</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737657</v>
+        <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6720,14 +6720,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>615264</v>
+        <v>614854</v>
       </c>
       <c r="R59" t="n">
-        <v>6560736</v>
+        <v>6560611</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737652</v>
+        <v>131737688</v>
       </c>
       <c r="B60" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6821,14 +6821,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615301</v>
+        <v>615310</v>
       </c>
       <c r="R60" t="n">
-        <v>6560755</v>
+        <v>6560543</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737688</v>
+        <v>131739008</v>
       </c>
       <c r="B61" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,34 +6902,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615310</v>
+        <v>614995</v>
       </c>
       <c r="R61" t="n">
-        <v>6560543</v>
+        <v>6560547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131738993</v>
+        <v>131739005</v>
       </c>
       <c r="B62" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7023,14 +7023,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614904</v>
+        <v>614968</v>
       </c>
       <c r="R62" t="n">
-        <v>6560578</v>
+        <v>6560572</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739008</v>
+        <v>131737652</v>
       </c>
       <c r="B63" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614995</v>
+        <v>615301</v>
       </c>
       <c r="R63" t="n">
-        <v>6560547</v>
+        <v>6560755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739005</v>
+        <v>131738993</v>
       </c>
       <c r="B64" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7225,14 +7225,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614968</v>
+        <v>614904</v>
       </c>
       <c r="R64" t="n">
-        <v>6560572</v>
+        <v>6560578</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131736575</v>
+        <v>131737686</v>
       </c>
       <c r="B65" t="n">
-        <v>93132</v>
+        <v>93155</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7306,21 +7306,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R65" t="n">
-        <v>6560577</v>
+        <v>6560599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,10 +7396,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737686</v>
+        <v>131736575</v>
       </c>
       <c r="B66" t="n">
-        <v>93154</v>
+        <v>93133</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615314</v>
+        <v>615336</v>
       </c>
       <c r="R66" t="n">
-        <v>6560599</v>
+        <v>6560577</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7500,7 +7500,7 @@
         <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>131737667</v>
       </c>
       <c r="B68" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737638</v>
+        <v>131740360</v>
       </c>
       <c r="B69" t="n">
-        <v>93154</v>
+        <v>93146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614943</v>
+        <v>615296</v>
       </c>
       <c r="R69" t="n">
-        <v>6560591</v>
+        <v>6560688</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,12 +7772,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7803,7 +7809,7 @@
         <v>131737658</v>
       </c>
       <c r="B70" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7901,10 +7907,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740360</v>
+        <v>131737638</v>
       </c>
       <c r="B71" t="n">
-        <v>93145</v>
+        <v>93155</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7912,34 +7918,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615296</v>
+        <v>614943</v>
       </c>
       <c r="R71" t="n">
-        <v>6560688</v>
+        <v>6560591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7974,18 +7980,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131739041</v>
       </c>
       <c r="B74" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,21 +8221,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>615269</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560500</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>131739011</v>
       </c>
       <c r="B75" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>615080</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560512</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131737644</v>
       </c>
       <c r="B76" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>615331</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560676</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,45 +8513,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737924</v>
+        <v>131737668</v>
       </c>
       <c r="B77" t="n">
-        <v>8453</v>
+        <v>93155</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615091</v>
+        <v>614990</v>
       </c>
       <c r="R77" t="n">
-        <v>6560504</v>
+        <v>6560601</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,45 +8614,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131737924</v>
       </c>
       <c r="B78" t="n">
-        <v>79879</v>
+        <v>8454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>615091</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560504</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B79" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,10 +8816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131739011</v>
+        <v>131738989</v>
       </c>
       <c r="B80" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8847,14 +8847,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615080</v>
+        <v>614945</v>
       </c>
       <c r="R80" t="n">
-        <v>6560512</v>
+        <v>6560637</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>131737674</v>
       </c>
       <c r="B81" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>131737782</v>
       </c>
       <c r="B82" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9229,10 +9229,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737653</v>
+        <v>131737624</v>
       </c>
       <c r="B84" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9260,14 +9260,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>615289</v>
+        <v>614910</v>
       </c>
       <c r="R84" t="n">
-        <v>6560767</v>
+        <v>6560612</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737624</v>
+        <v>131737653</v>
       </c>
       <c r="B85" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9361,14 +9361,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614910</v>
+        <v>615289</v>
       </c>
       <c r="R85" t="n">
-        <v>6560612</v>
+        <v>6560767</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737626</v>
+        <v>131738988</v>
       </c>
       <c r="B86" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614911</v>
+        <v>614862</v>
       </c>
       <c r="R86" t="n">
-        <v>6560610</v>
+        <v>6560592</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737642</v>
+        <v>131737626</v>
       </c>
       <c r="B87" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614884</v>
+        <v>614911</v>
       </c>
       <c r="R87" t="n">
-        <v>6560568</v>
+        <v>6560610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737687</v>
+        <v>131737642</v>
       </c>
       <c r="B88" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>615322</v>
+        <v>614884</v>
       </c>
       <c r="R88" t="n">
-        <v>6560582</v>
+        <v>6560568</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131738988</v>
+        <v>131737687</v>
       </c>
       <c r="B89" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9745,34 +9745,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614862</v>
+        <v>615322</v>
       </c>
       <c r="R89" t="n">
-        <v>6560592</v>
+        <v>6560582</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9838,7 +9838,7 @@
         <v>131737783</v>
       </c>
       <c r="B90" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737641</v>
+        <v>131737656</v>
       </c>
       <c r="B91" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,14 +9976,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614893</v>
+        <v>615271</v>
       </c>
       <c r="R91" t="n">
-        <v>6560582</v>
+        <v>6560749</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10046,10 +10046,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737656</v>
+        <v>131737641</v>
       </c>
       <c r="B92" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10077,14 +10077,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615271</v>
+        <v>614893</v>
       </c>
       <c r="R92" t="n">
-        <v>6560749</v>
+        <v>6560582</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10150,7 +10150,7 @@
         <v>131737666</v>
       </c>
       <c r="B93" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>131737676</v>
       </c>
       <c r="B94" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>131737646</v>
       </c>
       <c r="B95" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>131737690</v>
       </c>
       <c r="B96" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10551,10 +10551,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131738998</v>
+        <v>131737659</v>
       </c>
       <c r="B97" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10562,34 +10562,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615020</v>
+        <v>615267</v>
       </c>
       <c r="R97" t="n">
-        <v>6560533</v>
+        <v>6560667</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737659</v>
+        <v>131737649</v>
       </c>
       <c r="B98" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615267</v>
+        <v>615316</v>
       </c>
       <c r="R98" t="n">
-        <v>6560667</v>
+        <v>6560709</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737649</v>
+        <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615316</v>
+        <v>615020</v>
       </c>
       <c r="R99" t="n">
-        <v>6560709</v>
+        <v>6560533</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737619</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614885</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560613</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737625</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614918</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560620</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737645</v>
+        <v>131739013</v>
       </c>
       <c r="B102" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615304</v>
+        <v>615376</v>
       </c>
       <c r="R102" t="n">
-        <v>6560686</v>
+        <v>6560556</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737655</v>
+        <v>131739001</v>
       </c>
       <c r="B103" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11168,21 +11168,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615267</v>
+        <v>614955</v>
       </c>
       <c r="R103" t="n">
-        <v>6560777</v>
+        <v>6560579</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737636</v>
+        <v>131737619</v>
       </c>
       <c r="B104" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614960</v>
+        <v>614885</v>
       </c>
       <c r="R104" t="n">
-        <v>6560601</v>
+        <v>6560613</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737691</v>
+        <v>131737655</v>
       </c>
       <c r="B105" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615367</v>
+        <v>615267</v>
       </c>
       <c r="R105" t="n">
-        <v>6560553</v>
+        <v>6560777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131737636</v>
       </c>
       <c r="B106" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>614960</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560601</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739013</v>
+        <v>131737691</v>
       </c>
       <c r="B107" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615376</v>
+        <v>615367</v>
       </c>
       <c r="R107" t="n">
-        <v>6560556</v>
+        <v>6560553</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739004</v>
+        <v>131737664</v>
       </c>
       <c r="B108" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614958</v>
+        <v>614942</v>
       </c>
       <c r="R108" t="n">
-        <v>6560561</v>
+        <v>6560568</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131739004</v>
       </c>
       <c r="B109" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>614958</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560561</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,53 +11864,41 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740030</v>
+        <v>131740361</v>
       </c>
       <c r="B110" t="n">
-        <v>57086</v>
+        <v>93146</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614953</v>
+        <v>615309</v>
       </c>
       <c r="R110" t="n">
-        <v>6560578</v>
+        <v>6560557</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11945,17 +11933,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11981,7 +11965,7 @@
         <v>131737627</v>
       </c>
       <c r="B111" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12079,10 +12063,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737648</v>
+        <v>131737630</v>
       </c>
       <c r="B112" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12110,14 +12094,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615306</v>
+        <v>614948</v>
       </c>
       <c r="R112" t="n">
-        <v>6560663</v>
+        <v>6560611</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12180,10 +12164,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737630</v>
+        <v>131738990</v>
       </c>
       <c r="B113" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12191,34 +12175,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614948</v>
+        <v>614930</v>
       </c>
       <c r="R113" t="n">
-        <v>6560611</v>
+        <v>6560587</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12281,10 +12265,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740361</v>
+        <v>131736566</v>
       </c>
       <c r="B114" t="n">
-        <v>93145</v>
+        <v>93133</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12292,30 +12276,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615309</v>
+        <v>615319</v>
       </c>
       <c r="R114" t="n">
-        <v>6560557</v>
+        <v>6560579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12350,13 +12342,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12379,49 +12375,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131736566</v>
+        <v>131740030</v>
       </c>
       <c r="B115" t="n">
-        <v>93132</v>
+        <v>57087</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2059</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615319</v>
+        <v>614953</v>
       </c>
       <c r="R115" t="n">
-        <v>6560579</v>
+        <v>6560578</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12489,10 +12489,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738995</v>
+        <v>131737648</v>
       </c>
       <c r="B116" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12500,21 +12500,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12524,10 +12524,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615323</v>
+        <v>615306</v>
       </c>
       <c r="R116" t="n">
-        <v>6560647</v>
+        <v>6560663</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,10 +12590,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738990</v>
+        <v>131738995</v>
       </c>
       <c r="B117" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12621,14 +12621,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614930</v>
+        <v>615323</v>
       </c>
       <c r="R117" t="n">
-        <v>6560587</v>
+        <v>6560647</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12694,7 +12694,7 @@
         <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131739003</v>
       </c>
       <c r="B119" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614959</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560556</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131737665</v>
       </c>
       <c r="B120" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614993</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739003</v>
+        <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>79879</v>
+        <v>93155</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614959</v>
+        <v>614972</v>
       </c>
       <c r="R121" t="n">
-        <v>6560556</v>
+        <v>6560590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13095,49 +13095,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131735761</v>
+        <v>131738994</v>
       </c>
       <c r="B122" t="n">
-        <v>90593</v>
+        <v>79880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>615277</v>
+        <v>614890</v>
       </c>
       <c r="R122" t="n">
-        <v>6560691</v>
+        <v>6560564</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13170,11 +13166,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13205,10 +13196,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131738994</v>
+        <v>131739000</v>
       </c>
       <c r="B123" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13240,10 +13231,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614890</v>
+        <v>614941</v>
       </c>
       <c r="R123" t="n">
-        <v>6560564</v>
+        <v>6560553</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13306,45 +13297,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739000</v>
+        <v>131735761</v>
       </c>
       <c r="B124" t="n">
-        <v>79879</v>
+        <v>90594</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614941</v>
+        <v>615277</v>
       </c>
       <c r="R124" t="n">
-        <v>6560553</v>
+        <v>6560691</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13377,6 +13372,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13410,7 +13410,7 @@
         <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>131737678</v>
       </c>
       <c r="B127" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>131737681</v>
       </c>
       <c r="B128" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131739026</v>
+        <v>131738997</v>
       </c>
       <c r="B129" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13842,14 +13842,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615203</v>
+        <v>615026</v>
       </c>
       <c r="R129" t="n">
-        <v>6560503</v>
+        <v>6560531</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13876,12 +13876,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13912,10 +13912,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131738997</v>
+        <v>131739026</v>
       </c>
       <c r="B130" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13943,14 +13943,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615026</v>
+        <v>615203</v>
       </c>
       <c r="R130" t="n">
-        <v>6560531</v>
+        <v>6560503</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13977,12 +13977,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14013,10 +14013,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737682</v>
+        <v>131737673</v>
       </c>
       <c r="B131" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14044,14 +14044,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615350</v>
+        <v>614957</v>
       </c>
       <c r="R131" t="n">
-        <v>6560611</v>
+        <v>6560564</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,10 +14114,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737663</v>
+        <v>131738996</v>
       </c>
       <c r="B132" t="n">
-        <v>93154</v>
+        <v>79880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14125,34 +14125,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615046</v>
+        <v>615290</v>
       </c>
       <c r="R132" t="n">
-        <v>6560537</v>
+        <v>6560715</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,10 +14215,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737673</v>
+        <v>131737682</v>
       </c>
       <c r="B133" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614957</v>
+        <v>615350</v>
       </c>
       <c r="R133" t="n">
-        <v>6560564</v>
+        <v>6560611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,10 +14316,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737661</v>
+        <v>131737663</v>
       </c>
       <c r="B134" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615060</v>
+        <v>615046</v>
       </c>
       <c r="R134" t="n">
-        <v>6560565</v>
+        <v>6560537</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,45 +14417,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131735760</v>
+        <v>131737661</v>
       </c>
       <c r="B135" t="n">
-        <v>90593</v>
+        <v>93155</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615279</v>
+        <v>615060</v>
       </c>
       <c r="R135" t="n">
-        <v>6560699</v>
+        <v>6560565</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,32 +14518,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131735760</v>
       </c>
       <c r="B136" t="n">
-        <v>79879</v>
+        <v>90594</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>615279</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560699</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737671</v>
+        <v>131737654</v>
       </c>
       <c r="B18" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614965</v>
+        <v>615282</v>
       </c>
       <c r="R18" t="n">
-        <v>6560580</v>
+        <v>6560780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737631</v>
+        <v>131739009</v>
       </c>
       <c r="B19" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614937</v>
+        <v>614998</v>
       </c>
       <c r="R19" t="n">
-        <v>6560625</v>
+        <v>6560540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737632</v>
+        <v>131739006</v>
       </c>
       <c r="B20" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614949</v>
+        <v>614970</v>
       </c>
       <c r="R20" t="n">
-        <v>6560635</v>
+        <v>6560568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737637</v>
+        <v>131738992</v>
       </c>
       <c r="B21" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,34 +2826,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614949</v>
+        <v>614903</v>
       </c>
       <c r="R21" t="n">
-        <v>6560610</v>
+        <v>6560580</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737654</v>
+        <v>131737671</v>
       </c>
       <c r="B22" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615282</v>
+        <v>614965</v>
       </c>
       <c r="R22" t="n">
-        <v>6560780</v>
+        <v>6560580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737614</v>
+        <v>131737631</v>
       </c>
       <c r="B23" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,14 +3048,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614857</v>
+        <v>614937</v>
       </c>
       <c r="R23" t="n">
-        <v>6560612</v>
+        <v>6560625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131739009</v>
+        <v>131737632</v>
       </c>
       <c r="B24" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614998</v>
+        <v>614949</v>
       </c>
       <c r="R24" t="n">
-        <v>6560540</v>
+        <v>6560635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
         <v>131737647</v>
       </c>
       <c r="B25" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737650</v>
+        <v>131737637</v>
       </c>
       <c r="B26" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3351,14 +3351,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615325</v>
+        <v>614949</v>
       </c>
       <c r="R26" t="n">
-        <v>6560719</v>
+        <v>6560610</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131739006</v>
+        <v>131737650</v>
       </c>
       <c r="B27" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,34 +3432,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614970</v>
+        <v>615325</v>
       </c>
       <c r="R27" t="n">
-        <v>6560568</v>
+        <v>6560719</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738992</v>
+        <v>131737614</v>
       </c>
       <c r="B28" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,21 +3533,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614903</v>
+        <v>614857</v>
       </c>
       <c r="R28" t="n">
-        <v>6560580</v>
+        <v>6560612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737787</v>
+        <v>131737785</v>
       </c>
       <c r="B29" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R29" t="n">
-        <v>6560522</v>
+        <v>6560513</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737785</v>
+        <v>131737784</v>
       </c>
       <c r="B30" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615314</v>
+        <v>615291</v>
       </c>
       <c r="R30" t="n">
-        <v>6560513</v>
+        <v>6560497</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737784</v>
+        <v>131737787</v>
       </c>
       <c r="B31" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615291</v>
+        <v>615336</v>
       </c>
       <c r="R31" t="n">
-        <v>6560497</v>
+        <v>6560522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,10 +3953,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737629</v>
+        <v>131737651</v>
       </c>
       <c r="B32" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,14 +3984,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614941</v>
+        <v>615311</v>
       </c>
       <c r="R32" t="n">
-        <v>6560607</v>
+        <v>6560742</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737651</v>
+        <v>131737629</v>
       </c>
       <c r="B33" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4085,14 +4085,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615311</v>
+        <v>614941</v>
       </c>
       <c r="R33" t="n">
-        <v>6560742</v>
+        <v>6560607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,7 +4158,7 @@
         <v>131738991</v>
       </c>
       <c r="B34" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>131739043</v>
       </c>
       <c r="B35" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>131739007</v>
       </c>
       <c r="B36" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>131737786</v>
       </c>
       <c r="B37" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737669</v>
+        <v>131737685</v>
       </c>
       <c r="B38" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4599,14 +4599,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614973</v>
+        <v>615324</v>
       </c>
       <c r="R38" t="n">
-        <v>6560600</v>
+        <v>6560604</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737685</v>
+        <v>131737672</v>
       </c>
       <c r="B39" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4700,14 +4700,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615324</v>
+        <v>614950</v>
       </c>
       <c r="R39" t="n">
-        <v>6560604</v>
+        <v>6560576</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737672</v>
+        <v>131737662</v>
       </c>
       <c r="B40" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614950</v>
+        <v>615040</v>
       </c>
       <c r="R40" t="n">
-        <v>6560576</v>
+        <v>6560530</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4874,7 +4874,7 @@
         <v>131737620</v>
       </c>
       <c r="B41" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737660</v>
+        <v>131737634</v>
       </c>
       <c r="B42" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,14 +5003,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>615278</v>
+        <v>614954</v>
       </c>
       <c r="R42" t="n">
-        <v>6560662</v>
+        <v>6560617</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737640</v>
+        <v>131737669</v>
       </c>
       <c r="B43" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,14 +5104,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614934</v>
+        <v>614973</v>
       </c>
       <c r="R43" t="n">
-        <v>6560578</v>
+        <v>6560600</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737662</v>
+        <v>131737660</v>
       </c>
       <c r="B44" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615040</v>
+        <v>615278</v>
       </c>
       <c r="R44" t="n">
-        <v>6560530</v>
+        <v>6560662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737634</v>
+        <v>131737640</v>
       </c>
       <c r="B45" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614954</v>
+        <v>614934</v>
       </c>
       <c r="R45" t="n">
-        <v>6560617</v>
+        <v>6560578</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737635</v>
+        <v>131739002</v>
       </c>
       <c r="B46" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614963</v>
+        <v>614953</v>
       </c>
       <c r="R46" t="n">
-        <v>6560615</v>
+        <v>6560567</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737618</v>
+        <v>131737635</v>
       </c>
       <c r="B47" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614881</v>
+        <v>614963</v>
       </c>
       <c r="R47" t="n">
-        <v>6560601</v>
+        <v>6560615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131739002</v>
+        <v>131737618</v>
       </c>
       <c r="B48" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614953</v>
+        <v>614881</v>
       </c>
       <c r="R48" t="n">
-        <v>6560567</v>
+        <v>6560601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5682,7 +5682,7 @@
         <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5780,45 +5780,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737925</v>
       </c>
       <c r="B50" t="n">
-        <v>93155</v>
+        <v>8454</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615343</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560656</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,45 +5881,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737925</v>
+        <v>131737616</v>
       </c>
       <c r="B51" t="n">
-        <v>8454</v>
+        <v>93158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615343</v>
+        <v>614862</v>
       </c>
       <c r="R51" t="n">
-        <v>6560656</v>
+        <v>6560592</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
         <v>131737677</v>
       </c>
       <c r="B52" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737684</v>
       </c>
       <c r="B53" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131737617</v>
       </c>
       <c r="B54" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>131737675</v>
       </c>
       <c r="B55" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737688</v>
+        <v>131739005</v>
       </c>
       <c r="B60" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615310</v>
+        <v>614968</v>
       </c>
       <c r="R60" t="n">
-        <v>6560543</v>
+        <v>6560572</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739008</v>
+        <v>131738993</v>
       </c>
       <c r="B61" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6922,14 +6922,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614995</v>
+        <v>614904</v>
       </c>
       <c r="R61" t="n">
-        <v>6560547</v>
+        <v>6560578</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739005</v>
+        <v>131737652</v>
       </c>
       <c r="B62" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614968</v>
+        <v>615301</v>
       </c>
       <c r="R62" t="n">
-        <v>6560572</v>
+        <v>6560755</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737652</v>
+        <v>131737688</v>
       </c>
       <c r="B63" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7124,14 +7124,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615301</v>
+        <v>615310</v>
       </c>
       <c r="R63" t="n">
-        <v>6560755</v>
+        <v>6560543</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131738993</v>
+        <v>131739008</v>
       </c>
       <c r="B64" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7225,14 +7225,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614904</v>
+        <v>614995</v>
       </c>
       <c r="R64" t="n">
-        <v>6560578</v>
+        <v>6560547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737686</v>
+        <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93155</v>
+        <v>93136</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7306,21 +7306,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615314</v>
+        <v>615336</v>
       </c>
       <c r="R65" t="n">
-        <v>6560599</v>
+        <v>6560577</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,10 +7396,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131736575</v>
+        <v>131737686</v>
       </c>
       <c r="B66" t="n">
-        <v>93133</v>
+        <v>93158</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R66" t="n">
-        <v>6560577</v>
+        <v>6560599</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7500,7 +7500,7 @@
         <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737667</v>
+        <v>131739010</v>
       </c>
       <c r="B68" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,21 +7609,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614991</v>
+        <v>615012</v>
       </c>
       <c r="R68" t="n">
-        <v>6560587</v>
+        <v>6560549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131740360</v>
+        <v>131739015</v>
       </c>
       <c r="B69" t="n">
-        <v>93146</v>
+        <v>79883</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615296</v>
+        <v>615373</v>
       </c>
       <c r="R69" t="n">
-        <v>6560688</v>
+        <v>6560555</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,18 +7772,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7806,10 +7800,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737658</v>
+        <v>131737667</v>
       </c>
       <c r="B70" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7837,14 +7831,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>615282</v>
+        <v>614991</v>
       </c>
       <c r="R70" t="n">
-        <v>6560684</v>
+        <v>6560587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,10 +7901,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737638</v>
+        <v>131740360</v>
       </c>
       <c r="B71" t="n">
-        <v>93155</v>
+        <v>93149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7918,34 +7912,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614943</v>
+        <v>615296</v>
       </c>
       <c r="R71" t="n">
-        <v>6560591</v>
+        <v>6560688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7980,12 +7974,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739010</v>
+        <v>131737638</v>
       </c>
       <c r="B72" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>615012</v>
+        <v>614943</v>
       </c>
       <c r="R72" t="n">
-        <v>6560549</v>
+        <v>6560591</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131739015</v>
+        <v>131737658</v>
       </c>
       <c r="B73" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615373</v>
+        <v>615282</v>
       </c>
       <c r="R73" t="n">
-        <v>6560555</v>
+        <v>6560684</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739041</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,21 +8221,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615269</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560500</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739011</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615080</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560512</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737644</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615331</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560676</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737668</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614990</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560601</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737924</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
-        <v>8454</v>
+        <v>79883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615091</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560504</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737639</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614942</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560579</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8816,45 +8816,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131738989</v>
+        <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>79880</v>
+        <v>8454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614945</v>
+        <v>615091</v>
       </c>
       <c r="R80" t="n">
-        <v>6560637</v>
+        <v>6560504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737674</v>
+        <v>131737782</v>
       </c>
       <c r="B81" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8945,17 +8945,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614965</v>
+        <v>615216</v>
       </c>
       <c r="R81" t="n">
-        <v>6560563</v>
+        <v>6560514</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8982,12 +8986,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9018,10 +9027,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737782</v>
+        <v>131737674</v>
       </c>
       <c r="B82" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9046,21 +9055,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>615216</v>
+        <v>614965</v>
       </c>
       <c r="R82" t="n">
-        <v>6560514</v>
+        <v>6560563</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9087,17 +9092,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9131,7 +9131,7 @@
         <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9229,10 +9229,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737624</v>
+        <v>131737653</v>
       </c>
       <c r="B84" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9260,14 +9260,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614910</v>
+        <v>615289</v>
       </c>
       <c r="R84" t="n">
-        <v>6560612</v>
+        <v>6560767</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737653</v>
+        <v>131737624</v>
       </c>
       <c r="B85" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9361,14 +9361,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>615289</v>
+        <v>614910</v>
       </c>
       <c r="R85" t="n">
-        <v>6560767</v>
+        <v>6560612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131738988</v>
+        <v>131737626</v>
       </c>
       <c r="B86" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614862</v>
+        <v>614911</v>
       </c>
       <c r="R86" t="n">
-        <v>6560592</v>
+        <v>6560610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737626</v>
+        <v>131737642</v>
       </c>
       <c r="B87" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614911</v>
+        <v>614884</v>
       </c>
       <c r="R87" t="n">
-        <v>6560610</v>
+        <v>6560568</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737642</v>
+        <v>131737687</v>
       </c>
       <c r="B88" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614884</v>
+        <v>615322</v>
       </c>
       <c r="R88" t="n">
-        <v>6560568</v>
+        <v>6560582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737687</v>
+        <v>131738988</v>
       </c>
       <c r="B89" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9745,34 +9745,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>615322</v>
+        <v>614862</v>
       </c>
       <c r="R89" t="n">
-        <v>6560582</v>
+        <v>6560592</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9838,7 +9838,7 @@
         <v>131737783</v>
       </c>
       <c r="B90" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737656</v>
+        <v>131737649</v>
       </c>
       <c r="B91" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9976,14 +9976,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615271</v>
+        <v>615316</v>
       </c>
       <c r="R91" t="n">
-        <v>6560749</v>
+        <v>6560709</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10049,7 +10049,7 @@
         <v>131737641</v>
       </c>
       <c r="B92" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737666</v>
+        <v>131737656</v>
       </c>
       <c r="B93" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614995</v>
+        <v>615271</v>
       </c>
       <c r="R93" t="n">
-        <v>6560571</v>
+        <v>6560749</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737676</v>
+        <v>131737666</v>
       </c>
       <c r="B94" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10279,14 +10279,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615060</v>
+        <v>614995</v>
       </c>
       <c r="R94" t="n">
-        <v>6560536</v>
+        <v>6560571</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10349,10 +10349,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737646</v>
+        <v>131737676</v>
       </c>
       <c r="B95" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615289</v>
+        <v>615060</v>
       </c>
       <c r="R95" t="n">
-        <v>6560695</v>
+        <v>6560536</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737690</v>
+        <v>131737646</v>
       </c>
       <c r="B96" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615387</v>
+        <v>615289</v>
       </c>
       <c r="R96" t="n">
-        <v>6560558</v>
+        <v>6560695</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,10 +10551,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737659</v>
+        <v>131737690</v>
       </c>
       <c r="B97" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615267</v>
+        <v>615387</v>
       </c>
       <c r="R97" t="n">
-        <v>6560667</v>
+        <v>6560558</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737649</v>
+        <v>131737659</v>
       </c>
       <c r="B98" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615316</v>
+        <v>615267</v>
       </c>
       <c r="R98" t="n">
-        <v>6560709</v>
+        <v>6560667</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10756,7 +10756,7 @@
         <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>131737625</v>
       </c>
       <c r="B100" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>131737645</v>
       </c>
       <c r="B101" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739013</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615376</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560556</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131739001</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11168,21 +11168,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614955</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560579</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737619</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614885</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560613</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737655</v>
+        <v>131737619</v>
       </c>
       <c r="B105" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615267</v>
+        <v>614885</v>
       </c>
       <c r="R105" t="n">
-        <v>6560777</v>
+        <v>6560613</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737636</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614960</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560601</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737664</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614942</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560568</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739004</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614958</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560561</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,41 +11864,53 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740361</v>
+        <v>131740030</v>
       </c>
       <c r="B110" t="n">
-        <v>93146</v>
+        <v>57090</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615309</v>
+        <v>614953</v>
       </c>
       <c r="R110" t="n">
-        <v>6560557</v>
+        <v>6560578</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11933,13 +11945,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11962,10 +11978,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737627</v>
+        <v>131736566</v>
       </c>
       <c r="B111" t="n">
-        <v>93155</v>
+        <v>93136</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,34 +11989,38 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614921</v>
+        <v>615319</v>
       </c>
       <c r="R111" t="n">
-        <v>6560604</v>
+        <v>6560579</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12033,6 +12053,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12063,10 +12088,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737630</v>
+        <v>131740361</v>
       </c>
       <c r="B112" t="n">
-        <v>93155</v>
+        <v>93149</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12074,34 +12099,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614948</v>
+        <v>615309</v>
       </c>
       <c r="R112" t="n">
-        <v>6560611</v>
+        <v>6560557</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12142,6 +12163,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12164,10 +12186,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131738990</v>
+        <v>131737627</v>
       </c>
       <c r="B113" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12175,21 +12197,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12199,10 +12221,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614930</v>
+        <v>614921</v>
       </c>
       <c r="R113" t="n">
-        <v>6560587</v>
+        <v>6560604</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12265,10 +12287,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131736566</v>
+        <v>131737648</v>
       </c>
       <c r="B114" t="n">
-        <v>93133</v>
+        <v>93158</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12276,38 +12298,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615319</v>
+        <v>615306</v>
       </c>
       <c r="R114" t="n">
-        <v>6560579</v>
+        <v>6560663</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12340,11 +12358,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12375,53 +12388,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131740030</v>
+        <v>131737630</v>
       </c>
       <c r="B115" t="n">
-        <v>57087</v>
+        <v>93158</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614953</v>
+        <v>614948</v>
       </c>
       <c r="R115" t="n">
-        <v>6560578</v>
+        <v>6560611</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12454,11 +12459,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12489,10 +12489,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737648</v>
+        <v>131738995</v>
       </c>
       <c r="B116" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12500,21 +12500,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12524,10 +12524,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615306</v>
+        <v>615323</v>
       </c>
       <c r="R116" t="n">
-        <v>6560663</v>
+        <v>6560647</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,10 +12590,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738995</v>
+        <v>131738990</v>
       </c>
       <c r="B117" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12621,14 +12621,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>615323</v>
+        <v>614930</v>
       </c>
       <c r="R117" t="n">
-        <v>6560647</v>
+        <v>6560587</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12694,7 +12694,7 @@
         <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131739003</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614959</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560556</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737670</v>
+        <v>131739003</v>
       </c>
       <c r="B121" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614972</v>
+        <v>614959</v>
       </c>
       <c r="R121" t="n">
-        <v>6560590</v>
+        <v>6560556</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13095,45 +13095,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131738994</v>
+        <v>131735761</v>
       </c>
       <c r="B122" t="n">
-        <v>79880</v>
+        <v>90597</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614890</v>
+        <v>615277</v>
       </c>
       <c r="R122" t="n">
-        <v>6560564</v>
+        <v>6560691</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13166,6 +13170,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13196,10 +13205,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131739000</v>
+        <v>131738994</v>
       </c>
       <c r="B123" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13231,10 +13240,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614941</v>
+        <v>614890</v>
       </c>
       <c r="R123" t="n">
-        <v>6560553</v>
+        <v>6560564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13297,49 +13306,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131735761</v>
+        <v>131739000</v>
       </c>
       <c r="B124" t="n">
-        <v>90594</v>
+        <v>79883</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>615277</v>
+        <v>614941</v>
       </c>
       <c r="R124" t="n">
-        <v>6560691</v>
+        <v>6560553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13372,11 +13377,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13410,7 +13410,7 @@
         <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13609,10 +13609,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737678</v>
+        <v>131739026</v>
       </c>
       <c r="B127" t="n">
-        <v>93155</v>
+        <v>79883</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13620,21 +13620,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615054</v>
+        <v>615203</v>
       </c>
       <c r="R127" t="n">
-        <v>6560523</v>
+        <v>6560503</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13710,10 +13710,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737681</v>
+        <v>131737678</v>
       </c>
       <c r="B128" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13741,14 +13741,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615383</v>
+        <v>615054</v>
       </c>
       <c r="R128" t="n">
-        <v>6560632</v>
+        <v>6560523</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131738997</v>
+        <v>131737681</v>
       </c>
       <c r="B129" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13822,34 +13822,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615026</v>
+        <v>615383</v>
       </c>
       <c r="R129" t="n">
-        <v>6560531</v>
+        <v>6560632</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13912,10 +13912,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131739026</v>
+        <v>131738997</v>
       </c>
       <c r="B130" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13943,14 +13943,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615203</v>
+        <v>615026</v>
       </c>
       <c r="R130" t="n">
-        <v>6560503</v>
+        <v>6560531</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13977,12 +13977,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14013,10 +14013,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737673</v>
+        <v>131737682</v>
       </c>
       <c r="B131" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14044,14 +14044,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>614957</v>
+        <v>615350</v>
       </c>
       <c r="R131" t="n">
-        <v>6560564</v>
+        <v>6560611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,10 +14114,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131738996</v>
+        <v>131737663</v>
       </c>
       <c r="B132" t="n">
-        <v>79880</v>
+        <v>93158</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14125,34 +14125,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615290</v>
+        <v>615046</v>
       </c>
       <c r="R132" t="n">
-        <v>6560715</v>
+        <v>6560537</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,10 +14215,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737682</v>
+        <v>131737673</v>
       </c>
       <c r="B133" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615350</v>
+        <v>614957</v>
       </c>
       <c r="R133" t="n">
-        <v>6560611</v>
+        <v>6560564</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,10 +14316,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737663</v>
+        <v>131737661</v>
       </c>
       <c r="B134" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615046</v>
+        <v>615060</v>
       </c>
       <c r="R134" t="n">
-        <v>6560537</v>
+        <v>6560565</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,45 +14417,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737661</v>
+        <v>131735760</v>
       </c>
       <c r="B135" t="n">
-        <v>93155</v>
+        <v>90597</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615060</v>
+        <v>615279</v>
       </c>
       <c r="R135" t="n">
-        <v>6560565</v>
+        <v>6560699</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,32 +14518,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>90594</v>
+        <v>79883</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R136" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737654</v>
+        <v>131739009</v>
       </c>
       <c r="B18" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615282</v>
+        <v>614998</v>
       </c>
       <c r="R18" t="n">
-        <v>6560780</v>
+        <v>6560540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131739009</v>
+        <v>131737654</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614998</v>
+        <v>615282</v>
       </c>
       <c r="R19" t="n">
-        <v>6560540</v>
+        <v>6560780</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131739006</v>
+        <v>131737614</v>
       </c>
       <c r="B20" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,34 +2725,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614970</v>
+        <v>614857</v>
       </c>
       <c r="R20" t="n">
-        <v>6560568</v>
+        <v>6560612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131738992</v>
+        <v>131737671</v>
       </c>
       <c r="B21" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,31 +2826,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614903</v>
+        <v>614965</v>
       </c>
       <c r="R21" t="n">
         <v>6560580</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737671</v>
+        <v>131737631</v>
       </c>
       <c r="B22" t="n">
         <v>93158</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614965</v>
+        <v>614937</v>
       </c>
       <c r="R22" t="n">
-        <v>6560580</v>
+        <v>6560625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737631</v>
+        <v>131737632</v>
       </c>
       <c r="B23" t="n">
         <v>93158</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614937</v>
+        <v>614949</v>
       </c>
       <c r="R23" t="n">
-        <v>6560625</v>
+        <v>6560635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737632</v>
+        <v>131739006</v>
       </c>
       <c r="B24" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614949</v>
+        <v>614970</v>
       </c>
       <c r="R24" t="n">
-        <v>6560635</v>
+        <v>6560568</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131737614</v>
+        <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,21 +3533,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614857</v>
+        <v>614903</v>
       </c>
       <c r="R28" t="n">
-        <v>6560612</v>
+        <v>6560580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737785</v>
+        <v>131737787</v>
       </c>
       <c r="B29" t="n">
         <v>93158</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615314</v>
+        <v>615336</v>
       </c>
       <c r="R29" t="n">
-        <v>6560513</v>
+        <v>6560522</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,7 +3733,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737784</v>
+        <v>131737651</v>
       </c>
       <c r="B30" t="n">
         <v>93158</v>
@@ -3761,21 +3761,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615291</v>
+        <v>615311</v>
       </c>
       <c r="R30" t="n">
-        <v>6560497</v>
+        <v>6560742</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,17 +3798,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,7 +3834,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737787</v>
+        <v>131737785</v>
       </c>
       <c r="B31" t="n">
         <v>93158</v>
@@ -3873,7 +3864,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3882,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R31" t="n">
-        <v>6560522</v>
+        <v>6560513</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3913,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,7 +3944,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737651</v>
+        <v>131737784</v>
       </c>
       <c r="B32" t="n">
         <v>93158</v>
@@ -3981,17 +3972,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615311</v>
+        <v>615291</v>
       </c>
       <c r="R32" t="n">
-        <v>6560742</v>
+        <v>6560497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4018,12 +4013,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4568,7 +4568,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737685</v>
+        <v>131737662</v>
       </c>
       <c r="B38" t="n">
         <v>93158</v>
@@ -4599,14 +4599,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615324</v>
+        <v>615040</v>
       </c>
       <c r="R38" t="n">
-        <v>6560604</v>
+        <v>6560530</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737672</v>
+        <v>131737620</v>
       </c>
       <c r="B39" t="n">
         <v>93158</v>
@@ -4700,14 +4700,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614950</v>
+        <v>614896</v>
       </c>
       <c r="R39" t="n">
-        <v>6560576</v>
+        <v>6560613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737662</v>
+        <v>131737634</v>
       </c>
       <c r="B40" t="n">
         <v>93158</v>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615040</v>
+        <v>614954</v>
       </c>
       <c r="R40" t="n">
-        <v>6560530</v>
+        <v>6560617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737620</v>
+        <v>131737640</v>
       </c>
       <c r="B41" t="n">
         <v>93158</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614896</v>
+        <v>614934</v>
       </c>
       <c r="R41" t="n">
-        <v>6560613</v>
+        <v>6560578</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737634</v>
+        <v>131737685</v>
       </c>
       <c r="B42" t="n">
         <v>93158</v>
@@ -5003,14 +5003,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614954</v>
+        <v>615324</v>
       </c>
       <c r="R42" t="n">
-        <v>6560617</v>
+        <v>6560604</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737669</v>
+        <v>131737672</v>
       </c>
       <c r="B43" t="n">
         <v>93158</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614973</v>
+        <v>614950</v>
       </c>
       <c r="R43" t="n">
-        <v>6560600</v>
+        <v>6560576</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737660</v>
+        <v>131737669</v>
       </c>
       <c r="B44" t="n">
         <v>93158</v>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615278</v>
+        <v>614973</v>
       </c>
       <c r="R44" t="n">
-        <v>6560662</v>
+        <v>6560600</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737640</v>
+        <v>131737660</v>
       </c>
       <c r="B45" t="n">
         <v>93158</v>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614934</v>
+        <v>615278</v>
       </c>
       <c r="R45" t="n">
-        <v>6560578</v>
+        <v>6560662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739002</v>
+        <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614953</v>
+        <v>614963</v>
       </c>
       <c r="R46" t="n">
-        <v>6560567</v>
+        <v>6560615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B47" t="n">
         <v>93158</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R47" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131737618</v>
+        <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614881</v>
+        <v>614953</v>
       </c>
       <c r="R48" t="n">
-        <v>6560601</v>
+        <v>6560567</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131739012</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615022</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560527</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,32 +5780,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737925</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
-        <v>8454</v>
+        <v>93158</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615343</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560656</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737616</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
         <v>93158</v>
@@ -5912,14 +5912,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614862</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560592</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,32 +5982,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737677</v>
+        <v>131737925</v>
       </c>
       <c r="B52" t="n">
-        <v>93158</v>
+        <v>8454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615064</v>
+        <v>615343</v>
       </c>
       <c r="R52" t="n">
-        <v>6560525</v>
+        <v>6560656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B53" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6094,34 +6094,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R53" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737617</v>
+        <v>131737675</v>
       </c>
       <c r="B54" t="n">
         <v>93158</v>
@@ -6215,14 +6215,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614867</v>
+        <v>614961</v>
       </c>
       <c r="R54" t="n">
-        <v>6560588</v>
+        <v>6560552</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737675</v>
+        <v>131737617</v>
       </c>
       <c r="B55" t="n">
         <v>93158</v>
@@ -6316,14 +6316,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614961</v>
+        <v>614867</v>
       </c>
       <c r="R55" t="n">
-        <v>6560552</v>
+        <v>6560588</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739005</v>
+        <v>131737652</v>
       </c>
       <c r="B60" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614968</v>
+        <v>615301</v>
       </c>
       <c r="R60" t="n">
-        <v>6560572</v>
+        <v>6560755</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737652</v>
+        <v>131739008</v>
       </c>
       <c r="B62" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615301</v>
+        <v>614995</v>
       </c>
       <c r="R62" t="n">
-        <v>6560755</v>
+        <v>6560547</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739008</v>
+        <v>131739005</v>
       </c>
       <c r="B64" t="n">
         <v>79883</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614995</v>
+        <v>614968</v>
       </c>
       <c r="R64" t="n">
-        <v>6560547</v>
+        <v>6560572</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131739010</v>
+        <v>131737667</v>
       </c>
       <c r="B68" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,21 +7609,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615012</v>
+        <v>614991</v>
       </c>
       <c r="R68" t="n">
-        <v>6560549</v>
+        <v>6560587</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131739015</v>
+        <v>131740360</v>
       </c>
       <c r="B69" t="n">
-        <v>79883</v>
+        <v>93149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615373</v>
+        <v>615296</v>
       </c>
       <c r="R69" t="n">
-        <v>6560555</v>
+        <v>6560688</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,12 +7772,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7800,7 +7806,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737667</v>
+        <v>131737638</v>
       </c>
       <c r="B70" t="n">
         <v>93158</v>
@@ -7835,10 +7841,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614991</v>
+        <v>614943</v>
       </c>
       <c r="R70" t="n">
-        <v>6560587</v>
+        <v>6560591</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7901,10 +7907,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740360</v>
+        <v>131737658</v>
       </c>
       <c r="B71" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7912,34 +7918,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615296</v>
+        <v>615282</v>
       </c>
       <c r="R71" t="n">
-        <v>6560688</v>
+        <v>6560684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7974,18 +7980,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737638</v>
+        <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614943</v>
+        <v>615012</v>
       </c>
       <c r="R72" t="n">
-        <v>6560591</v>
+        <v>6560549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737658</v>
+        <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615282</v>
+        <v>615373</v>
       </c>
       <c r="R73" t="n">
-        <v>6560684</v>
+        <v>6560555</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131738989</v>
       </c>
       <c r="B74" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>614945</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560637</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131739041</v>
       </c>
       <c r="B76" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>615269</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560500</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8513,7 +8513,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738989</v>
+        <v>131739011</v>
       </c>
       <c r="B77" t="n">
         <v>79883</v>
@@ -8544,14 +8544,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614945</v>
+        <v>615080</v>
       </c>
       <c r="R77" t="n">
-        <v>6560637</v>
+        <v>6560512</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739041</v>
+        <v>131737924</v>
       </c>
       <c r="B78" t="n">
-        <v>79883</v>
+        <v>8454</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615269</v>
+        <v>615091</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560504</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739011</v>
+        <v>131737644</v>
       </c>
       <c r="B79" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615080</v>
+        <v>615331</v>
       </c>
       <c r="R79" t="n">
-        <v>6560512</v>
+        <v>6560676</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8816,45 +8816,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737924</v>
+        <v>131737668</v>
       </c>
       <c r="B80" t="n">
-        <v>8454</v>
+        <v>93158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615091</v>
+        <v>614990</v>
       </c>
       <c r="R80" t="n">
-        <v>6560504</v>
+        <v>6560601</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737782</v>
+        <v>131737674</v>
       </c>
       <c r="B81" t="n">
         <v>93158</v>
@@ -8945,21 +8945,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>615216</v>
+        <v>614965</v>
       </c>
       <c r="R81" t="n">
-        <v>6560514</v>
+        <v>6560563</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8986,17 +8982,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9027,7 +9018,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737674</v>
+        <v>131737782</v>
       </c>
       <c r="B82" t="n">
         <v>93158</v>
@@ -9055,17 +9046,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614965</v>
+        <v>615216</v>
       </c>
       <c r="R82" t="n">
-        <v>6560563</v>
+        <v>6560514</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9092,12 +9087,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737783</v>
+        <v>131738998</v>
       </c>
       <c r="B90" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,38 +9846,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615276</v>
+        <v>615020</v>
       </c>
       <c r="R90" t="n">
-        <v>6560495</v>
+        <v>6560533</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9904,17 +9900,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9945,7 +9936,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737649</v>
+        <v>131737783</v>
       </c>
       <c r="B91" t="n">
         <v>93158</v>
@@ -9973,17 +9964,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615316</v>
+        <v>615276</v>
       </c>
       <c r="R91" t="n">
-        <v>6560709</v>
+        <v>6560495</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10010,12 +10005,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131738998</v>
+        <v>131737649</v>
       </c>
       <c r="B99" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615020</v>
+        <v>615316</v>
       </c>
       <c r="R99" t="n">
-        <v>6560533</v>
+        <v>6560709</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737625</v>
+        <v>131739013</v>
       </c>
       <c r="B100" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614918</v>
+        <v>615376</v>
       </c>
       <c r="R100" t="n">
-        <v>6560620</v>
+        <v>6560556</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737645</v>
+        <v>131739004</v>
       </c>
       <c r="B101" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615304</v>
+        <v>614958</v>
       </c>
       <c r="R101" t="n">
-        <v>6560686</v>
+        <v>6560561</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737655</v>
+        <v>131739001</v>
       </c>
       <c r="B102" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615267</v>
+        <v>614955</v>
       </c>
       <c r="R102" t="n">
-        <v>6560777</v>
+        <v>6560579</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737636</v>
+        <v>131737625</v>
       </c>
       <c r="B103" t="n">
         <v>93158</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614960</v>
+        <v>614918</v>
       </c>
       <c r="R103" t="n">
-        <v>6560601</v>
+        <v>6560620</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737691</v>
+        <v>131737645</v>
       </c>
       <c r="B104" t="n">
         <v>93158</v>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615367</v>
+        <v>615304</v>
       </c>
       <c r="R104" t="n">
-        <v>6560553</v>
+        <v>6560686</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737619</v>
+        <v>131737655</v>
       </c>
       <c r="B105" t="n">
         <v>93158</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614885</v>
+        <v>615267</v>
       </c>
       <c r="R105" t="n">
-        <v>6560613</v>
+        <v>6560777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131737636</v>
       </c>
       <c r="B106" t="n">
         <v>93158</v>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>614960</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560601</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739013</v>
+        <v>131737691</v>
       </c>
       <c r="B107" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615376</v>
+        <v>615367</v>
       </c>
       <c r="R107" t="n">
-        <v>6560556</v>
+        <v>6560553</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739004</v>
+        <v>131737619</v>
       </c>
       <c r="B108" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614958</v>
+        <v>614885</v>
       </c>
       <c r="R108" t="n">
-        <v>6560561</v>
+        <v>6560613</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131737664</v>
       </c>
       <c r="B109" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>614942</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560568</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,53 +11864,41 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740030</v>
+        <v>131740361</v>
       </c>
       <c r="B110" t="n">
-        <v>57090</v>
+        <v>93149</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614953</v>
+        <v>615309</v>
       </c>
       <c r="R110" t="n">
-        <v>6560578</v>
+        <v>6560557</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11945,17 +11933,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11978,10 +11962,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131736566</v>
+        <v>131737627</v>
       </c>
       <c r="B111" t="n">
-        <v>93136</v>
+        <v>93158</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11989,38 +11973,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615319</v>
+        <v>614921</v>
       </c>
       <c r="R111" t="n">
-        <v>6560579</v>
+        <v>6560604</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,11 +12033,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12088,10 +12063,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131740361</v>
+        <v>131737648</v>
       </c>
       <c r="B112" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12099,19 +12074,23 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12119,10 +12098,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615309</v>
+        <v>615306</v>
       </c>
       <c r="R112" t="n">
-        <v>6560557</v>
+        <v>6560663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12163,7 +12142,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12186,7 +12164,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737627</v>
+        <v>131737630</v>
       </c>
       <c r="B113" t="n">
         <v>93158</v>
@@ -12217,14 +12195,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614921</v>
+        <v>614948</v>
       </c>
       <c r="R113" t="n">
-        <v>6560604</v>
+        <v>6560611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12287,10 +12265,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737648</v>
+        <v>131736566</v>
       </c>
       <c r="B114" t="n">
-        <v>93158</v>
+        <v>93136</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12298,34 +12276,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615306</v>
+        <v>615319</v>
       </c>
       <c r="R114" t="n">
-        <v>6560663</v>
+        <v>6560579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12358,6 +12340,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12388,10 +12375,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737630</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12399,34 +12386,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614948</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560611</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12489,7 +12476,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738995</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
         <v>79883</v>
@@ -12520,14 +12507,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615323</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560647</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,45 +12577,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738990</v>
+        <v>131740030</v>
       </c>
       <c r="B117" t="n">
-        <v>79883</v>
+        <v>57090</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614930</v>
+        <v>614953</v>
       </c>
       <c r="R117" t="n">
-        <v>6560587</v>
+        <v>6560578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131740081</v>
+        <v>131737665</v>
       </c>
       <c r="B118" t="n">
-        <v>91853</v>
+        <v>93158</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614974</v>
+        <v>614993</v>
       </c>
       <c r="R118" t="n">
-        <v>6560628</v>
+        <v>6560559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,7 +12792,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B119" t="n">
         <v>93158</v>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131740081</v>
       </c>
       <c r="B120" t="n">
-        <v>93158</v>
+        <v>91853</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614974</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560628</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12958,12 +12958,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13407,7 +13407,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737622</v>
+        <v>131737683</v>
       </c>
       <c r="B125" t="n">
         <v>93158</v>
@@ -13438,14 +13438,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614898</v>
+        <v>615337</v>
       </c>
       <c r="R125" t="n">
-        <v>6560601</v>
+        <v>6560617</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13508,7 +13508,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737683</v>
+        <v>131737678</v>
       </c>
       <c r="B126" t="n">
         <v>93158</v>
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615337</v>
+        <v>615054</v>
       </c>
       <c r="R126" t="n">
-        <v>6560617</v>
+        <v>6560523</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13609,10 +13609,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131739026</v>
+        <v>131737681</v>
       </c>
       <c r="B127" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13620,34 +13620,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615203</v>
+        <v>615383</v>
       </c>
       <c r="R127" t="n">
-        <v>6560503</v>
+        <v>6560632</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13710,10 +13710,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737678</v>
+        <v>131738997</v>
       </c>
       <c r="B128" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13721,34 +13721,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615054</v>
+        <v>615026</v>
       </c>
       <c r="R128" t="n">
-        <v>6560523</v>
+        <v>6560531</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,7 +13811,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737681</v>
+        <v>131737622</v>
       </c>
       <c r="B129" t="n">
         <v>93158</v>
@@ -13842,14 +13842,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615383</v>
+        <v>614898</v>
       </c>
       <c r="R129" t="n">
-        <v>6560632</v>
+        <v>6560601</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131738997</v>
+        <v>131739026</v>
       </c>
       <c r="B130" t="n">
         <v>79883</v>
@@ -13943,14 +13943,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615026</v>
+        <v>615203</v>
       </c>
       <c r="R130" t="n">
-        <v>6560531</v>
+        <v>6560503</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13977,12 +13977,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14013,7 +14013,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B131" t="n">
         <v>93158</v>
@@ -14044,14 +14044,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R131" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737663</v>
+        <v>131737673</v>
       </c>
       <c r="B132" t="n">
         <v>93158</v>
@@ -14149,10 +14149,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615046</v>
+        <v>614957</v>
       </c>
       <c r="R132" t="n">
-        <v>6560537</v>
+        <v>6560564</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737673</v>
+        <v>131737661</v>
       </c>
       <c r="B133" t="n">
         <v>93158</v>
@@ -14250,10 +14250,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614957</v>
+        <v>615060</v>
       </c>
       <c r="R133" t="n">
-        <v>6560564</v>
+        <v>6560565</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,45 +14316,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737661</v>
+        <v>131735760</v>
       </c>
       <c r="B134" t="n">
-        <v>93158</v>
+        <v>90597</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615060</v>
+        <v>615279</v>
       </c>
       <c r="R134" t="n">
-        <v>6560565</v>
+        <v>6560699</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,32 +14417,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B135" t="n">
-        <v>90597</v>
+        <v>79883</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R135" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131737682</v>
       </c>
       <c r="B136" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,21 +14529,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>615350</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560611</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131739009</v>
+        <v>131737631</v>
       </c>
       <c r="B18" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614998</v>
+        <v>614937</v>
       </c>
       <c r="R18" t="n">
-        <v>6560540</v>
+        <v>6560625</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737614</v>
+        <v>131737650</v>
       </c>
       <c r="B20" t="n">
         <v>93158</v>
@@ -2745,14 +2745,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614857</v>
+        <v>615325</v>
       </c>
       <c r="R20" t="n">
-        <v>6560612</v>
+        <v>6560719</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737671</v>
+        <v>131737637</v>
       </c>
       <c r="B21" t="n">
         <v>93158</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614965</v>
+        <v>614949</v>
       </c>
       <c r="R21" t="n">
-        <v>6560580</v>
+        <v>6560610</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737631</v>
+        <v>131737614</v>
       </c>
       <c r="B22" t="n">
         <v>93158</v>
@@ -2947,14 +2947,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614937</v>
+        <v>614857</v>
       </c>
       <c r="R22" t="n">
-        <v>6560625</v>
+        <v>6560612</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737632</v>
+        <v>131737647</v>
       </c>
       <c r="B23" t="n">
         <v>93158</v>
@@ -3048,14 +3048,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614949</v>
+        <v>615295</v>
       </c>
       <c r="R23" t="n">
-        <v>6560635</v>
+        <v>6560678</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131739006</v>
+        <v>131737671</v>
       </c>
       <c r="B24" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614970</v>
+        <v>614965</v>
       </c>
       <c r="R24" t="n">
-        <v>6560568</v>
+        <v>6560580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737647</v>
+        <v>131737632</v>
       </c>
       <c r="B25" t="n">
         <v>93158</v>
@@ -3250,14 +3250,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615295</v>
+        <v>614949</v>
       </c>
       <c r="R25" t="n">
-        <v>6560678</v>
+        <v>6560635</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737637</v>
+        <v>131739009</v>
       </c>
       <c r="B26" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,21 +3331,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614949</v>
+        <v>614998</v>
       </c>
       <c r="R26" t="n">
-        <v>6560610</v>
+        <v>6560540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737650</v>
+        <v>131739006</v>
       </c>
       <c r="B27" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,34 +3432,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>615325</v>
+        <v>614970</v>
       </c>
       <c r="R27" t="n">
-        <v>6560719</v>
+        <v>6560568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737787</v>
+        <v>131737651</v>
       </c>
       <c r="B29" t="n">
         <v>93158</v>
@@ -3651,21 +3651,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615336</v>
+        <v>615311</v>
       </c>
       <c r="R29" t="n">
-        <v>6560522</v>
+        <v>6560742</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3692,17 +3688,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,7 +3724,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737651</v>
+        <v>131737785</v>
       </c>
       <c r="B30" t="n">
         <v>93158</v>
@@ -3761,17 +3752,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615311</v>
+        <v>615314</v>
       </c>
       <c r="R30" t="n">
-        <v>6560742</v>
+        <v>6560513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,12 +3793,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,7 +3834,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737785</v>
+        <v>131737629</v>
       </c>
       <c r="B31" t="n">
         <v>93158</v>
@@ -3862,21 +3862,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615314</v>
+        <v>614941</v>
       </c>
       <c r="R31" t="n">
-        <v>6560513</v>
+        <v>6560607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,17 +3899,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737784</v>
+        <v>131737787</v>
       </c>
       <c r="B32" t="n">
         <v>93158</v>
@@ -3974,7 +3965,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3983,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615291</v>
+        <v>615336</v>
       </c>
       <c r="R32" t="n">
-        <v>6560497</v>
+        <v>6560522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4014,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,7 +4045,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737629</v>
+        <v>131737784</v>
       </c>
       <c r="B33" t="n">
         <v>93158</v>
@@ -4082,17 +4073,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614941</v>
+        <v>615291</v>
       </c>
       <c r="R33" t="n">
-        <v>6560607</v>
+        <v>6560497</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,12 +4114,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4458,7 +4458,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737786</v>
+        <v>131737669</v>
       </c>
       <c r="B37" t="n">
         <v>93158</v>
@@ -4486,21 +4486,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>615335</v>
+        <v>614973</v>
       </c>
       <c r="R37" t="n">
-        <v>6560536</v>
+        <v>6560600</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4527,17 +4523,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4568,7 +4559,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737662</v>
+        <v>131737660</v>
       </c>
       <c r="B38" t="n">
         <v>93158</v>
@@ -4599,14 +4590,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615040</v>
+        <v>615278</v>
       </c>
       <c r="R38" t="n">
-        <v>6560530</v>
+        <v>6560662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,7 +4660,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737620</v>
+        <v>131737685</v>
       </c>
       <c r="B39" t="n">
         <v>93158</v>
@@ -4700,14 +4691,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614896</v>
+        <v>615324</v>
       </c>
       <c r="R39" t="n">
-        <v>6560613</v>
+        <v>6560604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4972,7 +4963,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737685</v>
+        <v>131737786</v>
       </c>
       <c r="B42" t="n">
         <v>93158</v>
@@ -5000,17 +4991,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>615324</v>
+        <v>615335</v>
       </c>
       <c r="R42" t="n">
-        <v>6560604</v>
+        <v>6560536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5037,12 +5032,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5073,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737672</v>
+        <v>131737620</v>
       </c>
       <c r="B43" t="n">
         <v>93158</v>
@@ -5104,14 +5104,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614950</v>
+        <v>614896</v>
       </c>
       <c r="R43" t="n">
-        <v>6560576</v>
+        <v>6560613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737669</v>
+        <v>131737672</v>
       </c>
       <c r="B44" t="n">
         <v>93158</v>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614973</v>
+        <v>614950</v>
       </c>
       <c r="R44" t="n">
-        <v>6560600</v>
+        <v>6560576</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737660</v>
+        <v>131737662</v>
       </c>
       <c r="B45" t="n">
         <v>93158</v>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615278</v>
+        <v>615040</v>
       </c>
       <c r="R45" t="n">
-        <v>6560662</v>
+        <v>6560530</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5679,45 +5679,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131737925</v>
       </c>
       <c r="B49" t="n">
-        <v>93158</v>
+        <v>8454</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>615343</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737677</v>
+        <v>131737616</v>
       </c>
       <c r="B50" t="n">
         <v>93158</v>
@@ -5811,14 +5811,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615064</v>
+        <v>614862</v>
       </c>
       <c r="R50" t="n">
-        <v>6560525</v>
+        <v>6560592</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737684</v>
+        <v>131737677</v>
       </c>
       <c r="B51" t="n">
         <v>93158</v>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615333</v>
+        <v>615064</v>
       </c>
       <c r="R51" t="n">
-        <v>6560608</v>
+        <v>6560525</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,32 +5982,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737925</v>
+        <v>131737684</v>
       </c>
       <c r="B52" t="n">
-        <v>8454</v>
+        <v>93158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615343</v>
+        <v>615333</v>
       </c>
       <c r="R52" t="n">
-        <v>6560656</v>
+        <v>6560608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737675</v>
+        <v>131737617</v>
       </c>
       <c r="B54" t="n">
         <v>93158</v>
@@ -6215,14 +6215,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614961</v>
+        <v>614867</v>
       </c>
       <c r="R54" t="n">
-        <v>6560552</v>
+        <v>6560588</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737617</v>
+        <v>131737675</v>
       </c>
       <c r="B55" t="n">
         <v>93158</v>
@@ -6316,14 +6316,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614867</v>
+        <v>614961</v>
       </c>
       <c r="R55" t="n">
-        <v>6560588</v>
+        <v>6560552</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737633</v>
+        <v>131737615</v>
       </c>
       <c r="B57" t="n">
         <v>93158</v>
@@ -6518,14 +6518,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614946</v>
+        <v>614854</v>
       </c>
       <c r="R57" t="n">
-        <v>6560623</v>
+        <v>6560611</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737615</v>
+        <v>131737633</v>
       </c>
       <c r="B59" t="n">
         <v>93158</v>
@@ -6720,14 +6720,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614854</v>
+        <v>614946</v>
       </c>
       <c r="R59" t="n">
-        <v>6560611</v>
+        <v>6560623</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737652</v>
+        <v>131737688</v>
       </c>
       <c r="B60" t="n">
         <v>93158</v>
@@ -6821,14 +6821,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615301</v>
+        <v>615310</v>
       </c>
       <c r="R60" t="n">
-        <v>6560755</v>
+        <v>6560543</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B61" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,34 +6902,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R61" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739008</v>
+        <v>131738993</v>
       </c>
       <c r="B62" t="n">
         <v>79883</v>
@@ -7023,14 +7023,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614995</v>
+        <v>614904</v>
       </c>
       <c r="R62" t="n">
-        <v>6560547</v>
+        <v>6560578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737688</v>
+        <v>131739008</v>
       </c>
       <c r="B63" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,34 +7104,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615310</v>
+        <v>614995</v>
       </c>
       <c r="R63" t="n">
-        <v>6560543</v>
+        <v>6560547</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737667</v>
+        <v>131740360</v>
       </c>
       <c r="B68" t="n">
-        <v>93158</v>
+        <v>93149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,34 +7609,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614991</v>
+        <v>615296</v>
       </c>
       <c r="R68" t="n">
-        <v>6560587</v>
+        <v>6560688</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7671,12 +7671,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7699,10 +7705,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131740360</v>
+        <v>131737638</v>
       </c>
       <c r="B69" t="n">
-        <v>93149</v>
+        <v>93158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7716,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615296</v>
+        <v>614943</v>
       </c>
       <c r="R69" t="n">
-        <v>6560688</v>
+        <v>6560591</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,18 +7778,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7806,7 +7806,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737638</v>
+        <v>131737658</v>
       </c>
       <c r="B70" t="n">
         <v>93158</v>
@@ -7837,14 +7837,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614943</v>
+        <v>615282</v>
       </c>
       <c r="R70" t="n">
-        <v>6560591</v>
+        <v>6560684</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,7 +7907,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737658</v>
+        <v>131737667</v>
       </c>
       <c r="B71" t="n">
         <v>93158</v>
@@ -7938,14 +7938,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615282</v>
+        <v>614991</v>
       </c>
       <c r="R71" t="n">
-        <v>6560684</v>
+        <v>6560587</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131738989</v>
+        <v>131737668</v>
       </c>
       <c r="B74" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,21 +8221,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614945</v>
+        <v>614990</v>
       </c>
       <c r="R74" t="n">
-        <v>6560637</v>
+        <v>6560601</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131739041</v>
+        <v>131737644</v>
       </c>
       <c r="B76" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,21 +8423,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615269</v>
+        <v>615331</v>
       </c>
       <c r="R76" t="n">
-        <v>6560500</v>
+        <v>6560676</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8513,7 +8513,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131739011</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
         <v>79883</v>
@@ -8544,14 +8544,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615080</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560512</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737924</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
-        <v>8454</v>
+        <v>79883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615091</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560504</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737644</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615331</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560676</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8816,45 +8816,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737668</v>
+        <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>93158</v>
+        <v>8454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614990</v>
+        <v>615091</v>
       </c>
       <c r="R80" t="n">
-        <v>6560601</v>
+        <v>6560504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737674</v>
+        <v>131737653</v>
       </c>
       <c r="B81" t="n">
         <v>93158</v>
@@ -8952,10 +8952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614965</v>
+        <v>615289</v>
       </c>
       <c r="R81" t="n">
-        <v>6560563</v>
+        <v>6560767</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9018,7 +9018,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737782</v>
+        <v>131737680</v>
       </c>
       <c r="B82" t="n">
         <v>93158</v>
@@ -9046,21 +9046,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>615216</v>
+        <v>615390</v>
       </c>
       <c r="R82" t="n">
-        <v>6560514</v>
+        <v>6560614</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9087,17 +9083,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9128,7 +9119,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737680</v>
+        <v>131737674</v>
       </c>
       <c r="B83" t="n">
         <v>93158</v>
@@ -9159,14 +9150,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>615390</v>
+        <v>614965</v>
       </c>
       <c r="R83" t="n">
-        <v>6560614</v>
+        <v>6560563</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,7 +9220,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737653</v>
+        <v>131737624</v>
       </c>
       <c r="B84" t="n">
         <v>93158</v>
@@ -9260,14 +9251,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>615289</v>
+        <v>614910</v>
       </c>
       <c r="R84" t="n">
-        <v>6560767</v>
+        <v>6560612</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9330,7 +9321,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737624</v>
+        <v>131737782</v>
       </c>
       <c r="B85" t="n">
         <v>93158</v>
@@ -9358,17 +9349,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614910</v>
+        <v>615216</v>
       </c>
       <c r="R85" t="n">
-        <v>6560612</v>
+        <v>6560514</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9395,12 +9390,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9431,7 +9431,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737626</v>
+        <v>131737687</v>
       </c>
       <c r="B86" t="n">
         <v>93158</v>
@@ -9462,14 +9462,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614911</v>
+        <v>615322</v>
       </c>
       <c r="R86" t="n">
-        <v>6560610</v>
+        <v>6560582</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737642</v>
+        <v>131737626</v>
       </c>
       <c r="B87" t="n">
         <v>93158</v>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614884</v>
+        <v>614911</v>
       </c>
       <c r="R87" t="n">
-        <v>6560568</v>
+        <v>6560610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,7 +9633,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737687</v>
+        <v>131737642</v>
       </c>
       <c r="B88" t="n">
         <v>93158</v>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>615322</v>
+        <v>614884</v>
       </c>
       <c r="R88" t="n">
-        <v>6560582</v>
+        <v>6560568</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131738998</v>
+        <v>131737690</v>
       </c>
       <c r="B90" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,34 +9846,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615020</v>
+        <v>615387</v>
       </c>
       <c r="R90" t="n">
-        <v>6560533</v>
+        <v>6560558</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737783</v>
+        <v>131737676</v>
       </c>
       <c r="B91" t="n">
         <v>93158</v>
@@ -9964,21 +9964,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615276</v>
+        <v>615060</v>
       </c>
       <c r="R91" t="n">
-        <v>6560495</v>
+        <v>6560536</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10005,17 +10001,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10046,7 +10037,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737641</v>
+        <v>131737666</v>
       </c>
       <c r="B92" t="n">
         <v>93158</v>
@@ -10077,14 +10068,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614893</v>
+        <v>614995</v>
       </c>
       <c r="R92" t="n">
-        <v>6560582</v>
+        <v>6560571</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,7 +10138,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737656</v>
+        <v>131737649</v>
       </c>
       <c r="B93" t="n">
         <v>93158</v>
@@ -10178,14 +10169,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615271</v>
+        <v>615316</v>
       </c>
       <c r="R93" t="n">
-        <v>6560749</v>
+        <v>6560709</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,7 +10239,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737666</v>
+        <v>131737783</v>
       </c>
       <c r="B94" t="n">
         <v>93158</v>
@@ -10276,17 +10267,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614995</v>
+        <v>615276</v>
       </c>
       <c r="R94" t="n">
-        <v>6560571</v>
+        <v>6560495</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10313,12 +10308,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10349,7 +10349,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737676</v>
+        <v>131737659</v>
       </c>
       <c r="B95" t="n">
         <v>93158</v>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615060</v>
+        <v>615267</v>
       </c>
       <c r="R95" t="n">
-        <v>6560536</v>
+        <v>6560667</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737646</v>
+        <v>131738998</v>
       </c>
       <c r="B96" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10461,34 +10461,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615289</v>
+        <v>615020</v>
       </c>
       <c r="R96" t="n">
-        <v>6560695</v>
+        <v>6560533</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,7 +10551,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737690</v>
+        <v>131737641</v>
       </c>
       <c r="B97" t="n">
         <v>93158</v>
@@ -10582,14 +10582,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615387</v>
+        <v>614893</v>
       </c>
       <c r="R97" t="n">
-        <v>6560558</v>
+        <v>6560582</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737659</v>
+        <v>131737656</v>
       </c>
       <c r="B98" t="n">
         <v>93158</v>
@@ -10683,14 +10683,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615267</v>
+        <v>615271</v>
       </c>
       <c r="R98" t="n">
-        <v>6560667</v>
+        <v>6560749</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10753,7 +10753,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737649</v>
+        <v>131737646</v>
       </c>
       <c r="B99" t="n">
         <v>93158</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615316</v>
+        <v>615289</v>
       </c>
       <c r="R99" t="n">
-        <v>6560709</v>
+        <v>6560695</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739013</v>
+        <v>131737664</v>
       </c>
       <c r="B100" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615376</v>
+        <v>614942</v>
       </c>
       <c r="R100" t="n">
-        <v>6560556</v>
+        <v>6560568</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739004</v>
+        <v>131737691</v>
       </c>
       <c r="B101" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614958</v>
+        <v>615367</v>
       </c>
       <c r="R101" t="n">
-        <v>6560561</v>
+        <v>6560553</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739001</v>
+        <v>131737625</v>
       </c>
       <c r="B102" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614955</v>
+        <v>614918</v>
       </c>
       <c r="R102" t="n">
-        <v>6560579</v>
+        <v>6560620</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737625</v>
+        <v>131737645</v>
       </c>
       <c r="B103" t="n">
         <v>93158</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614918</v>
+        <v>615304</v>
       </c>
       <c r="R103" t="n">
-        <v>6560620</v>
+        <v>6560686</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737645</v>
+        <v>131737619</v>
       </c>
       <c r="B104" t="n">
         <v>93158</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615304</v>
+        <v>614885</v>
       </c>
       <c r="R104" t="n">
-        <v>6560686</v>
+        <v>6560613</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737655</v>
+        <v>131737636</v>
       </c>
       <c r="B105" t="n">
         <v>93158</v>
@@ -11394,10 +11394,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615267</v>
+        <v>614960</v>
       </c>
       <c r="R105" t="n">
-        <v>6560777</v>
+        <v>6560601</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737636</v>
+        <v>131739013</v>
       </c>
       <c r="B106" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614960</v>
+        <v>615376</v>
       </c>
       <c r="R106" t="n">
-        <v>6560601</v>
+        <v>6560556</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739004</v>
       </c>
       <c r="B107" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,34 +11572,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>614958</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737619</v>
+        <v>131739001</v>
       </c>
       <c r="B108" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614885</v>
+        <v>614955</v>
       </c>
       <c r="R108" t="n">
-        <v>6560613</v>
+        <v>6560579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737664</v>
+        <v>131737655</v>
       </c>
       <c r="B109" t="n">
         <v>93158</v>
@@ -11794,14 +11794,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614942</v>
+        <v>615267</v>
       </c>
       <c r="R109" t="n">
-        <v>6560568</v>
+        <v>6560777</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,41 +11864,53 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740361</v>
+        <v>131740030</v>
       </c>
       <c r="B110" t="n">
-        <v>93149</v>
+        <v>57090</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615309</v>
+        <v>614953</v>
       </c>
       <c r="R110" t="n">
-        <v>6560557</v>
+        <v>6560578</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11933,13 +11945,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11962,10 +11978,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737627</v>
+        <v>131738995</v>
       </c>
       <c r="B111" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,34 +11989,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614921</v>
+        <v>615323</v>
       </c>
       <c r="R111" t="n">
-        <v>6560604</v>
+        <v>6560647</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12063,10 +12079,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737648</v>
+        <v>131738990</v>
       </c>
       <c r="B112" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12074,34 +12090,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615306</v>
+        <v>614930</v>
       </c>
       <c r="R112" t="n">
-        <v>6560663</v>
+        <v>6560587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12164,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737630</v>
+        <v>131736566</v>
       </c>
       <c r="B113" t="n">
-        <v>93158</v>
+        <v>93136</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12175,34 +12191,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614948</v>
+        <v>615319</v>
       </c>
       <c r="R113" t="n">
-        <v>6560611</v>
+        <v>6560579</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12235,6 +12255,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12265,10 +12290,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131736566</v>
+        <v>131737630</v>
       </c>
       <c r="B114" t="n">
-        <v>93136</v>
+        <v>93158</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12276,38 +12301,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615319</v>
+        <v>614948</v>
       </c>
       <c r="R114" t="n">
-        <v>6560579</v>
+        <v>6560611</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12340,11 +12361,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12375,10 +12391,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131740361</v>
       </c>
       <c r="B115" t="n">
-        <v>79883</v>
+        <v>93149</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12386,23 +12402,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12410,10 +12422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>615309</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560557</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12454,6 +12466,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12476,10 +12489,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131737648</v>
       </c>
       <c r="B116" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12487,34 +12500,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>615306</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560663</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12577,53 +12590,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131740030</v>
+        <v>131737627</v>
       </c>
       <c r="B117" t="n">
-        <v>57090</v>
+        <v>93158</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614953</v>
+        <v>614921</v>
       </c>
       <c r="R117" t="n">
-        <v>6560578</v>
+        <v>6560604</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12656,11 +12661,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737665</v>
+        <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>93158</v>
+        <v>91853</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614993</v>
+        <v>614974</v>
       </c>
       <c r="R118" t="n">
-        <v>6560559</v>
+        <v>6560628</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,7 +12792,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737670</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
         <v>93158</v>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614972</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560590</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131740081</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
-        <v>91853</v>
+        <v>93158</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614974</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560628</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12958,12 +12958,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13407,7 +13407,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737683</v>
+        <v>131737622</v>
       </c>
       <c r="B125" t="n">
         <v>93158</v>
@@ -13438,14 +13438,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>615337</v>
+        <v>614898</v>
       </c>
       <c r="R125" t="n">
-        <v>6560617</v>
+        <v>6560601</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13710,10 +13710,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131738997</v>
+        <v>131737683</v>
       </c>
       <c r="B128" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13721,34 +13721,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615026</v>
+        <v>615337</v>
       </c>
       <c r="R128" t="n">
-        <v>6560531</v>
+        <v>6560617</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737622</v>
+        <v>131739026</v>
       </c>
       <c r="B129" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13822,34 +13822,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>614898</v>
+        <v>615203</v>
       </c>
       <c r="R129" t="n">
-        <v>6560601</v>
+        <v>6560503</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13876,12 +13876,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13912,7 +13912,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131739026</v>
+        <v>131738997</v>
       </c>
       <c r="B130" t="n">
         <v>79883</v>
@@ -13943,14 +13943,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615203</v>
+        <v>615026</v>
       </c>
       <c r="R130" t="n">
-        <v>6560503</v>
+        <v>6560531</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13977,12 +13977,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14013,7 +14013,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737663</v>
+        <v>131737661</v>
       </c>
       <c r="B131" t="n">
         <v>93158</v>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615046</v>
+        <v>615060</v>
       </c>
       <c r="R131" t="n">
-        <v>6560537</v>
+        <v>6560565</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737673</v>
+        <v>131737682</v>
       </c>
       <c r="B132" t="n">
         <v>93158</v>
@@ -14145,14 +14145,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614957</v>
+        <v>615350</v>
       </c>
       <c r="R132" t="n">
-        <v>6560564</v>
+        <v>6560611</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737661</v>
+        <v>131737673</v>
       </c>
       <c r="B133" t="n">
         <v>93158</v>
@@ -14250,10 +14250,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615060</v>
+        <v>614957</v>
       </c>
       <c r="R133" t="n">
-        <v>6560565</v>
+        <v>6560564</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,45 +14316,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131735760</v>
+        <v>131737663</v>
       </c>
       <c r="B134" t="n">
-        <v>90597</v>
+        <v>93158</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615279</v>
+        <v>615046</v>
       </c>
       <c r="R134" t="n">
-        <v>6560699</v>
+        <v>6560537</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,32 +14417,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131738996</v>
+        <v>131735760</v>
       </c>
       <c r="B135" t="n">
-        <v>79883</v>
+        <v>90597</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615290</v>
+        <v>615279</v>
       </c>
       <c r="R135" t="n">
-        <v>6560715</v>
+        <v>6560699</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737682</v>
+        <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,21 +14529,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615350</v>
+        <v>615290</v>
       </c>
       <c r="R136" t="n">
-        <v>6560611</v>
+        <v>6560715</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -4155,7 +4155,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738991</v>
+        <v>131739007</v>
       </c>
       <c r="B34" t="n">
         <v>79883</v>
@@ -4186,14 +4186,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614921</v>
+        <v>614970</v>
       </c>
       <c r="R34" t="n">
-        <v>6560577</v>
+        <v>6560560</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131739043</v>
+        <v>131738991</v>
       </c>
       <c r="B35" t="n">
         <v>79883</v>
@@ -4287,14 +4287,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614985</v>
+        <v>614921</v>
       </c>
       <c r="R35" t="n">
-        <v>6560565</v>
+        <v>6560577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739007</v>
+        <v>131739043</v>
       </c>
       <c r="B36" t="n">
         <v>79883</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614970</v>
+        <v>614985</v>
       </c>
       <c r="R36" t="n">
-        <v>6560560</v>
+        <v>6560565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5679,45 +5679,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737925</v>
+        <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>8454</v>
+        <v>79883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615343</v>
+        <v>615022</v>
       </c>
       <c r="R49" t="n">
-        <v>6560656</v>
+        <v>6560527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6083,45 +6083,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131739012</v>
+        <v>131737925</v>
       </c>
       <c r="B53" t="n">
-        <v>79883</v>
+        <v>8454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615022</v>
+        <v>615343</v>
       </c>
       <c r="R53" t="n">
-        <v>6560527</v>
+        <v>6560656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737688</v>
+        <v>131738993</v>
       </c>
       <c r="B60" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615310</v>
+        <v>614904</v>
       </c>
       <c r="R60" t="n">
-        <v>6560543</v>
+        <v>6560578</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737652</v>
+        <v>131739005</v>
       </c>
       <c r="B61" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,21 +6902,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615301</v>
+        <v>614968</v>
       </c>
       <c r="R61" t="n">
-        <v>6560755</v>
+        <v>6560572</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131738993</v>
+        <v>131737688</v>
       </c>
       <c r="B62" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614904</v>
+        <v>615310</v>
       </c>
       <c r="R62" t="n">
-        <v>6560578</v>
+        <v>6560543</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739008</v>
+        <v>131737652</v>
       </c>
       <c r="B63" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614995</v>
+        <v>615301</v>
       </c>
       <c r="R63" t="n">
-        <v>6560547</v>
+        <v>6560755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739005</v>
+        <v>131739008</v>
       </c>
       <c r="B64" t="n">
         <v>79883</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614968</v>
+        <v>614995</v>
       </c>
       <c r="R64" t="n">
-        <v>6560572</v>
+        <v>6560547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737653</v>
+        <v>131737624</v>
       </c>
       <c r="B81" t="n">
         <v>93158</v>
@@ -8948,14 +8948,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>615289</v>
+        <v>614910</v>
       </c>
       <c r="R81" t="n">
-        <v>6560767</v>
+        <v>6560612</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9018,7 +9018,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737680</v>
+        <v>131737782</v>
       </c>
       <c r="B82" t="n">
         <v>93158</v>
@@ -9046,17 +9046,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>615390</v>
+        <v>615216</v>
       </c>
       <c r="R82" t="n">
-        <v>6560614</v>
+        <v>6560514</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9083,12 +9087,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9119,7 +9128,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737674</v>
+        <v>131737653</v>
       </c>
       <c r="B83" t="n">
         <v>93158</v>
@@ -9154,10 +9163,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>614965</v>
+        <v>615289</v>
       </c>
       <c r="R83" t="n">
-        <v>6560563</v>
+        <v>6560767</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9220,7 +9229,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737624</v>
+        <v>131737680</v>
       </c>
       <c r="B84" t="n">
         <v>93158</v>
@@ -9251,14 +9260,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614910</v>
+        <v>615390</v>
       </c>
       <c r="R84" t="n">
-        <v>6560612</v>
+        <v>6560614</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9321,7 +9330,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737782</v>
+        <v>131737674</v>
       </c>
       <c r="B85" t="n">
         <v>93158</v>
@@ -9349,21 +9358,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>615216</v>
+        <v>614965</v>
       </c>
       <c r="R85" t="n">
-        <v>6560514</v>
+        <v>6560563</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9390,17 +9395,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9835,7 +9835,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737690</v>
+        <v>131737659</v>
       </c>
       <c r="B90" t="n">
         <v>93158</v>
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615387</v>
+        <v>615267</v>
       </c>
       <c r="R90" t="n">
-        <v>6560558</v>
+        <v>6560667</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737676</v>
+        <v>131737641</v>
       </c>
       <c r="B91" t="n">
         <v>93158</v>
@@ -9967,14 +9967,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615060</v>
+        <v>614893</v>
       </c>
       <c r="R91" t="n">
-        <v>6560536</v>
+        <v>6560582</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10037,7 +10037,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737666</v>
+        <v>131737649</v>
       </c>
       <c r="B92" t="n">
         <v>93158</v>
@@ -10068,14 +10068,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614995</v>
+        <v>615316</v>
       </c>
       <c r="R92" t="n">
-        <v>6560571</v>
+        <v>6560709</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10138,7 +10138,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737649</v>
+        <v>131737690</v>
       </c>
       <c r="B93" t="n">
         <v>93158</v>
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615316</v>
+        <v>615387</v>
       </c>
       <c r="R93" t="n">
-        <v>6560709</v>
+        <v>6560558</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10239,7 +10239,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737783</v>
+        <v>131737676</v>
       </c>
       <c r="B94" t="n">
         <v>93158</v>
@@ -10267,21 +10267,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615276</v>
+        <v>615060</v>
       </c>
       <c r="R94" t="n">
-        <v>6560495</v>
+        <v>6560536</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10308,17 +10304,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10349,7 +10340,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737659</v>
+        <v>131737783</v>
       </c>
       <c r="B95" t="n">
         <v>93158</v>
@@ -10377,17 +10368,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615267</v>
+        <v>615276</v>
       </c>
       <c r="R95" t="n">
-        <v>6560667</v>
+        <v>6560495</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10414,12 +10409,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131738998</v>
+        <v>131737666</v>
       </c>
       <c r="B96" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615020</v>
+        <v>614995</v>
       </c>
       <c r="R96" t="n">
-        <v>6560533</v>
+        <v>6560571</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,7 +10551,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737641</v>
+        <v>131737656</v>
       </c>
       <c r="B97" t="n">
         <v>93158</v>
@@ -10582,14 +10582,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>614893</v>
+        <v>615271</v>
       </c>
       <c r="R97" t="n">
-        <v>6560582</v>
+        <v>6560749</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737656</v>
+        <v>131737646</v>
       </c>
       <c r="B98" t="n">
         <v>93158</v>
@@ -10683,14 +10683,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615271</v>
+        <v>615289</v>
       </c>
       <c r="R98" t="n">
-        <v>6560749</v>
+        <v>6560695</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737646</v>
+        <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615289</v>
+        <v>615020</v>
       </c>
       <c r="R99" t="n">
-        <v>6560695</v>
+        <v>6560533</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11864,53 +11864,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740030</v>
+        <v>131737630</v>
       </c>
       <c r="B110" t="n">
-        <v>57090</v>
+        <v>93158</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614953</v>
+        <v>614948</v>
       </c>
       <c r="R110" t="n">
-        <v>6560578</v>
+        <v>6560611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11943,11 +11935,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11978,10 +11965,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738995</v>
+        <v>131740361</v>
       </c>
       <c r="B111" t="n">
-        <v>79883</v>
+        <v>93149</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11989,23 +11976,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12013,10 +11996,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615323</v>
+        <v>615309</v>
       </c>
       <c r="R111" t="n">
-        <v>6560647</v>
+        <v>6560557</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12057,6 +12040,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12079,10 +12063,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131738990</v>
+        <v>131737648</v>
       </c>
       <c r="B112" t="n">
-        <v>79883</v>
+        <v>93158</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12090,34 +12074,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614930</v>
+        <v>615306</v>
       </c>
       <c r="R112" t="n">
-        <v>6560587</v>
+        <v>6560663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12180,10 +12164,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131736566</v>
+        <v>131737627</v>
       </c>
       <c r="B113" t="n">
-        <v>93136</v>
+        <v>93158</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12191,38 +12175,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615319</v>
+        <v>614921</v>
       </c>
       <c r="R113" t="n">
-        <v>6560579</v>
+        <v>6560604</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12255,11 +12235,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12290,45 +12265,53 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737630</v>
+        <v>131740030</v>
       </c>
       <c r="B114" t="n">
-        <v>93158</v>
+        <v>57090</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614948</v>
+        <v>614953</v>
       </c>
       <c r="R114" t="n">
-        <v>6560611</v>
+        <v>6560578</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12361,6 +12344,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12391,10 +12379,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93149</v>
+        <v>79883</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12402,19 +12390,23 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12422,10 +12414,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12466,7 +12458,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12489,10 +12480,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737648</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
-        <v>93158</v>
+        <v>79883</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12500,34 +12491,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615306</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560663</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,10 +12581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737627</v>
+        <v>131736566</v>
       </c>
       <c r="B117" t="n">
-        <v>93158</v>
+        <v>93136</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12601,34 +12592,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614921</v>
+        <v>615319</v>
       </c>
       <c r="R117" t="n">
-        <v>6560604</v>
+        <v>6560579</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14417,32 +14417,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B135" t="n">
-        <v>90597</v>
+        <v>79883</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R135" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,32 +14518,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131735760</v>
       </c>
       <c r="B136" t="n">
-        <v>79883</v>
+        <v>90597</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>615279</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560699</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737631</v>
+        <v>131737671</v>
       </c>
       <c r="B18" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614937</v>
+        <v>614965</v>
       </c>
       <c r="R18" t="n">
-        <v>6560625</v>
+        <v>6560580</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737654</v>
+        <v>131737650</v>
       </c>
       <c r="B19" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,14 +2644,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615282</v>
+        <v>615325</v>
       </c>
       <c r="R19" t="n">
-        <v>6560780</v>
+        <v>6560719</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737650</v>
+        <v>131737654</v>
       </c>
       <c r="B20" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2745,14 +2745,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615325</v>
+        <v>615282</v>
       </c>
       <c r="R20" t="n">
-        <v>6560719</v>
+        <v>6560780</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737637</v>
+        <v>131737631</v>
       </c>
       <c r="B21" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614949</v>
+        <v>614937</v>
       </c>
       <c r="R21" t="n">
-        <v>6560610</v>
+        <v>6560625</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737614</v>
+        <v>131737632</v>
       </c>
       <c r="B22" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,14 +2947,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614857</v>
+        <v>614949</v>
       </c>
       <c r="R22" t="n">
-        <v>6560612</v>
+        <v>6560635</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>131737647</v>
       </c>
       <c r="B23" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737671</v>
+        <v>131737637</v>
       </c>
       <c r="B24" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614965</v>
+        <v>614949</v>
       </c>
       <c r="R24" t="n">
-        <v>6560580</v>
+        <v>6560610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737632</v>
+        <v>131737614</v>
       </c>
       <c r="B25" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,14 +3250,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614949</v>
+        <v>614857</v>
       </c>
       <c r="R25" t="n">
-        <v>6560635</v>
+        <v>6560612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131739009</v>
+        <v>131738992</v>
       </c>
       <c r="B26" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3351,14 +3351,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614998</v>
+        <v>614903</v>
       </c>
       <c r="R26" t="n">
-        <v>6560540</v>
+        <v>6560580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131739006</v>
+        <v>131739009</v>
       </c>
       <c r="B27" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614970</v>
+        <v>614998</v>
       </c>
       <c r="R27" t="n">
-        <v>6560568</v>
+        <v>6560540</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738992</v>
+        <v>131739006</v>
       </c>
       <c r="B28" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614903</v>
+        <v>614970</v>
       </c>
       <c r="R28" t="n">
-        <v>6560580</v>
+        <v>6560568</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737651</v>
+        <v>131738991</v>
       </c>
       <c r="B29" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,34 +3634,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615311</v>
+        <v>614921</v>
       </c>
       <c r="R29" t="n">
-        <v>6560742</v>
+        <v>6560577</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737785</v>
+        <v>131739043</v>
       </c>
       <c r="B30" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,38 +3735,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615314</v>
+        <v>614985</v>
       </c>
       <c r="R30" t="n">
-        <v>6560513</v>
+        <v>6560565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,17 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3837,7 +3828,7 @@
         <v>131737629</v>
       </c>
       <c r="B31" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,7 +3929,7 @@
         <v>131737787</v>
       </c>
       <c r="B32" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4045,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737784</v>
+        <v>131737651</v>
       </c>
       <c r="B33" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,21 +4064,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615291</v>
+        <v>615311</v>
       </c>
       <c r="R33" t="n">
-        <v>6560497</v>
+        <v>6560742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,17 +4101,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4155,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131739007</v>
+        <v>131737785</v>
       </c>
       <c r="B34" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,34 +4148,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614970</v>
+        <v>615314</v>
       </c>
       <c r="R34" t="n">
-        <v>6560560</v>
+        <v>6560513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,12 +4206,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4247,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131738991</v>
+        <v>131737784</v>
       </c>
       <c r="B35" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,34 +4258,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614921</v>
+        <v>615291</v>
       </c>
       <c r="R35" t="n">
-        <v>6560577</v>
+        <v>6560497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4316,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739043</v>
+        <v>131739007</v>
       </c>
       <c r="B36" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614985</v>
+        <v>614970</v>
       </c>
       <c r="R36" t="n">
-        <v>6560565</v>
+        <v>6560560</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737669</v>
+        <v>131737672</v>
       </c>
       <c r="B37" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614973</v>
+        <v>614950</v>
       </c>
       <c r="R37" t="n">
-        <v>6560600</v>
+        <v>6560576</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,10 +4559,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737660</v>
+        <v>131737786</v>
       </c>
       <c r="B38" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4587,17 +4587,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615278</v>
+        <v>615335</v>
       </c>
       <c r="R38" t="n">
-        <v>6560662</v>
+        <v>6560536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4624,12 +4628,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4660,10 +4669,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737685</v>
+        <v>131737620</v>
       </c>
       <c r="B39" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4691,14 +4700,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615324</v>
+        <v>614896</v>
       </c>
       <c r="R39" t="n">
-        <v>6560604</v>
+        <v>6560613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4764,7 +4773,7 @@
         <v>131737634</v>
       </c>
       <c r="B40" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737640</v>
+        <v>131737669</v>
       </c>
       <c r="B41" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4893,14 +4902,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614934</v>
+        <v>614973</v>
       </c>
       <c r="R41" t="n">
-        <v>6560578</v>
+        <v>6560600</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737786</v>
+        <v>131737660</v>
       </c>
       <c r="B42" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +5000,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>615335</v>
+        <v>615278</v>
       </c>
       <c r="R42" t="n">
-        <v>6560536</v>
+        <v>6560662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,17 +5037,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5073,10 +5073,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737620</v>
+        <v>131737662</v>
       </c>
       <c r="B43" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5104,14 +5104,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614896</v>
+        <v>615040</v>
       </c>
       <c r="R43" t="n">
-        <v>6560613</v>
+        <v>6560530</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737672</v>
+        <v>131737640</v>
       </c>
       <c r="B44" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614950</v>
+        <v>614934</v>
       </c>
       <c r="R44" t="n">
-        <v>6560576</v>
+        <v>6560578</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737662</v>
+        <v>131737685</v>
       </c>
       <c r="B45" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615040</v>
+        <v>615324</v>
       </c>
       <c r="R45" t="n">
-        <v>6560530</v>
+        <v>6560604</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5379,7 +5379,7 @@
         <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>131737618</v>
       </c>
       <c r="B47" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>131737616</v>
       </c>
       <c r="B50" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131737677</v>
       </c>
       <c r="B51" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131737684</v>
       </c>
       <c r="B52" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737617</v>
+        <v>131737675</v>
       </c>
       <c r="B54" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6215,14 +6215,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614867</v>
+        <v>614961</v>
       </c>
       <c r="R54" t="n">
-        <v>6560588</v>
+        <v>6560552</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737675</v>
+        <v>131737617</v>
       </c>
       <c r="B55" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6316,14 +6316,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614961</v>
+        <v>614867</v>
       </c>
       <c r="R55" t="n">
-        <v>6560552</v>
+        <v>6560588</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6389,7 +6389,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737615</v>
+        <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6518,14 +6518,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614854</v>
+        <v>614946</v>
       </c>
       <c r="R57" t="n">
-        <v>6560611</v>
+        <v>6560623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6591,7 +6591,7 @@
         <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737633</v>
+        <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6720,14 +6720,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614946</v>
+        <v>614854</v>
       </c>
       <c r="R59" t="n">
-        <v>6560623</v>
+        <v>6560611</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B60" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R60" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739005</v>
+        <v>131737688</v>
       </c>
       <c r="B61" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,34 +6902,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614968</v>
+        <v>615310</v>
       </c>
       <c r="R61" t="n">
-        <v>6560572</v>
+        <v>6560543</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737688</v>
+        <v>131738993</v>
       </c>
       <c r="B62" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615310</v>
+        <v>614904</v>
       </c>
       <c r="R62" t="n">
-        <v>6560543</v>
+        <v>6560578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737652</v>
+        <v>131739008</v>
       </c>
       <c r="B63" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615301</v>
+        <v>614995</v>
       </c>
       <c r="R63" t="n">
-        <v>6560755</v>
+        <v>6560547</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739008</v>
+        <v>131739005</v>
       </c>
       <c r="B64" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614995</v>
+        <v>614968</v>
       </c>
       <c r="R64" t="n">
-        <v>6560547</v>
+        <v>6560572</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7298,7 +7298,7 @@
         <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93136</v>
+        <v>93142</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>131737686</v>
       </c>
       <c r="B66" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>131740360</v>
       </c>
       <c r="B68" t="n">
-        <v>93149</v>
+        <v>93155</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7705,10 +7705,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737638</v>
+        <v>131737667</v>
       </c>
       <c r="B69" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614943</v>
+        <v>614991</v>
       </c>
       <c r="R69" t="n">
-        <v>6560591</v>
+        <v>6560587</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737658</v>
+        <v>131737638</v>
       </c>
       <c r="B70" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7837,14 +7837,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>615282</v>
+        <v>614943</v>
       </c>
       <c r="R70" t="n">
-        <v>6560684</v>
+        <v>6560591</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,10 +7907,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737667</v>
+        <v>131737658</v>
       </c>
       <c r="B71" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7938,14 +7938,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614991</v>
+        <v>615282</v>
       </c>
       <c r="R71" t="n">
-        <v>6560587</v>
+        <v>6560684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8011,7 +8011,7 @@
         <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737668</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8241,14 +8241,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614990</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560601</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
         <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737644</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615331</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560676</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8516,7 +8516,7 @@
         <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>131739041</v>
       </c>
       <c r="B78" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>131739011</v>
       </c>
       <c r="B79" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737624</v>
+        <v>131737674</v>
       </c>
       <c r="B81" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8948,14 +8948,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614910</v>
+        <v>614965</v>
       </c>
       <c r="R81" t="n">
-        <v>6560612</v>
+        <v>6560563</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9021,7 +9021,7 @@
         <v>131737782</v>
       </c>
       <c r="B82" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9128,10 +9128,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737653</v>
+        <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9159,14 +9159,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>615289</v>
+        <v>615390</v>
       </c>
       <c r="R83" t="n">
-        <v>6560767</v>
+        <v>6560614</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,10 +9229,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737680</v>
+        <v>131737653</v>
       </c>
       <c r="B84" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9260,14 +9260,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>615390</v>
+        <v>615289</v>
       </c>
       <c r="R84" t="n">
-        <v>6560614</v>
+        <v>6560767</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737674</v>
+        <v>131737624</v>
       </c>
       <c r="B85" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9361,14 +9361,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614965</v>
+        <v>614910</v>
       </c>
       <c r="R85" t="n">
-        <v>6560563</v>
+        <v>6560612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737687</v>
+        <v>131737626</v>
       </c>
       <c r="B86" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9462,14 +9462,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>615322</v>
+        <v>614911</v>
       </c>
       <c r="R86" t="n">
-        <v>6560582</v>
+        <v>6560610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737626</v>
+        <v>131737642</v>
       </c>
       <c r="B87" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614911</v>
+        <v>614884</v>
       </c>
       <c r="R87" t="n">
-        <v>6560610</v>
+        <v>6560568</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737642</v>
+        <v>131737687</v>
       </c>
       <c r="B88" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614884</v>
+        <v>615322</v>
       </c>
       <c r="R88" t="n">
-        <v>6560568</v>
+        <v>6560582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9737,7 +9737,7 @@
         <v>131738988</v>
       </c>
       <c r="B89" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737659</v>
+        <v>131737783</v>
       </c>
       <c r="B90" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9863,17 +9863,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615267</v>
+        <v>615276</v>
       </c>
       <c r="R90" t="n">
-        <v>6560667</v>
+        <v>6560495</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9900,12 +9904,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9939,7 +9948,7 @@
         <v>131737641</v>
       </c>
       <c r="B91" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10037,10 +10046,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737649</v>
+        <v>131737656</v>
       </c>
       <c r="B92" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10068,14 +10077,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615316</v>
+        <v>615271</v>
       </c>
       <c r="R92" t="n">
-        <v>6560709</v>
+        <v>6560749</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10138,10 +10147,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737690</v>
+        <v>131737666</v>
       </c>
       <c r="B93" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10169,14 +10178,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615387</v>
+        <v>614995</v>
       </c>
       <c r="R93" t="n">
-        <v>6560558</v>
+        <v>6560571</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10242,7 +10251,7 @@
         <v>131737676</v>
       </c>
       <c r="B94" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10340,10 +10349,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737783</v>
+        <v>131737646</v>
       </c>
       <c r="B95" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10368,21 +10377,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615276</v>
+        <v>615289</v>
       </c>
       <c r="R95" t="n">
-        <v>6560495</v>
+        <v>6560695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10409,17 +10414,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737666</v>
+        <v>131737690</v>
       </c>
       <c r="B96" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10481,14 +10481,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>614995</v>
+        <v>615387</v>
       </c>
       <c r="R96" t="n">
-        <v>6560571</v>
+        <v>6560558</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,10 +10551,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737656</v>
+        <v>131737659</v>
       </c>
       <c r="B97" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10582,14 +10582,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615271</v>
+        <v>615267</v>
       </c>
       <c r="R97" t="n">
-        <v>6560749</v>
+        <v>6560667</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737646</v>
+        <v>131737649</v>
       </c>
       <c r="B98" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615289</v>
+        <v>615316</v>
       </c>
       <c r="R98" t="n">
-        <v>6560695</v>
+        <v>6560709</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10756,7 +10756,7 @@
         <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737664</v>
+        <v>131737619</v>
       </c>
       <c r="B100" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614942</v>
+        <v>614885</v>
       </c>
       <c r="R100" t="n">
-        <v>6560568</v>
+        <v>6560613</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737691</v>
+        <v>131737625</v>
       </c>
       <c r="B101" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615367</v>
+        <v>614918</v>
       </c>
       <c r="R101" t="n">
-        <v>6560553</v>
+        <v>6560620</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737625</v>
+        <v>131737645</v>
       </c>
       <c r="B102" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11087,14 +11087,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614918</v>
+        <v>615304</v>
       </c>
       <c r="R102" t="n">
-        <v>6560620</v>
+        <v>6560686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737645</v>
+        <v>131737655</v>
       </c>
       <c r="B103" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615304</v>
+        <v>615267</v>
       </c>
       <c r="R103" t="n">
-        <v>6560686</v>
+        <v>6560777</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737619</v>
+        <v>131737636</v>
       </c>
       <c r="B104" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614885</v>
+        <v>614960</v>
       </c>
       <c r="R104" t="n">
-        <v>6560613</v>
+        <v>6560601</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737636</v>
+        <v>131737691</v>
       </c>
       <c r="B105" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614960</v>
+        <v>615367</v>
       </c>
       <c r="R105" t="n">
-        <v>6560601</v>
+        <v>6560553</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739013</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615376</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560556</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739004</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11592,14 +11592,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614958</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560561</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739001</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614955</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560579</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737655</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,21 +11774,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>615267</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560777</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,45 +11864,53 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131737630</v>
+        <v>131740030</v>
       </c>
       <c r="B110" t="n">
-        <v>93158</v>
+        <v>57092</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614948</v>
+        <v>614953</v>
       </c>
       <c r="R110" t="n">
-        <v>6560611</v>
+        <v>6560578</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11935,6 +11943,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11965,10 +11978,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B111" t="n">
-        <v>93149</v>
+        <v>79885</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11976,19 +11989,23 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11996,10 +12013,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R111" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12040,7 +12057,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12063,10 +12079,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737648</v>
+        <v>131738990</v>
       </c>
       <c r="B112" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12074,34 +12090,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615306</v>
+        <v>614930</v>
       </c>
       <c r="R112" t="n">
-        <v>6560663</v>
+        <v>6560587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12167,7 +12183,7 @@
         <v>131737627</v>
       </c>
       <c r="B113" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12265,53 +12281,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740030</v>
+        <v>131737648</v>
       </c>
       <c r="B114" t="n">
-        <v>57090</v>
+        <v>93164</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614953</v>
+        <v>615306</v>
       </c>
       <c r="R114" t="n">
-        <v>6560578</v>
+        <v>6560663</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12344,11 +12352,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12379,10 +12382,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131737630</v>
       </c>
       <c r="B115" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12390,34 +12393,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>614948</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560611</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12480,10 +12483,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131740361</v>
       </c>
       <c r="B116" t="n">
-        <v>79883</v>
+        <v>93155</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12491,34 +12494,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>615309</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560557</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12559,6 +12558,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>131736566</v>
       </c>
       <c r="B117" t="n">
-        <v>93136</v>
+        <v>93142</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131739003</v>
       </c>
       <c r="B119" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614959</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560556</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131737665</v>
       </c>
       <c r="B120" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614993</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739003</v>
+        <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614959</v>
+        <v>614972</v>
       </c>
       <c r="R121" t="n">
-        <v>6560556</v>
+        <v>6560590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13095,49 +13095,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131735761</v>
+        <v>131738994</v>
       </c>
       <c r="B122" t="n">
-        <v>90597</v>
+        <v>79885</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>615277</v>
+        <v>614890</v>
       </c>
       <c r="R122" t="n">
-        <v>6560691</v>
+        <v>6560564</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13170,11 +13166,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13205,10 +13196,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131738994</v>
+        <v>131739000</v>
       </c>
       <c r="B123" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13240,10 +13231,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614890</v>
+        <v>614941</v>
       </c>
       <c r="R123" t="n">
-        <v>6560564</v>
+        <v>6560553</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13306,45 +13297,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739000</v>
+        <v>131735761</v>
       </c>
       <c r="B124" t="n">
-        <v>79883</v>
+        <v>90603</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614941</v>
+        <v>615277</v>
       </c>
       <c r="R124" t="n">
-        <v>6560553</v>
+        <v>6560691</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13377,6 +13372,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13407,10 +13407,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737622</v>
+        <v>131739026</v>
       </c>
       <c r="B125" t="n">
-        <v>93158</v>
+        <v>79885</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13418,34 +13418,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614898</v>
+        <v>615203</v>
       </c>
       <c r="R125" t="n">
-        <v>6560601</v>
+        <v>6560503</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13472,12 +13472,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13508,10 +13508,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737678</v>
+        <v>131737622</v>
       </c>
       <c r="B126" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13539,14 +13539,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615054</v>
+        <v>614898</v>
       </c>
       <c r="R126" t="n">
-        <v>6560523</v>
+        <v>6560601</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13609,10 +13609,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737681</v>
+        <v>131737683</v>
       </c>
       <c r="B127" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13640,14 +13640,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615383</v>
+        <v>615337</v>
       </c>
       <c r="R127" t="n">
-        <v>6560632</v>
+        <v>6560617</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13710,10 +13710,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737683</v>
+        <v>131737678</v>
       </c>
       <c r="B128" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615337</v>
+        <v>615054</v>
       </c>
       <c r="R128" t="n">
-        <v>6560617</v>
+        <v>6560523</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131739026</v>
+        <v>131737681</v>
       </c>
       <c r="B129" t="n">
-        <v>79883</v>
+        <v>93164</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13822,34 +13822,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615203</v>
+        <v>615383</v>
       </c>
       <c r="R129" t="n">
-        <v>6560503</v>
+        <v>6560632</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13876,12 +13876,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13915,7 +13915,7 @@
         <v>131738997</v>
       </c>
       <c r="B130" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14013,45 +14013,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737661</v>
+        <v>131735760</v>
       </c>
       <c r="B131" t="n">
-        <v>93158</v>
+        <v>90603</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615060</v>
+        <v>615279</v>
       </c>
       <c r="R131" t="n">
-        <v>6560565</v>
+        <v>6560699</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14117,7 +14117,7 @@
         <v>131737682</v>
       </c>
       <c r="B132" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14215,10 +14215,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737673</v>
+        <v>131737663</v>
       </c>
       <c r="B133" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14250,10 +14250,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614957</v>
+        <v>615046</v>
       </c>
       <c r="R133" t="n">
-        <v>6560564</v>
+        <v>6560537</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,10 +14316,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737663</v>
+        <v>131737661</v>
       </c>
       <c r="B134" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615046</v>
+        <v>615060</v>
       </c>
       <c r="R134" t="n">
-        <v>6560537</v>
+        <v>6560565</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14420,7 +14420,7 @@
         <v>131738996</v>
       </c>
       <c r="B135" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14518,45 +14518,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131735760</v>
+        <v>131737673</v>
       </c>
       <c r="B136" t="n">
-        <v>90597</v>
+        <v>93164</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615279</v>
+        <v>614957</v>
       </c>
       <c r="R136" t="n">
-        <v>6560699</v>
+        <v>6560564</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738991</v>
+        <v>131737629</v>
       </c>
       <c r="B29" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,34 +3634,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614921</v>
+        <v>614941</v>
       </c>
       <c r="R29" t="n">
-        <v>6560577</v>
+        <v>6560607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131739043</v>
+        <v>131737787</v>
       </c>
       <c r="B30" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,34 +3735,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614985</v>
+        <v>615336</v>
       </c>
       <c r="R30" t="n">
-        <v>6560565</v>
+        <v>6560522</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,12 +3793,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,7 +3834,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737629</v>
+        <v>131737651</v>
       </c>
       <c r="B31" t="n">
         <v>93164</v>
@@ -3856,14 +3865,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614941</v>
+        <v>615311</v>
       </c>
       <c r="R31" t="n">
-        <v>6560607</v>
+        <v>6560742</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3926,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737787</v>
+        <v>131737785</v>
       </c>
       <c r="B32" t="n">
         <v>93164</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3965,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R32" t="n">
-        <v>6560522</v>
+        <v>6560513</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4014,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,7 +4045,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737651</v>
+        <v>131737784</v>
       </c>
       <c r="B33" t="n">
         <v>93164</v>
@@ -4064,17 +4073,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615311</v>
+        <v>615291</v>
       </c>
       <c r="R33" t="n">
-        <v>6560742</v>
+        <v>6560497</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,12 +4114,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,10 +4155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737785</v>
+        <v>131739007</v>
       </c>
       <c r="B34" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,38 +4166,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615314</v>
+        <v>614970</v>
       </c>
       <c r="R34" t="n">
-        <v>6560513</v>
+        <v>6560560</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,17 +4220,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4247,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737784</v>
+        <v>131738991</v>
       </c>
       <c r="B35" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4258,38 +4267,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615291</v>
+        <v>614921</v>
       </c>
       <c r="R35" t="n">
-        <v>6560497</v>
+        <v>6560577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,17 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739007</v>
+        <v>131739043</v>
       </c>
       <c r="B36" t="n">
         <v>79885</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614970</v>
+        <v>614985</v>
       </c>
       <c r="R36" t="n">
-        <v>6560560</v>
+        <v>6560565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737635</v>
+        <v>131739002</v>
       </c>
       <c r="B46" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614963</v>
+        <v>614953</v>
       </c>
       <c r="R46" t="n">
-        <v>6560615</v>
+        <v>6560567</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737618</v>
+        <v>131737635</v>
       </c>
       <c r="B47" t="n">
         <v>93164</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614881</v>
+        <v>614963</v>
       </c>
       <c r="R47" t="n">
-        <v>6560601</v>
+        <v>6560615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131739002</v>
+        <v>131737618</v>
       </c>
       <c r="B48" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614953</v>
+        <v>614881</v>
       </c>
       <c r="R48" t="n">
-        <v>6560567</v>
+        <v>6560601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739008</v>
+        <v>131739005</v>
       </c>
       <c r="B63" t="n">
         <v>79885</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614995</v>
+        <v>614968</v>
       </c>
       <c r="R63" t="n">
-        <v>6560547</v>
+        <v>6560572</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739005</v>
+        <v>131739008</v>
       </c>
       <c r="B64" t="n">
         <v>79885</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614968</v>
+        <v>614995</v>
       </c>
       <c r="R64" t="n">
-        <v>6560572</v>
+        <v>6560547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8210,32 +8210,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131737924</v>
       </c>
       <c r="B74" t="n">
-        <v>93164</v>
+        <v>8454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>615091</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560504</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,7 +8311,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>131737644</v>
       </c>
       <c r="B75" t="n">
         <v>93164</v>
@@ -8342,14 +8342,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>615331</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560676</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131737639</v>
       </c>
       <c r="B76" t="n">
         <v>93164</v>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>614942</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560579</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738989</v>
+        <v>131737668</v>
       </c>
       <c r="B77" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614945</v>
+        <v>614990</v>
       </c>
       <c r="R77" t="n">
-        <v>6560637</v>
+        <v>6560601</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739041</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
         <v>79885</v>
@@ -8645,14 +8645,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615269</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,7 +8715,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739011</v>
+        <v>131739041</v>
       </c>
       <c r="B79" t="n">
         <v>79885</v>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615080</v>
+        <v>615269</v>
       </c>
       <c r="R79" t="n">
-        <v>6560512</v>
+        <v>6560500</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737924</v>
+        <v>131739011</v>
       </c>
       <c r="B80" t="n">
-        <v>8454</v>
+        <v>79885</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615091</v>
+        <v>615080</v>
       </c>
       <c r="R80" t="n">
-        <v>6560504</v>
+        <v>6560512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737619</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
         <v>93164</v>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614885</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560613</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737625</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
         <v>93164</v>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614918</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560620</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737645</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
         <v>93164</v>
@@ -11087,14 +11087,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615304</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560686</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737655</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615267</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560777</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737636</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
         <v>93164</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614960</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560601</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737691</v>
+        <v>131737664</v>
       </c>
       <c r="B105" t="n">
         <v>93164</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615367</v>
+        <v>614942</v>
       </c>
       <c r="R105" t="n">
-        <v>6560553</v>
+        <v>6560568</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131739013</v>
       </c>
       <c r="B106" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>615376</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560556</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739013</v>
+        <v>131739004</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11592,14 +11592,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615376</v>
+        <v>614958</v>
       </c>
       <c r="R107" t="n">
-        <v>6560556</v>
+        <v>6560561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739004</v>
+        <v>131739001</v>
       </c>
       <c r="B108" t="n">
         <v>79885</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614958</v>
+        <v>614955</v>
       </c>
       <c r="R108" t="n">
-        <v>6560561</v>
+        <v>6560579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131737619</v>
       </c>
       <c r="B109" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>614885</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560613</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,53 +11864,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740030</v>
+        <v>131736566</v>
       </c>
       <c r="B110" t="n">
-        <v>57092</v>
+        <v>93142</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614953</v>
+        <v>615319</v>
       </c>
       <c r="R110" t="n">
-        <v>6560578</v>
+        <v>6560579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11947,7 +11943,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11978,10 +11974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738995</v>
+        <v>131737627</v>
       </c>
       <c r="B111" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11989,34 +11985,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615323</v>
+        <v>614921</v>
       </c>
       <c r="R111" t="n">
-        <v>6560647</v>
+        <v>6560604</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12079,10 +12075,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131738990</v>
+        <v>131737648</v>
       </c>
       <c r="B112" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12090,34 +12086,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614930</v>
+        <v>615306</v>
       </c>
       <c r="R112" t="n">
-        <v>6560587</v>
+        <v>6560663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12180,7 +12176,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737627</v>
+        <v>131737630</v>
       </c>
       <c r="B113" t="n">
         <v>93164</v>
@@ -12211,14 +12207,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614921</v>
+        <v>614948</v>
       </c>
       <c r="R113" t="n">
-        <v>6560604</v>
+        <v>6560611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12281,45 +12277,53 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737648</v>
+        <v>131740030</v>
       </c>
       <c r="B114" t="n">
-        <v>93164</v>
+        <v>57092</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615306</v>
+        <v>614953</v>
       </c>
       <c r="R114" t="n">
-        <v>6560663</v>
+        <v>6560578</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12352,6 +12356,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12382,10 +12391,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737630</v>
+        <v>131740361</v>
       </c>
       <c r="B115" t="n">
-        <v>93164</v>
+        <v>93155</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12393,34 +12402,30 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614948</v>
+        <v>615309</v>
       </c>
       <c r="R115" t="n">
-        <v>6560611</v>
+        <v>6560557</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12461,6 +12466,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12483,10 +12489,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B116" t="n">
-        <v>93155</v>
+        <v>79885</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12494,19 +12500,23 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12514,10 +12524,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R116" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12558,7 +12568,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12581,10 +12590,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131736566</v>
+        <v>131738990</v>
       </c>
       <c r="B117" t="n">
-        <v>93142</v>
+        <v>79885</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12592,38 +12601,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>615319</v>
+        <v>614930</v>
       </c>
       <c r="R117" t="n">
-        <v>6560579</v>
+        <v>6560587</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12656,11 +12661,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13095,45 +13095,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131738994</v>
+        <v>131735761</v>
       </c>
       <c r="B122" t="n">
-        <v>79885</v>
+        <v>90603</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614890</v>
+        <v>615277</v>
       </c>
       <c r="R122" t="n">
-        <v>6560564</v>
+        <v>6560691</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13166,6 +13170,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13196,7 +13205,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131739000</v>
+        <v>131738994</v>
       </c>
       <c r="B123" t="n">
         <v>79885</v>
@@ -13231,10 +13240,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614941</v>
+        <v>614890</v>
       </c>
       <c r="R123" t="n">
-        <v>6560553</v>
+        <v>6560564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13297,49 +13306,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131735761</v>
+        <v>131739000</v>
       </c>
       <c r="B124" t="n">
-        <v>90603</v>
+        <v>79885</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>615277</v>
+        <v>614941</v>
       </c>
       <c r="R124" t="n">
-        <v>6560691</v>
+        <v>6560553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13372,11 +13377,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737682</v>
+        <v>131737673</v>
       </c>
       <c r="B132" t="n">
         <v>93164</v>
@@ -14145,14 +14145,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615350</v>
+        <v>614957</v>
       </c>
       <c r="R132" t="n">
-        <v>6560611</v>
+        <v>6560564</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737663</v>
+        <v>131737682</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615046</v>
+        <v>615350</v>
       </c>
       <c r="R133" t="n">
-        <v>6560537</v>
+        <v>6560611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737661</v>
+        <v>131737663</v>
       </c>
       <c r="B134" t="n">
         <v>93164</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615060</v>
+        <v>615046</v>
       </c>
       <c r="R134" t="n">
-        <v>6560565</v>
+        <v>6560537</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131738996</v>
+        <v>131737661</v>
       </c>
       <c r="B135" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14428,34 +14428,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615290</v>
+        <v>615060</v>
       </c>
       <c r="R135" t="n">
-        <v>6560715</v>
+        <v>6560565</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737673</v>
+        <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,34 +14529,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614957</v>
+        <v>615290</v>
       </c>
       <c r="R136" t="n">
-        <v>6560564</v>
+        <v>6560715</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131739012</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615022</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560527</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
         <v>93164</v>
@@ -5811,14 +5811,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737677</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
         <v>93164</v>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615064</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560525</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B52" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,34 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R52" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -8210,32 +8210,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737924</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>8454</v>
+        <v>93164</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615091</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560504</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,7 +8311,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737644</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
         <v>93164</v>
@@ -8342,14 +8342,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615331</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560676</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737639</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
         <v>93164</v>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614942</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560579</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737668</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614990</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560601</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
         <v>79885</v>
@@ -8645,14 +8645,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,7 +8715,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739041</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
         <v>79885</v>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615269</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131739011</v>
+        <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>79885</v>
+        <v>8454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615080</v>
+        <v>615091</v>
       </c>
       <c r="R80" t="n">
-        <v>6560512</v>
+        <v>6560504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131739003</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614959</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560556</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,7 +12893,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
         <v>93164</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737670</v>
+        <v>131739003</v>
       </c>
       <c r="B121" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614972</v>
+        <v>614959</v>
       </c>
       <c r="R121" t="n">
-        <v>6560590</v>
+        <v>6560556</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737673</v>
+        <v>131737682</v>
       </c>
       <c r="B132" t="n">
         <v>93164</v>
@@ -14145,14 +14145,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614957</v>
+        <v>615350</v>
       </c>
       <c r="R132" t="n">
-        <v>6560564</v>
+        <v>6560611</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R133" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737663</v>
+        <v>131737661</v>
       </c>
       <c r="B134" t="n">
         <v>93164</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615046</v>
+        <v>615060</v>
       </c>
       <c r="R134" t="n">
-        <v>6560537</v>
+        <v>6560565</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737661</v>
+        <v>131738996</v>
       </c>
       <c r="B135" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14428,34 +14428,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615060</v>
+        <v>615290</v>
       </c>
       <c r="R135" t="n">
-        <v>6560565</v>
+        <v>6560715</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131737673</v>
       </c>
       <c r="B136" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,34 +14529,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>614957</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560564</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737787</v>
+        <v>131738991</v>
       </c>
       <c r="B30" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,38 +3735,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615336</v>
+        <v>614921</v>
       </c>
       <c r="R30" t="n">
-        <v>6560522</v>
+        <v>6560577</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,17 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737651</v>
+        <v>131739043</v>
       </c>
       <c r="B31" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,34 +3836,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615311</v>
+        <v>614985</v>
       </c>
       <c r="R31" t="n">
-        <v>6560742</v>
+        <v>6560565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,12 +3890,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,10 +3926,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737785</v>
+        <v>131739007</v>
       </c>
       <c r="B32" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,38 +3937,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615314</v>
+        <v>614970</v>
       </c>
       <c r="R32" t="n">
-        <v>6560513</v>
+        <v>6560560</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4004,17 +3991,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4027,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737784</v>
+        <v>131737787</v>
       </c>
       <c r="B33" t="n">
         <v>93164</v>
@@ -4075,7 +4057,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4084,10 +4066,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615291</v>
+        <v>615336</v>
       </c>
       <c r="R33" t="n">
-        <v>6560497</v>
+        <v>6560522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,7 +4106,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4155,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131739007</v>
+        <v>131737651</v>
       </c>
       <c r="B34" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,34 +4148,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614970</v>
+        <v>615311</v>
       </c>
       <c r="R34" t="n">
-        <v>6560560</v>
+        <v>6560742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4238,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131738991</v>
+        <v>131737785</v>
       </c>
       <c r="B35" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,34 +4249,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614921</v>
+        <v>615314</v>
       </c>
       <c r="R35" t="n">
-        <v>6560577</v>
+        <v>6560513</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4307,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739043</v>
+        <v>131737784</v>
       </c>
       <c r="B36" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,34 +4359,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614985</v>
+        <v>615291</v>
       </c>
       <c r="R36" t="n">
-        <v>6560565</v>
+        <v>6560497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4417,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -7093,7 +7093,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739005</v>
+        <v>131739008</v>
       </c>
       <c r="B63" t="n">
         <v>79885</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614968</v>
+        <v>614995</v>
       </c>
       <c r="R63" t="n">
-        <v>6560572</v>
+        <v>6560547</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739008</v>
+        <v>131739005</v>
       </c>
       <c r="B64" t="n">
         <v>79885</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614995</v>
+        <v>614968</v>
       </c>
       <c r="R64" t="n">
-        <v>6560547</v>
+        <v>6560572</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8210,32 +8210,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131737924</v>
       </c>
       <c r="B74" t="n">
-        <v>93164</v>
+        <v>8454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>615091</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560504</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,7 +8311,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>131737644</v>
       </c>
       <c r="B75" t="n">
         <v>93164</v>
@@ -8342,14 +8342,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>615331</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560676</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131737639</v>
       </c>
       <c r="B76" t="n">
         <v>93164</v>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>614942</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560579</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738989</v>
+        <v>131737668</v>
       </c>
       <c r="B77" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614945</v>
+        <v>614990</v>
       </c>
       <c r="R77" t="n">
-        <v>6560637</v>
+        <v>6560601</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739041</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
         <v>79885</v>
@@ -8645,14 +8645,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615269</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,7 +8715,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739011</v>
+        <v>131739041</v>
       </c>
       <c r="B79" t="n">
         <v>79885</v>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615080</v>
+        <v>615269</v>
       </c>
       <c r="R79" t="n">
-        <v>6560512</v>
+        <v>6560500</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737924</v>
+        <v>131739011</v>
       </c>
       <c r="B80" t="n">
-        <v>8454</v>
+        <v>79885</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615091</v>
+        <v>615080</v>
       </c>
       <c r="R80" t="n">
-        <v>6560504</v>
+        <v>6560512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737625</v>
+        <v>131737619</v>
       </c>
       <c r="B100" t="n">
         <v>93164</v>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614918</v>
+        <v>614885</v>
       </c>
       <c r="R100" t="n">
-        <v>6560620</v>
+        <v>6560613</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737645</v>
+        <v>131737625</v>
       </c>
       <c r="B101" t="n">
         <v>93164</v>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615304</v>
+        <v>614918</v>
       </c>
       <c r="R101" t="n">
-        <v>6560686</v>
+        <v>6560620</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737655</v>
+        <v>131737645</v>
       </c>
       <c r="B102" t="n">
         <v>93164</v>
@@ -11087,14 +11087,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615267</v>
+        <v>615304</v>
       </c>
       <c r="R102" t="n">
-        <v>6560777</v>
+        <v>6560686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737636</v>
+        <v>131737655</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614960</v>
+        <v>615267</v>
       </c>
       <c r="R103" t="n">
-        <v>6560601</v>
+        <v>6560777</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737691</v>
+        <v>131737636</v>
       </c>
       <c r="B104" t="n">
         <v>93164</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615367</v>
+        <v>614960</v>
       </c>
       <c r="R104" t="n">
-        <v>6560553</v>
+        <v>6560601</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737664</v>
+        <v>131737691</v>
       </c>
       <c r="B105" t="n">
         <v>93164</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614942</v>
+        <v>615367</v>
       </c>
       <c r="R105" t="n">
-        <v>6560568</v>
+        <v>6560553</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739013</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615376</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560556</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739004</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11592,14 +11592,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614958</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560561</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739001</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
         <v>79885</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614955</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560579</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737619</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614885</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560613</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131736566</v>
+        <v>131740361</v>
       </c>
       <c r="B110" t="n">
-        <v>93142</v>
+        <v>93155</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,38 +11875,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615319</v>
+        <v>615309</v>
       </c>
       <c r="R110" t="n">
-        <v>6560579</v>
+        <v>6560557</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11941,17 +11933,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12391,10 +12379,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93155</v>
+        <v>79885</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12402,19 +12390,23 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12422,10 +12414,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12466,7 +12458,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12489,7 +12480,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738995</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
         <v>79885</v>
@@ -12520,14 +12511,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615323</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560647</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,10 +12581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738990</v>
+        <v>131736566</v>
       </c>
       <c r="B117" t="n">
-        <v>79885</v>
+        <v>93142</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12601,34 +12592,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614930</v>
+        <v>615319</v>
       </c>
       <c r="R117" t="n">
-        <v>6560587</v>
+        <v>6560579</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131739003</v>
       </c>
       <c r="B119" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614959</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560556</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,7 +12893,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131737665</v>
       </c>
       <c r="B120" t="n">
         <v>93164</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614993</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739003</v>
+        <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614959</v>
+        <v>614972</v>
       </c>
       <c r="R121" t="n">
-        <v>6560556</v>
+        <v>6560590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131738991</v>
+        <v>131737787</v>
       </c>
       <c r="B30" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,34 +3735,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614921</v>
+        <v>615336</v>
       </c>
       <c r="R30" t="n">
-        <v>6560577</v>
+        <v>6560522</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,12 +3793,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3834,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131739043</v>
+        <v>131737651</v>
       </c>
       <c r="B31" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,34 +3845,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614985</v>
+        <v>615311</v>
       </c>
       <c r="R31" t="n">
-        <v>6560565</v>
+        <v>6560742</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,12 +3899,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131739007</v>
+        <v>131737785</v>
       </c>
       <c r="B32" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3937,34 +3946,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614970</v>
+        <v>615314</v>
       </c>
       <c r="R32" t="n">
-        <v>6560560</v>
+        <v>6560513</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,12 +4004,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4027,7 +4045,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737787</v>
+        <v>131737784</v>
       </c>
       <c r="B33" t="n">
         <v>93164</v>
@@ -4057,7 +4075,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4066,10 +4084,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615336</v>
+        <v>615291</v>
       </c>
       <c r="R33" t="n">
-        <v>6560522</v>
+        <v>6560497</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,7 +4124,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,10 +4155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737651</v>
+        <v>131739007</v>
       </c>
       <c r="B34" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,34 +4166,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615311</v>
+        <v>614970</v>
       </c>
       <c r="R34" t="n">
-        <v>6560742</v>
+        <v>6560560</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737785</v>
+        <v>131738991</v>
       </c>
       <c r="B35" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,38 +4267,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615314</v>
+        <v>614921</v>
       </c>
       <c r="R35" t="n">
-        <v>6560513</v>
+        <v>6560577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4307,17 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4348,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737784</v>
+        <v>131739043</v>
       </c>
       <c r="B36" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,38 +4368,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>615291</v>
+        <v>614985</v>
       </c>
       <c r="R36" t="n">
-        <v>6560497</v>
+        <v>6560565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4417,17 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,7 +4458,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737672</v>
+        <v>131737662</v>
       </c>
       <c r="B37" t="n">
         <v>93164</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614950</v>
+        <v>615040</v>
       </c>
       <c r="R37" t="n">
-        <v>6560576</v>
+        <v>6560530</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737786</v>
+        <v>131737640</v>
       </c>
       <c r="B38" t="n">
         <v>93164</v>
@@ -4587,21 +4587,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615335</v>
+        <v>614934</v>
       </c>
       <c r="R38" t="n">
-        <v>6560536</v>
+        <v>6560578</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,17 +4624,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,7 +4660,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737620</v>
+        <v>131737685</v>
       </c>
       <c r="B39" t="n">
         <v>93164</v>
@@ -4700,14 +4691,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614896</v>
+        <v>615324</v>
       </c>
       <c r="R39" t="n">
-        <v>6560613</v>
+        <v>6560604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4770,7 +4761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737634</v>
+        <v>131737672</v>
       </c>
       <c r="B40" t="n">
         <v>93164</v>
@@ -4805,10 +4796,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614954</v>
+        <v>614950</v>
       </c>
       <c r="R40" t="n">
-        <v>6560617</v>
+        <v>6560576</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,7 +4862,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737669</v>
+        <v>131737786</v>
       </c>
       <c r="B41" t="n">
         <v>93164</v>
@@ -4899,17 +4890,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614973</v>
+        <v>615335</v>
       </c>
       <c r="R41" t="n">
-        <v>6560600</v>
+        <v>6560536</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,12 +4931,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,7 +4972,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737660</v>
+        <v>131737620</v>
       </c>
       <c r="B42" t="n">
         <v>93164</v>
@@ -5003,14 +5003,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>615278</v>
+        <v>614896</v>
       </c>
       <c r="R42" t="n">
-        <v>6560662</v>
+        <v>6560613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737662</v>
+        <v>131737634</v>
       </c>
       <c r="B43" t="n">
         <v>93164</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615040</v>
+        <v>614954</v>
       </c>
       <c r="R43" t="n">
-        <v>6560530</v>
+        <v>6560617</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737640</v>
+        <v>131737669</v>
       </c>
       <c r="B44" t="n">
         <v>93164</v>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614934</v>
+        <v>614973</v>
       </c>
       <c r="R44" t="n">
-        <v>6560578</v>
+        <v>6560600</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737685</v>
+        <v>131737660</v>
       </c>
       <c r="B45" t="n">
         <v>93164</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615324</v>
+        <v>615278</v>
       </c>
       <c r="R45" t="n">
-        <v>6560604</v>
+        <v>6560662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739008</v>
+        <v>131739005</v>
       </c>
       <c r="B63" t="n">
         <v>79885</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614995</v>
+        <v>614968</v>
       </c>
       <c r="R63" t="n">
-        <v>6560547</v>
+        <v>6560572</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739005</v>
+        <v>131739008</v>
       </c>
       <c r="B64" t="n">
         <v>79885</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614968</v>
+        <v>614995</v>
       </c>
       <c r="R64" t="n">
-        <v>6560572</v>
+        <v>6560547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8210,32 +8210,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737924</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>8454</v>
+        <v>93164</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615091</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560504</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,7 +8311,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737644</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
         <v>93164</v>
@@ -8342,14 +8342,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615331</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560676</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737639</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
         <v>93164</v>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614942</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560579</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737668</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614990</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560601</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
         <v>79885</v>
@@ -8645,14 +8645,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,7 +8715,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739041</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
         <v>79885</v>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615269</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131739011</v>
+        <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>79885</v>
+        <v>8454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615080</v>
+        <v>615091</v>
       </c>
       <c r="R80" t="n">
-        <v>6560512</v>
+        <v>6560504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737619</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
         <v>93164</v>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614885</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560613</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737625</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
         <v>93164</v>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614918</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560620</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737645</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
         <v>93164</v>
@@ -11087,14 +11087,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615304</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560686</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737655</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615267</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560777</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737636</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
         <v>93164</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614960</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560601</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737691</v>
+        <v>131737664</v>
       </c>
       <c r="B105" t="n">
         <v>93164</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615367</v>
+        <v>614942</v>
       </c>
       <c r="R105" t="n">
-        <v>6560553</v>
+        <v>6560568</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131739013</v>
       </c>
       <c r="B106" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>615376</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560556</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739013</v>
+        <v>131739004</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11592,14 +11592,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615376</v>
+        <v>614958</v>
       </c>
       <c r="R107" t="n">
-        <v>6560556</v>
+        <v>6560561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739004</v>
+        <v>131739001</v>
       </c>
       <c r="B108" t="n">
         <v>79885</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614958</v>
+        <v>614955</v>
       </c>
       <c r="R108" t="n">
-        <v>6560561</v>
+        <v>6560579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131737619</v>
       </c>
       <c r="B109" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>614885</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560613</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740361</v>
+        <v>131736566</v>
       </c>
       <c r="B110" t="n">
-        <v>93155</v>
+        <v>93142</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,30 +11875,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615309</v>
+        <v>615319</v>
       </c>
       <c r="R110" t="n">
-        <v>6560557</v>
+        <v>6560579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11933,13 +11941,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12379,10 +12391,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131740361</v>
       </c>
       <c r="B115" t="n">
-        <v>79885</v>
+        <v>93155</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12390,23 +12402,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12414,10 +12422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>615309</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560557</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12458,6 +12466,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12480,7 +12489,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131738995</v>
       </c>
       <c r="B116" t="n">
         <v>79885</v>
@@ -12511,14 +12520,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>615323</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560647</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12581,10 +12590,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131736566</v>
+        <v>131738990</v>
       </c>
       <c r="B117" t="n">
-        <v>93142</v>
+        <v>79885</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12592,38 +12601,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>615319</v>
+        <v>614930</v>
       </c>
       <c r="R117" t="n">
-        <v>6560579</v>
+        <v>6560587</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12656,11 +12661,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737787</v>
+        <v>131738991</v>
       </c>
       <c r="B30" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,38 +3735,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615336</v>
+        <v>614921</v>
       </c>
       <c r="R30" t="n">
-        <v>6560522</v>
+        <v>6560577</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,17 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737651</v>
+        <v>131739043</v>
       </c>
       <c r="B31" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,34 +3836,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615311</v>
+        <v>614985</v>
       </c>
       <c r="R31" t="n">
-        <v>6560742</v>
+        <v>6560565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,12 +3890,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,10 +3926,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737785</v>
+        <v>131739007</v>
       </c>
       <c r="B32" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,38 +3937,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615314</v>
+        <v>614970</v>
       </c>
       <c r="R32" t="n">
-        <v>6560513</v>
+        <v>6560560</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4004,17 +3991,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4027,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737784</v>
+        <v>131737787</v>
       </c>
       <c r="B33" t="n">
         <v>93164</v>
@@ -4075,7 +4057,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4084,10 +4066,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615291</v>
+        <v>615336</v>
       </c>
       <c r="R33" t="n">
-        <v>6560497</v>
+        <v>6560522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,7 +4106,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4155,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131739007</v>
+        <v>131737651</v>
       </c>
       <c r="B34" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,34 +4148,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614970</v>
+        <v>615311</v>
       </c>
       <c r="R34" t="n">
-        <v>6560560</v>
+        <v>6560742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4238,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131738991</v>
+        <v>131737785</v>
       </c>
       <c r="B35" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,34 +4249,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614921</v>
+        <v>615314</v>
       </c>
       <c r="R35" t="n">
-        <v>6560577</v>
+        <v>6560513</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4307,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739043</v>
+        <v>131737784</v>
       </c>
       <c r="B36" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,34 +4359,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614985</v>
+        <v>615291</v>
       </c>
       <c r="R36" t="n">
-        <v>6560565</v>
+        <v>6560497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4417,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -10854,7 +10854,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737625</v>
+        <v>131737619</v>
       </c>
       <c r="B100" t="n">
         <v>93164</v>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614918</v>
+        <v>614885</v>
       </c>
       <c r="R100" t="n">
-        <v>6560620</v>
+        <v>6560613</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737645</v>
+        <v>131737625</v>
       </c>
       <c r="B101" t="n">
         <v>93164</v>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615304</v>
+        <v>614918</v>
       </c>
       <c r="R101" t="n">
-        <v>6560686</v>
+        <v>6560620</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737655</v>
+        <v>131737645</v>
       </c>
       <c r="B102" t="n">
         <v>93164</v>
@@ -11087,14 +11087,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615267</v>
+        <v>615304</v>
       </c>
       <c r="R102" t="n">
-        <v>6560777</v>
+        <v>6560686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737636</v>
+        <v>131737655</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614960</v>
+        <v>615267</v>
       </c>
       <c r="R103" t="n">
-        <v>6560601</v>
+        <v>6560777</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737691</v>
+        <v>131737636</v>
       </c>
       <c r="B104" t="n">
         <v>93164</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615367</v>
+        <v>614960</v>
       </c>
       <c r="R104" t="n">
-        <v>6560553</v>
+        <v>6560601</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737664</v>
+        <v>131737691</v>
       </c>
       <c r="B105" t="n">
         <v>93164</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614942</v>
+        <v>615367</v>
       </c>
       <c r="R105" t="n">
-        <v>6560568</v>
+        <v>6560553</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739013</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615376</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560556</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739004</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11592,14 +11592,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614958</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560561</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739001</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
         <v>79885</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614955</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560579</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737619</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614885</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560613</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131736566</v>
+        <v>131740361</v>
       </c>
       <c r="B110" t="n">
-        <v>93142</v>
+        <v>93155</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,38 +11875,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615319</v>
+        <v>615309</v>
       </c>
       <c r="R110" t="n">
-        <v>6560579</v>
+        <v>6560557</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11941,17 +11933,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12391,10 +12379,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93155</v>
+        <v>79885</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12402,19 +12390,23 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12422,10 +12414,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12466,7 +12458,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12489,7 +12480,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738995</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
         <v>79885</v>
@@ -12520,14 +12511,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615323</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560647</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,10 +12581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738990</v>
+        <v>131736566</v>
       </c>
       <c r="B117" t="n">
-        <v>79885</v>
+        <v>93142</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12601,34 +12592,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614930</v>
+        <v>615319</v>
       </c>
       <c r="R117" t="n">
-        <v>6560587</v>
+        <v>6560579</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131739003</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614959</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560556</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,7 +12893,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
         <v>93164</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737670</v>
+        <v>131739003</v>
       </c>
       <c r="B121" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614972</v>
+        <v>614959</v>
       </c>
       <c r="R121" t="n">
-        <v>6560590</v>
+        <v>6560556</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -4458,7 +4458,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737662</v>
+        <v>131737672</v>
       </c>
       <c r="B37" t="n">
         <v>93164</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>615040</v>
+        <v>614950</v>
       </c>
       <c r="R37" t="n">
-        <v>6560530</v>
+        <v>6560576</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737640</v>
+        <v>131737786</v>
       </c>
       <c r="B38" t="n">
         <v>93164</v>
@@ -4587,17 +4587,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614934</v>
+        <v>615335</v>
       </c>
       <c r="R38" t="n">
-        <v>6560578</v>
+        <v>6560536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4624,12 +4628,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4660,7 +4669,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737685</v>
+        <v>131737620</v>
       </c>
       <c r="B39" t="n">
         <v>93164</v>
@@ -4691,14 +4700,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615324</v>
+        <v>614896</v>
       </c>
       <c r="R39" t="n">
-        <v>6560604</v>
+        <v>6560613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,7 +4770,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737672</v>
+        <v>131737634</v>
       </c>
       <c r="B40" t="n">
         <v>93164</v>
@@ -4796,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614950</v>
+        <v>614954</v>
       </c>
       <c r="R40" t="n">
-        <v>6560576</v>
+        <v>6560617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4862,7 +4871,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737786</v>
+        <v>131737669</v>
       </c>
       <c r="B41" t="n">
         <v>93164</v>
@@ -4890,21 +4899,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>615335</v>
+        <v>614973</v>
       </c>
       <c r="R41" t="n">
-        <v>6560536</v>
+        <v>6560600</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,17 +4936,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,7 +4972,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737620</v>
+        <v>131737660</v>
       </c>
       <c r="B42" t="n">
         <v>93164</v>
@@ -5003,14 +5003,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614896</v>
+        <v>615278</v>
       </c>
       <c r="R42" t="n">
-        <v>6560613</v>
+        <v>6560662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737634</v>
+        <v>131737662</v>
       </c>
       <c r="B43" t="n">
         <v>93164</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614954</v>
+        <v>615040</v>
       </c>
       <c r="R43" t="n">
-        <v>6560617</v>
+        <v>6560530</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737669</v>
+        <v>131737640</v>
       </c>
       <c r="B44" t="n">
         <v>93164</v>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614973</v>
+        <v>614934</v>
       </c>
       <c r="R44" t="n">
-        <v>6560600</v>
+        <v>6560578</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737660</v>
+        <v>131737685</v>
       </c>
       <c r="B45" t="n">
         <v>93164</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615278</v>
+        <v>615324</v>
       </c>
       <c r="R45" t="n">
-        <v>6560662</v>
+        <v>6560604</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -10854,7 +10854,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737619</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
         <v>93164</v>
@@ -10889,10 +10889,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614885</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560613</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737625</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
         <v>93164</v>
@@ -10986,14 +10986,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614918</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560620</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737645</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
         <v>93164</v>
@@ -11087,14 +11087,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615304</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560686</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737655</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
         <v>93164</v>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615267</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560777</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737636</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
         <v>93164</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614960</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560601</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737691</v>
+        <v>131737664</v>
       </c>
       <c r="B105" t="n">
         <v>93164</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615367</v>
+        <v>614942</v>
       </c>
       <c r="R105" t="n">
-        <v>6560553</v>
+        <v>6560568</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131739013</v>
       </c>
       <c r="B106" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>615376</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560556</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739013</v>
+        <v>131739004</v>
       </c>
       <c r="B107" t="n">
         <v>79885</v>
@@ -11592,14 +11592,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615376</v>
+        <v>614958</v>
       </c>
       <c r="R107" t="n">
-        <v>6560556</v>
+        <v>6560561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739004</v>
+        <v>131739001</v>
       </c>
       <c r="B108" t="n">
         <v>79885</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614958</v>
+        <v>614955</v>
       </c>
       <c r="R108" t="n">
-        <v>6560561</v>
+        <v>6560579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131737619</v>
       </c>
       <c r="B109" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>614885</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560613</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131739003</v>
       </c>
       <c r="B119" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614959</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560556</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,7 +12893,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131737665</v>
       </c>
       <c r="B120" t="n">
         <v>93164</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614993</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739003</v>
+        <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614959</v>
+        <v>614972</v>
       </c>
       <c r="R121" t="n">
-        <v>6560556</v>
+        <v>6560590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737682</v>
+        <v>131737673</v>
       </c>
       <c r="B132" t="n">
         <v>93164</v>
@@ -14145,14 +14145,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615350</v>
+        <v>614957</v>
       </c>
       <c r="R132" t="n">
-        <v>6560611</v>
+        <v>6560564</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737663</v>
+        <v>131737682</v>
       </c>
       <c r="B133" t="n">
         <v>93164</v>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615046</v>
+        <v>615350</v>
       </c>
       <c r="R133" t="n">
-        <v>6560537</v>
+        <v>6560611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737661</v>
+        <v>131737663</v>
       </c>
       <c r="B134" t="n">
         <v>93164</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615060</v>
+        <v>615046</v>
       </c>
       <c r="R134" t="n">
-        <v>6560565</v>
+        <v>6560537</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131738996</v>
+        <v>131737661</v>
       </c>
       <c r="B135" t="n">
-        <v>79885</v>
+        <v>93164</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14428,34 +14428,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615290</v>
+        <v>615060</v>
       </c>
       <c r="R135" t="n">
-        <v>6560715</v>
+        <v>6560565</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737673</v>
+        <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>93164</v>
+        <v>79885</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,34 +14529,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614957</v>
+        <v>615290</v>
       </c>
       <c r="R136" t="n">
-        <v>6560564</v>
+        <v>6560715</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2515,7 +2515,7 @@
         <v>131737671</v>
       </c>
       <c r="B18" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737650</v>
+        <v>131737631</v>
       </c>
       <c r="B19" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,14 +2644,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615325</v>
+        <v>614937</v>
       </c>
       <c r="R19" t="n">
-        <v>6560719</v>
+        <v>6560625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737654</v>
+        <v>131737632</v>
       </c>
       <c r="B20" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615282</v>
+        <v>614949</v>
       </c>
       <c r="R20" t="n">
-        <v>6560780</v>
+        <v>6560635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737631</v>
+        <v>131737647</v>
       </c>
       <c r="B21" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,14 +2846,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614937</v>
+        <v>615295</v>
       </c>
       <c r="R21" t="n">
-        <v>6560625</v>
+        <v>6560678</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737632</v>
+        <v>131737637</v>
       </c>
       <c r="B22" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>614949</v>
       </c>
       <c r="R22" t="n">
-        <v>6560635</v>
+        <v>6560610</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737647</v>
+        <v>131737650</v>
       </c>
       <c r="B23" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615295</v>
+        <v>615325</v>
       </c>
       <c r="R23" t="n">
-        <v>6560678</v>
+        <v>6560719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737637</v>
+        <v>131737654</v>
       </c>
       <c r="B24" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614949</v>
+        <v>615282</v>
       </c>
       <c r="R24" t="n">
-        <v>6560610</v>
+        <v>6560780</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
         <v>131737614</v>
       </c>
       <c r="B25" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131738992</v>
+        <v>131739009</v>
       </c>
       <c r="B26" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3351,14 +3351,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614903</v>
+        <v>614998</v>
       </c>
       <c r="R26" t="n">
-        <v>6560580</v>
+        <v>6560540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131739009</v>
+        <v>131739006</v>
       </c>
       <c r="B27" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614998</v>
+        <v>614970</v>
       </c>
       <c r="R27" t="n">
-        <v>6560540</v>
+        <v>6560568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131739006</v>
+        <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614970</v>
+        <v>614903</v>
       </c>
       <c r="R28" t="n">
-        <v>6560568</v>
+        <v>6560580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737629</v>
+        <v>131738991</v>
       </c>
       <c r="B29" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,34 +3634,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614941</v>
+        <v>614921</v>
       </c>
       <c r="R29" t="n">
-        <v>6560607</v>
+        <v>6560577</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131738991</v>
+        <v>131739043</v>
       </c>
       <c r="B30" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3755,14 +3755,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614921</v>
+        <v>614985</v>
       </c>
       <c r="R30" t="n">
-        <v>6560577</v>
+        <v>6560565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131739043</v>
+        <v>131739007</v>
       </c>
       <c r="B31" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614985</v>
+        <v>614970</v>
       </c>
       <c r="R31" t="n">
-        <v>6560565</v>
+        <v>6560560</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,10 +3926,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131739007</v>
+        <v>131737787</v>
       </c>
       <c r="B32" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3937,34 +3937,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614970</v>
+        <v>615336</v>
       </c>
       <c r="R32" t="n">
-        <v>6560560</v>
+        <v>6560522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,12 +3995,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4027,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737787</v>
+        <v>131737651</v>
       </c>
       <c r="B33" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,21 +4064,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615336</v>
+        <v>615311</v>
       </c>
       <c r="R33" t="n">
-        <v>6560522</v>
+        <v>6560742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4096,17 +4101,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737651</v>
+        <v>131737785</v>
       </c>
       <c r="B34" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,17 +4165,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615311</v>
+        <v>615314</v>
       </c>
       <c r="R34" t="n">
-        <v>6560742</v>
+        <v>6560513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4202,12 +4206,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,10 +4247,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737785</v>
+        <v>131737784</v>
       </c>
       <c r="B35" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4268,7 +4277,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4277,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615314</v>
+        <v>615291</v>
       </c>
       <c r="R35" t="n">
-        <v>6560513</v>
+        <v>6560497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4317,7 +4326,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4348,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737784</v>
+        <v>131737629</v>
       </c>
       <c r="B36" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4376,21 +4385,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>615291</v>
+        <v>614941</v>
       </c>
       <c r="R36" t="n">
-        <v>6560497</v>
+        <v>6560607</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4417,17 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737672</v>
+        <v>131737685</v>
       </c>
       <c r="B37" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,14 +4489,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614950</v>
+        <v>615324</v>
       </c>
       <c r="R37" t="n">
-        <v>6560576</v>
+        <v>6560604</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,10 +4559,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737786</v>
+        <v>131737672</v>
       </c>
       <c r="B38" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4587,21 +4587,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615335</v>
+        <v>614950</v>
       </c>
       <c r="R38" t="n">
-        <v>6560536</v>
+        <v>6560576</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,17 +4624,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,10 +4660,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737620</v>
+        <v>131737786</v>
       </c>
       <c r="B39" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4697,17 +4688,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614896</v>
+        <v>615335</v>
       </c>
       <c r="R39" t="n">
-        <v>6560613</v>
+        <v>6560536</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4734,12 +4729,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737634</v>
+        <v>131737662</v>
       </c>
       <c r="B40" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614954</v>
+        <v>615040</v>
       </c>
       <c r="R40" t="n">
-        <v>6560617</v>
+        <v>6560530</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737669</v>
+        <v>131737620</v>
       </c>
       <c r="B41" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4902,14 +4902,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614973</v>
+        <v>614896</v>
       </c>
       <c r="R41" t="n">
-        <v>6560600</v>
+        <v>6560613</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737660</v>
+        <v>131737634</v>
       </c>
       <c r="B42" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,14 +5003,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>615278</v>
+        <v>614954</v>
       </c>
       <c r="R42" t="n">
-        <v>6560662</v>
+        <v>6560617</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,10 +5073,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737662</v>
+        <v>131737669</v>
       </c>
       <c r="B43" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615040</v>
+        <v>614973</v>
       </c>
       <c r="R43" t="n">
-        <v>6560530</v>
+        <v>6560600</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737640</v>
+        <v>131737660</v>
       </c>
       <c r="B44" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614934</v>
+        <v>615278</v>
       </c>
       <c r="R44" t="n">
-        <v>6560578</v>
+        <v>6560662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737685</v>
+        <v>131737640</v>
       </c>
       <c r="B45" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615324</v>
+        <v>614934</v>
       </c>
       <c r="R45" t="n">
-        <v>6560604</v>
+        <v>6560578</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5379,7 +5379,7 @@
         <v>131739002</v>
       </c>
       <c r="B46" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>131737635</v>
       </c>
       <c r="B47" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131737618</v>
       </c>
       <c r="B48" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>615022</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737677</v>
+        <v>131737616</v>
       </c>
       <c r="B50" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5811,14 +5811,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615064</v>
+        <v>614862</v>
       </c>
       <c r="R50" t="n">
-        <v>6560525</v>
+        <v>6560592</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,10 +5881,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737684</v>
+        <v>131737677</v>
       </c>
       <c r="B51" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615333</v>
+        <v>615064</v>
       </c>
       <c r="R51" t="n">
-        <v>6560608</v>
+        <v>6560525</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131739012</v>
+        <v>131737684</v>
       </c>
       <c r="B52" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,34 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615022</v>
+        <v>615333</v>
       </c>
       <c r="R52" t="n">
-        <v>6560527</v>
+        <v>6560608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6086,7 +6086,7 @@
         <v>131737925</v>
       </c>
       <c r="B53" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131737675</v>
       </c>
       <c r="B54" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>131737617</v>
       </c>
       <c r="B55" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737652</v>
+        <v>131738993</v>
       </c>
       <c r="B60" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615301</v>
+        <v>614904</v>
       </c>
       <c r="R60" t="n">
-        <v>6560755</v>
+        <v>6560578</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737688</v>
+        <v>131739008</v>
       </c>
       <c r="B61" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,34 +6902,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615310</v>
+        <v>614995</v>
       </c>
       <c r="R61" t="n">
-        <v>6560543</v>
+        <v>6560547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131738993</v>
+        <v>131739005</v>
       </c>
       <c r="B62" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7023,14 +7023,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614904</v>
+        <v>614968</v>
       </c>
       <c r="R62" t="n">
-        <v>6560578</v>
+        <v>6560572</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739005</v>
+        <v>131737652</v>
       </c>
       <c r="B63" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614968</v>
+        <v>615301</v>
       </c>
       <c r="R63" t="n">
-        <v>6560572</v>
+        <v>6560755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739008</v>
+        <v>131737688</v>
       </c>
       <c r="B64" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7205,34 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614995</v>
+        <v>615310</v>
       </c>
       <c r="R64" t="n">
-        <v>6560547</v>
+        <v>6560543</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7298,7 +7298,7 @@
         <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93142</v>
+        <v>93145</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>131737686</v>
       </c>
       <c r="B66" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131740360</v>
+        <v>131739010</v>
       </c>
       <c r="B68" t="n">
-        <v>93155</v>
+        <v>79888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,34 +7609,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615296</v>
+        <v>615012</v>
       </c>
       <c r="R68" t="n">
-        <v>6560688</v>
+        <v>6560549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7671,18 +7671,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7705,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737667</v>
+        <v>131739015</v>
       </c>
       <c r="B69" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7716,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614991</v>
+        <v>615373</v>
       </c>
       <c r="R69" t="n">
-        <v>6560587</v>
+        <v>6560555</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7806,10 +7800,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737638</v>
+        <v>131737667</v>
       </c>
       <c r="B70" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7841,10 +7835,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614943</v>
+        <v>614991</v>
       </c>
       <c r="R70" t="n">
-        <v>6560591</v>
+        <v>6560587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,10 +7901,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737658</v>
+        <v>131740360</v>
       </c>
       <c r="B71" t="n">
-        <v>93164</v>
+        <v>93158</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7918,34 +7912,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615282</v>
+        <v>615296</v>
       </c>
       <c r="R71" t="n">
-        <v>6560684</v>
+        <v>6560688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7980,12 +7974,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739010</v>
+        <v>131737638</v>
       </c>
       <c r="B72" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>615012</v>
+        <v>614943</v>
       </c>
       <c r="R72" t="n">
-        <v>6560549</v>
+        <v>6560591</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131739015</v>
+        <v>131737658</v>
       </c>
       <c r="B73" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615373</v>
+        <v>615282</v>
       </c>
       <c r="R73" t="n">
-        <v>6560555</v>
+        <v>6560684</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131738989</v>
       </c>
       <c r="B74" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>614945</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560637</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>131739041</v>
       </c>
       <c r="B75" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>615269</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560500</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131739011</v>
       </c>
       <c r="B76" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>615080</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560512</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738989</v>
+        <v>131737644</v>
       </c>
       <c r="B77" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,34 +8524,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614945</v>
+        <v>615331</v>
       </c>
       <c r="R77" t="n">
-        <v>6560637</v>
+        <v>6560676</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B78" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739011</v>
+        <v>131737668</v>
       </c>
       <c r="B79" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615080</v>
+        <v>614990</v>
       </c>
       <c r="R79" t="n">
-        <v>6560512</v>
+        <v>6560601</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8819,7 +8819,7 @@
         <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>131737674</v>
       </c>
       <c r="B81" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>131737782</v>
       </c>
       <c r="B82" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>131737653</v>
       </c>
       <c r="B84" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>131737624</v>
       </c>
       <c r="B85" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737626</v>
+        <v>131738988</v>
       </c>
       <c r="B86" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614911</v>
+        <v>614862</v>
       </c>
       <c r="R86" t="n">
-        <v>6560610</v>
+        <v>6560592</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737642</v>
+        <v>131737626</v>
       </c>
       <c r="B87" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614884</v>
+        <v>614911</v>
       </c>
       <c r="R87" t="n">
-        <v>6560568</v>
+        <v>6560610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737687</v>
+        <v>131737642</v>
       </c>
       <c r="B88" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>615322</v>
+        <v>614884</v>
       </c>
       <c r="R88" t="n">
-        <v>6560582</v>
+        <v>6560568</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131738988</v>
+        <v>131737687</v>
       </c>
       <c r="B89" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9745,34 +9745,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614862</v>
+        <v>615322</v>
       </c>
       <c r="R89" t="n">
-        <v>6560592</v>
+        <v>6560582</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737783</v>
+        <v>131738998</v>
       </c>
       <c r="B90" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,38 +9846,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615276</v>
+        <v>615020</v>
       </c>
       <c r="R90" t="n">
-        <v>6560495</v>
+        <v>6560533</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9904,17 +9900,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9945,10 +9936,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737641</v>
+        <v>131737783</v>
       </c>
       <c r="B91" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9973,17 +9964,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614893</v>
+        <v>615276</v>
       </c>
       <c r="R91" t="n">
-        <v>6560582</v>
+        <v>6560495</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10010,12 +10005,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10046,10 +10046,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737656</v>
+        <v>131737641</v>
       </c>
       <c r="B92" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10077,14 +10077,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615271</v>
+        <v>614893</v>
       </c>
       <c r="R92" t="n">
-        <v>6560749</v>
+        <v>6560582</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737666</v>
+        <v>131737656</v>
       </c>
       <c r="B93" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614995</v>
+        <v>615271</v>
       </c>
       <c r="R93" t="n">
-        <v>6560571</v>
+        <v>6560749</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737676</v>
+        <v>131737666</v>
       </c>
       <c r="B94" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10279,14 +10279,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615060</v>
+        <v>614995</v>
       </c>
       <c r="R94" t="n">
-        <v>6560536</v>
+        <v>6560571</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10349,10 +10349,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737646</v>
+        <v>131737676</v>
       </c>
       <c r="B95" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615289</v>
+        <v>615060</v>
       </c>
       <c r="R95" t="n">
-        <v>6560695</v>
+        <v>6560536</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737690</v>
+        <v>131737646</v>
       </c>
       <c r="B96" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615387</v>
+        <v>615289</v>
       </c>
       <c r="R96" t="n">
-        <v>6560558</v>
+        <v>6560695</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,10 +10551,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737659</v>
+        <v>131737690</v>
       </c>
       <c r="B97" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615267</v>
+        <v>615387</v>
       </c>
       <c r="R97" t="n">
-        <v>6560667</v>
+        <v>6560558</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737649</v>
+        <v>131737659</v>
       </c>
       <c r="B98" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615316</v>
+        <v>615267</v>
       </c>
       <c r="R98" t="n">
-        <v>6560709</v>
+        <v>6560667</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131738998</v>
+        <v>131737649</v>
       </c>
       <c r="B99" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615020</v>
+        <v>615316</v>
       </c>
       <c r="R99" t="n">
-        <v>6560533</v>
+        <v>6560709</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737625</v>
+        <v>131739013</v>
       </c>
       <c r="B100" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614918</v>
+        <v>615376</v>
       </c>
       <c r="R100" t="n">
-        <v>6560620</v>
+        <v>6560556</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737645</v>
+        <v>131739004</v>
       </c>
       <c r="B101" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615304</v>
+        <v>614958</v>
       </c>
       <c r="R101" t="n">
-        <v>6560686</v>
+        <v>6560561</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737655</v>
+        <v>131739001</v>
       </c>
       <c r="B102" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615267</v>
+        <v>614955</v>
       </c>
       <c r="R102" t="n">
-        <v>6560777</v>
+        <v>6560579</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737636</v>
+        <v>131737625</v>
       </c>
       <c r="B103" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614960</v>
+        <v>614918</v>
       </c>
       <c r="R103" t="n">
-        <v>6560601</v>
+        <v>6560620</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737691</v>
+        <v>131737645</v>
       </c>
       <c r="B104" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615367</v>
+        <v>615304</v>
       </c>
       <c r="R104" t="n">
-        <v>6560553</v>
+        <v>6560686</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737664</v>
+        <v>131737655</v>
       </c>
       <c r="B105" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614942</v>
+        <v>615267</v>
       </c>
       <c r="R105" t="n">
-        <v>6560568</v>
+        <v>6560777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739013</v>
+        <v>131737636</v>
       </c>
       <c r="B106" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615376</v>
+        <v>614960</v>
       </c>
       <c r="R106" t="n">
-        <v>6560556</v>
+        <v>6560601</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739004</v>
+        <v>131737691</v>
       </c>
       <c r="B107" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,34 +11572,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614958</v>
+        <v>615367</v>
       </c>
       <c r="R107" t="n">
-        <v>6560561</v>
+        <v>6560553</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739001</v>
+        <v>131737664</v>
       </c>
       <c r="B108" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614955</v>
+        <v>614942</v>
       </c>
       <c r="R108" t="n">
-        <v>6560579</v>
+        <v>6560568</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11766,7 +11766,7 @@
         <v>131737619</v>
       </c>
       <c r="B109" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B110" t="n">
-        <v>93155</v>
+        <v>79888</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,19 +11875,23 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11895,10 +11899,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R110" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11939,7 +11943,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11962,10 +11965,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737627</v>
+        <v>131738990</v>
       </c>
       <c r="B111" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,21 +11976,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11997,10 +12000,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614921</v>
+        <v>614930</v>
       </c>
       <c r="R111" t="n">
-        <v>6560604</v>
+        <v>6560587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12063,45 +12066,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737648</v>
+        <v>131740030</v>
       </c>
       <c r="B112" t="n">
-        <v>93164</v>
+        <v>57095</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615306</v>
+        <v>614953</v>
       </c>
       <c r="R112" t="n">
-        <v>6560663</v>
+        <v>6560578</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12134,6 +12145,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12164,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737630</v>
+        <v>131736566</v>
       </c>
       <c r="B113" t="n">
-        <v>93164</v>
+        <v>93145</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12175,34 +12191,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614948</v>
+        <v>615319</v>
       </c>
       <c r="R113" t="n">
-        <v>6560611</v>
+        <v>6560579</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12235,6 +12255,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12265,53 +12290,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740030</v>
+        <v>131740361</v>
       </c>
       <c r="B114" t="n">
-        <v>57092</v>
+        <v>93158</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614953</v>
+        <v>615309</v>
       </c>
       <c r="R114" t="n">
-        <v>6560578</v>
+        <v>6560557</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12346,17 +12359,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12379,10 +12388,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131737627</v>
       </c>
       <c r="B115" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12390,34 +12399,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>614921</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560604</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12480,10 +12489,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131737648</v>
       </c>
       <c r="B116" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12491,34 +12500,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>615306</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560663</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12581,10 +12590,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131736566</v>
+        <v>131737630</v>
       </c>
       <c r="B117" t="n">
-        <v>93142</v>
+        <v>93167</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12592,38 +12601,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>615319</v>
+        <v>614948</v>
       </c>
       <c r="R117" t="n">
-        <v>6560579</v>
+        <v>6560611</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12656,11 +12661,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131740081</v>
+        <v>131739003</v>
       </c>
       <c r="B118" t="n">
-        <v>91859</v>
+        <v>79888</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614974</v>
+        <v>614959</v>
       </c>
       <c r="R118" t="n">
-        <v>6560628</v>
+        <v>6560556</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131739003</v>
+        <v>131740081</v>
       </c>
       <c r="B119" t="n">
-        <v>79885</v>
+        <v>91862</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614959</v>
+        <v>614974</v>
       </c>
       <c r="R119" t="n">
-        <v>6560556</v>
+        <v>6560628</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12896,7 +12896,7 @@
         <v>131737665</v>
       </c>
       <c r="B120" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13095,49 +13095,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131735761</v>
+        <v>131738994</v>
       </c>
       <c r="B122" t="n">
-        <v>90603</v>
+        <v>79888</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>615277</v>
+        <v>614890</v>
       </c>
       <c r="R122" t="n">
-        <v>6560691</v>
+        <v>6560564</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13170,11 +13166,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13205,10 +13196,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131738994</v>
+        <v>131739000</v>
       </c>
       <c r="B123" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13240,10 +13231,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614890</v>
+        <v>614941</v>
       </c>
       <c r="R123" t="n">
-        <v>6560564</v>
+        <v>6560553</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13306,45 +13297,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739000</v>
+        <v>131735761</v>
       </c>
       <c r="B124" t="n">
-        <v>79885</v>
+        <v>90606</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614941</v>
+        <v>615277</v>
       </c>
       <c r="R124" t="n">
-        <v>6560553</v>
+        <v>6560691</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13377,6 +13372,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13407,10 +13407,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131739026</v>
+        <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13418,34 +13418,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>615203</v>
+        <v>614898</v>
       </c>
       <c r="R125" t="n">
-        <v>6560503</v>
+        <v>6560601</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13472,12 +13472,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13508,10 +13508,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737622</v>
+        <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13539,14 +13539,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614898</v>
+        <v>615337</v>
       </c>
       <c r="R126" t="n">
-        <v>6560601</v>
+        <v>6560617</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13609,10 +13609,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737683</v>
+        <v>131737678</v>
       </c>
       <c r="B127" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615337</v>
+        <v>615054</v>
       </c>
       <c r="R127" t="n">
-        <v>6560617</v>
+        <v>6560523</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13710,10 +13710,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737678</v>
+        <v>131737681</v>
       </c>
       <c r="B128" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13741,14 +13741,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615054</v>
+        <v>615383</v>
       </c>
       <c r="R128" t="n">
-        <v>6560523</v>
+        <v>6560632</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737681</v>
+        <v>131739026</v>
       </c>
       <c r="B129" t="n">
-        <v>93164</v>
+        <v>79888</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13822,34 +13822,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615383</v>
+        <v>615203</v>
       </c>
       <c r="R129" t="n">
-        <v>6560632</v>
+        <v>6560503</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13876,12 +13876,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13915,7 +13915,7 @@
         <v>131738997</v>
       </c>
       <c r="B130" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B131" t="n">
-        <v>90603</v>
+        <v>79888</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R131" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,45 +14114,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737673</v>
+        <v>131735760</v>
       </c>
       <c r="B132" t="n">
-        <v>93164</v>
+        <v>90606</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>614957</v>
+        <v>615279</v>
       </c>
       <c r="R132" t="n">
-        <v>6560564</v>
+        <v>6560699</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14218,7 +14218,7 @@
         <v>131737682</v>
       </c>
       <c r="B133" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>131737663</v>
       </c>
       <c r="B134" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737661</v>
+        <v>131737673</v>
       </c>
       <c r="B135" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615060</v>
+        <v>614957</v>
       </c>
       <c r="R135" t="n">
-        <v>6560565</v>
+        <v>6560564</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131737661</v>
       </c>
       <c r="B136" t="n">
-        <v>79885</v>
+        <v>93167</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,34 +14529,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>615060</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560565</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2515,7 +2515,7 @@
         <v>131737671</v>
       </c>
       <c r="B18" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>131737631</v>
       </c>
       <c r="B19" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>131737632</v>
       </c>
       <c r="B20" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131737647</v>
       </c>
       <c r="B21" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131737637</v>
       </c>
       <c r="B22" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>131737650</v>
       </c>
       <c r="B23" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>131737654</v>
       </c>
       <c r="B24" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>131737614</v>
       </c>
       <c r="B25" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>131739009</v>
       </c>
       <c r="B26" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>131739006</v>
       </c>
       <c r="B27" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738991</v>
+        <v>131737787</v>
       </c>
       <c r="B29" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,34 +3634,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614921</v>
+        <v>615336</v>
       </c>
       <c r="R29" t="n">
-        <v>6560577</v>
+        <v>6560522</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,12 +3692,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131739043</v>
+        <v>131737651</v>
       </c>
       <c r="B30" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,34 +3744,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614985</v>
+        <v>615311</v>
       </c>
       <c r="R30" t="n">
-        <v>6560565</v>
+        <v>6560742</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,12 +3798,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3834,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131739007</v>
+        <v>131737785</v>
       </c>
       <c r="B31" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,34 +3845,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614970</v>
+        <v>615314</v>
       </c>
       <c r="R31" t="n">
-        <v>6560560</v>
+        <v>6560513</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,12 +3903,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737787</v>
+        <v>131737784</v>
       </c>
       <c r="B32" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3956,7 +3974,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3965,10 +3983,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615336</v>
+        <v>615291</v>
       </c>
       <c r="R32" t="n">
-        <v>6560522</v>
+        <v>6560497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4023,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,10 +4054,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737651</v>
+        <v>131737629</v>
       </c>
       <c r="B33" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,14 +4085,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615311</v>
+        <v>614941</v>
       </c>
       <c r="R33" t="n">
-        <v>6560742</v>
+        <v>6560607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,10 +4155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737785</v>
+        <v>131738991</v>
       </c>
       <c r="B34" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,38 +4166,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615314</v>
+        <v>614921</v>
       </c>
       <c r="R34" t="n">
-        <v>6560513</v>
+        <v>6560577</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,17 +4220,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4247,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737784</v>
+        <v>131739043</v>
       </c>
       <c r="B35" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4258,38 +4267,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615291</v>
+        <v>614985</v>
       </c>
       <c r="R35" t="n">
-        <v>6560497</v>
+        <v>6560565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,17 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737629</v>
+        <v>131739007</v>
       </c>
       <c r="B36" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614941</v>
+        <v>614970</v>
       </c>
       <c r="R36" t="n">
-        <v>6560607</v>
+        <v>6560560</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
         <v>131737685</v>
       </c>
       <c r="B37" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>131737672</v>
       </c>
       <c r="B38" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>131737786</v>
       </c>
       <c r="B39" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>131737662</v>
       </c>
       <c r="B40" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>131737620</v>
       </c>
       <c r="B41" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>131737634</v>
       </c>
       <c r="B42" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>131737669</v>
       </c>
       <c r="B43" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>131737660</v>
       </c>
       <c r="B44" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>131737640</v>
       </c>
       <c r="B45" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739002</v>
+        <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614953</v>
+        <v>614963</v>
       </c>
       <c r="R46" t="n">
-        <v>6560567</v>
+        <v>6560615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B47" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R47" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131737618</v>
+        <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614881</v>
+        <v>614953</v>
       </c>
       <c r="R48" t="n">
-        <v>6560601</v>
+        <v>6560567</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131739012</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615022</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560527</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5811,14 +5811,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,10 +5881,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737677</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615064</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560525</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B52" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,34 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R52" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
         <v>131737675</v>
       </c>
       <c r="B54" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>131737617</v>
       </c>
       <c r="B55" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B60" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R60" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739008</v>
+        <v>131737688</v>
       </c>
       <c r="B61" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,34 +6902,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614995</v>
+        <v>615310</v>
       </c>
       <c r="R61" t="n">
-        <v>6560547</v>
+        <v>6560543</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739005</v>
+        <v>131738993</v>
       </c>
       <c r="B62" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7023,14 +7023,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614968</v>
+        <v>614904</v>
       </c>
       <c r="R62" t="n">
-        <v>6560572</v>
+        <v>6560578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737652</v>
+        <v>131739008</v>
       </c>
       <c r="B63" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615301</v>
+        <v>614995</v>
       </c>
       <c r="R63" t="n">
-        <v>6560755</v>
+        <v>6560547</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737688</v>
+        <v>131739005</v>
       </c>
       <c r="B64" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7205,34 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>615310</v>
+        <v>614968</v>
       </c>
       <c r="R64" t="n">
-        <v>6560543</v>
+        <v>6560572</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131736575</v>
+        <v>131737686</v>
       </c>
       <c r="B65" t="n">
-        <v>93145</v>
+        <v>93172</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7306,21 +7306,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R65" t="n">
-        <v>6560577</v>
+        <v>6560599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,10 +7396,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737686</v>
+        <v>131737643</v>
       </c>
       <c r="B66" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615314</v>
+        <v>615322</v>
       </c>
       <c r="R66" t="n">
-        <v>6560599</v>
+        <v>6560634</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737643</v>
+        <v>131736575</v>
       </c>
       <c r="B67" t="n">
-        <v>93167</v>
+        <v>93150</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615322</v>
+        <v>615336</v>
       </c>
       <c r="R67" t="n">
-        <v>6560634</v>
+        <v>6560577</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131739010</v>
+        <v>131737667</v>
       </c>
       <c r="B68" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,21 +7609,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615012</v>
+        <v>614991</v>
       </c>
       <c r="R68" t="n">
-        <v>6560549</v>
+        <v>6560587</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131739015</v>
+        <v>131740360</v>
       </c>
       <c r="B69" t="n">
-        <v>79888</v>
+        <v>93163</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615373</v>
+        <v>615296</v>
       </c>
       <c r="R69" t="n">
-        <v>6560555</v>
+        <v>6560688</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,12 +7772,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7800,10 +7806,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737667</v>
+        <v>131737638</v>
       </c>
       <c r="B70" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7835,10 +7841,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614991</v>
+        <v>614943</v>
       </c>
       <c r="R70" t="n">
-        <v>6560587</v>
+        <v>6560591</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7901,10 +7907,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131740360</v>
+        <v>131737658</v>
       </c>
       <c r="B71" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7912,34 +7918,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615296</v>
+        <v>615282</v>
       </c>
       <c r="R71" t="n">
-        <v>6560688</v>
+        <v>6560684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7974,18 +7980,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737638</v>
+        <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614943</v>
+        <v>615012</v>
       </c>
       <c r="R72" t="n">
-        <v>6560591</v>
+        <v>6560549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131737658</v>
+        <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615282</v>
+        <v>615373</v>
       </c>
       <c r="R73" t="n">
-        <v>6560684</v>
+        <v>6560555</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131738989</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614945</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560637</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131739011</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615080</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560512</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,32 +8513,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737644</v>
+        <v>131737924</v>
       </c>
       <c r="B77" t="n">
-        <v>93167</v>
+        <v>8455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615331</v>
+        <v>615091</v>
       </c>
       <c r="R77" t="n">
-        <v>6560676</v>
+        <v>6560504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737639</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614942</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560579</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737668</v>
+        <v>131739041</v>
       </c>
       <c r="B79" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614990</v>
+        <v>615269</v>
       </c>
       <c r="R79" t="n">
-        <v>6560601</v>
+        <v>6560500</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737924</v>
+        <v>131739011</v>
       </c>
       <c r="B80" t="n">
-        <v>8455</v>
+        <v>79893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615091</v>
+        <v>615080</v>
       </c>
       <c r="R80" t="n">
-        <v>6560504</v>
+        <v>6560512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>131737674</v>
       </c>
       <c r="B81" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>131737782</v>
       </c>
       <c r="B82" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>131737653</v>
       </c>
       <c r="B84" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>131737624</v>
       </c>
       <c r="B85" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>131738988</v>
       </c>
       <c r="B86" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>131737626</v>
       </c>
       <c r="B87" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>131737642</v>
       </c>
       <c r="B88" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>131737687</v>
       </c>
       <c r="B89" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>131738998</v>
       </c>
       <c r="B90" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>131737783</v>
       </c>
       <c r="B91" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>131737641</v>
       </c>
       <c r="B92" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>131737656</v>
       </c>
       <c r="B93" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>131737666</v>
       </c>
       <c r="B94" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>131737676</v>
       </c>
       <c r="B95" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>131737646</v>
       </c>
       <c r="B96" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>131737690</v>
       </c>
       <c r="B97" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>131737659</v>
       </c>
       <c r="B98" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>131737649</v>
       </c>
       <c r="B99" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739013</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615376</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560556</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739004</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614958</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560561</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739001</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
-        <v>79888</v>
+        <v>93172</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614955</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560579</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737625</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614918</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560620</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737645</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615304</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560686</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737655</v>
+        <v>131737619</v>
       </c>
       <c r="B105" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615267</v>
+        <v>614885</v>
       </c>
       <c r="R105" t="n">
-        <v>6560777</v>
+        <v>6560613</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737636</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614960</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560601</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737664</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614942</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560568</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737619</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614885</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560613</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131738995</v>
+        <v>131736566</v>
       </c>
       <c r="B110" t="n">
-        <v>79888</v>
+        <v>93150</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,34 +11875,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615323</v>
+        <v>615319</v>
       </c>
       <c r="R110" t="n">
-        <v>6560647</v>
+        <v>6560579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11935,6 +11939,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11965,10 +11974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738990</v>
+        <v>131740361</v>
       </c>
       <c r="B111" t="n">
-        <v>79888</v>
+        <v>93163</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11976,34 +11985,30 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614930</v>
+        <v>615309</v>
       </c>
       <c r="R111" t="n">
-        <v>6560587</v>
+        <v>6560557</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12044,6 +12049,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12066,53 +12072,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131740030</v>
+        <v>131737627</v>
       </c>
       <c r="B112" t="n">
-        <v>57095</v>
+        <v>93172</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614953</v>
+        <v>614921</v>
       </c>
       <c r="R112" t="n">
-        <v>6560578</v>
+        <v>6560604</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12145,11 +12143,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12180,10 +12173,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131736566</v>
+        <v>131737648</v>
       </c>
       <c r="B113" t="n">
-        <v>93145</v>
+        <v>93172</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12191,38 +12184,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615319</v>
+        <v>615306</v>
       </c>
       <c r="R113" t="n">
-        <v>6560579</v>
+        <v>6560663</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12255,11 +12244,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12290,10 +12274,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740361</v>
+        <v>131737630</v>
       </c>
       <c r="B114" t="n">
-        <v>93158</v>
+        <v>93172</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12301,30 +12285,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615309</v>
+        <v>614948</v>
       </c>
       <c r="R114" t="n">
-        <v>6560557</v>
+        <v>6560611</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12365,7 +12353,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12388,45 +12375,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737627</v>
+        <v>131740030</v>
       </c>
       <c r="B115" t="n">
-        <v>93167</v>
+        <v>57100</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614921</v>
+        <v>614953</v>
       </c>
       <c r="R115" t="n">
-        <v>6560604</v>
+        <v>6560578</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12459,6 +12454,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12489,10 +12489,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737648</v>
+        <v>131738995</v>
       </c>
       <c r="B116" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12500,21 +12500,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12524,10 +12524,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615306</v>
+        <v>615323</v>
       </c>
       <c r="R116" t="n">
-        <v>6560663</v>
+        <v>6560647</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,10 +12590,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737630</v>
+        <v>131738990</v>
       </c>
       <c r="B117" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12601,34 +12601,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614948</v>
+        <v>614930</v>
       </c>
       <c r="R117" t="n">
-        <v>6560611</v>
+        <v>6560587</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12694,7 +12694,7 @@
         <v>131739003</v>
       </c>
       <c r="B118" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131740081</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
-        <v>91862</v>
+        <v>93172</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614974</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560628</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737670</v>
+        <v>131740081</v>
       </c>
       <c r="B121" t="n">
-        <v>93167</v>
+        <v>91867</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614972</v>
+        <v>614974</v>
       </c>
       <c r="R121" t="n">
-        <v>6560590</v>
+        <v>6560628</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13059,12 +13059,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13095,45 +13095,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131738994</v>
+        <v>131735761</v>
       </c>
       <c r="B122" t="n">
-        <v>79888</v>
+        <v>90611</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614890</v>
+        <v>615277</v>
       </c>
       <c r="R122" t="n">
-        <v>6560564</v>
+        <v>6560691</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13166,6 +13170,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13196,10 +13205,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131739000</v>
+        <v>131738994</v>
       </c>
       <c r="B123" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13231,10 +13240,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614941</v>
+        <v>614890</v>
       </c>
       <c r="R123" t="n">
-        <v>6560553</v>
+        <v>6560564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13297,49 +13306,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131735761</v>
+        <v>131739000</v>
       </c>
       <c r="B124" t="n">
-        <v>90606</v>
+        <v>79893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>615277</v>
+        <v>614941</v>
       </c>
       <c r="R124" t="n">
-        <v>6560691</v>
+        <v>6560553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13372,11 +13377,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13410,7 +13410,7 @@
         <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>131737678</v>
       </c>
       <c r="B127" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>131737681</v>
       </c>
       <c r="B128" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>131739026</v>
       </c>
       <c r="B129" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>131738997</v>
       </c>
       <c r="B130" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131738996</v>
+        <v>131735760</v>
       </c>
       <c r="B131" t="n">
-        <v>79888</v>
+        <v>90611</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615290</v>
+        <v>615279</v>
       </c>
       <c r="R131" t="n">
-        <v>6560715</v>
+        <v>6560699</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,32 +14114,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131735760</v>
+        <v>131737682</v>
       </c>
       <c r="B132" t="n">
-        <v>90606</v>
+        <v>93172</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14149,10 +14149,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615279</v>
+        <v>615350</v>
       </c>
       <c r="R132" t="n">
-        <v>6560699</v>
+        <v>6560611</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,10 +14215,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B133" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R133" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,10 +14316,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737663</v>
+        <v>131737673</v>
       </c>
       <c r="B134" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615046</v>
+        <v>614957</v>
       </c>
       <c r="R134" t="n">
-        <v>6560537</v>
+        <v>6560564</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,10 +14417,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737673</v>
+        <v>131737661</v>
       </c>
       <c r="B135" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614957</v>
+        <v>615060</v>
       </c>
       <c r="R135" t="n">
-        <v>6560564</v>
+        <v>6560565</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,10 +14518,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737661</v>
+        <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>93167</v>
+        <v>79893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14529,34 +14529,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615060</v>
+        <v>615290</v>
       </c>
       <c r="R136" t="n">
-        <v>6560565</v>
+        <v>6560715</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737787</v>
+        <v>131738991</v>
       </c>
       <c r="B29" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,38 +3634,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615336</v>
+        <v>614921</v>
       </c>
       <c r="R29" t="n">
-        <v>6560522</v>
+        <v>6560577</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3692,17 +3688,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737651</v>
+        <v>131739043</v>
       </c>
       <c r="B30" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3744,34 +3735,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615311</v>
+        <v>614985</v>
       </c>
       <c r="R30" t="n">
-        <v>6560742</v>
+        <v>6560565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,12 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737785</v>
+        <v>131739007</v>
       </c>
       <c r="B31" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,38 +3836,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615314</v>
+        <v>614970</v>
       </c>
       <c r="R31" t="n">
-        <v>6560513</v>
+        <v>6560560</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,17 +3890,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,7 +3926,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737784</v>
+        <v>131737787</v>
       </c>
       <c r="B32" t="n">
         <v>93172</v>
@@ -3974,7 +3956,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3983,10 +3965,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615291</v>
+        <v>615336</v>
       </c>
       <c r="R32" t="n">
-        <v>6560497</v>
+        <v>6560522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4023,7 +4005,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,7 +4036,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737629</v>
+        <v>131737651</v>
       </c>
       <c r="B33" t="n">
         <v>93172</v>
@@ -4085,14 +4067,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614941</v>
+        <v>615311</v>
       </c>
       <c r="R33" t="n">
-        <v>6560607</v>
+        <v>6560742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738991</v>
+        <v>131737785</v>
       </c>
       <c r="B34" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,34 +4148,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614921</v>
+        <v>615314</v>
       </c>
       <c r="R34" t="n">
-        <v>6560577</v>
+        <v>6560513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,12 +4206,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4247,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131739043</v>
+        <v>131737784</v>
       </c>
       <c r="B35" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,34 +4258,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614985</v>
+        <v>615291</v>
       </c>
       <c r="R35" t="n">
-        <v>6560565</v>
+        <v>6560497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4316,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739007</v>
+        <v>131737629</v>
       </c>
       <c r="B36" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614970</v>
+        <v>614941</v>
       </c>
       <c r="R36" t="n">
-        <v>6560560</v>
+        <v>6560607</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737635</v>
+        <v>131739002</v>
       </c>
       <c r="B46" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614963</v>
+        <v>614953</v>
       </c>
       <c r="R46" t="n">
-        <v>6560615</v>
+        <v>6560567</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737618</v>
+        <v>131737635</v>
       </c>
       <c r="B47" t="n">
         <v>93172</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614881</v>
+        <v>614963</v>
       </c>
       <c r="R47" t="n">
-        <v>6560601</v>
+        <v>6560615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131739002</v>
+        <v>131737618</v>
       </c>
       <c r="B48" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614953</v>
+        <v>614881</v>
       </c>
       <c r="R48" t="n">
-        <v>6560567</v>
+        <v>6560601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>615022</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,32 +5780,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737677</v>
+        <v>131737925</v>
       </c>
       <c r="B50" t="n">
-        <v>93172</v>
+        <v>8455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615064</v>
+        <v>615343</v>
       </c>
       <c r="R50" t="n">
-        <v>6560525</v>
+        <v>6560656</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737684</v>
+        <v>131737616</v>
       </c>
       <c r="B51" t="n">
         <v>93172</v>
@@ -5912,14 +5912,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615333</v>
+        <v>614862</v>
       </c>
       <c r="R51" t="n">
-        <v>6560608</v>
+        <v>6560592</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131739012</v>
+        <v>131737677</v>
       </c>
       <c r="B52" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,34 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615022</v>
+        <v>615064</v>
       </c>
       <c r="R52" t="n">
-        <v>6560527</v>
+        <v>6560525</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6083,32 +6083,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737925</v>
+        <v>131737684</v>
       </c>
       <c r="B53" t="n">
-        <v>8455</v>
+        <v>93172</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615343</v>
+        <v>615333</v>
       </c>
       <c r="R53" t="n">
-        <v>6560656</v>
+        <v>6560608</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131737686</v>
+        <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93172</v>
+        <v>93150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7306,21 +7306,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615314</v>
+        <v>615336</v>
       </c>
       <c r="R65" t="n">
-        <v>6560599</v>
+        <v>6560577</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,7 +7396,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737643</v>
+        <v>131737686</v>
       </c>
       <c r="B66" t="n">
         <v>93172</v>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615322</v>
+        <v>615314</v>
       </c>
       <c r="R66" t="n">
-        <v>6560634</v>
+        <v>6560599</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131736575</v>
+        <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93150</v>
+        <v>93172</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615336</v>
+        <v>615322</v>
       </c>
       <c r="R67" t="n">
-        <v>6560577</v>
+        <v>6560634</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131738989</v>
       </c>
       <c r="B74" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>614945</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560637</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>131739041</v>
       </c>
       <c r="B75" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>615269</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560500</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131739011</v>
       </c>
       <c r="B76" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>615080</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560512</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131737644</v>
       </c>
       <c r="B78" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>615331</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560676</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B79" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,10 +8816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131739011</v>
+        <v>131737668</v>
       </c>
       <c r="B80" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8827,34 +8827,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615080</v>
+        <v>614990</v>
       </c>
       <c r="R80" t="n">
-        <v>6560512</v>
+        <v>6560601</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B111" t="n">
-        <v>93163</v>
+        <v>79893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11985,19 +11985,23 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12005,10 +12009,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R111" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12049,7 +12053,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12072,10 +12075,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737627</v>
+        <v>131738990</v>
       </c>
       <c r="B112" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12083,21 +12086,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12107,10 +12110,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614921</v>
+        <v>614930</v>
       </c>
       <c r="R112" t="n">
-        <v>6560604</v>
+        <v>6560587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12173,10 +12176,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737648</v>
+        <v>131740361</v>
       </c>
       <c r="B113" t="n">
-        <v>93172</v>
+        <v>93163</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12184,23 +12187,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12208,10 +12207,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615306</v>
+        <v>615309</v>
       </c>
       <c r="R113" t="n">
-        <v>6560663</v>
+        <v>6560557</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12252,6 +12251,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737630</v>
+        <v>131737627</v>
       </c>
       <c r="B114" t="n">
         <v>93172</v>
@@ -12305,14 +12305,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614948</v>
+        <v>614921</v>
       </c>
       <c r="R114" t="n">
-        <v>6560611</v>
+        <v>6560604</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12375,53 +12375,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131740030</v>
+        <v>131737648</v>
       </c>
       <c r="B115" t="n">
-        <v>57100</v>
+        <v>93172</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614953</v>
+        <v>615306</v>
       </c>
       <c r="R115" t="n">
-        <v>6560578</v>
+        <v>6560663</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12454,11 +12446,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12489,10 +12476,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738995</v>
+        <v>131737630</v>
       </c>
       <c r="B116" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12500,34 +12487,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615323</v>
+        <v>614948</v>
       </c>
       <c r="R116" t="n">
-        <v>6560647</v>
+        <v>6560611</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,45 +12577,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738990</v>
+        <v>131740030</v>
       </c>
       <c r="B117" t="n">
-        <v>79893</v>
+        <v>57100</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614930</v>
+        <v>614953</v>
       </c>
       <c r="R117" t="n">
-        <v>6560587</v>
+        <v>6560578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131739003</v>
+        <v>131737665</v>
       </c>
       <c r="B118" t="n">
-        <v>79893</v>
+        <v>93172</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614959</v>
+        <v>614993</v>
       </c>
       <c r="R118" t="n">
-        <v>6560556</v>
+        <v>6560559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B119" t="n">
         <v>93172</v>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131739003</v>
       </c>
       <c r="B120" t="n">
-        <v>93172</v>
+        <v>79893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614959</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560556</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131735760</v>
+        <v>131737682</v>
       </c>
       <c r="B131" t="n">
-        <v>90611</v>
+        <v>93172</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615279</v>
+        <v>615350</v>
       </c>
       <c r="R131" t="n">
-        <v>6560699</v>
+        <v>6560611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,7 +14114,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B132" t="n">
         <v>93172</v>
@@ -14145,14 +14145,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R132" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737663</v>
+        <v>131737673</v>
       </c>
       <c r="B133" t="n">
         <v>93172</v>
@@ -14250,10 +14250,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615046</v>
+        <v>614957</v>
       </c>
       <c r="R133" t="n">
-        <v>6560537</v>
+        <v>6560564</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737673</v>
+        <v>131737661</v>
       </c>
       <c r="B134" t="n">
         <v>93172</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614957</v>
+        <v>615060</v>
       </c>
       <c r="R134" t="n">
-        <v>6560564</v>
+        <v>6560565</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,45 +14417,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737661</v>
+        <v>131735760</v>
       </c>
       <c r="B135" t="n">
-        <v>93172</v>
+        <v>90611</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615060</v>
+        <v>615279</v>
       </c>
       <c r="R135" t="n">
-        <v>6560565</v>
+        <v>6560699</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2515,7 +2515,7 @@
         <v>131737671</v>
       </c>
       <c r="B18" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>131737631</v>
       </c>
       <c r="B19" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>131737632</v>
       </c>
       <c r="B20" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131737647</v>
       </c>
       <c r="B21" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>131737637</v>
       </c>
       <c r="B22" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>131737650</v>
       </c>
       <c r="B23" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>131737654</v>
       </c>
       <c r="B24" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>131737614</v>
       </c>
       <c r="B25" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131739009</v>
+        <v>131739006</v>
       </c>
       <c r="B26" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614998</v>
+        <v>614970</v>
       </c>
       <c r="R26" t="n">
-        <v>6560540</v>
+        <v>6560568</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131739006</v>
+        <v>131739009</v>
       </c>
       <c r="B27" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614970</v>
+        <v>614998</v>
       </c>
       <c r="R27" t="n">
-        <v>6560568</v>
+        <v>6560540</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
         <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738991</v>
+        <v>131739043</v>
       </c>
       <c r="B29" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,14 +3654,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614921</v>
+        <v>614985</v>
       </c>
       <c r="R29" t="n">
-        <v>6560577</v>
+        <v>6560565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131739043</v>
+        <v>131739007</v>
       </c>
       <c r="B30" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614985</v>
+        <v>614970</v>
       </c>
       <c r="R30" t="n">
-        <v>6560565</v>
+        <v>6560560</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131739007</v>
+        <v>131737787</v>
       </c>
       <c r="B31" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,34 +3836,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614970</v>
+        <v>615336</v>
       </c>
       <c r="R31" t="n">
-        <v>6560560</v>
+        <v>6560522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,12 +3894,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737787</v>
+        <v>131737651</v>
       </c>
       <c r="B32" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,21 +3963,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615336</v>
+        <v>615311</v>
       </c>
       <c r="R32" t="n">
-        <v>6560522</v>
+        <v>6560742</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3995,17 +4000,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737651</v>
+        <v>131737785</v>
       </c>
       <c r="B33" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,17 +4064,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615311</v>
+        <v>615314</v>
       </c>
       <c r="R33" t="n">
-        <v>6560742</v>
+        <v>6560513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4101,12 +4105,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,10 +4146,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737785</v>
+        <v>131737784</v>
       </c>
       <c r="B34" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4167,7 +4176,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4176,10 +4185,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615314</v>
+        <v>615291</v>
       </c>
       <c r="R34" t="n">
-        <v>6560513</v>
+        <v>6560497</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,7 +4225,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4247,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737784</v>
+        <v>131737629</v>
       </c>
       <c r="B35" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,21 +4284,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615291</v>
+        <v>614941</v>
       </c>
       <c r="R35" t="n">
-        <v>6560497</v>
+        <v>6560607</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,17 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737629</v>
+        <v>131738991</v>
       </c>
       <c r="B36" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,34 +4368,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614941</v>
+        <v>614921</v>
       </c>
       <c r="R36" t="n">
-        <v>6560607</v>
+        <v>6560577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
         <v>131737685</v>
       </c>
       <c r="B37" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>131737672</v>
       </c>
       <c r="B38" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>131737786</v>
       </c>
       <c r="B39" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>131737662</v>
       </c>
       <c r="B40" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>131737620</v>
       </c>
       <c r="B41" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>131737634</v>
       </c>
       <c r="B42" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>131737669</v>
       </c>
       <c r="B43" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>131737660</v>
       </c>
       <c r="B44" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>131737640</v>
       </c>
       <c r="B45" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739002</v>
+        <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614953</v>
+        <v>614963</v>
       </c>
       <c r="R46" t="n">
-        <v>6560567</v>
+        <v>6560615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B47" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R47" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131737618</v>
+        <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614881</v>
+        <v>614953</v>
       </c>
       <c r="R48" t="n">
-        <v>6560601</v>
+        <v>6560567</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131739012</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615022</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560527</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,32 +5780,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737925</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>93174</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615343</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560656</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,10 +5881,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737616</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5912,14 +5912,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614862</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560592</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,32 +5982,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737677</v>
+        <v>131737925</v>
       </c>
       <c r="B52" t="n">
-        <v>93172</v>
+        <v>8455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615064</v>
+        <v>615343</v>
       </c>
       <c r="R52" t="n">
-        <v>6560525</v>
+        <v>6560656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B53" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6094,34 +6094,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R53" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
         <v>131737675</v>
       </c>
       <c r="B54" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>131737617</v>
       </c>
       <c r="B55" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737652</v>
+        <v>131738993</v>
       </c>
       <c r="B60" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615301</v>
+        <v>614904</v>
       </c>
       <c r="R60" t="n">
-        <v>6560755</v>
+        <v>6560578</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737688</v>
+        <v>131737652</v>
       </c>
       <c r="B61" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6922,14 +6922,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615310</v>
+        <v>615301</v>
       </c>
       <c r="R61" t="n">
-        <v>6560543</v>
+        <v>6560755</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131738993</v>
+        <v>131737688</v>
       </c>
       <c r="B62" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614904</v>
+        <v>615310</v>
       </c>
       <c r="R62" t="n">
-        <v>6560578</v>
+        <v>6560543</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7096,7 +7096,7 @@
         <v>131739008</v>
       </c>
       <c r="B63" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>131739005</v>
       </c>
       <c r="B64" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93150</v>
+        <v>93152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>131737686</v>
       </c>
       <c r="B66" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737667</v>
+        <v>131739010</v>
       </c>
       <c r="B68" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,21 +7609,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614991</v>
+        <v>615012</v>
       </c>
       <c r="R68" t="n">
-        <v>6560587</v>
+        <v>6560549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131740360</v>
+        <v>131737667</v>
       </c>
       <c r="B69" t="n">
-        <v>93163</v>
+        <v>93174</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615296</v>
+        <v>614991</v>
       </c>
       <c r="R69" t="n">
-        <v>6560688</v>
+        <v>6560587</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,18 +7772,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7806,10 +7800,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737638</v>
+        <v>131740360</v>
       </c>
       <c r="B70" t="n">
-        <v>93172</v>
+        <v>93165</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7817,34 +7811,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614943</v>
+        <v>615296</v>
       </c>
       <c r="R70" t="n">
-        <v>6560591</v>
+        <v>6560688</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7879,12 +7873,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7907,10 +7907,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737658</v>
+        <v>131737638</v>
       </c>
       <c r="B71" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7938,14 +7938,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615282</v>
+        <v>614943</v>
       </c>
       <c r="R71" t="n">
-        <v>6560684</v>
+        <v>6560591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739010</v>
+        <v>131737658</v>
       </c>
       <c r="B72" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,34 +8019,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>615012</v>
+        <v>615282</v>
       </c>
       <c r="R72" t="n">
-        <v>6560549</v>
+        <v>6560684</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8112,7 +8112,7 @@
         <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131738989</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614945</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560637</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131739011</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615080</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560512</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737644</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615331</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560676</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737639</v>
+        <v>131739041</v>
       </c>
       <c r="B79" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614942</v>
+        <v>615269</v>
       </c>
       <c r="R79" t="n">
-        <v>6560579</v>
+        <v>6560500</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,10 +8816,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737668</v>
+        <v>131739011</v>
       </c>
       <c r="B80" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8827,34 +8827,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>614990</v>
+        <v>615080</v>
       </c>
       <c r="R80" t="n">
-        <v>6560601</v>
+        <v>6560512</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>131737674</v>
       </c>
       <c r="B81" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>131737782</v>
       </c>
       <c r="B82" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>131737653</v>
       </c>
       <c r="B84" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>131737624</v>
       </c>
       <c r="B85" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131738988</v>
+        <v>131737626</v>
       </c>
       <c r="B86" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614862</v>
+        <v>614911</v>
       </c>
       <c r="R86" t="n">
-        <v>6560592</v>
+        <v>6560610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737626</v>
+        <v>131737642</v>
       </c>
       <c r="B87" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614911</v>
+        <v>614884</v>
       </c>
       <c r="R87" t="n">
-        <v>6560610</v>
+        <v>6560568</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737642</v>
+        <v>131737687</v>
       </c>
       <c r="B88" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614884</v>
+        <v>615322</v>
       </c>
       <c r="R88" t="n">
-        <v>6560568</v>
+        <v>6560582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737687</v>
+        <v>131738988</v>
       </c>
       <c r="B89" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9745,34 +9745,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>615322</v>
+        <v>614862</v>
       </c>
       <c r="R89" t="n">
-        <v>6560582</v>
+        <v>6560592</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131738998</v>
+        <v>131737783</v>
       </c>
       <c r="B90" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,34 +9846,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615020</v>
+        <v>615276</v>
       </c>
       <c r="R90" t="n">
-        <v>6560533</v>
+        <v>6560495</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9900,12 +9904,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9936,10 +9945,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737783</v>
+        <v>131737641</v>
       </c>
       <c r="B91" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9964,21 +9973,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615276</v>
+        <v>614893</v>
       </c>
       <c r="R91" t="n">
-        <v>6560495</v>
+        <v>6560582</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10005,17 +10010,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10046,10 +10046,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737641</v>
+        <v>131737656</v>
       </c>
       <c r="B92" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10077,14 +10077,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614893</v>
+        <v>615271</v>
       </c>
       <c r="R92" t="n">
-        <v>6560582</v>
+        <v>6560749</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737656</v>
+        <v>131737666</v>
       </c>
       <c r="B93" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615271</v>
+        <v>614995</v>
       </c>
       <c r="R93" t="n">
-        <v>6560749</v>
+        <v>6560571</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737666</v>
+        <v>131737676</v>
       </c>
       <c r="B94" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10279,14 +10279,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614995</v>
+        <v>615060</v>
       </c>
       <c r="R94" t="n">
-        <v>6560571</v>
+        <v>6560536</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10349,10 +10349,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737676</v>
+        <v>131737646</v>
       </c>
       <c r="B95" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615060</v>
+        <v>615289</v>
       </c>
       <c r="R95" t="n">
-        <v>6560536</v>
+        <v>6560695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737646</v>
+        <v>131737690</v>
       </c>
       <c r="B96" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615289</v>
+        <v>615387</v>
       </c>
       <c r="R96" t="n">
-        <v>6560695</v>
+        <v>6560558</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,10 +10551,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737690</v>
+        <v>131737659</v>
       </c>
       <c r="B97" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615387</v>
+        <v>615267</v>
       </c>
       <c r="R97" t="n">
-        <v>6560558</v>
+        <v>6560667</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737659</v>
+        <v>131737649</v>
       </c>
       <c r="B98" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615267</v>
+        <v>615316</v>
       </c>
       <c r="R98" t="n">
-        <v>6560667</v>
+        <v>6560709</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737649</v>
+        <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615316</v>
+        <v>615020</v>
       </c>
       <c r="R99" t="n">
-        <v>6560709</v>
+        <v>6560533</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10857,7 +10857,7 @@
         <v>131737625</v>
       </c>
       <c r="B100" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>131737645</v>
       </c>
       <c r="B101" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>131737655</v>
       </c>
       <c r="B102" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>131737636</v>
       </c>
       <c r="B103" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>131737691</v>
       </c>
       <c r="B104" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>131737619</v>
       </c>
       <c r="B105" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>131739013</v>
       </c>
       <c r="B107" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>131739004</v>
       </c>
       <c r="B108" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>131736566</v>
       </c>
       <c r="B110" t="n">
-        <v>93150</v>
+        <v>93152</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>131738995</v>
       </c>
       <c r="B111" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12075,45 +12075,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131738990</v>
+        <v>131740030</v>
       </c>
       <c r="B112" t="n">
-        <v>79893</v>
+        <v>57102</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614930</v>
+        <v>614953</v>
       </c>
       <c r="R112" t="n">
-        <v>6560587</v>
+        <v>6560578</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12146,6 +12154,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12176,10 +12189,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131740361</v>
+        <v>131737627</v>
       </c>
       <c r="B113" t="n">
-        <v>93163</v>
+        <v>93174</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12187,30 +12200,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615309</v>
+        <v>614921</v>
       </c>
       <c r="R113" t="n">
-        <v>6560557</v>
+        <v>6560604</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12251,7 +12268,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12274,10 +12290,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737627</v>
+        <v>131737630</v>
       </c>
       <c r="B114" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12305,14 +12321,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614921</v>
+        <v>614948</v>
       </c>
       <c r="R114" t="n">
-        <v>6560604</v>
+        <v>6560611</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12375,10 +12391,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737648</v>
+        <v>131738990</v>
       </c>
       <c r="B115" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12386,34 +12402,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615306</v>
+        <v>614930</v>
       </c>
       <c r="R115" t="n">
-        <v>6560663</v>
+        <v>6560587</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12476,10 +12492,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737630</v>
+        <v>131740361</v>
       </c>
       <c r="B116" t="n">
-        <v>93172</v>
+        <v>93165</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12487,34 +12503,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614948</v>
+        <v>615309</v>
       </c>
       <c r="R116" t="n">
-        <v>6560611</v>
+        <v>6560557</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12555,6 +12567,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12577,53 +12590,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131740030</v>
+        <v>131737648</v>
       </c>
       <c r="B117" t="n">
-        <v>57100</v>
+        <v>93174</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614953</v>
+        <v>615306</v>
       </c>
       <c r="R117" t="n">
-        <v>6560578</v>
+        <v>6560663</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12656,11 +12661,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737665</v>
+        <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>93172</v>
+        <v>91869</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614993</v>
+        <v>614974</v>
       </c>
       <c r="R118" t="n">
-        <v>6560559</v>
+        <v>6560628</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737670</v>
+        <v>131739003</v>
       </c>
       <c r="B119" t="n">
-        <v>93172</v>
+        <v>79895</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614972</v>
+        <v>614959</v>
       </c>
       <c r="R119" t="n">
-        <v>6560590</v>
+        <v>6560556</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131739003</v>
+        <v>131737665</v>
       </c>
       <c r="B120" t="n">
-        <v>79893</v>
+        <v>93174</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614959</v>
+        <v>614993</v>
       </c>
       <c r="R120" t="n">
-        <v>6560556</v>
+        <v>6560559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131740081</v>
+        <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>91867</v>
+        <v>93174</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614974</v>
+        <v>614972</v>
       </c>
       <c r="R121" t="n">
-        <v>6560628</v>
+        <v>6560590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13059,12 +13059,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13095,49 +13095,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131735761</v>
+        <v>131739000</v>
       </c>
       <c r="B122" t="n">
-        <v>90611</v>
+        <v>79895</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>615277</v>
+        <v>614941</v>
       </c>
       <c r="R122" t="n">
-        <v>6560691</v>
+        <v>6560553</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13170,11 +13166,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13205,45 +13196,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131738994</v>
+        <v>131735761</v>
       </c>
       <c r="B123" t="n">
-        <v>79893</v>
+        <v>90613</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614890</v>
+        <v>615277</v>
       </c>
       <c r="R123" t="n">
-        <v>6560564</v>
+        <v>6560691</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13276,6 +13271,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13306,10 +13306,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739000</v>
+        <v>131738994</v>
       </c>
       <c r="B124" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13341,10 +13341,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614941</v>
+        <v>614890</v>
       </c>
       <c r="R124" t="n">
-        <v>6560553</v>
+        <v>6560564</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13410,7 +13410,7 @@
         <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>131737678</v>
       </c>
       <c r="B127" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>131737681</v>
       </c>
       <c r="B128" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>131739026</v>
       </c>
       <c r="B129" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>131738997</v>
       </c>
       <c r="B130" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>131737682</v>
       </c>
       <c r="B131" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>131737663</v>
       </c>
       <c r="B132" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>131737673</v>
       </c>
       <c r="B133" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>131737661</v>
       </c>
       <c r="B134" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>131735760</v>
       </c>
       <c r="B135" t="n">
-        <v>90611</v>
+        <v>90613</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>131738996</v>
       </c>
       <c r="B136" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,7 +2512,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737671</v>
+        <v>131737637</v>
       </c>
       <c r="B18" t="n">
         <v>93174</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614965</v>
+        <v>614949</v>
       </c>
       <c r="R18" t="n">
-        <v>6560580</v>
+        <v>6560610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737631</v>
+        <v>131737650</v>
       </c>
       <c r="B19" t="n">
         <v>93174</v>
@@ -2644,14 +2644,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614937</v>
+        <v>615325</v>
       </c>
       <c r="R19" t="n">
-        <v>6560625</v>
+        <v>6560719</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737632</v>
+        <v>131737654</v>
       </c>
       <c r="B20" t="n">
         <v>93174</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614949</v>
+        <v>615282</v>
       </c>
       <c r="R20" t="n">
-        <v>6560635</v>
+        <v>6560780</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737647</v>
+        <v>131739009</v>
       </c>
       <c r="B21" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,34 +2826,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615295</v>
+        <v>614998</v>
       </c>
       <c r="R21" t="n">
-        <v>6560678</v>
+        <v>6560540</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737637</v>
+        <v>131738992</v>
       </c>
       <c r="B22" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,34 +2927,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614949</v>
+        <v>614903</v>
       </c>
       <c r="R22" t="n">
-        <v>6560610</v>
+        <v>6560580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737650</v>
+        <v>131737671</v>
       </c>
       <c r="B23" t="n">
         <v>93174</v>
@@ -3048,14 +3048,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615325</v>
+        <v>614965</v>
       </c>
       <c r="R23" t="n">
-        <v>6560719</v>
+        <v>6560580</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737654</v>
+        <v>131737631</v>
       </c>
       <c r="B24" t="n">
         <v>93174</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615282</v>
+        <v>614937</v>
       </c>
       <c r="R24" t="n">
-        <v>6560780</v>
+        <v>6560625</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737614</v>
+        <v>131737632</v>
       </c>
       <c r="B25" t="n">
         <v>93174</v>
@@ -3250,14 +3250,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614857</v>
+        <v>614949</v>
       </c>
       <c r="R25" t="n">
-        <v>6560612</v>
+        <v>6560635</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131739006</v>
+        <v>131737647</v>
       </c>
       <c r="B26" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,34 +3331,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614970</v>
+        <v>615295</v>
       </c>
       <c r="R26" t="n">
-        <v>6560568</v>
+        <v>6560678</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131739009</v>
+        <v>131737614</v>
       </c>
       <c r="B27" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3432,34 +3432,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614998</v>
+        <v>614857</v>
       </c>
       <c r="R27" t="n">
-        <v>6560540</v>
+        <v>6560612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738992</v>
+        <v>131739006</v>
       </c>
       <c r="B28" t="n">
         <v>79895</v>
@@ -3553,14 +3553,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614903</v>
+        <v>614970</v>
       </c>
       <c r="R28" t="n">
-        <v>6560580</v>
+        <v>6560568</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131739043</v>
+        <v>131737787</v>
       </c>
       <c r="B29" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,34 +3634,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614985</v>
+        <v>615336</v>
       </c>
       <c r="R29" t="n">
-        <v>6560565</v>
+        <v>6560522</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,12 +3692,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131739007</v>
+        <v>131737651</v>
       </c>
       <c r="B30" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,34 +3744,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614970</v>
+        <v>615311</v>
       </c>
       <c r="R30" t="n">
-        <v>6560560</v>
+        <v>6560742</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3825,7 +3834,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737787</v>
+        <v>131737785</v>
       </c>
       <c r="B31" t="n">
         <v>93174</v>
@@ -3855,7 +3864,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3864,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R31" t="n">
-        <v>6560522</v>
+        <v>6560513</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3904,7 +3913,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,7 +3944,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737651</v>
+        <v>131737784</v>
       </c>
       <c r="B32" t="n">
         <v>93174</v>
@@ -3963,17 +3972,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615311</v>
+        <v>615291</v>
       </c>
       <c r="R32" t="n">
-        <v>6560742</v>
+        <v>6560497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,12 +4013,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737785</v>
+        <v>131737629</v>
       </c>
       <c r="B33" t="n">
         <v>93174</v>
@@ -4064,21 +4082,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615314</v>
+        <v>614941</v>
       </c>
       <c r="R33" t="n">
-        <v>6560513</v>
+        <v>6560607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4105,17 +4119,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,10 +4155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737784</v>
+        <v>131738991</v>
       </c>
       <c r="B34" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4157,38 +4166,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615291</v>
+        <v>614921</v>
       </c>
       <c r="R34" t="n">
-        <v>6560497</v>
+        <v>6560577</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4215,17 +4220,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737629</v>
+        <v>131739043</v>
       </c>
       <c r="B35" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614941</v>
+        <v>614985</v>
       </c>
       <c r="R35" t="n">
-        <v>6560607</v>
+        <v>6560565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,7 +4357,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131738991</v>
+        <v>131739007</v>
       </c>
       <c r="B36" t="n">
         <v>79895</v>
@@ -4388,14 +4388,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614921</v>
+        <v>614970</v>
       </c>
       <c r="R36" t="n">
-        <v>6560577</v>
+        <v>6560560</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B46" t="n">
         <v>93174</v>
@@ -5407,14 +5407,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R46" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737618</v>
+        <v>131737635</v>
       </c>
       <c r="B47" t="n">
         <v>93174</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614881</v>
+        <v>614963</v>
       </c>
       <c r="R47" t="n">
-        <v>6560601</v>
+        <v>6560615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5982,45 +5982,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737925</v>
+        <v>131739012</v>
       </c>
       <c r="B52" t="n">
-        <v>8455</v>
+        <v>79895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615343</v>
+        <v>615022</v>
       </c>
       <c r="R52" t="n">
-        <v>6560656</v>
+        <v>6560527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6083,45 +6083,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131739012</v>
+        <v>131737925</v>
       </c>
       <c r="B53" t="n">
-        <v>79895</v>
+        <v>8455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615022</v>
+        <v>615343</v>
       </c>
       <c r="R53" t="n">
-        <v>6560527</v>
+        <v>6560656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B60" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R60" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737652</v>
+        <v>131737688</v>
       </c>
       <c r="B61" t="n">
         <v>93174</v>
@@ -6922,14 +6922,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615301</v>
+        <v>615310</v>
       </c>
       <c r="R61" t="n">
-        <v>6560755</v>
+        <v>6560543</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737688</v>
+        <v>131738993</v>
       </c>
       <c r="B62" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615310</v>
+        <v>614904</v>
       </c>
       <c r="R62" t="n">
-        <v>6560543</v>
+        <v>6560578</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8513,45 +8513,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737924</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>8455</v>
+        <v>79895</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615091</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560504</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
         <v>79895</v>
@@ -8645,14 +8645,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,7 +8715,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739041</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
         <v>79895</v>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615269</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131739011</v>
+        <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>79895</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615080</v>
+        <v>615091</v>
       </c>
       <c r="R80" t="n">
-        <v>6560512</v>
+        <v>6560504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737625</v>
+        <v>131739013</v>
       </c>
       <c r="B100" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614918</v>
+        <v>615376</v>
       </c>
       <c r="R100" t="n">
-        <v>6560620</v>
+        <v>6560556</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737645</v>
+        <v>131739004</v>
       </c>
       <c r="B101" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615304</v>
+        <v>614958</v>
       </c>
       <c r="R101" t="n">
-        <v>6560686</v>
+        <v>6560561</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737655</v>
+        <v>131739001</v>
       </c>
       <c r="B102" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615267</v>
+        <v>614955</v>
       </c>
       <c r="R102" t="n">
-        <v>6560777</v>
+        <v>6560579</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737636</v>
+        <v>131737625</v>
       </c>
       <c r="B103" t="n">
         <v>93174</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614960</v>
+        <v>614918</v>
       </c>
       <c r="R103" t="n">
-        <v>6560601</v>
+        <v>6560620</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737691</v>
+        <v>131737645</v>
       </c>
       <c r="B104" t="n">
         <v>93174</v>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615367</v>
+        <v>615304</v>
       </c>
       <c r="R104" t="n">
-        <v>6560553</v>
+        <v>6560686</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737619</v>
+        <v>131737655</v>
       </c>
       <c r="B105" t="n">
         <v>93174</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614885</v>
+        <v>615267</v>
       </c>
       <c r="R105" t="n">
-        <v>6560613</v>
+        <v>6560777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131737636</v>
       </c>
       <c r="B106" t="n">
         <v>93174</v>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>614960</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560601</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739013</v>
+        <v>131737691</v>
       </c>
       <c r="B107" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615376</v>
+        <v>615367</v>
       </c>
       <c r="R107" t="n">
-        <v>6560556</v>
+        <v>6560553</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739004</v>
+        <v>131737619</v>
       </c>
       <c r="B108" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614958</v>
+        <v>614885</v>
       </c>
       <c r="R108" t="n">
-        <v>6560561</v>
+        <v>6560613</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131737664</v>
       </c>
       <c r="B109" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>614942</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560568</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131736566</v>
+        <v>131740361</v>
       </c>
       <c r="B110" t="n">
-        <v>93152</v>
+        <v>93165</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,38 +11875,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615319</v>
+        <v>615309</v>
       </c>
       <c r="R110" t="n">
-        <v>6560579</v>
+        <v>6560557</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11941,17 +11933,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11974,10 +11962,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738995</v>
+        <v>131737627</v>
       </c>
       <c r="B111" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11985,34 +11973,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615323</v>
+        <v>614921</v>
       </c>
       <c r="R111" t="n">
-        <v>6560647</v>
+        <v>6560604</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12075,53 +12063,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131740030</v>
+        <v>131737648</v>
       </c>
       <c r="B112" t="n">
-        <v>57102</v>
+        <v>93174</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614953</v>
+        <v>615306</v>
       </c>
       <c r="R112" t="n">
-        <v>6560578</v>
+        <v>6560663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12154,11 +12134,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12189,7 +12164,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737627</v>
+        <v>131737630</v>
       </c>
       <c r="B113" t="n">
         <v>93174</v>
@@ -12220,14 +12195,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614921</v>
+        <v>614948</v>
       </c>
       <c r="R113" t="n">
-        <v>6560604</v>
+        <v>6560611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12290,10 +12265,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737630</v>
+        <v>131736566</v>
       </c>
       <c r="B114" t="n">
-        <v>93174</v>
+        <v>93152</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12301,34 +12276,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614948</v>
+        <v>615319</v>
       </c>
       <c r="R114" t="n">
-        <v>6560611</v>
+        <v>6560579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12361,6 +12340,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12391,7 +12375,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738990</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
         <v>79895</v>
@@ -12422,14 +12406,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614930</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560587</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12492,10 +12476,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131740361</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12503,30 +12487,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615309</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560557</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12567,7 +12555,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12590,45 +12577,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737648</v>
+        <v>131740030</v>
       </c>
       <c r="B117" t="n">
-        <v>93174</v>
+        <v>57102</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>615306</v>
+        <v>614953</v>
       </c>
       <c r="R117" t="n">
-        <v>6560663</v>
+        <v>6560578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14417,32 +14417,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B135" t="n">
-        <v>90613</v>
+        <v>79895</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R135" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,32 +14518,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131735760</v>
       </c>
       <c r="B136" t="n">
-        <v>79895</v>
+        <v>90613</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>615279</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560699</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,7 +2512,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737637</v>
+        <v>131737671</v>
       </c>
       <c r="B18" t="n">
         <v>93174</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614949</v>
+        <v>614965</v>
       </c>
       <c r="R18" t="n">
-        <v>6560610</v>
+        <v>6560580</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737650</v>
+        <v>131737637</v>
       </c>
       <c r="B19" t="n">
         <v>93174</v>
@@ -2644,14 +2644,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615325</v>
+        <v>614949</v>
       </c>
       <c r="R19" t="n">
-        <v>6560719</v>
+        <v>6560610</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737654</v>
+        <v>131739009</v>
       </c>
       <c r="B20" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615282</v>
+        <v>614998</v>
       </c>
       <c r="R20" t="n">
-        <v>6560780</v>
+        <v>6560540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131739009</v>
+        <v>131739006</v>
       </c>
       <c r="B21" t="n">
         <v>79895</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614998</v>
+        <v>614970</v>
       </c>
       <c r="R21" t="n">
-        <v>6560540</v>
+        <v>6560568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737671</v>
+        <v>131737631</v>
       </c>
       <c r="B23" t="n">
         <v>93174</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614965</v>
+        <v>614937</v>
       </c>
       <c r="R23" t="n">
-        <v>6560580</v>
+        <v>6560625</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737631</v>
+        <v>131737632</v>
       </c>
       <c r="B24" t="n">
         <v>93174</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614937</v>
+        <v>614949</v>
       </c>
       <c r="R24" t="n">
-        <v>6560625</v>
+        <v>6560635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737632</v>
+        <v>131737647</v>
       </c>
       <c r="B25" t="n">
         <v>93174</v>
@@ -3250,14 +3250,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614949</v>
+        <v>615295</v>
       </c>
       <c r="R25" t="n">
-        <v>6560635</v>
+        <v>6560678</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737647</v>
+        <v>131737650</v>
       </c>
       <c r="B26" t="n">
         <v>93174</v>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>615295</v>
+        <v>615325</v>
       </c>
       <c r="R26" t="n">
-        <v>6560678</v>
+        <v>6560719</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131737614</v>
+        <v>131737654</v>
       </c>
       <c r="B27" t="n">
         <v>93174</v>
@@ -3452,14 +3452,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614857</v>
+        <v>615282</v>
       </c>
       <c r="R27" t="n">
-        <v>6560612</v>
+        <v>6560780</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131739006</v>
+        <v>131737614</v>
       </c>
       <c r="B28" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,34 +3533,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614970</v>
+        <v>614857</v>
       </c>
       <c r="R28" t="n">
-        <v>6560568</v>
+        <v>6560612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737787</v>
+        <v>131737784</v>
       </c>
       <c r="B29" t="n">
         <v>93174</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615336</v>
+        <v>615291</v>
       </c>
       <c r="R29" t="n">
-        <v>6560522</v>
+        <v>6560497</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,7 +3733,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737651</v>
+        <v>131737629</v>
       </c>
       <c r="B30" t="n">
         <v>93174</v>
@@ -3764,14 +3764,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615311</v>
+        <v>614941</v>
       </c>
       <c r="R30" t="n">
-        <v>6560742</v>
+        <v>6560607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737785</v>
+        <v>131737787</v>
       </c>
       <c r="B31" t="n">
         <v>93174</v>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615314</v>
+        <v>615336</v>
       </c>
       <c r="R31" t="n">
-        <v>6560513</v>
+        <v>6560522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,7 +3944,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737784</v>
+        <v>131737651</v>
       </c>
       <c r="B32" t="n">
         <v>93174</v>
@@ -3972,21 +3972,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615291</v>
+        <v>615311</v>
       </c>
       <c r="R32" t="n">
-        <v>6560497</v>
+        <v>6560742</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,17 +4009,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,7 +4045,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737629</v>
+        <v>131737785</v>
       </c>
       <c r="B33" t="n">
         <v>93174</v>
@@ -4082,17 +4073,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614941</v>
+        <v>615314</v>
       </c>
       <c r="R33" t="n">
-        <v>6560607</v>
+        <v>6560513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,12 +4114,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737672</v>
+        <v>131737786</v>
       </c>
       <c r="B38" t="n">
         <v>93174</v>
@@ -4587,17 +4587,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614950</v>
+        <v>615335</v>
       </c>
       <c r="R38" t="n">
-        <v>6560576</v>
+        <v>6560536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4624,12 +4628,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4660,7 +4669,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737786</v>
+        <v>131737662</v>
       </c>
       <c r="B39" t="n">
         <v>93174</v>
@@ -4688,21 +4697,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615335</v>
+        <v>615040</v>
       </c>
       <c r="R39" t="n">
-        <v>6560536</v>
+        <v>6560530</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,17 +4734,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,7 +4770,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737662</v>
+        <v>131737620</v>
       </c>
       <c r="B40" t="n">
         <v>93174</v>
@@ -4801,14 +4801,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615040</v>
+        <v>614896</v>
       </c>
       <c r="R40" t="n">
-        <v>6560530</v>
+        <v>6560613</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737620</v>
+        <v>131737634</v>
       </c>
       <c r="B41" t="n">
         <v>93174</v>
@@ -4902,14 +4902,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614896</v>
+        <v>614954</v>
       </c>
       <c r="R41" t="n">
-        <v>6560613</v>
+        <v>6560617</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737634</v>
+        <v>131737669</v>
       </c>
       <c r="B42" t="n">
         <v>93174</v>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614954</v>
+        <v>614973</v>
       </c>
       <c r="R42" t="n">
-        <v>6560617</v>
+        <v>6560600</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737669</v>
+        <v>131737660</v>
       </c>
       <c r="B43" t="n">
         <v>93174</v>
@@ -5104,14 +5104,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614973</v>
+        <v>615278</v>
       </c>
       <c r="R43" t="n">
-        <v>6560600</v>
+        <v>6560662</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737660</v>
+        <v>131737640</v>
       </c>
       <c r="B44" t="n">
         <v>93174</v>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615278</v>
+        <v>614934</v>
       </c>
       <c r="R44" t="n">
-        <v>6560662</v>
+        <v>6560578</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737640</v>
+        <v>131737672</v>
       </c>
       <c r="B45" t="n">
         <v>93174</v>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614934</v>
+        <v>614950</v>
       </c>
       <c r="R45" t="n">
-        <v>6560578</v>
+        <v>6560576</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737618</v>
+        <v>131737635</v>
       </c>
       <c r="B46" t="n">
         <v>93174</v>
@@ -5407,14 +5407,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614881</v>
+        <v>614963</v>
       </c>
       <c r="R46" t="n">
-        <v>6560601</v>
+        <v>6560615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B47" t="n">
         <v>93174</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R47" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131739012</v>
       </c>
       <c r="B49" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>615022</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737677</v>
+        <v>131737616</v>
       </c>
       <c r="B50" t="n">
         <v>93174</v>
@@ -5811,14 +5811,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615064</v>
+        <v>614862</v>
       </c>
       <c r="R50" t="n">
-        <v>6560525</v>
+        <v>6560592</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737684</v>
+        <v>131737677</v>
       </c>
       <c r="B51" t="n">
         <v>93174</v>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615333</v>
+        <v>615064</v>
       </c>
       <c r="R51" t="n">
-        <v>6560608</v>
+        <v>6560525</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131739012</v>
+        <v>131737684</v>
       </c>
       <c r="B52" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,34 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615022</v>
+        <v>615333</v>
       </c>
       <c r="R52" t="n">
-        <v>6560527</v>
+        <v>6560608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737652</v>
+        <v>131737688</v>
       </c>
       <c r="B60" t="n">
         <v>93174</v>
@@ -6821,14 +6821,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615301</v>
+        <v>615310</v>
       </c>
       <c r="R60" t="n">
-        <v>6560755</v>
+        <v>6560543</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737688</v>
+        <v>131737652</v>
       </c>
       <c r="B61" t="n">
         <v>93174</v>
@@ -6922,14 +6922,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615310</v>
+        <v>615301</v>
       </c>
       <c r="R61" t="n">
-        <v>6560543</v>
+        <v>6560755</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131739010</v>
+        <v>131737667</v>
       </c>
       <c r="B68" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,21 +7609,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615012</v>
+        <v>614991</v>
       </c>
       <c r="R68" t="n">
-        <v>6560549</v>
+        <v>6560587</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737667</v>
+        <v>131740360</v>
       </c>
       <c r="B69" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614991</v>
+        <v>615296</v>
       </c>
       <c r="R69" t="n">
-        <v>6560587</v>
+        <v>6560688</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,12 +7772,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7800,10 +7806,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131740360</v>
+        <v>131737638</v>
       </c>
       <c r="B70" t="n">
-        <v>93165</v>
+        <v>93174</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7811,34 +7817,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>615296</v>
+        <v>614943</v>
       </c>
       <c r="R70" t="n">
-        <v>6560688</v>
+        <v>6560591</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7873,18 +7879,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7907,7 +7907,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737638</v>
+        <v>131737658</v>
       </c>
       <c r="B71" t="n">
         <v>93174</v>
@@ -7938,14 +7938,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614943</v>
+        <v>615282</v>
       </c>
       <c r="R71" t="n">
-        <v>6560591</v>
+        <v>6560684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131737658</v>
+        <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,34 +8019,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>615282</v>
+        <v>615012</v>
       </c>
       <c r="R72" t="n">
-        <v>6560684</v>
+        <v>6560549</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>131737668</v>
       </c>
       <c r="B74" t="n">
         <v>93174</v>
@@ -8241,14 +8241,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>614990</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560601</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>131738989</v>
       </c>
       <c r="B75" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>614945</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560637</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>131739041</v>
       </c>
       <c r="B76" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,34 +8423,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>615269</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560500</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8513,7 +8513,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738989</v>
+        <v>131739011</v>
       </c>
       <c r="B77" t="n">
         <v>79895</v>
@@ -8544,14 +8544,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614945</v>
+        <v>615080</v>
       </c>
       <c r="R77" t="n">
-        <v>6560637</v>
+        <v>6560512</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739041</v>
+        <v>131737644</v>
       </c>
       <c r="B78" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615269</v>
+        <v>615331</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560676</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739011</v>
+        <v>131737639</v>
       </c>
       <c r="B79" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615080</v>
+        <v>614942</v>
       </c>
       <c r="R79" t="n">
-        <v>6560512</v>
+        <v>6560579</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737674</v>
+        <v>131737624</v>
       </c>
       <c r="B81" t="n">
         <v>93174</v>
@@ -8948,14 +8948,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614965</v>
+        <v>614910</v>
       </c>
       <c r="R81" t="n">
-        <v>6560563</v>
+        <v>6560612</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9018,7 +9018,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737782</v>
+        <v>131737674</v>
       </c>
       <c r="B82" t="n">
         <v>93174</v>
@@ -9046,21 +9046,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>615216</v>
+        <v>614965</v>
       </c>
       <c r="R82" t="n">
-        <v>6560514</v>
+        <v>6560563</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9087,17 +9083,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9128,7 +9119,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737680</v>
+        <v>131737782</v>
       </c>
       <c r="B83" t="n">
         <v>93174</v>
@@ -9156,17 +9147,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>615390</v>
+        <v>615216</v>
       </c>
       <c r="R83" t="n">
-        <v>6560614</v>
+        <v>6560514</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9193,12 +9188,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9229,7 +9229,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737653</v>
+        <v>131737680</v>
       </c>
       <c r="B84" t="n">
         <v>93174</v>
@@ -9260,14 +9260,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>615289</v>
+        <v>615390</v>
       </c>
       <c r="R84" t="n">
-        <v>6560767</v>
+        <v>6560614</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737624</v>
+        <v>131737653</v>
       </c>
       <c r="B85" t="n">
         <v>93174</v>
@@ -9361,14 +9361,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614910</v>
+        <v>615289</v>
       </c>
       <c r="R85" t="n">
-        <v>6560612</v>
+        <v>6560767</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737626</v>
+        <v>131738988</v>
       </c>
       <c r="B86" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614911</v>
+        <v>614862</v>
       </c>
       <c r="R86" t="n">
-        <v>6560610</v>
+        <v>6560592</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737642</v>
+        <v>131737626</v>
       </c>
       <c r="B87" t="n">
         <v>93174</v>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614884</v>
+        <v>614911</v>
       </c>
       <c r="R87" t="n">
-        <v>6560568</v>
+        <v>6560610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,7 +9633,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737687</v>
+        <v>131737642</v>
       </c>
       <c r="B88" t="n">
         <v>93174</v>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>615322</v>
+        <v>614884</v>
       </c>
       <c r="R88" t="n">
-        <v>6560582</v>
+        <v>6560568</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131738988</v>
+        <v>131737687</v>
       </c>
       <c r="B89" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9745,34 +9745,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614862</v>
+        <v>615322</v>
       </c>
       <c r="R89" t="n">
-        <v>6560592</v>
+        <v>6560582</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737783</v>
+        <v>131738998</v>
       </c>
       <c r="B90" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,38 +9846,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615276</v>
+        <v>615020</v>
       </c>
       <c r="R90" t="n">
-        <v>6560495</v>
+        <v>6560533</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9904,17 +9900,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9945,7 +9936,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737641</v>
+        <v>131737656</v>
       </c>
       <c r="B91" t="n">
         <v>93174</v>
@@ -9976,14 +9967,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614893</v>
+        <v>615271</v>
       </c>
       <c r="R91" t="n">
-        <v>6560582</v>
+        <v>6560749</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10046,7 +10037,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737656</v>
+        <v>131737666</v>
       </c>
       <c r="B92" t="n">
         <v>93174</v>
@@ -10081,10 +10072,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615271</v>
+        <v>614995</v>
       </c>
       <c r="R92" t="n">
-        <v>6560749</v>
+        <v>6560571</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,7 +10138,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737666</v>
+        <v>131737676</v>
       </c>
       <c r="B93" t="n">
         <v>93174</v>
@@ -10178,14 +10169,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614995</v>
+        <v>615060</v>
       </c>
       <c r="R93" t="n">
-        <v>6560571</v>
+        <v>6560536</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,7 +10239,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737676</v>
+        <v>131737646</v>
       </c>
       <c r="B94" t="n">
         <v>93174</v>
@@ -10283,10 +10274,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615060</v>
+        <v>615289</v>
       </c>
       <c r="R94" t="n">
-        <v>6560536</v>
+        <v>6560695</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10349,7 +10340,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737646</v>
+        <v>131737690</v>
       </c>
       <c r="B95" t="n">
         <v>93174</v>
@@ -10384,10 +10375,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615289</v>
+        <v>615387</v>
       </c>
       <c r="R95" t="n">
-        <v>6560695</v>
+        <v>6560558</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,7 +10441,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737690</v>
+        <v>131737659</v>
       </c>
       <c r="B96" t="n">
         <v>93174</v>
@@ -10485,10 +10476,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615387</v>
+        <v>615267</v>
       </c>
       <c r="R96" t="n">
-        <v>6560558</v>
+        <v>6560667</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,7 +10542,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737659</v>
+        <v>131737649</v>
       </c>
       <c r="B97" t="n">
         <v>93174</v>
@@ -10586,10 +10577,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615267</v>
+        <v>615316</v>
       </c>
       <c r="R97" t="n">
-        <v>6560667</v>
+        <v>6560709</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,7 +10643,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737649</v>
+        <v>131737783</v>
       </c>
       <c r="B98" t="n">
         <v>93174</v>
@@ -10680,17 +10671,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615316</v>
+        <v>615276</v>
       </c>
       <c r="R98" t="n">
-        <v>6560709</v>
+        <v>6560495</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10717,12 +10712,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131738998</v>
+        <v>131737641</v>
       </c>
       <c r="B99" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615020</v>
+        <v>614893</v>
       </c>
       <c r="R99" t="n">
-        <v>6560533</v>
+        <v>6560582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B110" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,19 +11875,23 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11895,10 +11899,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R110" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11939,7 +11943,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11962,10 +11965,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131737627</v>
+        <v>131738990</v>
       </c>
       <c r="B111" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11973,21 +11976,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11997,10 +12000,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614921</v>
+        <v>614930</v>
       </c>
       <c r="R111" t="n">
-        <v>6560604</v>
+        <v>6560587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12063,10 +12066,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737648</v>
+        <v>131736566</v>
       </c>
       <c r="B112" t="n">
-        <v>93174</v>
+        <v>93152</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12074,34 +12077,38 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615306</v>
+        <v>615319</v>
       </c>
       <c r="R112" t="n">
-        <v>6560663</v>
+        <v>6560579</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12134,6 +12141,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12164,10 +12176,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737630</v>
+        <v>131740361</v>
       </c>
       <c r="B113" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12175,34 +12187,30 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614948</v>
+        <v>615309</v>
       </c>
       <c r="R113" t="n">
-        <v>6560611</v>
+        <v>6560557</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12243,6 +12251,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12265,10 +12274,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131736566</v>
+        <v>131737627</v>
       </c>
       <c r="B114" t="n">
-        <v>93152</v>
+        <v>93174</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12276,38 +12285,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615319</v>
+        <v>614921</v>
       </c>
       <c r="R114" t="n">
-        <v>6560579</v>
+        <v>6560604</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12340,11 +12345,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12375,10 +12375,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131737648</v>
       </c>
       <c r="B115" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12386,21 +12386,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12410,10 +12410,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>615306</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560663</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12476,10 +12476,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131737630</v>
       </c>
       <c r="B116" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12487,34 +12487,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>614948</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560611</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13609,7 +13609,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737678</v>
+        <v>131737681</v>
       </c>
       <c r="B127" t="n">
         <v>93174</v>
@@ -13640,14 +13640,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615054</v>
+        <v>615383</v>
       </c>
       <c r="R127" t="n">
-        <v>6560523</v>
+        <v>6560632</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737681</v>
+        <v>131737678</v>
       </c>
       <c r="B128" t="n">
         <v>93174</v>
@@ -13741,14 +13741,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615383</v>
+        <v>615054</v>
       </c>
       <c r="R128" t="n">
-        <v>6560632</v>
+        <v>6560523</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14013,7 +14013,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B131" t="n">
         <v>93174</v>
@@ -14044,14 +14044,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R131" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,10 +14114,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737663</v>
+        <v>131738996</v>
       </c>
       <c r="B132" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14125,34 +14125,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615046</v>
+        <v>615290</v>
       </c>
       <c r="R132" t="n">
-        <v>6560537</v>
+        <v>6560715</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737673</v>
+        <v>131737682</v>
       </c>
       <c r="B133" t="n">
         <v>93174</v>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>614957</v>
+        <v>615350</v>
       </c>
       <c r="R133" t="n">
-        <v>6560564</v>
+        <v>6560611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737661</v>
+        <v>131737673</v>
       </c>
       <c r="B134" t="n">
         <v>93174</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615060</v>
+        <v>614957</v>
       </c>
       <c r="R134" t="n">
-        <v>6560565</v>
+        <v>6560564</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,32 +14417,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131738996</v>
+        <v>131735760</v>
       </c>
       <c r="B135" t="n">
-        <v>79895</v>
+        <v>90613</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615290</v>
+        <v>615279</v>
       </c>
       <c r="R135" t="n">
-        <v>6560715</v>
+        <v>6560699</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,45 +14518,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131735760</v>
+        <v>131737661</v>
       </c>
       <c r="B136" t="n">
-        <v>90613</v>
+        <v>93174</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615279</v>
+        <v>615060</v>
       </c>
       <c r="R136" t="n">
-        <v>6560699</v>
+        <v>6560565</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737671</v>
+        <v>131739009</v>
       </c>
       <c r="B18" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614965</v>
+        <v>614998</v>
       </c>
       <c r="R18" t="n">
-        <v>6560580</v>
+        <v>6560540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737637</v>
+        <v>131739006</v>
       </c>
       <c r="B19" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614949</v>
+        <v>614970</v>
       </c>
       <c r="R19" t="n">
-        <v>6560610</v>
+        <v>6560568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131739009</v>
+        <v>131738992</v>
       </c>
       <c r="B20" t="n">
         <v>79895</v>
@@ -2745,14 +2745,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614998</v>
+        <v>614903</v>
       </c>
       <c r="R20" t="n">
-        <v>6560540</v>
+        <v>6560580</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131739006</v>
+        <v>131737671</v>
       </c>
       <c r="B21" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614970</v>
+        <v>614965</v>
       </c>
       <c r="R21" t="n">
-        <v>6560568</v>
+        <v>6560580</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131738992</v>
+        <v>131737631</v>
       </c>
       <c r="B22" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,34 +2927,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614903</v>
+        <v>614937</v>
       </c>
       <c r="R22" t="n">
-        <v>6560580</v>
+        <v>6560625</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737631</v>
+        <v>131737632</v>
       </c>
       <c r="B23" t="n">
         <v>93174</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614937</v>
+        <v>614949</v>
       </c>
       <c r="R23" t="n">
-        <v>6560625</v>
+        <v>6560635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737632</v>
+        <v>131737647</v>
       </c>
       <c r="B24" t="n">
         <v>93174</v>
@@ -3149,14 +3149,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614949</v>
+        <v>615295</v>
       </c>
       <c r="R24" t="n">
-        <v>6560635</v>
+        <v>6560678</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737647</v>
+        <v>131737637</v>
       </c>
       <c r="B25" t="n">
         <v>93174</v>
@@ -3250,14 +3250,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615295</v>
+        <v>614949</v>
       </c>
       <c r="R25" t="n">
-        <v>6560678</v>
+        <v>6560610</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737784</v>
+        <v>131738991</v>
       </c>
       <c r="B29" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,38 +3634,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615291</v>
+        <v>614921</v>
       </c>
       <c r="R29" t="n">
-        <v>6560497</v>
+        <v>6560577</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3692,17 +3688,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,10 +3724,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737629</v>
+        <v>131739043</v>
       </c>
       <c r="B30" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3744,21 +3735,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3768,10 +3759,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614941</v>
+        <v>614985</v>
       </c>
       <c r="R30" t="n">
-        <v>6560607</v>
+        <v>6560565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,12 +3789,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737787</v>
+        <v>131739007</v>
       </c>
       <c r="B31" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,38 +3836,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615336</v>
+        <v>614970</v>
       </c>
       <c r="R31" t="n">
-        <v>6560522</v>
+        <v>6560560</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,17 +3890,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,7 +3926,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737651</v>
+        <v>131737787</v>
       </c>
       <c r="B32" t="n">
         <v>93174</v>
@@ -3972,17 +3954,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615311</v>
+        <v>615336</v>
       </c>
       <c r="R32" t="n">
-        <v>6560742</v>
+        <v>6560522</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4009,12 +3995,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,7 +4036,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737785</v>
+        <v>131737651</v>
       </c>
       <c r="B33" t="n">
         <v>93174</v>
@@ -4073,21 +4064,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615314</v>
+        <v>615311</v>
       </c>
       <c r="R33" t="n">
-        <v>6560513</v>
+        <v>6560742</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,17 +4101,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4155,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738991</v>
+        <v>131737785</v>
       </c>
       <c r="B34" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4166,34 +4148,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614921</v>
+        <v>615314</v>
       </c>
       <c r="R34" t="n">
-        <v>6560577</v>
+        <v>6560513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,12 +4206,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4256,10 +4247,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131739043</v>
+        <v>131737784</v>
       </c>
       <c r="B35" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4267,34 +4258,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614985</v>
+        <v>615291</v>
       </c>
       <c r="R35" t="n">
-        <v>6560565</v>
+        <v>6560497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4321,12 +4316,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739007</v>
+        <v>131737629</v>
       </c>
       <c r="B36" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614970</v>
+        <v>614941</v>
       </c>
       <c r="R36" t="n">
-        <v>6560560</v>
+        <v>6560607</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737786</v>
+        <v>131737672</v>
       </c>
       <c r="B38" t="n">
         <v>93174</v>
@@ -4587,21 +4587,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615335</v>
+        <v>614950</v>
       </c>
       <c r="R38" t="n">
-        <v>6560536</v>
+        <v>6560576</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,17 +4624,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,7 +4660,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737662</v>
+        <v>131737786</v>
       </c>
       <c r="B39" t="n">
         <v>93174</v>
@@ -4697,17 +4688,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615040</v>
+        <v>615335</v>
       </c>
       <c r="R39" t="n">
-        <v>6560530</v>
+        <v>6560536</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4734,12 +4729,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4770,7 +4770,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737620</v>
+        <v>131737662</v>
       </c>
       <c r="B40" t="n">
         <v>93174</v>
@@ -4801,14 +4801,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614896</v>
+        <v>615040</v>
       </c>
       <c r="R40" t="n">
-        <v>6560613</v>
+        <v>6560530</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737634</v>
+        <v>131737620</v>
       </c>
       <c r="B41" t="n">
         <v>93174</v>
@@ -4902,14 +4902,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614954</v>
+        <v>614896</v>
       </c>
       <c r="R41" t="n">
-        <v>6560617</v>
+        <v>6560613</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737669</v>
+        <v>131737634</v>
       </c>
       <c r="B42" t="n">
         <v>93174</v>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614973</v>
+        <v>614954</v>
       </c>
       <c r="R42" t="n">
-        <v>6560600</v>
+        <v>6560617</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737660</v>
+        <v>131737669</v>
       </c>
       <c r="B43" t="n">
         <v>93174</v>
@@ -5104,14 +5104,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>615278</v>
+        <v>614973</v>
       </c>
       <c r="R43" t="n">
-        <v>6560662</v>
+        <v>6560600</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737640</v>
+        <v>131737660</v>
       </c>
       <c r="B44" t="n">
         <v>93174</v>
@@ -5205,14 +5205,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614934</v>
+        <v>615278</v>
       </c>
       <c r="R44" t="n">
-        <v>6560578</v>
+        <v>6560662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737672</v>
+        <v>131737640</v>
       </c>
       <c r="B45" t="n">
         <v>93174</v>
@@ -5306,14 +5306,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614950</v>
+        <v>614934</v>
       </c>
       <c r="R45" t="n">
-        <v>6560576</v>
+        <v>6560578</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737688</v>
+        <v>131739005</v>
       </c>
       <c r="B60" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,34 +6801,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615310</v>
+        <v>614968</v>
       </c>
       <c r="R60" t="n">
-        <v>6560543</v>
+        <v>6560572</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131738993</v>
+        <v>131737688</v>
       </c>
       <c r="B62" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614904</v>
+        <v>615310</v>
       </c>
       <c r="R62" t="n">
-        <v>6560578</v>
+        <v>6560543</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739008</v>
+        <v>131738993</v>
       </c>
       <c r="B63" t="n">
         <v>79895</v>
@@ -7124,14 +7124,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614995</v>
+        <v>614904</v>
       </c>
       <c r="R63" t="n">
-        <v>6560547</v>
+        <v>6560578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739005</v>
+        <v>131739008</v>
       </c>
       <c r="B64" t="n">
         <v>79895</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614968</v>
+        <v>614995</v>
       </c>
       <c r="R64" t="n">
-        <v>6560572</v>
+        <v>6560547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131736575</v>
+        <v>131737686</v>
       </c>
       <c r="B65" t="n">
-        <v>93152</v>
+        <v>93174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7306,21 +7306,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615336</v>
+        <v>615314</v>
       </c>
       <c r="R65" t="n">
-        <v>6560577</v>
+        <v>6560599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,7 +7396,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737686</v>
+        <v>131737643</v>
       </c>
       <c r="B66" t="n">
         <v>93174</v>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615314</v>
+        <v>615322</v>
       </c>
       <c r="R66" t="n">
-        <v>6560599</v>
+        <v>6560634</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737643</v>
+        <v>131736575</v>
       </c>
       <c r="B67" t="n">
-        <v>93174</v>
+        <v>93152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615322</v>
+        <v>615336</v>
       </c>
       <c r="R67" t="n">
-        <v>6560634</v>
+        <v>6560577</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737667</v>
+        <v>131739010</v>
       </c>
       <c r="B68" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7609,21 +7609,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614991</v>
+        <v>615012</v>
       </c>
       <c r="R68" t="n">
-        <v>6560587</v>
+        <v>6560549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131740360</v>
+        <v>131739015</v>
       </c>
       <c r="B69" t="n">
-        <v>93165</v>
+        <v>79895</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7710,34 +7710,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615296</v>
+        <v>615373</v>
       </c>
       <c r="R69" t="n">
-        <v>6560688</v>
+        <v>6560555</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,18 +7772,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7806,7 +7800,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737638</v>
+        <v>131737667</v>
       </c>
       <c r="B70" t="n">
         <v>93174</v>
@@ -7841,10 +7835,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614943</v>
+        <v>614991</v>
       </c>
       <c r="R70" t="n">
-        <v>6560591</v>
+        <v>6560587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,10 +7901,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737658</v>
+        <v>131740360</v>
       </c>
       <c r="B71" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7918,34 +7912,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615282</v>
+        <v>615296</v>
       </c>
       <c r="R71" t="n">
-        <v>6560684</v>
+        <v>6560688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7980,12 +7974,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8008,10 +8008,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739010</v>
+        <v>131737638</v>
       </c>
       <c r="B72" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>615012</v>
+        <v>614943</v>
       </c>
       <c r="R72" t="n">
-        <v>6560549</v>
+        <v>6560591</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131739015</v>
+        <v>131737658</v>
       </c>
       <c r="B73" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615373</v>
+        <v>615282</v>
       </c>
       <c r="R73" t="n">
-        <v>6560555</v>
+        <v>6560684</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737668</v>
+        <v>131739041</v>
       </c>
       <c r="B74" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,34 +8221,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614990</v>
+        <v>615269</v>
       </c>
       <c r="R74" t="n">
-        <v>6560601</v>
+        <v>6560500</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8311,7 +8311,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131738989</v>
+        <v>131739011</v>
       </c>
       <c r="B75" t="n">
         <v>79895</v>
@@ -8342,14 +8342,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614945</v>
+        <v>615080</v>
       </c>
       <c r="R75" t="n">
-        <v>6560637</v>
+        <v>6560512</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131739041</v>
+        <v>131737644</v>
       </c>
       <c r="B76" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8423,21 +8423,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615269</v>
+        <v>615331</v>
       </c>
       <c r="R76" t="n">
-        <v>6560500</v>
+        <v>6560676</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131739011</v>
+        <v>131737639</v>
       </c>
       <c r="B77" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,34 +8524,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615080</v>
+        <v>614942</v>
       </c>
       <c r="R77" t="n">
-        <v>6560512</v>
+        <v>6560579</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737644</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,34 +8625,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615331</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560676</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8715,7 +8715,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737639</v>
+        <v>131737668</v>
       </c>
       <c r="B79" t="n">
         <v>93174</v>
@@ -8746,14 +8746,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614942</v>
+        <v>614990</v>
       </c>
       <c r="R79" t="n">
-        <v>6560579</v>
+        <v>6560601</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737624</v>
+        <v>131737674</v>
       </c>
       <c r="B81" t="n">
         <v>93174</v>
@@ -8948,14 +8948,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614910</v>
+        <v>614965</v>
       </c>
       <c r="R81" t="n">
-        <v>6560612</v>
+        <v>6560563</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9018,7 +9018,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737674</v>
+        <v>131737782</v>
       </c>
       <c r="B82" t="n">
         <v>93174</v>
@@ -9046,17 +9046,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>614965</v>
+        <v>615216</v>
       </c>
       <c r="R82" t="n">
-        <v>6560563</v>
+        <v>6560514</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9083,12 +9087,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9119,7 +9128,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737782</v>
+        <v>131737680</v>
       </c>
       <c r="B83" t="n">
         <v>93174</v>
@@ -9147,21 +9156,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>615216</v>
+        <v>615390</v>
       </c>
       <c r="R83" t="n">
-        <v>6560514</v>
+        <v>6560614</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9188,17 +9193,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9229,7 +9229,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737680</v>
+        <v>131737653</v>
       </c>
       <c r="B84" t="n">
         <v>93174</v>
@@ -9260,14 +9260,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>615390</v>
+        <v>615289</v>
       </c>
       <c r="R84" t="n">
-        <v>6560614</v>
+        <v>6560767</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737653</v>
+        <v>131737624</v>
       </c>
       <c r="B85" t="n">
         <v>93174</v>
@@ -9361,14 +9361,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>615289</v>
+        <v>614910</v>
       </c>
       <c r="R85" t="n">
-        <v>6560767</v>
+        <v>6560612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131738998</v>
+        <v>131737641</v>
       </c>
       <c r="B90" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,34 +9846,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615020</v>
+        <v>614893</v>
       </c>
       <c r="R90" t="n">
-        <v>6560533</v>
+        <v>6560582</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737656</v>
+        <v>131738998</v>
       </c>
       <c r="B91" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9947,21 +9947,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9971,10 +9971,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615271</v>
+        <v>615020</v>
       </c>
       <c r="R91" t="n">
-        <v>6560749</v>
+        <v>6560533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10037,7 +10037,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737666</v>
+        <v>131737783</v>
       </c>
       <c r="B92" t="n">
         <v>93174</v>
@@ -10065,17 +10065,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614995</v>
+        <v>615276</v>
       </c>
       <c r="R92" t="n">
-        <v>6560571</v>
+        <v>6560495</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10102,12 +10106,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10138,7 +10147,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737676</v>
+        <v>131737656</v>
       </c>
       <c r="B93" t="n">
         <v>93174</v>
@@ -10169,14 +10178,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615060</v>
+        <v>615271</v>
       </c>
       <c r="R93" t="n">
-        <v>6560536</v>
+        <v>6560749</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10239,7 +10248,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737646</v>
+        <v>131737666</v>
       </c>
       <c r="B94" t="n">
         <v>93174</v>
@@ -10270,14 +10279,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615289</v>
+        <v>614995</v>
       </c>
       <c r="R94" t="n">
-        <v>6560695</v>
+        <v>6560571</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10340,7 +10349,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737690</v>
+        <v>131737676</v>
       </c>
       <c r="B95" t="n">
         <v>93174</v>
@@ -10375,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615387</v>
+        <v>615060</v>
       </c>
       <c r="R95" t="n">
-        <v>6560558</v>
+        <v>6560536</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10441,7 +10450,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737659</v>
+        <v>131737646</v>
       </c>
       <c r="B96" t="n">
         <v>93174</v>
@@ -10476,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615267</v>
+        <v>615289</v>
       </c>
       <c r="R96" t="n">
-        <v>6560667</v>
+        <v>6560695</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10542,7 +10551,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737649</v>
+        <v>131737690</v>
       </c>
       <c r="B97" t="n">
         <v>93174</v>
@@ -10577,10 +10586,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615316</v>
+        <v>615387</v>
       </c>
       <c r="R97" t="n">
-        <v>6560709</v>
+        <v>6560558</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10643,7 +10652,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737783</v>
+        <v>131737659</v>
       </c>
       <c r="B98" t="n">
         <v>93174</v>
@@ -10671,21 +10680,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615276</v>
+        <v>615267</v>
       </c>
       <c r="R98" t="n">
-        <v>6560495</v>
+        <v>6560667</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10712,17 +10717,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10753,7 +10753,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737641</v>
+        <v>131737649</v>
       </c>
       <c r="B99" t="n">
         <v>93174</v>
@@ -10784,14 +10784,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>614893</v>
+        <v>615316</v>
       </c>
       <c r="R99" t="n">
-        <v>6560582</v>
+        <v>6560709</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739013</v>
+        <v>131737655</v>
       </c>
       <c r="B100" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615376</v>
+        <v>615267</v>
       </c>
       <c r="R100" t="n">
-        <v>6560556</v>
+        <v>6560777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739004</v>
+        <v>131737636</v>
       </c>
       <c r="B101" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,21 +10966,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614958</v>
+        <v>614960</v>
       </c>
       <c r="R101" t="n">
-        <v>6560561</v>
+        <v>6560601</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739001</v>
+        <v>131737645</v>
       </c>
       <c r="B102" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614955</v>
+        <v>615304</v>
       </c>
       <c r="R102" t="n">
-        <v>6560579</v>
+        <v>6560686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737625</v>
+        <v>131737691</v>
       </c>
       <c r="B103" t="n">
         <v>93174</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614918</v>
+        <v>615367</v>
       </c>
       <c r="R103" t="n">
-        <v>6560620</v>
+        <v>6560553</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737645</v>
+        <v>131737619</v>
       </c>
       <c r="B104" t="n">
         <v>93174</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615304</v>
+        <v>614885</v>
       </c>
       <c r="R104" t="n">
-        <v>6560686</v>
+        <v>6560613</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737655</v>
+        <v>131737664</v>
       </c>
       <c r="B105" t="n">
         <v>93174</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615267</v>
+        <v>614942</v>
       </c>
       <c r="R105" t="n">
-        <v>6560777</v>
+        <v>6560568</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737636</v>
+        <v>131739013</v>
       </c>
       <c r="B106" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614960</v>
+        <v>615376</v>
       </c>
       <c r="R106" t="n">
-        <v>6560601</v>
+        <v>6560556</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739004</v>
       </c>
       <c r="B107" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,34 +11572,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>614958</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737619</v>
+        <v>131739001</v>
       </c>
       <c r="B108" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614885</v>
+        <v>614955</v>
       </c>
       <c r="R108" t="n">
-        <v>6560613</v>
+        <v>6560579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737664</v>
+        <v>131737625</v>
       </c>
       <c r="B109" t="n">
         <v>93174</v>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614942</v>
+        <v>614918</v>
       </c>
       <c r="R109" t="n">
-        <v>6560568</v>
+        <v>6560620</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131738995</v>
+        <v>131736566</v>
       </c>
       <c r="B110" t="n">
-        <v>79895</v>
+        <v>93152</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,34 +11875,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615323</v>
+        <v>615319</v>
       </c>
       <c r="R110" t="n">
-        <v>6560647</v>
+        <v>6560579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11935,6 +11939,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11965,7 +11974,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738990</v>
+        <v>131738995</v>
       </c>
       <c r="B111" t="n">
         <v>79895</v>
@@ -11996,14 +12005,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>614930</v>
+        <v>615323</v>
       </c>
       <c r="R111" t="n">
-        <v>6560587</v>
+        <v>6560647</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12066,10 +12075,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131736566</v>
+        <v>131738990</v>
       </c>
       <c r="B112" t="n">
-        <v>93152</v>
+        <v>79895</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12077,38 +12086,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615319</v>
+        <v>614930</v>
       </c>
       <c r="R112" t="n">
-        <v>6560579</v>
+        <v>6560587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12141,11 +12146,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131740081</v>
+        <v>131737665</v>
       </c>
       <c r="B118" t="n">
-        <v>91869</v>
+        <v>93174</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614974</v>
+        <v>614993</v>
       </c>
       <c r="R118" t="n">
-        <v>6560628</v>
+        <v>6560559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131739003</v>
+        <v>131737670</v>
       </c>
       <c r="B119" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614959</v>
+        <v>614972</v>
       </c>
       <c r="R119" t="n">
-        <v>6560556</v>
+        <v>6560590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737665</v>
+        <v>131739003</v>
       </c>
       <c r="B120" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614993</v>
+        <v>614959</v>
       </c>
       <c r="R120" t="n">
-        <v>6560559</v>
+        <v>6560556</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737670</v>
+        <v>131740081</v>
       </c>
       <c r="B121" t="n">
-        <v>93174</v>
+        <v>91869</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614972</v>
+        <v>614974</v>
       </c>
       <c r="R121" t="n">
-        <v>6560590</v>
+        <v>6560628</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13059,12 +13059,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13095,45 +13095,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131739000</v>
+        <v>131735761</v>
       </c>
       <c r="B122" t="n">
-        <v>79895</v>
+        <v>90613</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614941</v>
+        <v>615277</v>
       </c>
       <c r="R122" t="n">
-        <v>6560553</v>
+        <v>6560691</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13166,6 +13170,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13196,49 +13205,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131735761</v>
+        <v>131738994</v>
       </c>
       <c r="B123" t="n">
-        <v>90613</v>
+        <v>79895</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>615277</v>
+        <v>614890</v>
       </c>
       <c r="R123" t="n">
-        <v>6560691</v>
+        <v>6560564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13271,11 +13276,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13306,7 +13306,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131738994</v>
+        <v>131739000</v>
       </c>
       <c r="B124" t="n">
         <v>79895</v>
@@ -13341,10 +13341,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614890</v>
+        <v>614941</v>
       </c>
       <c r="R124" t="n">
-        <v>6560564</v>
+        <v>6560553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13407,10 +13407,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737622</v>
+        <v>131739026</v>
       </c>
       <c r="B125" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13418,34 +13418,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614898</v>
+        <v>615203</v>
       </c>
       <c r="R125" t="n">
-        <v>6560601</v>
+        <v>6560503</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13472,12 +13472,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13508,10 +13508,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737683</v>
+        <v>131738997</v>
       </c>
       <c r="B126" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13519,34 +13519,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615337</v>
+        <v>615026</v>
       </c>
       <c r="R126" t="n">
-        <v>6560617</v>
+        <v>6560531</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13609,7 +13609,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737681</v>
+        <v>131737622</v>
       </c>
       <c r="B127" t="n">
         <v>93174</v>
@@ -13640,14 +13640,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615383</v>
+        <v>614898</v>
       </c>
       <c r="R127" t="n">
-        <v>6560632</v>
+        <v>6560601</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737678</v>
+        <v>131737683</v>
       </c>
       <c r="B128" t="n">
         <v>93174</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615054</v>
+        <v>615337</v>
       </c>
       <c r="R128" t="n">
-        <v>6560523</v>
+        <v>6560617</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13811,10 +13811,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131739026</v>
+        <v>131737678</v>
       </c>
       <c r="B129" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13822,21 +13822,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13846,10 +13846,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615203</v>
+        <v>615054</v>
       </c>
       <c r="R129" t="n">
-        <v>6560503</v>
+        <v>6560523</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13876,12 +13876,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13912,10 +13912,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131738997</v>
+        <v>131737681</v>
       </c>
       <c r="B130" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13923,34 +13923,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615026</v>
+        <v>615383</v>
       </c>
       <c r="R130" t="n">
-        <v>6560531</v>
+        <v>6560632</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14013,45 +14013,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737663</v>
+        <v>131735760</v>
       </c>
       <c r="B131" t="n">
-        <v>93174</v>
+        <v>90613</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615046</v>
+        <v>615279</v>
       </c>
       <c r="R131" t="n">
-        <v>6560537</v>
+        <v>6560699</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737673</v>
+        <v>131737663</v>
       </c>
       <c r="B134" t="n">
         <v>93174</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614957</v>
+        <v>615046</v>
       </c>
       <c r="R134" t="n">
-        <v>6560564</v>
+        <v>6560537</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,45 +14417,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131735760</v>
+        <v>131737673</v>
       </c>
       <c r="B135" t="n">
-        <v>90613</v>
+        <v>93174</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615279</v>
+        <v>614957</v>
       </c>
       <c r="R135" t="n">
-        <v>6560699</v>
+        <v>6560564</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739005</v>
+        <v>131738993</v>
       </c>
       <c r="B60" t="n">
         <v>79895</v>
@@ -6821,14 +6821,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614968</v>
+        <v>614904</v>
       </c>
       <c r="R60" t="n">
-        <v>6560572</v>
+        <v>6560578</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737652</v>
+        <v>131739008</v>
       </c>
       <c r="B61" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,21 +6902,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615301</v>
+        <v>614995</v>
       </c>
       <c r="R61" t="n">
-        <v>6560755</v>
+        <v>6560547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737688</v>
+        <v>131739005</v>
       </c>
       <c r="B62" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615310</v>
+        <v>614968</v>
       </c>
       <c r="R62" t="n">
-        <v>6560543</v>
+        <v>6560572</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B63" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,34 +7104,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R63" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739008</v>
+        <v>131737688</v>
       </c>
       <c r="B64" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7205,34 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614995</v>
+        <v>615310</v>
       </c>
       <c r="R64" t="n">
-        <v>6560547</v>
+        <v>6560543</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737655</v>
+        <v>131739013</v>
       </c>
       <c r="B100" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615267</v>
+        <v>615376</v>
       </c>
       <c r="R100" t="n">
-        <v>6560777</v>
+        <v>6560556</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737636</v>
+        <v>131739004</v>
       </c>
       <c r="B101" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,21 +10966,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614960</v>
+        <v>614958</v>
       </c>
       <c r="R101" t="n">
-        <v>6560601</v>
+        <v>6560561</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737645</v>
+        <v>131739001</v>
       </c>
       <c r="B102" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615304</v>
+        <v>614955</v>
       </c>
       <c r="R102" t="n">
-        <v>6560686</v>
+        <v>6560579</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737691</v>
+        <v>131737625</v>
       </c>
       <c r="B103" t="n">
         <v>93174</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615367</v>
+        <v>614918</v>
       </c>
       <c r="R103" t="n">
-        <v>6560553</v>
+        <v>6560620</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737619</v>
+        <v>131737645</v>
       </c>
       <c r="B104" t="n">
         <v>93174</v>
@@ -11289,14 +11289,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614885</v>
+        <v>615304</v>
       </c>
       <c r="R104" t="n">
-        <v>6560613</v>
+        <v>6560686</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737664</v>
+        <v>131737655</v>
       </c>
       <c r="B105" t="n">
         <v>93174</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614942</v>
+        <v>615267</v>
       </c>
       <c r="R105" t="n">
-        <v>6560568</v>
+        <v>6560777</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,10 +11460,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131739013</v>
+        <v>131737636</v>
       </c>
       <c r="B106" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11471,34 +11471,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615376</v>
+        <v>614960</v>
       </c>
       <c r="R106" t="n">
-        <v>6560556</v>
+        <v>6560601</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739004</v>
+        <v>131737691</v>
       </c>
       <c r="B107" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,34 +11572,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614958</v>
+        <v>615367</v>
       </c>
       <c r="R107" t="n">
-        <v>6560561</v>
+        <v>6560553</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739001</v>
+        <v>131737619</v>
       </c>
       <c r="B108" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614955</v>
+        <v>614885</v>
       </c>
       <c r="R108" t="n">
-        <v>6560579</v>
+        <v>6560613</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737625</v>
+        <v>131737664</v>
       </c>
       <c r="B109" t="n">
         <v>93174</v>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614918</v>
+        <v>614942</v>
       </c>
       <c r="R109" t="n">
-        <v>6560620</v>
+        <v>6560568</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737665</v>
+        <v>131739003</v>
       </c>
       <c r="B118" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614993</v>
+        <v>614959</v>
       </c>
       <c r="R118" t="n">
-        <v>6560559</v>
+        <v>6560556</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737670</v>
+        <v>131740081</v>
       </c>
       <c r="B119" t="n">
-        <v>93174</v>
+        <v>91869</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614972</v>
+        <v>614974</v>
       </c>
       <c r="R119" t="n">
-        <v>6560590</v>
+        <v>6560628</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12893,10 +12893,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131739003</v>
+        <v>131737665</v>
       </c>
       <c r="B120" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614959</v>
+        <v>614993</v>
       </c>
       <c r="R120" t="n">
-        <v>6560556</v>
+        <v>6560559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131740081</v>
+        <v>131737670</v>
       </c>
       <c r="B121" t="n">
-        <v>91869</v>
+        <v>93174</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614974</v>
+        <v>614972</v>
       </c>
       <c r="R121" t="n">
-        <v>6560628</v>
+        <v>6560590</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13059,12 +13059,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -6790,7 +6790,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131738993</v>
+        <v>131739005</v>
       </c>
       <c r="B60" t="n">
         <v>79895</v>
@@ -6821,14 +6821,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614904</v>
+        <v>614968</v>
       </c>
       <c r="R60" t="n">
-        <v>6560578</v>
+        <v>6560572</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131739008</v>
+        <v>131737652</v>
       </c>
       <c r="B61" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,21 +6902,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614995</v>
+        <v>615301</v>
       </c>
       <c r="R61" t="n">
-        <v>6560547</v>
+        <v>6560755</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739005</v>
+        <v>131737688</v>
       </c>
       <c r="B62" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614968</v>
+        <v>615310</v>
       </c>
       <c r="R62" t="n">
-        <v>6560572</v>
+        <v>6560543</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131737652</v>
+        <v>131738993</v>
       </c>
       <c r="B63" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,34 +7104,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>615301</v>
+        <v>614904</v>
       </c>
       <c r="R63" t="n">
-        <v>6560755</v>
+        <v>6560578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131737688</v>
+        <v>131739008</v>
       </c>
       <c r="B64" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7205,34 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>615310</v>
+        <v>614995</v>
       </c>
       <c r="R64" t="n">
-        <v>6560543</v>
+        <v>6560547</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737641</v>
+        <v>131738998</v>
       </c>
       <c r="B90" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,34 +9846,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>614893</v>
+        <v>615020</v>
       </c>
       <c r="R90" t="n">
-        <v>6560582</v>
+        <v>6560533</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131738998</v>
+        <v>131737783</v>
       </c>
       <c r="B91" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9947,34 +9947,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615020</v>
+        <v>615276</v>
       </c>
       <c r="R91" t="n">
-        <v>6560533</v>
+        <v>6560495</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10001,12 +10005,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10037,7 +10046,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737783</v>
+        <v>131737641</v>
       </c>
       <c r="B92" t="n">
         <v>93174</v>
@@ -10065,21 +10074,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615276</v>
+        <v>614893</v>
       </c>
       <c r="R92" t="n">
-        <v>6560495</v>
+        <v>6560582</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10106,17 +10111,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12176,41 +12176,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131740361</v>
+        <v>131740030</v>
       </c>
       <c r="B113" t="n">
-        <v>93165</v>
+        <v>57102</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615309</v>
+        <v>614953</v>
       </c>
       <c r="R113" t="n">
-        <v>6560557</v>
+        <v>6560578</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12245,13 +12257,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12274,10 +12290,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737627</v>
+        <v>131740361</v>
       </c>
       <c r="B114" t="n">
-        <v>93174</v>
+        <v>93165</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12285,34 +12301,30 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614921</v>
+        <v>615309</v>
       </c>
       <c r="R114" t="n">
-        <v>6560604</v>
+        <v>6560557</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12353,6 +12365,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12375,7 +12388,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737648</v>
+        <v>131737627</v>
       </c>
       <c r="B115" t="n">
         <v>93174</v>
@@ -12406,14 +12419,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615306</v>
+        <v>614921</v>
       </c>
       <c r="R115" t="n">
-        <v>6560663</v>
+        <v>6560604</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12476,7 +12489,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737630</v>
+        <v>131737648</v>
       </c>
       <c r="B116" t="n">
         <v>93174</v>
@@ -12507,14 +12520,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614948</v>
+        <v>615306</v>
       </c>
       <c r="R116" t="n">
-        <v>6560611</v>
+        <v>6560663</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12577,53 +12590,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131740030</v>
+        <v>131737630</v>
       </c>
       <c r="B117" t="n">
-        <v>57102</v>
+        <v>93174</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614953</v>
+        <v>614948</v>
       </c>
       <c r="R117" t="n">
-        <v>6560578</v>
+        <v>6560611</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12656,11 +12661,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -3623,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738991</v>
+        <v>131737787</v>
       </c>
       <c r="B29" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,34 +3634,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614921</v>
+        <v>615336</v>
       </c>
       <c r="R29" t="n">
-        <v>6560577</v>
+        <v>6560522</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,12 +3692,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131739043</v>
+        <v>131737651</v>
       </c>
       <c r="B30" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,34 +3744,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614985</v>
+        <v>615311</v>
       </c>
       <c r="R30" t="n">
-        <v>6560565</v>
+        <v>6560742</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3789,12 +3798,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3834,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131739007</v>
+        <v>131737785</v>
       </c>
       <c r="B31" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,34 +3845,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614970</v>
+        <v>615314</v>
       </c>
       <c r="R31" t="n">
-        <v>6560560</v>
+        <v>6560513</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,12 +3903,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3926,7 +3944,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737787</v>
+        <v>131737784</v>
       </c>
       <c r="B32" t="n">
         <v>93174</v>
@@ -3956,7 +3974,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3965,10 +3983,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615336</v>
+        <v>615291</v>
       </c>
       <c r="R32" t="n">
-        <v>6560522</v>
+        <v>6560497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4005,7 +4023,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737651</v>
+        <v>131737629</v>
       </c>
       <c r="B33" t="n">
         <v>93174</v>
@@ -4067,14 +4085,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>615311</v>
+        <v>614941</v>
       </c>
       <c r="R33" t="n">
-        <v>6560742</v>
+        <v>6560607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,10 +4155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737785</v>
+        <v>131738991</v>
       </c>
       <c r="B34" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,38 +4166,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>615314</v>
+        <v>614921</v>
       </c>
       <c r="R34" t="n">
-        <v>6560513</v>
+        <v>6560577</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,17 +4220,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4247,10 +4256,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737784</v>
+        <v>131739043</v>
       </c>
       <c r="B35" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4258,38 +4267,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>615291</v>
+        <v>614985</v>
       </c>
       <c r="R35" t="n">
-        <v>6560497</v>
+        <v>6560565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,17 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737629</v>
+        <v>131739007</v>
       </c>
       <c r="B36" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614941</v>
+        <v>614970</v>
       </c>
       <c r="R36" t="n">
-        <v>6560607</v>
+        <v>6560560</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737635</v>
+        <v>131739002</v>
       </c>
       <c r="B46" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614963</v>
+        <v>614953</v>
       </c>
       <c r="R46" t="n">
-        <v>6560615</v>
+        <v>6560567</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737618</v>
+        <v>131737635</v>
       </c>
       <c r="B47" t="n">
         <v>93174</v>
@@ -5508,14 +5508,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614881</v>
+        <v>614963</v>
       </c>
       <c r="R47" t="n">
-        <v>6560601</v>
+        <v>6560615</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131739002</v>
+        <v>131737618</v>
       </c>
       <c r="B48" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5589,34 +5589,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614953</v>
+        <v>614881</v>
       </c>
       <c r="R48" t="n">
-        <v>6560567</v>
+        <v>6560601</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131739012</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615022</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560527</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
         <v>93174</v>
@@ -5811,14 +5811,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737677</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
         <v>93174</v>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615064</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560525</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B52" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,34 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R52" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131739005</v>
+        <v>131738993</v>
       </c>
       <c r="B60" t="n">
         <v>79895</v>
@@ -6821,14 +6821,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614968</v>
+        <v>614904</v>
       </c>
       <c r="R60" t="n">
-        <v>6560572</v>
+        <v>6560578</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737652</v>
+        <v>131739008</v>
       </c>
       <c r="B61" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,21 +6902,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615301</v>
+        <v>614995</v>
       </c>
       <c r="R61" t="n">
-        <v>6560755</v>
+        <v>6560547</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131737688</v>
+        <v>131739005</v>
       </c>
       <c r="B62" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7003,34 +7003,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>615310</v>
+        <v>614968</v>
       </c>
       <c r="R62" t="n">
-        <v>6560543</v>
+        <v>6560572</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131738993</v>
+        <v>131737652</v>
       </c>
       <c r="B63" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7104,34 +7104,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614904</v>
+        <v>615301</v>
       </c>
       <c r="R63" t="n">
-        <v>6560578</v>
+        <v>6560755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739008</v>
+        <v>131737688</v>
       </c>
       <c r="B64" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7205,34 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614995</v>
+        <v>615310</v>
       </c>
       <c r="R64" t="n">
-        <v>6560547</v>
+        <v>6560543</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131739041</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8221,21 +8221,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615269</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560500</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8311,10 +8311,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739011</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8322,34 +8322,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615080</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560512</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737644</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
         <v>93174</v>
@@ -8443,14 +8443,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615331</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560676</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737639</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8524,34 +8524,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614942</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560579</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
         <v>79895</v>
@@ -8645,14 +8645,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737668</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614990</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560601</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131738988</v>
+        <v>131737626</v>
       </c>
       <c r="B86" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614862</v>
+        <v>614911</v>
       </c>
       <c r="R86" t="n">
-        <v>6560592</v>
+        <v>6560610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737626</v>
+        <v>131737642</v>
       </c>
       <c r="B87" t="n">
         <v>93174</v>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614911</v>
+        <v>614884</v>
       </c>
       <c r="R87" t="n">
-        <v>6560610</v>
+        <v>6560568</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9633,7 +9633,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737642</v>
+        <v>131737687</v>
       </c>
       <c r="B88" t="n">
         <v>93174</v>
@@ -9664,14 +9664,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614884</v>
+        <v>615322</v>
       </c>
       <c r="R88" t="n">
-        <v>6560568</v>
+        <v>6560582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737687</v>
+        <v>131738988</v>
       </c>
       <c r="B89" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9745,34 +9745,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>615322</v>
+        <v>614862</v>
       </c>
       <c r="R89" t="n">
-        <v>6560582</v>
+        <v>6560592</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131738998</v>
+        <v>131737783</v>
       </c>
       <c r="B90" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9846,34 +9846,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615020</v>
+        <v>615276</v>
       </c>
       <c r="R90" t="n">
-        <v>6560533</v>
+        <v>6560495</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9900,12 +9904,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9936,7 +9945,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737783</v>
+        <v>131737641</v>
       </c>
       <c r="B91" t="n">
         <v>93174</v>
@@ -9964,21 +9973,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615276</v>
+        <v>614893</v>
       </c>
       <c r="R91" t="n">
-        <v>6560495</v>
+        <v>6560582</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10005,17 +10010,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10046,7 +10046,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737641</v>
+        <v>131737656</v>
       </c>
       <c r="B92" t="n">
         <v>93174</v>
@@ -10077,14 +10077,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614893</v>
+        <v>615271</v>
       </c>
       <c r="R92" t="n">
-        <v>6560582</v>
+        <v>6560749</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,7 +10147,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737656</v>
+        <v>131737666</v>
       </c>
       <c r="B93" t="n">
         <v>93174</v>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615271</v>
+        <v>614995</v>
       </c>
       <c r="R93" t="n">
-        <v>6560749</v>
+        <v>6560571</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737666</v>
+        <v>131737676</v>
       </c>
       <c r="B94" t="n">
         <v>93174</v>
@@ -10279,14 +10279,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614995</v>
+        <v>615060</v>
       </c>
       <c r="R94" t="n">
-        <v>6560571</v>
+        <v>6560536</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10349,7 +10349,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737676</v>
+        <v>131737646</v>
       </c>
       <c r="B95" t="n">
         <v>93174</v>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615060</v>
+        <v>615289</v>
       </c>
       <c r="R95" t="n">
-        <v>6560536</v>
+        <v>6560695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737646</v>
+        <v>131737690</v>
       </c>
       <c r="B96" t="n">
         <v>93174</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615289</v>
+        <v>615387</v>
       </c>
       <c r="R96" t="n">
-        <v>6560695</v>
+        <v>6560558</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10551,7 +10551,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737690</v>
+        <v>131737659</v>
       </c>
       <c r="B97" t="n">
         <v>93174</v>
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615387</v>
+        <v>615267</v>
       </c>
       <c r="R97" t="n">
-        <v>6560558</v>
+        <v>6560667</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737659</v>
+        <v>131737649</v>
       </c>
       <c r="B98" t="n">
         <v>93174</v>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615267</v>
+        <v>615316</v>
       </c>
       <c r="R98" t="n">
-        <v>6560667</v>
+        <v>6560709</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10753,10 +10753,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737649</v>
+        <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10764,34 +10764,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615316</v>
+        <v>615020</v>
       </c>
       <c r="R99" t="n">
-        <v>6560709</v>
+        <v>6560533</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739013</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10865,34 +10865,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615376</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560556</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739004</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10966,34 +10966,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614958</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560561</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11056,10 +11056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739001</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614955</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560579</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737625</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
         <v>93174</v>
@@ -11188,14 +11188,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614918</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560620</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737645</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
         <v>93174</v>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615304</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560686</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737655</v>
+        <v>131737619</v>
       </c>
       <c r="B105" t="n">
         <v>93174</v>
@@ -11390,14 +11390,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615267</v>
+        <v>614885</v>
       </c>
       <c r="R105" t="n">
-        <v>6560777</v>
+        <v>6560613</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737636</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
         <v>93174</v>
@@ -11491,14 +11491,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614960</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560601</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11561,10 +11561,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739013</v>
       </c>
       <c r="B107" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11572,21 +11572,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>615376</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560556</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737619</v>
+        <v>131739004</v>
       </c>
       <c r="B108" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11673,34 +11673,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614885</v>
+        <v>614958</v>
       </c>
       <c r="R108" t="n">
-        <v>6560613</v>
+        <v>6560561</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737664</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614942</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560568</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11864,10 +11864,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131736566</v>
+        <v>131740361</v>
       </c>
       <c r="B110" t="n">
-        <v>93152</v>
+        <v>93165</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,38 +11875,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615319</v>
+        <v>615309</v>
       </c>
       <c r="R110" t="n">
-        <v>6560579</v>
+        <v>6560557</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11941,17 +11933,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11974,10 +11962,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738995</v>
+        <v>131737627</v>
       </c>
       <c r="B111" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11985,34 +11973,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615323</v>
+        <v>614921</v>
       </c>
       <c r="R111" t="n">
-        <v>6560647</v>
+        <v>6560604</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12075,10 +12063,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131738990</v>
+        <v>131737648</v>
       </c>
       <c r="B112" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12086,34 +12074,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614930</v>
+        <v>615306</v>
       </c>
       <c r="R112" t="n">
-        <v>6560587</v>
+        <v>6560663</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12176,53 +12164,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131740030</v>
+        <v>131737630</v>
       </c>
       <c r="B113" t="n">
-        <v>57102</v>
+        <v>93174</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614953</v>
+        <v>614948</v>
       </c>
       <c r="R113" t="n">
-        <v>6560578</v>
+        <v>6560611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12255,11 +12235,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12290,10 +12265,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740361</v>
+        <v>131736566</v>
       </c>
       <c r="B114" t="n">
-        <v>93165</v>
+        <v>93152</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12301,30 +12276,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615309</v>
+        <v>615319</v>
       </c>
       <c r="R114" t="n">
-        <v>6560557</v>
+        <v>6560579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12359,13 +12342,17 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12388,10 +12375,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737627</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12399,34 +12386,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614921</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560604</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12489,10 +12476,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737648</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12500,34 +12487,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615306</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560663</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12590,45 +12577,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737630</v>
+        <v>131740030</v>
       </c>
       <c r="B117" t="n">
-        <v>93174</v>
+        <v>57102</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614948</v>
+        <v>614953</v>
       </c>
       <c r="R117" t="n">
-        <v>6560611</v>
+        <v>6560578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12661,6 +12656,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131739003</v>
+        <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>79895</v>
+        <v>91869</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614959</v>
+        <v>614974</v>
       </c>
       <c r="R118" t="n">
-        <v>6560556</v>
+        <v>6560628</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12792,10 +12792,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131740081</v>
+        <v>131737665</v>
       </c>
       <c r="B119" t="n">
-        <v>91869</v>
+        <v>93174</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614974</v>
+        <v>614993</v>
       </c>
       <c r="R119" t="n">
-        <v>6560628</v>
+        <v>6560559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12893,7 +12893,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B120" t="n">
         <v>93174</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R120" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131737670</v>
+        <v>131739003</v>
       </c>
       <c r="B121" t="n">
-        <v>93174</v>
+        <v>79895</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614972</v>
+        <v>614959</v>
       </c>
       <c r="R121" t="n">
-        <v>6560590</v>
+        <v>6560556</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13205,7 +13205,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131738994</v>
+        <v>131739000</v>
       </c>
       <c r="B123" t="n">
         <v>79895</v>
@@ -13240,10 +13240,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614890</v>
+        <v>614941</v>
       </c>
       <c r="R123" t="n">
-        <v>6560564</v>
+        <v>6560553</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13306,7 +13306,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739000</v>
+        <v>131738994</v>
       </c>
       <c r="B124" t="n">
         <v>79895</v>
@@ -13341,10 +13341,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614941</v>
+        <v>614890</v>
       </c>
       <c r="R124" t="n">
-        <v>6560553</v>
+        <v>6560564</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14013,32 +14013,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131735760</v>
+        <v>131738996</v>
       </c>
       <c r="B131" t="n">
-        <v>90613</v>
+        <v>79895</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615279</v>
+        <v>615290</v>
       </c>
       <c r="R131" t="n">
-        <v>6560699</v>
+        <v>6560715</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14114,10 +14114,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131738996</v>
+        <v>131737682</v>
       </c>
       <c r="B132" t="n">
-        <v>79895</v>
+        <v>93174</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14125,21 +14125,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14149,10 +14149,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615290</v>
+        <v>615350</v>
       </c>
       <c r="R132" t="n">
-        <v>6560715</v>
+        <v>6560611</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14215,7 +14215,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B133" t="n">
         <v>93174</v>
@@ -14246,14 +14246,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R133" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737663</v>
+        <v>131737673</v>
       </c>
       <c r="B134" t="n">
         <v>93174</v>
@@ -14351,10 +14351,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>615046</v>
+        <v>614957</v>
       </c>
       <c r="R134" t="n">
-        <v>6560537</v>
+        <v>6560564</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14417,7 +14417,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737673</v>
+        <v>131737661</v>
       </c>
       <c r="B135" t="n">
         <v>93174</v>
@@ -14452,10 +14452,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>614957</v>
+        <v>615060</v>
       </c>
       <c r="R135" t="n">
-        <v>6560564</v>
+        <v>6560565</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14518,45 +14518,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737661</v>
+        <v>131735760</v>
       </c>
       <c r="B136" t="n">
-        <v>93174</v>
+        <v>90613</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615060</v>
+        <v>615279</v>
       </c>
       <c r="R136" t="n">
-        <v>6560565</v>
+        <v>6560699</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737671</v>
+        <v>131739009</v>
       </c>
       <c r="B18" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614965</v>
+        <v>614998</v>
       </c>
       <c r="R18" t="n">
-        <v>6560580</v>
+        <v>6560540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737631</v>
+        <v>131737671</v>
       </c>
       <c r="B19" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614937</v>
+        <v>614965</v>
       </c>
       <c r="R19" t="n">
-        <v>6560625</v>
+        <v>6560580</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737632</v>
+        <v>131737631</v>
       </c>
       <c r="B20" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614949</v>
+        <v>614937</v>
       </c>
       <c r="R20" t="n">
-        <v>6560635</v>
+        <v>6560625</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737647</v>
+        <v>131737632</v>
       </c>
       <c r="B21" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,14 +2831,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615295</v>
+        <v>614949</v>
       </c>
       <c r="R21" t="n">
-        <v>6560678</v>
+        <v>6560635</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737637</v>
+        <v>131737647</v>
       </c>
       <c r="B22" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,14 +2932,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614949</v>
+        <v>615295</v>
       </c>
       <c r="R22" t="n">
-        <v>6560610</v>
+        <v>6560678</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737650</v>
+        <v>131737637</v>
       </c>
       <c r="B23" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,14 +3033,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615325</v>
+        <v>614949</v>
       </c>
       <c r="R23" t="n">
-        <v>6560719</v>
+        <v>6560610</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737654</v>
+        <v>131737650</v>
       </c>
       <c r="B24" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,14 +3134,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615282</v>
+        <v>615325</v>
       </c>
       <c r="R24" t="n">
-        <v>6560780</v>
+        <v>6560719</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3204,10 +3204,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737614</v>
+        <v>131737654</v>
       </c>
       <c r="B25" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,14 +3235,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614857</v>
+        <v>615282</v>
       </c>
       <c r="R25" t="n">
-        <v>6560612</v>
+        <v>6560780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131739009</v>
+        <v>131737614</v>
       </c>
       <c r="B26" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,34 +3316,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614998</v>
+        <v>614857</v>
       </c>
       <c r="R26" t="n">
-        <v>6560540</v>
+        <v>6560612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3409,7 @@
         <v>131739006</v>
       </c>
       <c r="B27" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>131738992</v>
       </c>
       <c r="B28" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>131737787</v>
       </c>
       <c r="B29" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131737651</v>
       </c>
       <c r="B30" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>131737785</v>
       </c>
       <c r="B31" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>131737784</v>
       </c>
       <c r="B32" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>131737629</v>
       </c>
       <c r="B33" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>131738991</v>
       </c>
       <c r="B34" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>131739043</v>
       </c>
       <c r="B35" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>131739007</v>
       </c>
       <c r="B36" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737685</v>
+        <v>131737640</v>
       </c>
       <c r="B37" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,14 +4474,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>615324</v>
+        <v>614934</v>
       </c>
       <c r="R37" t="n">
-        <v>6560604</v>
+        <v>6560578</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737672</v>
+        <v>131737685</v>
       </c>
       <c r="B38" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,14 +4575,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614950</v>
+        <v>615324</v>
       </c>
       <c r="R38" t="n">
-        <v>6560576</v>
+        <v>6560604</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4645,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737786</v>
+        <v>131737672</v>
       </c>
       <c r="B39" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,21 +4673,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>615335</v>
+        <v>614950</v>
       </c>
       <c r="R39" t="n">
-        <v>6560536</v>
+        <v>6560576</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,17 +4710,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4755,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737662</v>
+        <v>131737786</v>
       </c>
       <c r="B40" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4783,17 +4774,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615040</v>
+        <v>615335</v>
       </c>
       <c r="R40" t="n">
-        <v>6560530</v>
+        <v>6560536</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4820,12 +4815,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4856,10 +4856,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737620</v>
+        <v>131737662</v>
       </c>
       <c r="B41" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,14 +4887,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614896</v>
+        <v>615040</v>
       </c>
       <c r="R41" t="n">
-        <v>6560613</v>
+        <v>6560530</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737634</v>
+        <v>131737620</v>
       </c>
       <c r="B42" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4988,14 +4988,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614954</v>
+        <v>614896</v>
       </c>
       <c r="R42" t="n">
-        <v>6560617</v>
+        <v>6560613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5058,10 +5058,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737669</v>
+        <v>131737634</v>
       </c>
       <c r="B43" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614973</v>
+        <v>614954</v>
       </c>
       <c r="R43" t="n">
-        <v>6560600</v>
+        <v>6560617</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737660</v>
+        <v>131737669</v>
       </c>
       <c r="B44" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5190,14 +5190,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>615278</v>
+        <v>614973</v>
       </c>
       <c r="R44" t="n">
-        <v>6560662</v>
+        <v>6560600</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737640</v>
+        <v>131737660</v>
       </c>
       <c r="B45" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5291,14 +5291,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614934</v>
+        <v>615278</v>
       </c>
       <c r="R45" t="n">
-        <v>6560578</v>
+        <v>6560662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5361,10 +5361,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131739002</v>
+        <v>131737635</v>
       </c>
       <c r="B46" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,21 +5372,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614953</v>
+        <v>614963</v>
       </c>
       <c r="R46" t="n">
-        <v>6560567</v>
+        <v>6560615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737635</v>
+        <v>131737618</v>
       </c>
       <c r="B47" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5493,14 +5493,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614963</v>
+        <v>614881</v>
       </c>
       <c r="R47" t="n">
-        <v>6560615</v>
+        <v>6560601</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5563,10 +5563,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131737618</v>
+        <v>131739002</v>
       </c>
       <c r="B48" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5574,34 +5574,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614881</v>
+        <v>614953</v>
       </c>
       <c r="R48" t="n">
-        <v>6560601</v>
+        <v>6560567</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5664,45 +5664,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737925</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
-        <v>8455</v>
+        <v>93218</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615343</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560656</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5765,10 +5765,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5796,14 +5796,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,10 +5866,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737677</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615064</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560525</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,10 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737684</v>
+        <v>131739012</v>
       </c>
       <c r="B52" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5978,34 +5978,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615333</v>
+        <v>615022</v>
       </c>
       <c r="R52" t="n">
-        <v>6560608</v>
+        <v>6560527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,45 +6068,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131739012</v>
+        <v>131737925</v>
       </c>
       <c r="B53" t="n">
-        <v>79934</v>
+        <v>8455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615022</v>
+        <v>615343</v>
       </c>
       <c r="R53" t="n">
-        <v>6560527</v>
+        <v>6560656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
         <v>131737675</v>
       </c>
       <c r="B54" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>131737617</v>
       </c>
       <c r="B55" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>131737621</v>
       </c>
       <c r="B56" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>131737633</v>
       </c>
       <c r="B57" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>131737657</v>
       </c>
       <c r="B58" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>131737615</v>
       </c>
       <c r="B59" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>131737652</v>
       </c>
       <c r="B60" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>131737688</v>
       </c>
       <c r="B61" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>131738993</v>
       </c>
       <c r="B62" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>131739008</v>
       </c>
       <c r="B63" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>131739005</v>
       </c>
       <c r="B64" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>131736575</v>
       </c>
       <c r="B65" t="n">
-        <v>93193</v>
+        <v>93196</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>131737686</v>
       </c>
       <c r="B66" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>131737643</v>
       </c>
       <c r="B67" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131737667</v>
+        <v>131740360</v>
       </c>
       <c r="B68" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7594,34 +7594,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614991</v>
+        <v>615296</v>
       </c>
       <c r="R68" t="n">
-        <v>6560587</v>
+        <v>6560688</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7656,12 +7656,18 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7684,10 +7690,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131740360</v>
+        <v>131737658</v>
       </c>
       <c r="B69" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7695,34 +7701,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615296</v>
+        <v>615282</v>
       </c>
       <c r="R69" t="n">
-        <v>6560688</v>
+        <v>6560684</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7757,18 +7763,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737638</v>
+        <v>131737667</v>
       </c>
       <c r="B70" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614943</v>
+        <v>614991</v>
       </c>
       <c r="R70" t="n">
-        <v>6560591</v>
+        <v>6560587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7892,10 +7892,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737658</v>
+        <v>131737638</v>
       </c>
       <c r="B71" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7923,14 +7923,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>615282</v>
+        <v>614943</v>
       </c>
       <c r="R71" t="n">
-        <v>6560684</v>
+        <v>6560591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7996,7 +7996,7 @@
         <v>131739010</v>
       </c>
       <c r="B72" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>131739015</v>
       </c>
       <c r="B73" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8195,45 +8195,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737924</v>
+        <v>131738989</v>
       </c>
       <c r="B74" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615091</v>
+        <v>614945</v>
       </c>
       <c r="R74" t="n">
-        <v>6560504</v>
+        <v>6560637</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8296,10 +8296,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737644</v>
+        <v>131739041</v>
       </c>
       <c r="B75" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8307,21 +8307,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615331</v>
+        <v>615269</v>
       </c>
       <c r="R75" t="n">
-        <v>6560676</v>
+        <v>6560500</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737639</v>
+        <v>131739011</v>
       </c>
       <c r="B76" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8408,34 +8408,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614942</v>
+        <v>615080</v>
       </c>
       <c r="R76" t="n">
-        <v>6560579</v>
+        <v>6560512</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8498,10 +8498,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737668</v>
+        <v>131737644</v>
       </c>
       <c r="B77" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,14 +8529,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614990</v>
+        <v>615331</v>
       </c>
       <c r="R77" t="n">
-        <v>6560601</v>
+        <v>6560676</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8599,10 +8599,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131738989</v>
+        <v>131737639</v>
       </c>
       <c r="B78" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8610,34 +8610,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614945</v>
+        <v>614942</v>
       </c>
       <c r="R78" t="n">
-        <v>6560637</v>
+        <v>6560579</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8700,10 +8700,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739041</v>
+        <v>131737668</v>
       </c>
       <c r="B79" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8711,34 +8711,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615269</v>
+        <v>614990</v>
       </c>
       <c r="R79" t="n">
-        <v>6560500</v>
+        <v>6560601</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8765,12 +8765,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8801,32 +8801,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131739011</v>
+        <v>131737924</v>
       </c>
       <c r="B80" t="n">
-        <v>79934</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615080</v>
+        <v>615091</v>
       </c>
       <c r="R80" t="n">
-        <v>6560512</v>
+        <v>6560504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8905,7 +8905,7 @@
         <v>131737674</v>
       </c>
       <c r="B81" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>131737782</v>
       </c>
       <c r="B82" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9113,10 +9113,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737653</v>
+        <v>131737680</v>
       </c>
       <c r="B83" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9144,14 +9144,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>615289</v>
+        <v>615390</v>
       </c>
       <c r="R83" t="n">
-        <v>6560767</v>
+        <v>6560614</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737624</v>
+        <v>131737653</v>
       </c>
       <c r="B84" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9245,14 +9245,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>614910</v>
+        <v>615289</v>
       </c>
       <c r="R84" t="n">
-        <v>6560612</v>
+        <v>6560767</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,10 +9315,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737680</v>
+        <v>131737624</v>
       </c>
       <c r="B85" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9346,14 +9346,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>615390</v>
+        <v>614910</v>
       </c>
       <c r="R85" t="n">
-        <v>6560614</v>
+        <v>6560612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9416,10 +9416,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737626</v>
+        <v>131738988</v>
       </c>
       <c r="B86" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9427,21 +9427,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614911</v>
+        <v>614862</v>
       </c>
       <c r="R86" t="n">
-        <v>6560610</v>
+        <v>6560592</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9517,10 +9517,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737642</v>
+        <v>131737626</v>
       </c>
       <c r="B87" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614884</v>
+        <v>614911</v>
       </c>
       <c r="R87" t="n">
-        <v>6560568</v>
+        <v>6560610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737687</v>
+        <v>131737642</v>
       </c>
       <c r="B88" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9649,14 +9649,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>615322</v>
+        <v>614884</v>
       </c>
       <c r="R88" t="n">
-        <v>6560582</v>
+        <v>6560568</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131738988</v>
+        <v>131737687</v>
       </c>
       <c r="B89" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9730,34 +9730,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614862</v>
+        <v>615322</v>
       </c>
       <c r="R89" t="n">
-        <v>6560592</v>
+        <v>6560582</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9820,10 +9820,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737783</v>
+        <v>131737676</v>
       </c>
       <c r="B90" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9848,21 +9848,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615276</v>
+        <v>615060</v>
       </c>
       <c r="R90" t="n">
-        <v>6560495</v>
+        <v>6560536</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9889,17 +9885,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9930,10 +9921,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737641</v>
+        <v>131737783</v>
       </c>
       <c r="B91" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9958,17 +9949,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>614893</v>
+        <v>615276</v>
       </c>
       <c r="R91" t="n">
-        <v>6560582</v>
+        <v>6560495</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9995,12 +9990,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10031,10 +10031,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737656</v>
+        <v>131737641</v>
       </c>
       <c r="B92" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10062,14 +10062,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615271</v>
+        <v>614893</v>
       </c>
       <c r="R92" t="n">
-        <v>6560749</v>
+        <v>6560582</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10132,10 +10132,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737666</v>
+        <v>131737656</v>
       </c>
       <c r="B93" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614995</v>
+        <v>615271</v>
       </c>
       <c r="R93" t="n">
-        <v>6560571</v>
+        <v>6560749</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737676</v>
+        <v>131737666</v>
       </c>
       <c r="B94" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10264,14 +10264,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615060</v>
+        <v>614995</v>
       </c>
       <c r="R94" t="n">
-        <v>6560536</v>
+        <v>6560571</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10337,7 +10337,7 @@
         <v>131737646</v>
       </c>
       <c r="B95" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>131737690</v>
       </c>
       <c r="B96" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>131737659</v>
       </c>
       <c r="B97" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>131737649</v>
       </c>
       <c r="B98" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>131738998</v>
       </c>
       <c r="B99" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10839,10 +10839,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739013</v>
+        <v>131737625</v>
       </c>
       <c r="B100" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10850,34 +10850,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>615376</v>
+        <v>614918</v>
       </c>
       <c r="R100" t="n">
-        <v>6560556</v>
+        <v>6560620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10940,10 +10940,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131739004</v>
+        <v>131737645</v>
       </c>
       <c r="B101" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10951,34 +10951,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614958</v>
+        <v>615304</v>
       </c>
       <c r="R101" t="n">
-        <v>6560561</v>
+        <v>6560686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11041,10 +11041,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131739001</v>
+        <v>131737655</v>
       </c>
       <c r="B102" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11052,21 +11052,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11076,10 +11076,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>614955</v>
+        <v>615267</v>
       </c>
       <c r="R102" t="n">
-        <v>6560579</v>
+        <v>6560777</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11142,10 +11142,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737625</v>
+        <v>131737636</v>
       </c>
       <c r="B103" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11173,14 +11173,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614918</v>
+        <v>614960</v>
       </c>
       <c r="R103" t="n">
-        <v>6560620</v>
+        <v>6560601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737645</v>
+        <v>131737691</v>
       </c>
       <c r="B104" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615304</v>
+        <v>615367</v>
       </c>
       <c r="R104" t="n">
-        <v>6560686</v>
+        <v>6560553</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11344,10 +11344,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737636</v>
+        <v>131737619</v>
       </c>
       <c r="B105" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11375,14 +11375,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614960</v>
+        <v>614885</v>
       </c>
       <c r="R105" t="n">
-        <v>6560601</v>
+        <v>6560613</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11445,10 +11445,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737655</v>
+        <v>131737664</v>
       </c>
       <c r="B106" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11476,14 +11476,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>615267</v>
+        <v>614942</v>
       </c>
       <c r="R106" t="n">
-        <v>6560777</v>
+        <v>6560568</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11546,10 +11546,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737691</v>
+        <v>131739004</v>
       </c>
       <c r="B107" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11557,34 +11557,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>615367</v>
+        <v>614958</v>
       </c>
       <c r="R107" t="n">
-        <v>6560553</v>
+        <v>6560561</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11647,10 +11647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131737619</v>
+        <v>131739013</v>
       </c>
       <c r="B108" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11658,34 +11658,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>614885</v>
+        <v>615376</v>
       </c>
       <c r="R108" t="n">
-        <v>6560613</v>
+        <v>6560556</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11748,10 +11748,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131737664</v>
+        <v>131739001</v>
       </c>
       <c r="B109" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11759,34 +11759,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614942</v>
+        <v>614955</v>
       </c>
       <c r="R109" t="n">
-        <v>6560568</v>
+        <v>6560579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11849,53 +11849,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131740030</v>
+        <v>131736566</v>
       </c>
       <c r="B110" t="n">
-        <v>57136</v>
+        <v>93196</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>614953</v>
+        <v>615319</v>
       </c>
       <c r="R110" t="n">
-        <v>6560578</v>
+        <v>6560579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11932,7 +11928,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11963,10 +11959,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131736566</v>
+        <v>131740361</v>
       </c>
       <c r="B111" t="n">
-        <v>93193</v>
+        <v>93209</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11974,38 +11970,30 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615319</v>
+        <v>615309</v>
       </c>
       <c r="R111" t="n">
-        <v>6560579</v>
+        <v>6560557</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12040,17 +12028,13 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12073,10 +12057,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131740361</v>
+        <v>131737627</v>
       </c>
       <c r="B112" t="n">
-        <v>93206</v>
+        <v>93218</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12084,30 +12068,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>615309</v>
+        <v>614921</v>
       </c>
       <c r="R112" t="n">
-        <v>6560557</v>
+        <v>6560604</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12148,7 +12136,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12171,10 +12158,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737627</v>
+        <v>131737648</v>
       </c>
       <c r="B113" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12202,14 +12189,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614921</v>
+        <v>615306</v>
       </c>
       <c r="R113" t="n">
-        <v>6560604</v>
+        <v>6560663</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,10 +12259,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737648</v>
+        <v>131737630</v>
       </c>
       <c r="B114" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12303,14 +12290,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615306</v>
+        <v>614948</v>
       </c>
       <c r="R114" t="n">
-        <v>6560663</v>
+        <v>6560611</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12373,10 +12360,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737630</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12384,34 +12371,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614948</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560611</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12474,10 +12461,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738995</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12505,14 +12492,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615323</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560647</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12575,45 +12562,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131738990</v>
+        <v>131740030</v>
       </c>
       <c r="B117" t="n">
-        <v>79934</v>
+        <v>57136</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614930</v>
+        <v>614953</v>
       </c>
       <c r="R117" t="n">
-        <v>6560587</v>
+        <v>6560578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12646,6 +12641,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12679,7 +12679,7 @@
         <v>131740081</v>
       </c>
       <c r="B118" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>131737665</v>
       </c>
       <c r="B119" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>131737670</v>
       </c>
       <c r="B120" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>131739003</v>
       </c>
       <c r="B121" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13080,45 +13080,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131738994</v>
+        <v>131735761</v>
       </c>
       <c r="B122" t="n">
-        <v>79934</v>
+        <v>90657</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614890</v>
+        <v>615277</v>
       </c>
       <c r="R122" t="n">
-        <v>6560564</v>
+        <v>6560691</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13151,6 +13155,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13181,10 +13190,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131739000</v>
+        <v>131738994</v>
       </c>
       <c r="B123" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13216,10 +13225,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614941</v>
+        <v>614890</v>
       </c>
       <c r="R123" t="n">
-        <v>6560553</v>
+        <v>6560564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13282,49 +13291,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131735761</v>
+        <v>131739000</v>
       </c>
       <c r="B124" t="n">
-        <v>90654</v>
+        <v>79936</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>615277</v>
+        <v>614941</v>
       </c>
       <c r="R124" t="n">
-        <v>6560691</v>
+        <v>6560553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13357,11 +13362,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13392,10 +13392,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131739026</v>
+        <v>131737622</v>
       </c>
       <c r="B125" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13403,34 +13403,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>615203</v>
+        <v>614898</v>
       </c>
       <c r="R125" t="n">
-        <v>6560503</v>
+        <v>6560601</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13457,12 +13457,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13493,10 +13493,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131738997</v>
+        <v>131737683</v>
       </c>
       <c r="B126" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13504,34 +13504,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615026</v>
+        <v>615337</v>
       </c>
       <c r="R126" t="n">
-        <v>6560531</v>
+        <v>6560617</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13594,10 +13594,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737622</v>
+        <v>131737678</v>
       </c>
       <c r="B127" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13625,14 +13625,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>614898</v>
+        <v>615054</v>
       </c>
       <c r="R127" t="n">
-        <v>6560601</v>
+        <v>6560523</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13695,10 +13695,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737683</v>
+        <v>131737681</v>
       </c>
       <c r="B128" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13726,14 +13726,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615337</v>
+        <v>615383</v>
       </c>
       <c r="R128" t="n">
-        <v>6560617</v>
+        <v>6560632</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737678</v>
+        <v>131738997</v>
       </c>
       <c r="B129" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13807,34 +13807,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615054</v>
+        <v>615026</v>
       </c>
       <c r="R129" t="n">
-        <v>6560523</v>
+        <v>6560531</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13897,10 +13897,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131737681</v>
+        <v>131739026</v>
       </c>
       <c r="B130" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13908,34 +13908,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615383</v>
+        <v>615203</v>
       </c>
       <c r="R130" t="n">
-        <v>6560632</v>
+        <v>6560503</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13998,45 +13998,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131737663</v>
+        <v>131735760</v>
       </c>
       <c r="B131" t="n">
-        <v>93215</v>
+        <v>90657</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615046</v>
+        <v>615279</v>
       </c>
       <c r="R131" t="n">
-        <v>6560537</v>
+        <v>6560699</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14099,32 +14099,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131735760</v>
+        <v>131737682</v>
       </c>
       <c r="B132" t="n">
-        <v>90654</v>
+        <v>93218</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14134,10 +14134,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615279</v>
+        <v>615350</v>
       </c>
       <c r="R132" t="n">
-        <v>6560699</v>
+        <v>6560611</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14200,10 +14200,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737682</v>
+        <v>131737663</v>
       </c>
       <c r="B133" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14231,14 +14231,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615350</v>
+        <v>615046</v>
       </c>
       <c r="R133" t="n">
-        <v>6560611</v>
+        <v>6560537</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14304,7 +14304,7 @@
         <v>131737673</v>
       </c>
       <c r="B134" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14402,10 +14402,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737661</v>
+        <v>131738996</v>
       </c>
       <c r="B135" t="n">
-        <v>93215</v>
+        <v>79936</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14413,34 +14413,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615060</v>
+        <v>615290</v>
       </c>
       <c r="R135" t="n">
-        <v>6560565</v>
+        <v>6560715</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14503,10 +14503,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131738996</v>
+        <v>131737661</v>
       </c>
       <c r="B136" t="n">
-        <v>79934</v>
+        <v>93218</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14514,34 +14514,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615290</v>
+        <v>615060</v>
       </c>
       <c r="R136" t="n">
-        <v>6560715</v>
+        <v>6560565</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2497,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131739009</v>
+        <v>131737671</v>
       </c>
       <c r="B18" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614998</v>
+        <v>614965</v>
       </c>
       <c r="R18" t="n">
-        <v>6560540</v>
+        <v>6560580</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737671</v>
+        <v>131737631</v>
       </c>
       <c r="B19" t="n">
         <v>93218</v>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614965</v>
+        <v>614937</v>
       </c>
       <c r="R19" t="n">
-        <v>6560580</v>
+        <v>6560625</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737631</v>
+        <v>131737632</v>
       </c>
       <c r="B20" t="n">
         <v>93218</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614937</v>
+        <v>614949</v>
       </c>
       <c r="R20" t="n">
-        <v>6560625</v>
+        <v>6560635</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737632</v>
+        <v>131737647</v>
       </c>
       <c r="B21" t="n">
         <v>93218</v>
@@ -2831,14 +2831,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614949</v>
+        <v>615295</v>
       </c>
       <c r="R21" t="n">
-        <v>6560635</v>
+        <v>6560678</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737647</v>
+        <v>131737637</v>
       </c>
       <c r="B22" t="n">
         <v>93218</v>
@@ -2932,14 +2932,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615295</v>
+        <v>614949</v>
       </c>
       <c r="R22" t="n">
-        <v>6560678</v>
+        <v>6560610</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737637</v>
+        <v>131737650</v>
       </c>
       <c r="B23" t="n">
         <v>93218</v>
@@ -3033,14 +3033,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614949</v>
+        <v>615325</v>
       </c>
       <c r="R23" t="n">
-        <v>6560610</v>
+        <v>6560719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737650</v>
+        <v>131737654</v>
       </c>
       <c r="B24" t="n">
         <v>93218</v>
@@ -3134,14 +3134,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615325</v>
+        <v>615282</v>
       </c>
       <c r="R24" t="n">
-        <v>6560719</v>
+        <v>6560780</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737654</v>
+        <v>131737614</v>
       </c>
       <c r="B25" t="n">
         <v>93218</v>
@@ -3235,14 +3235,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>615282</v>
+        <v>614857</v>
       </c>
       <c r="R25" t="n">
-        <v>6560780</v>
+        <v>6560612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131737614</v>
+        <v>131739009</v>
       </c>
       <c r="B26" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,34 +3316,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614857</v>
+        <v>614998</v>
       </c>
       <c r="R26" t="n">
-        <v>6560612</v>
+        <v>6560540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131737684</v>
       </c>
       <c r="B49" t="n">
         <v>93218</v>
@@ -5695,14 +5695,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>615333</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560608</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5765,7 +5765,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737677</v>
+        <v>131737616</v>
       </c>
       <c r="B50" t="n">
         <v>93218</v>
@@ -5796,14 +5796,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615064</v>
+        <v>614862</v>
       </c>
       <c r="R50" t="n">
-        <v>6560525</v>
+        <v>6560592</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737684</v>
+        <v>131737677</v>
       </c>
       <c r="B51" t="n">
         <v>93218</v>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615333</v>
+        <v>615064</v>
       </c>
       <c r="R51" t="n">
-        <v>6560608</v>
+        <v>6560525</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,45 +5967,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131739012</v>
+        <v>131737925</v>
       </c>
       <c r="B52" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615022</v>
+        <v>615343</v>
       </c>
       <c r="R52" t="n">
-        <v>6560527</v>
+        <v>6560656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,45 +6068,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737925</v>
+        <v>131739012</v>
       </c>
       <c r="B53" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615343</v>
+        <v>615022</v>
       </c>
       <c r="R53" t="n">
-        <v>6560656</v>
+        <v>6560527</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -9820,10 +9820,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131737676</v>
+        <v>131738998</v>
       </c>
       <c r="B90" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615060</v>
+        <v>615020</v>
       </c>
       <c r="R90" t="n">
-        <v>6560536</v>
+        <v>6560533</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9921,7 +9921,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737783</v>
+        <v>131737676</v>
       </c>
       <c r="B91" t="n">
         <v>93218</v>
@@ -9949,21 +9949,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615276</v>
+        <v>615060</v>
       </c>
       <c r="R91" t="n">
-        <v>6560495</v>
+        <v>6560536</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9990,17 +9986,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10031,7 +10022,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737641</v>
+        <v>131737783</v>
       </c>
       <c r="B92" t="n">
         <v>93218</v>
@@ -10059,17 +10050,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>614893</v>
+        <v>615276</v>
       </c>
       <c r="R92" t="n">
-        <v>6560582</v>
+        <v>6560495</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10096,12 +10091,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10132,7 +10132,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737656</v>
+        <v>131737641</v>
       </c>
       <c r="B93" t="n">
         <v>93218</v>
@@ -10163,14 +10163,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>615271</v>
+        <v>614893</v>
       </c>
       <c r="R93" t="n">
-        <v>6560749</v>
+        <v>6560582</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10233,7 +10233,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737666</v>
+        <v>131737656</v>
       </c>
       <c r="B94" t="n">
         <v>93218</v>
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>614995</v>
+        <v>615271</v>
       </c>
       <c r="R94" t="n">
-        <v>6560571</v>
+        <v>6560749</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737646</v>
+        <v>131737666</v>
       </c>
       <c r="B95" t="n">
         <v>93218</v>
@@ -10365,14 +10365,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>615289</v>
+        <v>614995</v>
       </c>
       <c r="R95" t="n">
-        <v>6560695</v>
+        <v>6560571</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10435,7 +10435,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737690</v>
+        <v>131737646</v>
       </c>
       <c r="B96" t="n">
         <v>93218</v>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615387</v>
+        <v>615289</v>
       </c>
       <c r="R96" t="n">
-        <v>6560558</v>
+        <v>6560695</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10536,7 +10536,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737659</v>
+        <v>131737690</v>
       </c>
       <c r="B97" t="n">
         <v>93218</v>
@@ -10571,10 +10571,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615267</v>
+        <v>615387</v>
       </c>
       <c r="R97" t="n">
-        <v>6560667</v>
+        <v>6560558</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10637,7 +10637,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737649</v>
+        <v>131737659</v>
       </c>
       <c r="B98" t="n">
         <v>93218</v>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615316</v>
+        <v>615267</v>
       </c>
       <c r="R98" t="n">
-        <v>6560709</v>
+        <v>6560667</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10738,10 +10738,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131738998</v>
+        <v>131737649</v>
       </c>
       <c r="B99" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10749,34 +10749,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615020</v>
+        <v>615316</v>
       </c>
       <c r="R99" t="n">
-        <v>6560533</v>
+        <v>6560709</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10839,10 +10839,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131737625</v>
+        <v>131739004</v>
       </c>
       <c r="B100" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10850,34 +10850,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614918</v>
+        <v>614958</v>
       </c>
       <c r="R100" t="n">
-        <v>6560620</v>
+        <v>6560561</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10940,7 +10940,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737645</v>
+        <v>131737625</v>
       </c>
       <c r="B101" t="n">
         <v>93218</v>
@@ -10971,14 +10971,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>615304</v>
+        <v>614918</v>
       </c>
       <c r="R101" t="n">
-        <v>6560686</v>
+        <v>6560620</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11041,7 +11041,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737655</v>
+        <v>131737645</v>
       </c>
       <c r="B102" t="n">
         <v>93218</v>
@@ -11072,14 +11072,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615267</v>
+        <v>615304</v>
       </c>
       <c r="R102" t="n">
-        <v>6560777</v>
+        <v>6560686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11142,7 +11142,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737636</v>
+        <v>131737655</v>
       </c>
       <c r="B103" t="n">
         <v>93218</v>
@@ -11177,10 +11177,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>614960</v>
+        <v>615267</v>
       </c>
       <c r="R103" t="n">
-        <v>6560601</v>
+        <v>6560777</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11243,7 +11243,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737691</v>
+        <v>131737636</v>
       </c>
       <c r="B104" t="n">
         <v>93218</v>
@@ -11274,14 +11274,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>615367</v>
+        <v>614960</v>
       </c>
       <c r="R104" t="n">
-        <v>6560553</v>
+        <v>6560601</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11344,7 +11344,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737619</v>
+        <v>131737691</v>
       </c>
       <c r="B105" t="n">
         <v>93218</v>
@@ -11375,14 +11375,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>614885</v>
+        <v>615367</v>
       </c>
       <c r="R105" t="n">
-        <v>6560613</v>
+        <v>6560553</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737664</v>
+        <v>131737619</v>
       </c>
       <c r="B106" t="n">
         <v>93218</v>
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614942</v>
+        <v>614885</v>
       </c>
       <c r="R106" t="n">
-        <v>6560568</v>
+        <v>6560613</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11546,10 +11546,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131739004</v>
+        <v>131737664</v>
       </c>
       <c r="B107" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11557,34 +11557,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614958</v>
+        <v>614942</v>
       </c>
       <c r="R107" t="n">
-        <v>6560561</v>
+        <v>6560568</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131740361</v>
+        <v>131738995</v>
       </c>
       <c r="B111" t="n">
-        <v>93209</v>
+        <v>79936</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11970,19 +11970,23 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11990,10 +11994,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615309</v>
+        <v>615323</v>
       </c>
       <c r="R111" t="n">
-        <v>6560557</v>
+        <v>6560647</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12034,7 +12038,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12057,10 +12060,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737627</v>
+        <v>131738990</v>
       </c>
       <c r="B112" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12068,21 +12071,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12092,10 +12095,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614921</v>
+        <v>614930</v>
       </c>
       <c r="R112" t="n">
-        <v>6560604</v>
+        <v>6560587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12158,45 +12161,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737648</v>
+        <v>131740030</v>
       </c>
       <c r="B113" t="n">
-        <v>93218</v>
+        <v>57136</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615306</v>
+        <v>614953</v>
       </c>
       <c r="R113" t="n">
-        <v>6560663</v>
+        <v>6560578</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12229,6 +12240,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12259,10 +12275,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737630</v>
+        <v>131740361</v>
       </c>
       <c r="B114" t="n">
-        <v>93218</v>
+        <v>93209</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12270,34 +12286,30 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614948</v>
+        <v>615309</v>
       </c>
       <c r="R114" t="n">
-        <v>6560611</v>
+        <v>6560557</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12338,6 +12350,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12360,10 +12373,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131737627</v>
       </c>
       <c r="B115" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12371,34 +12384,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>614921</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560604</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12461,10 +12474,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131737648</v>
       </c>
       <c r="B116" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12472,34 +12485,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>615306</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560663</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12562,53 +12575,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131740030</v>
+        <v>131737630</v>
       </c>
       <c r="B117" t="n">
-        <v>57136</v>
+        <v>93218</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614953</v>
+        <v>614948</v>
       </c>
       <c r="R117" t="n">
-        <v>6560578</v>
+        <v>6560611</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12641,11 +12646,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13080,49 +13080,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131735761</v>
+        <v>131738994</v>
       </c>
       <c r="B122" t="n">
-        <v>90657</v>
+        <v>79936</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1596</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>615277</v>
+        <v>614890</v>
       </c>
       <c r="R122" t="n">
-        <v>6560691</v>
+        <v>6560564</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13155,11 +13151,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13190,7 +13181,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131738994</v>
+        <v>131739000</v>
       </c>
       <c r="B123" t="n">
         <v>79936</v>
@@ -13225,10 +13216,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614890</v>
+        <v>614941</v>
       </c>
       <c r="R123" t="n">
-        <v>6560564</v>
+        <v>6560553</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13291,45 +13282,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131739000</v>
+        <v>131735761</v>
       </c>
       <c r="B124" t="n">
-        <v>79936</v>
+        <v>90657</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>1596</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>614941</v>
+        <v>615277</v>
       </c>
       <c r="R124" t="n">
-        <v>6560553</v>
+        <v>6560691</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13362,6 +13357,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14099,7 +14099,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737682</v>
+        <v>131737661</v>
       </c>
       <c r="B132" t="n">
         <v>93218</v>
@@ -14130,14 +14130,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615350</v>
+        <v>615060</v>
       </c>
       <c r="R132" t="n">
-        <v>6560611</v>
+        <v>6560565</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14200,10 +14200,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131737663</v>
+        <v>131738996</v>
       </c>
       <c r="B133" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14211,34 +14211,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615046</v>
+        <v>615290</v>
       </c>
       <c r="R133" t="n">
-        <v>6560537</v>
+        <v>6560715</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14301,7 +14301,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131737673</v>
+        <v>131737682</v>
       </c>
       <c r="B134" t="n">
         <v>93218</v>
@@ -14332,14 +14332,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>614957</v>
+        <v>615350</v>
       </c>
       <c r="R134" t="n">
-        <v>6560564</v>
+        <v>6560611</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14402,10 +14402,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131738996</v>
+        <v>131737663</v>
       </c>
       <c r="B135" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14413,34 +14413,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615290</v>
+        <v>615046</v>
       </c>
       <c r="R135" t="n">
-        <v>6560715</v>
+        <v>6560537</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14503,7 +14503,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737661</v>
+        <v>131737673</v>
       </c>
       <c r="B136" t="n">
         <v>93218</v>
@@ -14538,10 +14538,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>615060</v>
+        <v>614957</v>
       </c>
       <c r="R136" t="n">
-        <v>6560565</v>
+        <v>6560564</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -5664,7 +5664,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737684</v>
+        <v>131737616</v>
       </c>
       <c r="B49" t="n">
         <v>93218</v>
@@ -5695,14 +5695,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>615333</v>
+        <v>614862</v>
       </c>
       <c r="R49" t="n">
-        <v>6560608</v>
+        <v>6560592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5765,7 +5765,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737616</v>
+        <v>131737677</v>
       </c>
       <c r="B50" t="n">
         <v>93218</v>
@@ -5796,14 +5796,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614862</v>
+        <v>615064</v>
       </c>
       <c r="R50" t="n">
-        <v>6560592</v>
+        <v>6560525</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737677</v>
+        <v>131737684</v>
       </c>
       <c r="B51" t="n">
         <v>93218</v>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615064</v>
+        <v>615333</v>
       </c>
       <c r="R51" t="n">
-        <v>6560525</v>
+        <v>6560608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,45 +5967,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131737925</v>
+        <v>131739012</v>
       </c>
       <c r="B52" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615343</v>
+        <v>615022</v>
       </c>
       <c r="R52" t="n">
-        <v>6560656</v>
+        <v>6560527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,45 +6068,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131739012</v>
+        <v>131737925</v>
       </c>
       <c r="B53" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615022</v>
+        <v>615343</v>
       </c>
       <c r="R53" t="n">
-        <v>6560527</v>
+        <v>6560656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -8195,10 +8195,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131738989</v>
+        <v>131737644</v>
       </c>
       <c r="B74" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8206,34 +8206,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614945</v>
+        <v>615331</v>
       </c>
       <c r="R74" t="n">
-        <v>6560637</v>
+        <v>6560676</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8296,10 +8296,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131739041</v>
+        <v>131737639</v>
       </c>
       <c r="B75" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8307,34 +8307,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>615269</v>
+        <v>614942</v>
       </c>
       <c r="R75" t="n">
-        <v>6560500</v>
+        <v>6560579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131739011</v>
+        <v>131737668</v>
       </c>
       <c r="B76" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8408,34 +8408,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>615080</v>
+        <v>614990</v>
       </c>
       <c r="R76" t="n">
-        <v>6560512</v>
+        <v>6560601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8498,10 +8498,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131737644</v>
+        <v>131738989</v>
       </c>
       <c r="B77" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8509,34 +8509,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>615331</v>
+        <v>614945</v>
       </c>
       <c r="R77" t="n">
-        <v>6560676</v>
+        <v>6560637</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8599,10 +8599,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131737639</v>
+        <v>131739041</v>
       </c>
       <c r="B78" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8610,34 +8610,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>614942</v>
+        <v>615269</v>
       </c>
       <c r="R78" t="n">
-        <v>6560579</v>
+        <v>6560500</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8664,12 +8664,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8700,10 +8700,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131737668</v>
+        <v>131739011</v>
       </c>
       <c r="B79" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8711,34 +8711,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>614990</v>
+        <v>615080</v>
       </c>
       <c r="R79" t="n">
-        <v>6560601</v>
+        <v>6560512</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9416,10 +9416,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131738988</v>
+        <v>131737626</v>
       </c>
       <c r="B86" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9427,21 +9427,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614862</v>
+        <v>614911</v>
       </c>
       <c r="R86" t="n">
-        <v>6560592</v>
+        <v>6560610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9517,7 +9517,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737626</v>
+        <v>131737642</v>
       </c>
       <c r="B87" t="n">
         <v>93218</v>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614911</v>
+        <v>614884</v>
       </c>
       <c r="R87" t="n">
-        <v>6560610</v>
+        <v>6560568</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737642</v>
+        <v>131737687</v>
       </c>
       <c r="B88" t="n">
         <v>93218</v>
@@ -9649,14 +9649,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>614884</v>
+        <v>615322</v>
       </c>
       <c r="R88" t="n">
-        <v>6560568</v>
+        <v>6560582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131737687</v>
+        <v>131738988</v>
       </c>
       <c r="B89" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9730,34 +9730,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>615322</v>
+        <v>614862</v>
       </c>
       <c r="R89" t="n">
-        <v>6560582</v>
+        <v>6560592</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131738995</v>
+        <v>131740361</v>
       </c>
       <c r="B111" t="n">
-        <v>79936</v>
+        <v>93209</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11970,23 +11970,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11994,10 +11990,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>615323</v>
+        <v>615309</v>
       </c>
       <c r="R111" t="n">
-        <v>6560647</v>
+        <v>6560557</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12038,6 +12034,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12060,10 +12057,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131738990</v>
+        <v>131737627</v>
       </c>
       <c r="B112" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12071,21 +12068,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12095,10 +12092,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614930</v>
+        <v>614921</v>
       </c>
       <c r="R112" t="n">
-        <v>6560587</v>
+        <v>6560604</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12161,53 +12158,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131740030</v>
+        <v>131737648</v>
       </c>
       <c r="B113" t="n">
-        <v>57136</v>
+        <v>93218</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>614953</v>
+        <v>615306</v>
       </c>
       <c r="R113" t="n">
-        <v>6560578</v>
+        <v>6560663</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12240,11 +12229,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12275,10 +12259,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131740361</v>
+        <v>131737630</v>
       </c>
       <c r="B114" t="n">
-        <v>93209</v>
+        <v>93218</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12286,30 +12270,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>615309</v>
+        <v>614948</v>
       </c>
       <c r="R114" t="n">
-        <v>6560557</v>
+        <v>6560611</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12350,7 +12338,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12373,10 +12360,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131737627</v>
+        <v>131738995</v>
       </c>
       <c r="B115" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12384,34 +12371,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>614921</v>
+        <v>615323</v>
       </c>
       <c r="R115" t="n">
-        <v>6560604</v>
+        <v>6560647</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12474,10 +12461,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131737648</v>
+        <v>131738990</v>
       </c>
       <c r="B116" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12485,34 +12472,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>615306</v>
+        <v>614930</v>
       </c>
       <c r="R116" t="n">
-        <v>6560663</v>
+        <v>6560587</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12575,45 +12562,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131737630</v>
+        <v>131740030</v>
       </c>
       <c r="B117" t="n">
-        <v>93218</v>
+        <v>57136</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614948</v>
+        <v>614953</v>
       </c>
       <c r="R117" t="n">
-        <v>6560611</v>
+        <v>6560578</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12646,6 +12641,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12676,10 +12676,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131740081</v>
+        <v>131737665</v>
       </c>
       <c r="B118" t="n">
-        <v>91913</v>
+        <v>93218</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12687,21 +12687,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12711,10 +12711,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614974</v>
+        <v>614993</v>
       </c>
       <c r="R118" t="n">
-        <v>6560628</v>
+        <v>6560559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12741,12 +12741,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12777,7 +12777,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737665</v>
+        <v>131737670</v>
       </c>
       <c r="B119" t="n">
         <v>93218</v>
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614993</v>
+        <v>614972</v>
       </c>
       <c r="R119" t="n">
-        <v>6560559</v>
+        <v>6560590</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12878,10 +12878,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131737670</v>
+        <v>131740081</v>
       </c>
       <c r="B120" t="n">
-        <v>93218</v>
+        <v>91913</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12889,21 +12889,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12913,10 +12913,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614972</v>
+        <v>614974</v>
       </c>
       <c r="R120" t="n">
-        <v>6560590</v>
+        <v>6560628</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12943,12 +12943,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13392,10 +13392,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131737622</v>
+        <v>131738997</v>
       </c>
       <c r="B125" t="n">
-        <v>93218</v>
+        <v>79936</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13403,34 +13403,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>614898</v>
+        <v>615026</v>
       </c>
       <c r="R125" t="n">
-        <v>6560601</v>
+        <v>6560531</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13493,7 +13493,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737683</v>
+        <v>131737622</v>
       </c>
       <c r="B126" t="n">
         <v>93218</v>
@@ -13524,14 +13524,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>615337</v>
+        <v>614898</v>
       </c>
       <c r="R126" t="n">
-        <v>6560617</v>
+        <v>6560601</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13594,7 +13594,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737678</v>
+        <v>131737683</v>
       </c>
       <c r="B127" t="n">
         <v>93218</v>
@@ -13629,10 +13629,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615054</v>
+        <v>615337</v>
       </c>
       <c r="R127" t="n">
-        <v>6560523</v>
+        <v>6560617</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13695,7 +13695,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737681</v>
+        <v>131737678</v>
       </c>
       <c r="B128" t="n">
         <v>93218</v>
@@ -13726,14 +13726,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615383</v>
+        <v>615054</v>
       </c>
       <c r="R128" t="n">
-        <v>6560632</v>
+        <v>6560523</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131738997</v>
+        <v>131737681</v>
       </c>
       <c r="B129" t="n">
-        <v>79936</v>
+        <v>93218</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13807,34 +13807,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615026</v>
+        <v>615383</v>
       </c>
       <c r="R129" t="n">
-        <v>6560531</v>
+        <v>6560632</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>122747219</v>
       </c>
       <c r="B15" t="n">
-        <v>79948</v>
+        <v>79951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>122747220</v>
       </c>
       <c r="B16" t="n">
-        <v>79948</v>
+        <v>79951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>122747218</v>
       </c>
       <c r="B17" t="n">
-        <v>78995</v>
+        <v>78998</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120287681</v>
+        <v>120287690</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615320</v>
+        <v>615236</v>
       </c>
       <c r="R2" t="n">
-        <v>6560647</v>
+        <v>6560476</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120287686</v>
+        <v>122747218</v>
       </c>
       <c r="B3" t="n">
-        <v>91931</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,44 +801,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nystugan, Nystugan, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615132</v>
+        <v>615184</v>
       </c>
       <c r="R3" t="n">
-        <v>6560670</v>
+        <v>6560537</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,27 +875,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120287679</v>
+        <v>131732526</v>
       </c>
       <c r="B4" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,40 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nystugan, Nystugan, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615119</v>
+        <v>615179</v>
       </c>
       <c r="R4" t="n">
-        <v>6560500</v>
+        <v>6560472</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +956,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Noterad</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,27 +981,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120287682</v>
+        <v>131737265</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,40 +1008,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nystugan, Nystugan, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615292</v>
+        <v>615132</v>
       </c>
       <c r="R5" t="n">
-        <v>6560674</v>
+        <v>6560489</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1066,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,68 +1091,68 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120287685</v>
+        <v>131737266</v>
       </c>
       <c r="B6" t="n">
-        <v>91908</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nystugan, Nystugan, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615181</v>
+        <v>615141</v>
       </c>
       <c r="R6" t="n">
-        <v>6560482</v>
+        <v>6560479</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,22 +1176,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,27 +1201,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120287683</v>
+        <v>120287685</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>615121</v>
+        <v>615181</v>
       </c>
       <c r="R7" t="n">
-        <v>6560512</v>
+        <v>6560482</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,15 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120287687</v>
+        <v>131732769</v>
       </c>
       <c r="B8" t="n">
-        <v>91931</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,44 +1338,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nystugan, Nystugan, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>615148</v>
+        <v>615104</v>
       </c>
       <c r="R8" t="n">
-        <v>6560597</v>
+        <v>6560485</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,22 +1392,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Återkommer spritt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,27 +1417,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120546355</v>
+        <v>120547055</v>
       </c>
       <c r="B9" t="n">
-        <v>79214</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615349</v>
+        <v>615073</v>
       </c>
       <c r="R9" t="n">
-        <v>6560530</v>
+        <v>6560506</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,15 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120546798</v>
+        <v>131740081</v>
       </c>
       <c r="B10" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,43 +1551,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nystugan, Nystugan, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615073</v>
+        <v>614974</v>
       </c>
       <c r="R10" t="n">
-        <v>6560557</v>
+        <v>6560628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,22 +1605,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,62 +1625,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120550625</v>
+        <v>131740369</v>
       </c>
       <c r="B11" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan, Nyckelsjötäppan, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614935</v>
+        <v>615152</v>
       </c>
       <c r="R11" t="n">
-        <v>6560562</v>
+        <v>6560500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,22 +1706,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,33 +1725,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120743622</v>
+        <v>131740402</v>
       </c>
       <c r="B12" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93300</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,46 +1759,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NV Nystugan, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615072</v>
+        <v>615135</v>
       </c>
       <c r="R12" t="n">
-        <v>6560566</v>
+        <v>6560485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,22 +1813,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 25st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,33 +1832,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120546766</v>
+        <v>120287686</v>
       </c>
       <c r="B13" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,27 +1885,25 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nystugan, Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615069</v>
+        <v>615132</v>
       </c>
       <c r="R13" t="n">
-        <v>6560570</v>
+        <v>6560670</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2040,22 +1927,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,27 +1957,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120550687</v>
+        <v>120287687</v>
       </c>
       <c r="B14" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,20 +1997,27 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan, Nyckelsjötäppan, Srm</t>
+          <t>Nystugan, Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615023</v>
+        <v>615148</v>
       </c>
       <c r="R14" t="n">
-        <v>6560654</v>
+        <v>6560597</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2152,22 +2041,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,22 +2071,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747219</v>
+        <v>120287688</v>
       </c>
       <c r="B15" t="n">
-        <v>79951</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,37 +2094,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Nystugan, Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615229</v>
+        <v>615158</v>
       </c>
       <c r="R15" t="n">
-        <v>6560552</v>
+        <v>6560470</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,12 +2155,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,26 +2185,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747220</v>
+        <v>120546766</v>
       </c>
       <c r="B16" t="n">
-        <v>79951</v>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,34 +2208,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Nystugan, Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615234</v>
+        <v>615069</v>
       </c>
       <c r="R16" t="n">
-        <v>6560540</v>
+        <v>6560570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,12 +2271,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,26 +2301,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747218</v>
+        <v>120550625</v>
       </c>
       <c r="B17" t="n">
-        <v>78998</v>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2407,34 +2324,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Nyckelsjötäppan, Nyckelsjötäppan, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615184</v>
+        <v>614935</v>
       </c>
       <c r="R17" t="n">
-        <v>6560537</v>
+        <v>6560562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,12 +2378,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,26 +2408,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737671</v>
+        <v>120550687</v>
       </c>
       <c r="B18" t="n">
-        <v>93218</v>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,14 +2451,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan, Nyckelsjötäppan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>614965</v>
+        <v>615023</v>
       </c>
       <c r="R18" t="n">
-        <v>6560580</v>
+        <v>6560654</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,12 +2485,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,26 +2515,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Josefin Mellberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737631</v>
+        <v>131737599</v>
       </c>
       <c r="B19" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,14 +2558,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614937</v>
+        <v>615246</v>
       </c>
       <c r="R19" t="n">
-        <v>6560625</v>
+        <v>6560472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131737632</v>
+        <v>131737600</v>
       </c>
       <c r="B20" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,14 +2659,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614949</v>
+        <v>615227</v>
       </c>
       <c r="R20" t="n">
-        <v>6560635</v>
+        <v>6560476</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737647</v>
+        <v>131737601</v>
       </c>
       <c r="B21" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,10 +2764,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615295</v>
+        <v>615212</v>
       </c>
       <c r="R21" t="n">
-        <v>6560678</v>
+        <v>6560475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737637</v>
+        <v>131737602</v>
       </c>
       <c r="B22" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,14 +2861,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614949</v>
+        <v>615184</v>
       </c>
       <c r="R22" t="n">
-        <v>6560610</v>
+        <v>6560472</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3002,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737650</v>
+        <v>131737603</v>
       </c>
       <c r="B23" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615325</v>
+        <v>615176</v>
       </c>
       <c r="R23" t="n">
-        <v>6560719</v>
+        <v>6560478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737654</v>
+        <v>131737614</v>
       </c>
       <c r="B24" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,14 +3063,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615282</v>
+        <v>614857</v>
       </c>
       <c r="R24" t="n">
-        <v>6560780</v>
+        <v>6560612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3204,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737614</v>
+        <v>131737615</v>
       </c>
       <c r="B25" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614857</v>
+        <v>614854</v>
       </c>
       <c r="R25" t="n">
-        <v>6560612</v>
+        <v>6560611</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131739009</v>
+        <v>131737616</v>
       </c>
       <c r="B26" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,34 +3245,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614998</v>
+        <v>614862</v>
       </c>
       <c r="R26" t="n">
-        <v>6560540</v>
+        <v>6560592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3406,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131739006</v>
+        <v>131737617</v>
       </c>
       <c r="B27" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,34 +3346,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614970</v>
+        <v>614867</v>
       </c>
       <c r="R27" t="n">
-        <v>6560568</v>
+        <v>6560588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131738992</v>
+        <v>131737618</v>
       </c>
       <c r="B28" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,21 +3447,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3542,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614903</v>
+        <v>614881</v>
       </c>
       <c r="R28" t="n">
-        <v>6560580</v>
+        <v>6560601</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131737787</v>
+        <v>131737619</v>
       </c>
       <c r="B29" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3636,21 +3565,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>615336</v>
+        <v>614885</v>
       </c>
       <c r="R29" t="n">
-        <v>6560522</v>
+        <v>6560613</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,17 +3602,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131737651</v>
+        <v>131737620</v>
       </c>
       <c r="B30" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,14 +3669,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>615311</v>
+        <v>614896</v>
       </c>
       <c r="R30" t="n">
-        <v>6560742</v>
+        <v>6560613</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3819,10 +3739,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737785</v>
+        <v>131737621</v>
       </c>
       <c r="B31" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,21 +3767,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>615314</v>
+        <v>614898</v>
       </c>
       <c r="R31" t="n">
-        <v>6560513</v>
+        <v>6560597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,17 +3804,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>39</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737784</v>
+        <v>131737622</v>
       </c>
       <c r="B32" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3868,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>615291</v>
+        <v>614898</v>
       </c>
       <c r="R32" t="n">
-        <v>6560497</v>
+        <v>6560601</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3998,17 +3905,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737629</v>
+        <v>131737624</v>
       </c>
       <c r="B33" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,14 +3972,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614941</v>
+        <v>614910</v>
       </c>
       <c r="R33" t="n">
-        <v>6560607</v>
+        <v>6560612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4140,10 +4042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131738991</v>
+        <v>131737625</v>
       </c>
       <c r="B34" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,21 +4053,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4175,10 +4077,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614921</v>
+        <v>614918</v>
       </c>
       <c r="R34" t="n">
-        <v>6560577</v>
+        <v>6560620</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,10 +4143,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131739043</v>
+        <v>131737626</v>
       </c>
       <c r="B35" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4252,34 +4154,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614985</v>
+        <v>614911</v>
       </c>
       <c r="R35" t="n">
-        <v>6560565</v>
+        <v>6560610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4306,12 +4208,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4342,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131739007</v>
+        <v>131737627</v>
       </c>
       <c r="B36" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,34 +4255,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614970</v>
+        <v>614921</v>
       </c>
       <c r="R36" t="n">
-        <v>6560560</v>
+        <v>6560604</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4443,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131737640</v>
+        <v>131737629</v>
       </c>
       <c r="B37" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,14 +4376,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614934</v>
+        <v>614941</v>
       </c>
       <c r="R37" t="n">
-        <v>6560578</v>
+        <v>6560607</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4544,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131737685</v>
+        <v>131737630</v>
       </c>
       <c r="B38" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,14 +4477,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>615324</v>
+        <v>614948</v>
       </c>
       <c r="R38" t="n">
-        <v>6560604</v>
+        <v>6560611</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4645,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131737672</v>
+        <v>131737631</v>
       </c>
       <c r="B39" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4680,10 +4582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614950</v>
+        <v>614937</v>
       </c>
       <c r="R39" t="n">
-        <v>6560576</v>
+        <v>6560625</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4746,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737786</v>
+        <v>131737632</v>
       </c>
       <c r="B40" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4774,21 +4676,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>615335</v>
+        <v>614949</v>
       </c>
       <c r="R40" t="n">
-        <v>6560536</v>
+        <v>6560635</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4815,17 +4713,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4856,10 +4749,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131737662</v>
+        <v>131737633</v>
       </c>
       <c r="B41" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,10 +4784,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>615040</v>
+        <v>614946</v>
       </c>
       <c r="R41" t="n">
-        <v>6560530</v>
+        <v>6560623</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4957,10 +4850,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131737620</v>
+        <v>131737634</v>
       </c>
       <c r="B42" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4988,14 +4881,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614896</v>
+        <v>614954</v>
       </c>
       <c r="R42" t="n">
-        <v>6560613</v>
+        <v>6560617</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5058,10 +4951,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131737634</v>
+        <v>131737635</v>
       </c>
       <c r="B43" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5093,10 +4986,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614954</v>
+        <v>614963</v>
       </c>
       <c r="R43" t="n">
-        <v>6560617</v>
+        <v>6560615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,10 +5052,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131737669</v>
+        <v>131737636</v>
       </c>
       <c r="B44" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5194,10 +5087,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614973</v>
+        <v>614960</v>
       </c>
       <c r="R44" t="n">
-        <v>6560600</v>
+        <v>6560601</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5260,10 +5153,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131737660</v>
+        <v>131737637</v>
       </c>
       <c r="B45" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5291,14 +5184,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>615278</v>
+        <v>614949</v>
       </c>
       <c r="R45" t="n">
-        <v>6560662</v>
+        <v>6560610</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5361,10 +5254,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131737635</v>
+        <v>131737638</v>
       </c>
       <c r="B46" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5396,10 +5289,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614963</v>
+        <v>614943</v>
       </c>
       <c r="R46" t="n">
-        <v>6560615</v>
+        <v>6560591</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,10 +5355,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131737618</v>
+        <v>131737639</v>
       </c>
       <c r="B47" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5497,10 +5390,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614881</v>
+        <v>614942</v>
       </c>
       <c r="R47" t="n">
-        <v>6560601</v>
+        <v>6560579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5563,10 +5456,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131739002</v>
+        <v>131737640</v>
       </c>
       <c r="B48" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5574,34 +5467,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614953</v>
+        <v>614934</v>
       </c>
       <c r="R48" t="n">
-        <v>6560567</v>
+        <v>6560578</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5664,10 +5557,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131737616</v>
+        <v>131737641</v>
       </c>
       <c r="B49" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,10 +5592,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614862</v>
+        <v>614893</v>
       </c>
       <c r="R49" t="n">
-        <v>6560592</v>
+        <v>6560582</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5765,10 +5658,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131737677</v>
+        <v>131737642</v>
       </c>
       <c r="B50" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5796,14 +5689,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>615064</v>
+        <v>614884</v>
       </c>
       <c r="R50" t="n">
-        <v>6560525</v>
+        <v>6560568</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,10 +5759,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131737684</v>
+        <v>131737661</v>
       </c>
       <c r="B51" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5897,14 +5790,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>615333</v>
+        <v>615060</v>
       </c>
       <c r="R51" t="n">
-        <v>6560608</v>
+        <v>6560565</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,10 +5860,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131739012</v>
+        <v>131737662</v>
       </c>
       <c r="B52" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5978,21 +5871,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6002,10 +5895,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>615022</v>
+        <v>615040</v>
       </c>
       <c r="R52" t="n">
-        <v>6560527</v>
+        <v>6560530</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,45 +5961,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131737925</v>
+        <v>131737663</v>
       </c>
       <c r="B53" t="n">
-        <v>8455</v>
+        <v>93309</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>615343</v>
+        <v>615046</v>
       </c>
       <c r="R53" t="n">
-        <v>6560656</v>
+        <v>6560537</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6169,10 +6062,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131737675</v>
+        <v>131737664</v>
       </c>
       <c r="B54" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6200,14 +6093,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614961</v>
+        <v>614942</v>
       </c>
       <c r="R54" t="n">
-        <v>6560552</v>
+        <v>6560568</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6270,10 +6163,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737617</v>
+        <v>131737665</v>
       </c>
       <c r="B55" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6301,14 +6194,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614867</v>
+        <v>614993</v>
       </c>
       <c r="R55" t="n">
-        <v>6560588</v>
+        <v>6560559</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6371,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131737621</v>
+        <v>131737666</v>
       </c>
       <c r="B56" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6402,14 +6295,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614898</v>
+        <v>614995</v>
       </c>
       <c r="R56" t="n">
-        <v>6560597</v>
+        <v>6560571</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6472,10 +6365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737633</v>
+        <v>131737667</v>
       </c>
       <c r="B57" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6507,10 +6400,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614946</v>
+        <v>614991</v>
       </c>
       <c r="R57" t="n">
-        <v>6560623</v>
+        <v>6560587</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6573,10 +6466,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737657</v>
+        <v>131737668</v>
       </c>
       <c r="B58" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6608,10 +6501,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>615264</v>
+        <v>614990</v>
       </c>
       <c r="R58" t="n">
-        <v>6560736</v>
+        <v>6560601</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6674,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737615</v>
+        <v>131737669</v>
       </c>
       <c r="B59" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6705,14 +6598,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614854</v>
+        <v>614973</v>
       </c>
       <c r="R59" t="n">
-        <v>6560611</v>
+        <v>6560600</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6775,10 +6668,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737652</v>
+        <v>131737670</v>
       </c>
       <c r="B60" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6810,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>615301</v>
+        <v>614972</v>
       </c>
       <c r="R60" t="n">
-        <v>6560755</v>
+        <v>6560590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6876,10 +6769,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737688</v>
+        <v>131737671</v>
       </c>
       <c r="B61" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6907,14 +6800,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>615310</v>
+        <v>614965</v>
       </c>
       <c r="R61" t="n">
-        <v>6560543</v>
+        <v>6560580</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6977,10 +6870,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131738993</v>
+        <v>131737672</v>
       </c>
       <c r="B62" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6988,34 +6881,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614904</v>
+        <v>614950</v>
       </c>
       <c r="R62" t="n">
-        <v>6560578</v>
+        <v>6560576</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7078,10 +6971,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739008</v>
+        <v>131737673</v>
       </c>
       <c r="B63" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7089,21 +6982,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7113,10 +7006,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614995</v>
+        <v>614957</v>
       </c>
       <c r="R63" t="n">
-        <v>6560547</v>
+        <v>6560564</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7179,10 +7072,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739005</v>
+        <v>131737674</v>
       </c>
       <c r="B64" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7190,21 +7083,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7214,10 +7107,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614968</v>
+        <v>614965</v>
       </c>
       <c r="R64" t="n">
-        <v>6560572</v>
+        <v>6560563</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7280,10 +7173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131736575</v>
+        <v>131737675</v>
       </c>
       <c r="B65" t="n">
-        <v>93196</v>
+        <v>93309</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7291,34 +7184,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>615336</v>
+        <v>614961</v>
       </c>
       <c r="R65" t="n">
-        <v>6560577</v>
+        <v>6560552</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7345,12 +7238,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7381,10 +7274,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131737686</v>
+        <v>131737676</v>
       </c>
       <c r="B66" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7416,10 +7309,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>615314</v>
+        <v>615060</v>
       </c>
       <c r="R66" t="n">
-        <v>6560599</v>
+        <v>6560536</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7482,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131737643</v>
+        <v>131737677</v>
       </c>
       <c r="B67" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7517,10 +7410,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>615322</v>
+        <v>615064</v>
       </c>
       <c r="R67" t="n">
-        <v>6560634</v>
+        <v>6560525</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7583,10 +7476,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131740360</v>
+        <v>131737678</v>
       </c>
       <c r="B68" t="n">
-        <v>93209</v>
+        <v>93309</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7594,34 +7487,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>615296</v>
+        <v>615054</v>
       </c>
       <c r="R68" t="n">
-        <v>6560688</v>
+        <v>6560523</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7656,18 +7549,12 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7690,10 +7577,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131737658</v>
+        <v>131737779</v>
       </c>
       <c r="B69" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,17 +7605,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>615282</v>
+        <v>615173</v>
       </c>
       <c r="R69" t="n">
-        <v>6560684</v>
+        <v>6560476</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7755,12 +7646,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7791,10 +7687,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131737667</v>
+        <v>131737780</v>
       </c>
       <c r="B70" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7819,17 +7715,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614991</v>
+        <v>615164</v>
       </c>
       <c r="R70" t="n">
-        <v>6560587</v>
+        <v>6560465</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7856,12 +7756,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7892,10 +7797,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131737638</v>
+        <v>131737781</v>
       </c>
       <c r="B71" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7920,17 +7825,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614943</v>
+        <v>615158</v>
       </c>
       <c r="R71" t="n">
-        <v>6560591</v>
+        <v>6560491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7957,12 +7866,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7993,10 +7907,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131739010</v>
+        <v>131737782</v>
       </c>
       <c r="B72" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8004,34 +7918,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>615012</v>
+        <v>615216</v>
       </c>
       <c r="R72" t="n">
-        <v>6560549</v>
+        <v>6560514</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8058,12 +7976,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8094,48 +8017,51 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131739015</v>
+        <v>120287679</v>
       </c>
       <c r="B73" t="n">
-        <v>79936</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan, Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>615373</v>
+        <v>615119</v>
       </c>
       <c r="R73" t="n">
-        <v>6560555</v>
+        <v>6560500</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8159,12 +8085,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8179,26 +8115,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Josefin Mellberg</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131737644</v>
+        <v>120287683</v>
       </c>
       <c r="B74" t="n">
-        <v>93218</v>
+        <v>79946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8206,37 +8138,40 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan, Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>615331</v>
+        <v>615121</v>
       </c>
       <c r="R74" t="n">
-        <v>6560676</v>
+        <v>6560512</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8260,12 +8195,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8280,26 +8225,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Josefin Mellberg</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131737639</v>
+        <v>122747219</v>
       </c>
       <c r="B75" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8307,34 +8248,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614942</v>
+        <v>615229</v>
       </c>
       <c r="R75" t="n">
-        <v>6560579</v>
+        <v>6560552</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8361,12 +8302,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8386,7 +8327,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Josefin Mellberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8397,10 +8338,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131737668</v>
+        <v>122747220</v>
       </c>
       <c r="B76" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8408,34 +8349,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614990</v>
+        <v>615234</v>
       </c>
       <c r="R76" t="n">
-        <v>6560601</v>
+        <v>6560540</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8462,12 +8403,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8487,7 +8428,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Josefin Mellberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8498,10 +8439,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131738989</v>
+        <v>131738988</v>
       </c>
       <c r="B77" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,14 +8470,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>614945</v>
+        <v>614862</v>
       </c>
       <c r="R77" t="n">
-        <v>6560637</v>
+        <v>6560592</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8599,10 +8540,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131739041</v>
+        <v>131738989</v>
       </c>
       <c r="B78" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,14 +8571,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>615269</v>
+        <v>614945</v>
       </c>
       <c r="R78" t="n">
-        <v>6560500</v>
+        <v>6560637</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8664,12 +8605,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8700,10 +8641,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131739011</v>
+        <v>131738990</v>
       </c>
       <c r="B79" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8731,14 +8672,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>615080</v>
+        <v>614930</v>
       </c>
       <c r="R79" t="n">
-        <v>6560512</v>
+        <v>6560587</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8801,45 +8742,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131737924</v>
+        <v>131738991</v>
       </c>
       <c r="B80" t="n">
-        <v>8455</v>
+        <v>79992</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>615091</v>
+        <v>614921</v>
       </c>
       <c r="R80" t="n">
-        <v>6560504</v>
+        <v>6560577</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8902,10 +8843,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131737674</v>
+        <v>131738992</v>
       </c>
       <c r="B81" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8913,34 +8854,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>614965</v>
+        <v>614903</v>
       </c>
       <c r="R81" t="n">
-        <v>6560563</v>
+        <v>6560580</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9003,10 +8944,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131737782</v>
+        <v>131738993</v>
       </c>
       <c r="B82" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9014,38 +8955,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>615216</v>
+        <v>614904</v>
       </c>
       <c r="R82" t="n">
-        <v>6560514</v>
+        <v>6560578</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9072,17 +9009,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9113,10 +9045,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131737680</v>
+        <v>131738994</v>
       </c>
       <c r="B83" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9124,34 +9056,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>615390</v>
+        <v>614890</v>
       </c>
       <c r="R83" t="n">
-        <v>6560614</v>
+        <v>6560564</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9214,10 +9146,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131737653</v>
+        <v>131738997</v>
       </c>
       <c r="B84" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9225,21 +9157,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9249,10 +9181,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>615289</v>
+        <v>615026</v>
       </c>
       <c r="R84" t="n">
-        <v>6560767</v>
+        <v>6560531</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9315,10 +9247,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131737624</v>
+        <v>131738998</v>
       </c>
       <c r="B85" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9326,34 +9258,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>614910</v>
+        <v>615020</v>
       </c>
       <c r="R85" t="n">
-        <v>6560612</v>
+        <v>6560533</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9416,10 +9348,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131737626</v>
+        <v>131738999</v>
       </c>
       <c r="B86" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9427,34 +9359,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>614911</v>
+        <v>615013</v>
       </c>
       <c r="R86" t="n">
-        <v>6560610</v>
+        <v>6560527</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9517,10 +9449,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131737642</v>
+        <v>131739000</v>
       </c>
       <c r="B87" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9528,21 +9460,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9552,10 +9484,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>614884</v>
+        <v>614941</v>
       </c>
       <c r="R87" t="n">
-        <v>6560568</v>
+        <v>6560553</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9618,10 +9550,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131737687</v>
+        <v>131739001</v>
       </c>
       <c r="B88" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9629,34 +9561,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>615322</v>
+        <v>614955</v>
       </c>
       <c r="R88" t="n">
-        <v>6560582</v>
+        <v>6560579</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9719,10 +9651,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131738988</v>
+        <v>131739002</v>
       </c>
       <c r="B89" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9750,14 +9682,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>614862</v>
+        <v>614953</v>
       </c>
       <c r="R89" t="n">
-        <v>6560592</v>
+        <v>6560567</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9820,10 +9752,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131738998</v>
+        <v>131739003</v>
       </c>
       <c r="B90" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9855,10 +9787,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>615020</v>
+        <v>614959</v>
       </c>
       <c r="R90" t="n">
-        <v>6560533</v>
+        <v>6560556</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9921,10 +9853,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131737676</v>
+        <v>131739004</v>
       </c>
       <c r="B91" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9932,34 +9864,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>615060</v>
+        <v>614958</v>
       </c>
       <c r="R91" t="n">
-        <v>6560536</v>
+        <v>6560561</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10022,10 +9954,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131737783</v>
+        <v>131739005</v>
       </c>
       <c r="B92" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10033,38 +9965,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>615276</v>
+        <v>614968</v>
       </c>
       <c r="R92" t="n">
-        <v>6560495</v>
+        <v>6560572</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10091,17 +10019,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10132,10 +10055,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131737641</v>
+        <v>131739006</v>
       </c>
       <c r="B93" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10143,34 +10066,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>614893</v>
+        <v>614970</v>
       </c>
       <c r="R93" t="n">
-        <v>6560582</v>
+        <v>6560568</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10233,10 +10156,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131737656</v>
+        <v>131739007</v>
       </c>
       <c r="B94" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10244,21 +10167,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10268,10 +10191,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>615271</v>
+        <v>614970</v>
       </c>
       <c r="R94" t="n">
-        <v>6560749</v>
+        <v>6560560</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10334,10 +10257,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131737666</v>
+        <v>131739008</v>
       </c>
       <c r="B95" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10345,21 +10268,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10372,7 +10295,7 @@
         <v>614995</v>
       </c>
       <c r="R95" t="n">
-        <v>6560571</v>
+        <v>6560547</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10435,10 +10358,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131737646</v>
+        <v>131739009</v>
       </c>
       <c r="B96" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10446,34 +10369,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>615289</v>
+        <v>614998</v>
       </c>
       <c r="R96" t="n">
-        <v>6560695</v>
+        <v>6560540</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10536,10 +10459,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131737690</v>
+        <v>131739010</v>
       </c>
       <c r="B97" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10547,34 +10470,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>615387</v>
+        <v>615012</v>
       </c>
       <c r="R97" t="n">
-        <v>6560558</v>
+        <v>6560549</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10637,10 +10560,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131737659</v>
+        <v>131739011</v>
       </c>
       <c r="B98" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10648,21 +10571,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10672,10 +10595,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>615267</v>
+        <v>615080</v>
       </c>
       <c r="R98" t="n">
-        <v>6560667</v>
+        <v>6560512</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10738,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131737649</v>
+        <v>131739012</v>
       </c>
       <c r="B99" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10749,34 +10672,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>615316</v>
+        <v>615022</v>
       </c>
       <c r="R99" t="n">
-        <v>6560709</v>
+        <v>6560527</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10839,10 +10762,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131739004</v>
+        <v>131739026</v>
       </c>
       <c r="B100" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10870,14 +10793,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>614958</v>
+        <v>615203</v>
       </c>
       <c r="R100" t="n">
-        <v>6560561</v>
+        <v>6560503</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10904,12 +10827,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10940,10 +10863,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131737625</v>
+        <v>131739043</v>
       </c>
       <c r="B101" t="n">
-        <v>93218</v>
+        <v>79992</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10951,34 +10874,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>614918</v>
+        <v>614985</v>
       </c>
       <c r="R101" t="n">
-        <v>6560620</v>
+        <v>6560565</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11005,12 +10928,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11041,45 +10964,57 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131737645</v>
+        <v>120743622</v>
       </c>
       <c r="B102" t="n">
-        <v>93218</v>
+        <v>57141</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>NV Nystugan, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>615304</v>
+        <v>615072</v>
       </c>
       <c r="R102" t="n">
-        <v>6560686</v>
+        <v>6560566</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11106,12 +11041,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11126,61 +11071,65 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Josefin Mellberg</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131737655</v>
+        <v>131740030</v>
       </c>
       <c r="B103" t="n">
-        <v>93218</v>
+        <v>57162</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>615267</v>
+        <v>614953</v>
       </c>
       <c r="R103" t="n">
-        <v>6560777</v>
+        <v>6560578</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11213,6 +11162,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11243,45 +11197,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131737636</v>
+        <v>131737924</v>
       </c>
       <c r="B104" t="n">
-        <v>93218</v>
+        <v>8460</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>614960</v>
+        <v>615091</v>
       </c>
       <c r="R104" t="n">
-        <v>6560601</v>
+        <v>6560504</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11344,45 +11298,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131737691</v>
+        <v>131733476</v>
       </c>
       <c r="B105" t="n">
-        <v>93218</v>
+        <v>8449</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>106554</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Öst, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>615367</v>
+        <v>614831</v>
       </c>
       <c r="R105" t="n">
-        <v>6560553</v>
+        <v>6560599</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11409,12 +11363,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11445,45 +11399,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131737619</v>
+        <v>131735760</v>
       </c>
       <c r="B106" t="n">
-        <v>93218</v>
+        <v>90739</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>614885</v>
+        <v>615279</v>
       </c>
       <c r="R106" t="n">
-        <v>6560613</v>
+        <v>6560699</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11546,45 +11500,49 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131737664</v>
+        <v>131735761</v>
       </c>
       <c r="B107" t="n">
-        <v>93218</v>
+        <v>90739</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5966</v>
+        <v>1596</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>614942</v>
+        <v>615277</v>
       </c>
       <c r="R107" t="n">
-        <v>6560568</v>
+        <v>6560691</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11617,6 +11575,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11647,45 +11610,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131739013</v>
+        <v>131736566</v>
       </c>
       <c r="B108" t="n">
-        <v>79936</v>
+        <v>93287</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>615376</v>
+        <v>615319</v>
       </c>
       <c r="R108" t="n">
-        <v>6560556</v>
+        <v>6560579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11718,6 +11685,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11748,45 +11720,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131739001</v>
+        <v>131736575</v>
       </c>
       <c r="B109" t="n">
-        <v>79936</v>
+        <v>93287</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>614955</v>
+        <v>615336</v>
       </c>
       <c r="R109" t="n">
-        <v>6560579</v>
+        <v>6560577</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11813,12 +11785,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11849,37 +11821,33 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131736566</v>
+        <v>131740360</v>
       </c>
       <c r="B110" t="n">
-        <v>93196</v>
+        <v>93300</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11888,10 +11856,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>615319</v>
+        <v>615296</v>
       </c>
       <c r="R110" t="n">
-        <v>6560579</v>
+        <v>6560688</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11928,7 +11896,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11937,6 +11905,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11962,11 +11931,11 @@
         <v>131740361</v>
       </c>
       <c r="B111" t="n">
-        <v>93209</v>
+        <v>93300</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -12057,10 +12026,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131737627</v>
+        <v>131737598</v>
       </c>
       <c r="B112" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12088,14 +12057,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>614921</v>
+        <v>615292</v>
       </c>
       <c r="R112" t="n">
-        <v>6560604</v>
+        <v>6560469</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12158,10 +12127,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131737648</v>
+        <v>131737643</v>
       </c>
       <c r="B113" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12193,10 +12162,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>615306</v>
+        <v>615322</v>
       </c>
       <c r="R113" t="n">
-        <v>6560663</v>
+        <v>6560634</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12259,10 +12228,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131737630</v>
+        <v>131737644</v>
       </c>
       <c r="B114" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12290,14 +12259,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>614948</v>
+        <v>615331</v>
       </c>
       <c r="R114" t="n">
-        <v>6560611</v>
+        <v>6560676</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12360,10 +12329,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131738995</v>
+        <v>131737645</v>
       </c>
       <c r="B115" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12371,21 +12340,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12395,10 +12364,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>615323</v>
+        <v>615304</v>
       </c>
       <c r="R115" t="n">
-        <v>6560647</v>
+        <v>6560686</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12461,10 +12430,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131738990</v>
+        <v>131737646</v>
       </c>
       <c r="B116" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12472,34 +12441,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>614930</v>
+        <v>615289</v>
       </c>
       <c r="R116" t="n">
-        <v>6560587</v>
+        <v>6560695</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12562,53 +12531,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131740030</v>
+        <v>131737647</v>
       </c>
       <c r="B117" t="n">
-        <v>57136</v>
+        <v>93309</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>614953</v>
+        <v>615295</v>
       </c>
       <c r="R117" t="n">
-        <v>6560578</v>
+        <v>6560678</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12641,11 +12602,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12676,10 +12632,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131737665</v>
+        <v>131737648</v>
       </c>
       <c r="B118" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12707,14 +12663,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>614993</v>
+        <v>615306</v>
       </c>
       <c r="R118" t="n">
-        <v>6560559</v>
+        <v>6560663</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12777,10 +12733,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131737670</v>
+        <v>131737649</v>
       </c>
       <c r="B119" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12808,14 +12764,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>614972</v>
+        <v>615316</v>
       </c>
       <c r="R119" t="n">
-        <v>6560590</v>
+        <v>6560709</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12878,10 +12834,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131740081</v>
+        <v>131737650</v>
       </c>
       <c r="B120" t="n">
-        <v>91913</v>
+        <v>93309</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12889,34 +12845,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>614974</v>
+        <v>615325</v>
       </c>
       <c r="R120" t="n">
-        <v>6560628</v>
+        <v>6560719</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12943,12 +12899,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12979,10 +12935,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131739003</v>
+        <v>131737651</v>
       </c>
       <c r="B121" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12990,34 +12946,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>614959</v>
+        <v>615311</v>
       </c>
       <c r="R121" t="n">
-        <v>6560556</v>
+        <v>6560742</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13080,10 +13036,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131738994</v>
+        <v>131737652</v>
       </c>
       <c r="B122" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13091,34 +13047,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>614890</v>
+        <v>615301</v>
       </c>
       <c r="R122" t="n">
-        <v>6560564</v>
+        <v>6560755</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13181,10 +13137,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131739000</v>
+        <v>131737653</v>
       </c>
       <c r="B123" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13192,34 +13148,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>614941</v>
+        <v>615289</v>
       </c>
       <c r="R123" t="n">
-        <v>6560553</v>
+        <v>6560767</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13282,49 +13238,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131735761</v>
+        <v>131737654</v>
       </c>
       <c r="B124" t="n">
-        <v>90657</v>
+        <v>93309</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>615277</v>
+        <v>615282</v>
       </c>
       <c r="R124" t="n">
-        <v>6560691</v>
+        <v>6560780</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13357,11 +13309,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13392,10 +13339,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131738997</v>
+        <v>131737655</v>
       </c>
       <c r="B125" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13403,21 +13350,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13427,10 +13374,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>615026</v>
+        <v>615267</v>
       </c>
       <c r="R125" t="n">
-        <v>6560531</v>
+        <v>6560777</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13493,10 +13440,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131737622</v>
+        <v>131737656</v>
       </c>
       <c r="B126" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13524,14 +13471,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Öst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>614898</v>
+        <v>615271</v>
       </c>
       <c r="R126" t="n">
-        <v>6560601</v>
+        <v>6560749</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13594,10 +13541,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131737683</v>
+        <v>131737657</v>
       </c>
       <c r="B127" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13625,14 +13572,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nyckelsjötäppan Sydost, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>615337</v>
+        <v>615264</v>
       </c>
       <c r="R127" t="n">
-        <v>6560617</v>
+        <v>6560736</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13695,10 +13642,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131737678</v>
+        <v>131737658</v>
       </c>
       <c r="B128" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13730,10 +13677,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>615054</v>
+        <v>615282</v>
       </c>
       <c r="R128" t="n">
-        <v>6560523</v>
+        <v>6560684</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13796,10 +13743,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131737681</v>
+        <v>131737659</v>
       </c>
       <c r="B129" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13827,14 +13774,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Nystugan Väst, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>615383</v>
+        <v>615267</v>
       </c>
       <c r="R129" t="n">
-        <v>6560632</v>
+        <v>6560667</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13897,10 +13844,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131739026</v>
+        <v>131737660</v>
       </c>
       <c r="B130" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13908,21 +13855,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13932,10 +13879,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>615203</v>
+        <v>615278</v>
       </c>
       <c r="R130" t="n">
-        <v>6560503</v>
+        <v>6560662</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13962,12 +13909,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13998,45 +13945,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131735760</v>
+        <v>131737679</v>
       </c>
       <c r="B131" t="n">
-        <v>90657</v>
+        <v>93309</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1596</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>615279</v>
+        <v>615410</v>
       </c>
       <c r="R131" t="n">
-        <v>6560699</v>
+        <v>6560592</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14099,10 +14046,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131737661</v>
+        <v>131737680</v>
       </c>
       <c r="B132" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14130,14 +14077,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>615060</v>
+        <v>615390</v>
       </c>
       <c r="R132" t="n">
-        <v>6560565</v>
+        <v>6560614</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14200,10 +14147,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131738996</v>
+        <v>131737681</v>
       </c>
       <c r="B133" t="n">
-        <v>79936</v>
+        <v>93309</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14211,34 +14158,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Nystugan Nordväst, Srm</t>
+          <t>Nystugan Väst, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>615290</v>
+        <v>615383</v>
       </c>
       <c r="R133" t="n">
-        <v>6560715</v>
+        <v>6560632</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14304,7 +14251,7 @@
         <v>131737682</v>
       </c>
       <c r="B134" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14402,10 +14349,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131737663</v>
+        <v>131737683</v>
       </c>
       <c r="B135" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14433,14 +14380,14 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>615046</v>
+        <v>615337</v>
       </c>
       <c r="R135" t="n">
-        <v>6560537</v>
+        <v>6560617</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14503,10 +14450,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131737673</v>
+        <v>131737684</v>
       </c>
       <c r="B136" t="n">
-        <v>93218</v>
+        <v>93309</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14534,14 +14481,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nyckelsjötäppan Sydost, Srm</t>
+          <t>Nystugan Nordväst, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>614957</v>
+        <v>615333</v>
       </c>
       <c r="R136" t="n">
-        <v>6560564</v>
+        <v>6560608</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14597,6 +14544,2411 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>131737685</v>
+      </c>
+      <c r="B137" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>615324</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6560604</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>131737686</v>
+      </c>
+      <c r="B138" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>615314</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6560599</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>131737687</v>
+      </c>
+      <c r="B139" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>615322</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6560582</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>131737688</v>
+      </c>
+      <c r="B140" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>615310</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6560543</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>131737689</v>
+      </c>
+      <c r="B141" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Nystugan Väst, Srm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>615400</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6560559</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>131737690</v>
+      </c>
+      <c r="B142" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>615387</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6560558</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>131737691</v>
+      </c>
+      <c r="B143" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>615367</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6560553</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>131737692</v>
+      </c>
+      <c r="B144" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>615382</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6560526</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>131737783</v>
+      </c>
+      <c r="B145" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>615276</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6560495</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>131737784</v>
+      </c>
+      <c r="B146" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>615291</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6560497</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>131737785</v>
+      </c>
+      <c r="B147" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>615314</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6560513</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>131737786</v>
+      </c>
+      <c r="B148" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>615335</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6560536</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>131737787</v>
+      </c>
+      <c r="B149" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>615336</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6560522</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>131737788</v>
+      </c>
+      <c r="B150" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>615372</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6560527</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>120287681</v>
+      </c>
+      <c r="B151" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Nystugan, Nystugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>615320</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6560647</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>120287682</v>
+      </c>
+      <c r="B152" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Nystugan, Nystugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>615292</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6560674</v>
+      </c>
+      <c r="S152" t="n">
+        <v>2</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>120546355</v>
+      </c>
+      <c r="B153" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Nystugan, Nystugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>615349</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6560530</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>131738995</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>615323</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6560647</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>131738996</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>615290</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6560715</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>131739013</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>615376</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6560556</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>131739015</v>
+      </c>
+      <c r="B157" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>615373</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6560555</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>131739041</v>
+      </c>
+      <c r="B158" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>615269</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6560500</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>131737925</v>
+      </c>
+      <c r="B159" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Nystugan Nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>615343</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6560656</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Josefin Mellberg</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 43303-2024 artfynd.xlsx
+++ b/artfynd/A 43303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY159"/>
+  <dimension ref="A1:AZ159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747218</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732526</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737266</t>
         </is>
       </c>
     </row>
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287685</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732769</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120547055</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740369</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740402</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287686</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287687</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287688</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120546766</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120550625</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2409,6 +2489,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120550687</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737602</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2611,6 +2701,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737603</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737614</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2813,6 +2913,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737615</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737616</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737617</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3116,6 +3231,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737618</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3217,6 +3337,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737619</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3318,6 +3443,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737620</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737621</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3520,6 +3655,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737622</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3621,6 +3761,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737624</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3722,6 +3867,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737625</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3823,6 +3973,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737626</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3924,6 +4079,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737627</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4025,6 +4185,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737629</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4126,6 +4291,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737630</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4227,6 +4397,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737631</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4328,6 +4503,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737632</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4429,6 +4609,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737633</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4530,6 +4715,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737634</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4631,6 +4821,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737635</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4732,6 +4927,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737636</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4833,6 +5033,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737637</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4934,6 +5139,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737638</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5035,6 +5245,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737639</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5136,6 +5351,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737640</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5237,6 +5457,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737641</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5338,6 +5563,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737642</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5439,6 +5669,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737661</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5540,6 +5775,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737662</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5641,6 +5881,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737663</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5742,6 +5987,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737664</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5843,6 +6093,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737665</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5944,6 +6199,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737666</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6045,6 +6305,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737667</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6146,6 +6411,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737668</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6247,6 +6517,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737669</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6348,6 +6623,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737670</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6449,6 +6729,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737671</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6550,6 +6835,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737672</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6651,6 +6941,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737673</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6752,6 +7047,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737674</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6853,6 +7153,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737675</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6954,6 +7259,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737676</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7055,6 +7365,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737677</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7156,6 +7471,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737678</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7266,6 +7586,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737779</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7376,6 +7701,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737780</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7484,6 +7814,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737781</t>
         </is>
       </c>
     </row>
@@ -7596,6 +7931,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287679</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7706,6 +8046,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287683</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7807,6 +8152,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738988</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7908,6 +8258,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738989</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8009,6 +8364,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738990</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8110,6 +8470,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738991</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8211,6 +8576,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738992</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8312,6 +8682,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738993</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8413,6 +8788,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738994</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8514,6 +8894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738997</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8615,6 +9000,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738998</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8716,6 +9106,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738999</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8817,6 +9212,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739000</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8918,6 +9318,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739001</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9019,6 +9424,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739002</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9120,6 +9530,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739003</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9221,6 +9636,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739004</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9322,6 +9742,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739005</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9423,6 +9848,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739006</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9524,6 +9954,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739007</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9625,6 +10060,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739008</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9726,6 +10166,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739009</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9827,6 +10272,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739010</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9928,6 +10378,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739011</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10029,6 +10484,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739012</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10130,6 +10590,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739026</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10231,6 +10696,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739043</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10350,6 +10820,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743622</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10464,6 +10939,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740030</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10565,6 +11045,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737924</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10664,6 +11149,11 @@
       <c r="AY98" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733476</t>
         </is>
       </c>
     </row>
@@ -10781,6 +11271,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287690</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10882,6 +11377,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735760</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10992,6 +11492,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735761</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11102,6 +11607,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736566</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11203,6 +11713,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736575</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11310,6 +11825,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740360</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11408,6 +11928,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740361</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11509,6 +12034,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737598</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11610,6 +12140,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737599</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11711,6 +12246,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737600</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11812,6 +12352,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737601</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11913,6 +12458,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737643</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12014,6 +12564,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737644</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12115,6 +12670,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737645</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12216,6 +12776,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737646</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12317,6 +12882,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737647</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12418,6 +12988,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737648</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12519,6 +13094,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737649</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12620,6 +13200,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737650</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12721,6 +13306,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737651</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12822,6 +13412,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737652</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12923,6 +13518,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737653</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13024,6 +13624,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737654</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13125,6 +13730,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737655</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13226,6 +13836,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737656</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13327,6 +13942,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737657</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13428,6 +14048,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737658</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13529,6 +14154,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737659</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13630,6 +14260,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737660</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13731,6 +14366,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737679</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13832,6 +14472,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737680</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13933,6 +14578,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737681</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14034,6 +14684,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737682</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14135,6 +14790,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737683</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14236,6 +14896,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737684</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14337,6 +15002,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737685</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14438,6 +15108,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737686</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14539,6 +15214,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737687</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14640,6 +15320,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737688</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14741,6 +15426,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737689</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14842,6 +15532,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737690</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14943,6 +15638,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737691</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15044,6 +15744,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737692</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15154,6 +15859,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737782</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15264,6 +15974,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737783</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15374,6 +16089,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737784</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15484,6 +16204,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737785</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15594,6 +16319,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737786</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15704,6 +16434,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737787</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15814,6 +16549,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737788</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15928,6 +16668,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287681</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16038,6 +16783,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120287682</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16145,6 +16895,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120546355</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16246,6 +17001,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747219</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16347,6 +17107,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747220</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16448,6 +17213,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738995</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16549,6 +17319,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738996</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16650,6 +17425,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739013</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16751,6 +17531,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739015</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16852,6 +17637,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739041</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16953,8 +17743,173 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>